--- a/VerveStacks_IND_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{402DEC4C-03BE-47ED-8337-C5AC2C4087A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{01960541-079E-4BDD-AC81-3A758C39037F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1375,18 +1375,462 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IND_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IND_002</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_IND_072</t>
   </si>
   <si>
@@ -1405,456 +1849,234 @@
     <t>connecting solar to buses in cluster 33</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_IN659-765_IND,e_w453513742-765_IND,e_IN642-765_IND,e_w429459345-765_IND,e_w492377703-765_IND,e_w293597835-765_IND,e_w608461884-765_IND,e_w318050929-765_IND,e_w316463122-765_IND</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND,e_w355560316-765_IND,e_w492377703-765_IND,e_w386018740-765_IND</t>
+  </si>
+  <si>
+    <t>e_w369866141-765_IND,e_IN146-765_IND,e_IN142-765_IND,e_IN230-765_IND,e_IN137-765_IND,e_IN140-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN798-765_IND</t>
+  </si>
+  <si>
+    <t>e_w408924420-765_IND,e_w192782338-765_IND,e_IN476-765_IND,e_IN457-765_IND,e_w408924427-765_IND,e_w319423421-765_IND,e_IN439-765_IND,e_w506461670-765_IND,e_IN400-765_IND,e_IN539-765_IND,e_IN404-765_IND,e_IN399-765_IND,e_IN390-765_IND,e_IN388-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN684-765_IND,e_w409158116-765_IND,e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN539-765_IND,e_w202980838-765_IND,e_IN416-765_IND,e_IN405-765_IND,e_w353914865-765_IND,e_w477691456-765_IND,e_IN540-765_IND,e_w196563905-765_IND,e_w353914761-765_IND,e_IN548-765_IND,e_w354062412-765_IND,e_w248385304-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN607-765_IND,e_IN578-765_IND,e_w248385304-765_IND,e_w323266562-765_IND,e_w149822703-400_IND,e_w759521252-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1001700959-765_IND,e_IN218-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN218-765_IND,e_w1001700959-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_IN215-765_IND,e_IN191-765_IND,e_w1143180503-765_IND,e_IN163-765_IND,e_w654736039-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1207477934-765_IND,e_w840600239-765_IND,e_w506461670-765_IND,e_IN684-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311954703-765_IND,e_w1246177377-765_IND,e_IN540-765_IND,e_IN599-765_IND,e_IN586-765_IND,e_w353914761-765_IND,e_IN583-765_IND,e_IN555-765_IND,e_IN578-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN235-400_IND,e_w239498664-400_IND,e_IN265-400_IND,e_w1265489491-400_IND,e_w610646823-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN163-765_IND,e_w1143180503-765_IND,e_w654736039-765_IND,e_w631917408-765_IND,e_IN146-765_IND,e_w1077819664-765_IND,e_w311176519-765_IND,e_w369866141-765_IND,e_IN142-765_IND,e_IN108-765_IND,e_IN107-765_IND,e_IN94-765_IND</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND,e_IN610-765_IND,e_IN617-765_IND,e_w323266562-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1072445901-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w1336628403-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w688672798-765_IND,e_IN218-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND,e_IN659-765_IND</t>
+  </si>
+  <si>
+    <t>e_w331275940-765_IND,e_IN529-765_IND,e_w688672798-765_IND,e_w655683221-765_IND,e_IN489-765_IND,e_IN488-765_IND,e_IN486-765_IND</t>
+  </si>
+  <si>
+    <t>e_w654736039-765_IND,e_w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>e_w492377703-765_IND,e_w293597835-765_IND,e_w608461884-765_IND,e_w386018740-765_IND,e_w801704865-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311571096-765_IND,e_IN250-765_IND,e_IN247-765_IND,e_IN233-765_IND,e_w193216698-765_IND,e_w423702239-765_IND,e_IN295-765_IND,e_IN264-765_IND,e_w131484738-765_IND,e_IN246-765_IND,e_IN272-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311103617-765_IND,e_w166692103-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN235-400_IND,e_w465787206-400_IND,e_IN265-400_IND,e_w1265489491-400_IND</t>
+  </si>
+  <si>
+    <t>e_w342204888-765_IND,e_w245128370-765_IND,e_IN742-765_IND,e_w315824842-765_IND,e_w923365745-765_IND,e_w910151268-765_IND,e_w1074489047-765_IND</t>
+  </si>
+  <si>
+    <t>e_w759521252-765_IND,e_w118228036-400_IND,e_w793144832-765_IND,e_IN339-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1099365579-400_IND,e_w375941438-400_IND</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN486-765_IND,e_w655683221-765_IND,e_IN473-765_IND,e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN798-765_IND,e_w386153973-765_IND,e_w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>e_w315823978-765_IND,e_w386018740-765_IND,e_w801704865-765_IND,e_IN742-765_IND,e_w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN10-765_IND,e_w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND,e_w1206014676-765_IND,e_w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN300-765_IND,e_w166692103-400_IND,e_IN290-400_IND,e_w97392607-400_IND,e_w50885643-400_IND,e_w324059200-400_IND,e_IN317-400_IND,e_w50885643-765_IND,e_w577176545-400_IND,e_w209806624-400_IND,e_w1044735753-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN145-400_IND</t>
+  </si>
+  <si>
+    <t>e_w372701897-765_IND,e_IN10-765_IND,e_w311176519-765_IND</t>
+  </si>
+  <si>
+    <t>e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND,e_w311571096-765_IND,e_w514344408-765_IND,e_w193216698-765_IND</t>
+  </si>
+  <si>
+    <t>e_w698045832-765_IND,e_w315477169-765_IND,e_w408924420-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN42-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN440-400_IND,e_IN386-400_IND,e_w1072445901-400_IND</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND,e_w331275940-765_IND,e_IN642-765_IND,e_w318090288-765_IND,e_IN489-765_IND,e_IN486-765_IND,e_w316463122-765_IND,e_w698045832-765_IND</t>
+  </si>
+  <si>
+    <t>e_w466424134-765_IND,e_w1207477934-765_IND,e_w840600239-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN295-765_IND,e_IN277-765_IND,e_IN457-765_IND,e_w423702239-765_IND,e_IN289-765_IND,e_IN288-765_IND,e_IN439-765_IND,e_IN321-765_IND,e_IN343-765_IND,e_IN327-765_IND,e_IN400-765_IND,e_IN370-765_IND,e_w195459361-765_IND,e_IN323-765_IND</t>
+  </si>
+  <si>
+    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN539-765_IND,e_w311954703-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN365-765_IND,e_IN293-765_IND,e_IN373-765_IND,e_w422204218-765_IND,e_IN283-765_IND,e_IN395-765_IND,e_IN312-765_IND,e_IN302-765_IND,e_IN298-765_IND,e_IN375-765_IND,e_w409798382-400_IND,e_IN300-765_IND,e_w196933682-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN325-400_IND,e_IN315-400_IND,e_IN339-400_IND,e_w205942950-400_IND,e_w324064297-400_IND,e_IN320-400_IND,e_IN336-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN155-400_IND,e_w116541259-400_IND,e_IN235-400_IND</t>
+  </si>
+  <si>
+    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w311571096-765_IND,e_w369866141-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN100-765_IND,e_w247861059-765_IND,e_w311176519-765_IND,e_IN105-765_IND,e_w105373531-765_IND,e_w274106872-765_IND,e_IN136-765_IND,e_w420797421-765_IND,e_w417569420-765_IND,e_IN135-765_IND,e_w1341291951-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN270-765_IND,e_IN196-765_IND,e_IN174-765_IND,e_w1329624553-765_IND,e_IN276-765_IND,e_IN200-765_IND,e_w607439318-765_IND,e_IN229-765_IND,e_IN183-765_IND,e_IN160-765_IND,e_w352619220-765_IND,e_IN267-765_IND,e_IN232-765_IND,e_IN254-765_IND,e_w100470285-765_IND,e_IN275-765_IND,e_w311118424-765_IND,e_IN283-765_IND,e_w311103617-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN260-400_IND,e_w203673991-400_IND,e_w1265496720-400_IND,e_w610646823-400_IND,e_w375084335-400_IND,e_IN177-400_IND,e_IN176-400_IND,e_w375941438-400_IND,e_IN145-400_IND</t>
+  </si>
+  <si>
+    <t>e_w608461884-765_IND,e_w318050929-765_IND,e_w315477169-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311176519-765_IND,e_w372701897-765_IND,e_w105373531-765_IND,e_IN10-765_IND,e_IN42-765_IND,e_w1341291951-765_IND</t>
+  </si>
+  <si>
+    <t>e_w801704865-765_IND,e_w1207477934-765_IND,e_w923365745-765_IND,e_IN684-765_IND</t>
+  </si>
+  <si>
+    <t>e_w840600239-765_IND,e_w408924427-765_IND,e_w506461670-765_IND</t>
+  </si>
+  <si>
+    <t>e_w409158116-765_IND,e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>e_w386153973-765_IND,e_w342204888-765_IND,e_w751947947-765_IND,e_w910151268-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN128-765_IND,e_IN116-765_IND,e_w1341291951-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND,e_IN180-765_IND,e_IN206-765_IND,e_w311103617-765_IND</t>
+  </si>
+  <si>
+    <t>e_w374367235-400_IND,e_IN260-400_IND,e_w439006823-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND,e_w1127651311-765_IND,e_w331275940-765_IND,e_w688672798-765_IND</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND,e_w429459345-765_IND</t>
+  </si>
+  <si>
+    <t>e_w316463122-765_IND,e_w318090288-765_IND,e_w318050929-765_IND,e_w315477169-765_IND,e_w698045832-765_IND</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND,e_IN806-765_IND,e_IN798-765_IND,e_w1206014676-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1127651311-765_IND,e_w688672798-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN806-765_IND,e_IN801-765_IND,e_IN798-765_IND,e_w425401901-765_IND,e_w1206014676-765_IND,e_IN809-765_IND,e_IN803-765_IND,e_w386153973-765_IND,e_w751947947-765_IND,e_w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND,e_IN749-765_IND,e_IN748-765_IND,e_w342204888-765_IND,e_w245128370-765_IND</t>
+  </si>
+  <si>
+    <t>e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND,e_IN685-765_IND</t>
+  </si>
+  <si>
+    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN684-765_IND,e_w409112085-765_IND,e_IN599-765_IND</t>
+  </si>
+  <si>
+    <t>e_w196933682-765_IND,e_w923418232-400_IND,e_w1015325412-400_IND,e_w248385304-765_IND,e_IN353-400_IND,e_w149822703-400_IND,e_IN363-400_IND,e_w209806624-765_IND,e_w96821783-400_IND,e_w209806650-400_IND,e_w485873968-400_IND</t>
+  </si>
+  <si>
+    <t>e_w166692103-400_IND,e_w1044735753-400_IND,e_w1012817818-400_IND,e_w92994753-400_IND,e_w92360278-400_IND,e_w1238123371-400_IND,e_w94199110-400_IND,e_w485873934-400_IND,e_IN179-400_IND,e_IN286-400_IND,e_IN181-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1072445901-400_IND</t>
+  </si>
+  <si>
+    <t>e_w375941438-400_IND,e_IN145-400_IND</t>
+  </si>
+  <si>
     <t>e_w688672798-765_IND,e_IN218-765_IND,e_IN215-765_IND,e_IN199-765_IND,e_IN194-765_IND,e_IN191-765_IND,e_w631917408-765_IND</t>
   </si>
   <si>
@@ -1867,226 +2089,280 @@
     <t>e_w1341647644-400_IND,e_IN263-400_IND,e_w93160503-400_IND,e_w526897229-400_IND,e_IN259-400_IND,e_IN320-400_IND,e_IN235-400_IND</t>
   </si>
   <si>
-    <t>e_IN10-765_IND,e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>e_w425401901-765_IND,e_w1206014676-765_IND,e_w545571850-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN300-765_IND,e_w166692103-400_IND,e_IN290-400_IND,e_w97392607-400_IND,e_w50885643-400_IND,e_w324059200-400_IND,e_IN317-400_IND,e_w50885643-765_IND,e_w577176545-400_IND,e_w209806624-400_IND,e_w1044735753-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN145-400_IND</t>
-  </si>
-  <si>
-    <t>e_w386153973-765_IND,e_w342204888-765_IND,e_w751947947-765_IND,e_w910151268-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN128-765_IND,e_IN116-765_IND,e_w1341291951-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND,e_IN180-765_IND,e_IN206-765_IND,e_w311103617-765_IND</t>
-  </si>
-  <si>
-    <t>e_w374367235-400_IND,e_IN260-400_IND,e_w439006823-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
-  </si>
-  <si>
-    <t>e_w166692103-400_IND,e_w1044735753-400_IND,e_w1012817818-400_IND,e_w92994753-400_IND,e_w92360278-400_IND,e_w1238123371-400_IND,e_w94199110-400_IND,e_w485873934-400_IND,e_IN179-400_IND,e_IN286-400_IND,e_IN181-400_IND</t>
-  </si>
-  <si>
-    <t>e_w1072445901-400_IND</t>
-  </si>
-  <si>
-    <t>e_w375941438-400_IND,e_IN145-400_IND</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w1336628403-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w688672798-765_IND,e_IN218-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND</t>
-  </si>
-  <si>
-    <t>e_w473902678-765_IND,e_IN659-765_IND</t>
-  </si>
-  <si>
-    <t>e_w331275940-765_IND,e_IN529-765_IND,e_w688672798-765_IND,e_w655683221-765_IND,e_IN489-765_IND,e_IN488-765_IND,e_IN486-765_IND</t>
-  </si>
-  <si>
-    <t>e_w654736039-765_IND,e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>e_w355560316-765_IND</t>
-  </si>
-  <si>
-    <t>e_w492377703-765_IND,e_w293597835-765_IND,e_w608461884-765_IND,e_w386018740-765_IND,e_w801704865-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311571096-765_IND,e_IN250-765_IND,e_IN247-765_IND,e_IN233-765_IND,e_w193216698-765_IND,e_w423702239-765_IND,e_IN295-765_IND,e_IN264-765_IND,e_w131484738-765_IND,e_IN246-765_IND,e_IN272-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311103617-765_IND,e_w166692103-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN235-400_IND,e_w465787206-400_IND,e_IN265-400_IND,e_w1265489491-400_IND</t>
-  </si>
-  <si>
-    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w311571096-765_IND,e_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN100-765_IND,e_w247861059-765_IND,e_w311176519-765_IND,e_IN105-765_IND,e_w105373531-765_IND,e_w274106872-765_IND,e_IN136-765_IND,e_w420797421-765_IND,e_w417569420-765_IND,e_IN135-765_IND,e_w1341291951-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN270-765_IND,e_IN196-765_IND,e_IN174-765_IND,e_w1329624553-765_IND,e_IN276-765_IND,e_IN200-765_IND,e_w607439318-765_IND,e_IN229-765_IND,e_IN183-765_IND,e_IN160-765_IND,e_w352619220-765_IND,e_IN267-765_IND,e_IN232-765_IND,e_IN254-765_IND,e_w100470285-765_IND,e_IN275-765_IND,e_w311118424-765_IND,e_IN283-765_IND,e_w311103617-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN260-400_IND,e_w203673991-400_IND,e_w1265496720-400_IND,e_w610646823-400_IND,e_w375084335-400_IND,e_IN177-400_IND,e_IN176-400_IND,e_w375941438-400_IND,e_IN145-400_IND</t>
-  </si>
-  <si>
-    <t>e_w473902678-765_IND,e_w1127651311-765_IND,e_w331275940-765_IND,e_w688672798-765_IND</t>
-  </si>
-  <si>
-    <t>e_w355560316-765_IND,e_w429459345-765_IND</t>
-  </si>
-  <si>
-    <t>e_w316463122-765_IND,e_w318090288-765_IND,e_w318050929-765_IND,e_w315477169-765_IND,e_w698045832-765_IND</t>
-  </si>
-  <si>
-    <t>e_w425401901-765_IND,e_IN806-765_IND,e_IN798-765_IND,e_w1206014676-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN659-765_IND,e_w453513742-765_IND,e_IN642-765_IND,e_w429459345-765_IND,e_w492377703-765_IND,e_w293597835-765_IND,e_w608461884-765_IND,e_w318050929-765_IND,e_w316463122-765_IND</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND,e_w355560316-765_IND,e_w492377703-765_IND,e_w386018740-765_IND</t>
-  </si>
-  <si>
-    <t>e_w369866141-765_IND,e_IN146-765_IND,e_IN142-765_IND,e_IN230-765_IND,e_IN137-765_IND,e_IN140-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN798-765_IND</t>
-  </si>
-  <si>
-    <t>e_w408924420-765_IND,e_w192782338-765_IND,e_IN476-765_IND,e_IN457-765_IND,e_w408924427-765_IND,e_w319423421-765_IND,e_IN439-765_IND,e_w506461670-765_IND,e_IN400-765_IND,e_IN539-765_IND,e_IN404-765_IND,e_IN399-765_IND,e_IN390-765_IND,e_IN388-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN684-765_IND,e_w409158116-765_IND,e_w409112085-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN539-765_IND,e_w202980838-765_IND,e_IN416-765_IND,e_IN405-765_IND,e_w353914865-765_IND,e_w477691456-765_IND,e_IN540-765_IND,e_w196563905-765_IND,e_w353914761-765_IND,e_IN548-765_IND,e_w354062412-765_IND,e_w248385304-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN607-765_IND,e_IN578-765_IND,e_w248385304-765_IND,e_w323266562-765_IND,e_w149822703-400_IND,e_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>e_w608461884-765_IND,e_w318050929-765_IND,e_w315477169-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311176519-765_IND,e_w372701897-765_IND,e_w105373531-765_IND,e_IN10-765_IND,e_IN42-765_IND,e_w1341291951-765_IND</t>
-  </si>
-  <si>
-    <t>e_w801704865-765_IND,e_w1207477934-765_IND,e_w923365745-765_IND,e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>e_w840600239-765_IND,e_w408924427-765_IND,e_w506461670-765_IND</t>
-  </si>
-  <si>
-    <t>e_w409158116-765_IND,e_w409112085-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1127651311-765_IND,e_w688672798-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN806-765_IND,e_IN801-765_IND,e_IN798-765_IND,e_w425401901-765_IND,e_w1206014676-765_IND,e_IN809-765_IND,e_IN803-765_IND,e_w386153973-765_IND,e_w751947947-765_IND,e_w545571850-765_IND</t>
-  </si>
-  <si>
-    <t>e_w355560316-765_IND,e_IN749-765_IND,e_IN748-765_IND,e_w342204888-765_IND,e_w245128370-765_IND</t>
-  </si>
-  <si>
-    <t>e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND,e_IN685-765_IND</t>
-  </si>
-  <si>
-    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN684-765_IND,e_w409112085-765_IND,e_IN599-765_IND</t>
-  </si>
-  <si>
-    <t>e_w196933682-765_IND,e_w923418232-400_IND,e_w1015325412-400_IND,e_w248385304-765_IND,e_IN353-400_IND,e_w149822703-400_IND,e_IN363-400_IND,e_w209806624-765_IND,e_w96821783-400_IND,e_w209806650-400_IND,e_w485873968-400_IND</t>
-  </si>
-  <si>
-    <t>e_w1001700959-765_IND,e_IN218-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN218-765_IND,e_w1001700959-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_IN215-765_IND,e_IN191-765_IND,e_w1143180503-765_IND,e_IN163-765_IND,e_w654736039-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1207477934-765_IND,e_w840600239-765_IND,e_w506461670-765_IND,e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311954703-765_IND,e_w1246177377-765_IND,e_IN540-765_IND,e_IN599-765_IND,e_IN586-765_IND,e_w353914761-765_IND,e_IN583-765_IND,e_IN555-765_IND,e_IN578-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN235-400_IND,e_w239498664-400_IND,e_IN265-400_IND,e_w1265489491-400_IND,e_w610646823-400_IND</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN486-765_IND,e_w655683221-765_IND,e_IN473-765_IND,e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN798-765_IND,e_w386153973-765_IND,e_w355560316-765_IND</t>
-  </si>
-  <si>
-    <t>e_w315823978-765_IND,e_w386018740-765_IND,e_w801704865-765_IND,e_IN742-765_IND,e_w923365745-765_IND</t>
-  </si>
-  <si>
-    <t>e_w342204888-765_IND,e_w245128370-765_IND,e_IN742-765_IND,e_w315824842-765_IND,e_w923365745-765_IND,e_w910151268-765_IND,e_w1074489047-765_IND</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND,e_w118228036-400_IND,e_w793144832-765_IND,e_IN339-400_IND</t>
-  </si>
-  <si>
-    <t>e_w1099365579-400_IND,e_w375941438-400_IND</t>
-  </si>
-  <si>
-    <t>e_w372701897-765_IND,e_IN10-765_IND,e_w311176519-765_IND</t>
-  </si>
-  <si>
-    <t>e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND,e_w311571096-765_IND,e_w514344408-765_IND,e_w193216698-765_IND</t>
-  </si>
-  <si>
-    <t>e_w698045832-765_IND,e_w315477169-765_IND,e_w408924420-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN42-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN440-400_IND,e_IN386-400_IND,e_w1072445901-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN163-765_IND,e_w1143180503-765_IND,e_w654736039-765_IND,e_w631917408-765_IND,e_IN146-765_IND,e_w1077819664-765_IND,e_w311176519-765_IND,e_w369866141-765_IND,e_IN142-765_IND,e_IN108-765_IND,e_IN107-765_IND,e_IN94-765_IND</t>
-  </si>
-  <si>
-    <t>e_w409112085-765_IND,e_IN610-765_IND,e_IN617-765_IND,e_w323266562-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1072445901-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
-  </si>
-  <si>
-    <t>e_w473902678-765_IND,e_w331275940-765_IND,e_IN642-765_IND,e_w318090288-765_IND,e_IN489-765_IND,e_IN486-765_IND,e_w316463122-765_IND,e_w698045832-765_IND</t>
-  </si>
-  <si>
-    <t>e_w466424134-765_IND,e_w1207477934-765_IND,e_w840600239-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN295-765_IND,e_IN277-765_IND,e_IN457-765_IND,e_w423702239-765_IND,e_IN289-765_IND,e_IN288-765_IND,e_IN439-765_IND,e_IN321-765_IND,e_IN343-765_IND,e_IN327-765_IND,e_IN400-765_IND,e_IN370-765_IND,e_w195459361-765_IND,e_IN323-765_IND</t>
-  </si>
-  <si>
-    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN539-765_IND,e_w311954703-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN365-765_IND,e_IN293-765_IND,e_IN373-765_IND,e_w422204218-765_IND,e_IN283-765_IND,e_IN395-765_IND,e_IN312-765_IND,e_IN302-765_IND,e_IN298-765_IND,e_IN375-765_IND,e_w409798382-400_IND,e_IN300-765_IND,e_w196933682-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN325-400_IND,e_IN315-400_IND,e_IN339-400_IND,e_w205942950-400_IND,e_w324064297-400_IND,e_IN320-400_IND,e_IN336-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN155-400_IND,e_w116541259-400_IND,e_IN235-400_IND</t>
+    <t>distr_wonelc_won_IND_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
   </si>
   <si>
     <t>distr_wonelc_won_IND_048</t>
@@ -2113,6 +2389,42 @@
     <t>connecting wind onshore to buses in cluster 22</t>
   </si>
   <si>
+    <t>distr_wonelc_won_IND_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_IND_067</t>
   </si>
   <si>
@@ -2143,34 +2455,22 @@
     <t>connecting wind onshore to buses in cluster 26</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
+    <t>distr_wonelc_won_IND_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
   </si>
   <si>
     <t>distr_wonelc_won_IND_008</t>
@@ -2191,304 +2491,277 @@
     <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
+    <t>elc_won_IND_056</t>
+  </si>
+  <si>
+    <t>e_w655683221-765_IND,e_IN473-765_IND,e_w311571096-765_IND,e_w209826798-765_IND,e_w360424761-765_IND,e_w193216698-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_054</t>
+  </si>
+  <si>
+    <t>e_w514344408-765_IND,e_w360424761-765_IND,e_w193216698-765_IND,e_IN476-765_IND,e_w192782338-765_IND,e_IN457-765_IND,e_w319423421-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_014</t>
+  </si>
+  <si>
+    <t>e_w408924427-765_IND,e_w506461670-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_049</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_047</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND,e_w355560316-765_IND,e_w492377703-765_IND,e_w293597835-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_035</t>
+  </si>
+  <si>
+    <t>e_w318090288-765_IND,e_IN486-765_IND,e_w316463122-765_IND,e_w698045832-765_IND,e_w608461884-765_IND,e_w318050929-765_IND,e_w315477169-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_062</t>
+  </si>
+  <si>
+    <t>e_w369866141-765_IND,e_IN142-765_IND,e_IN107-765_IND,e_IN230-765_IND,e_IN137-765_IND,e_IN140-765_IND,e_IN250-765_IND,e_w274106872-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_033</t>
+  </si>
+  <si>
+    <t>e_w315477169-765_IND,e_w408924420-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_060</t>
+  </si>
+  <si>
+    <t>e_w423702239-765_IND,e_IN250-765_IND,e_w193216698-765_IND,e_IN295-765_IND,e_IN264-765_IND,e_w131484738-765_IND,e_IN272-765_IND,e_IN289-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_010</t>
+  </si>
+  <si>
+    <t>e_IN404-765_IND,e_IN399-765_IND,e_w202980838-765_IND,e_IN390-765_IND,e_IN416-765_IND,e_w477691456-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_019</t>
+  </si>
+  <si>
+    <t>e_w422204218-765_IND,e_IN293-765_IND,e_IN312-765_IND,e_IN302-765_IND,e_IN375-765_IND,e_w409798382-400_IND,e_IN300-765_IND,e_IN290-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_017</t>
+  </si>
+  <si>
+    <t>e_IN290-400_IND,e_w50885643-400_IND,e_w166692103-400_IND,e_w50885643-765_IND,e_w577176545-400_IND,e_w1044735753-400_IND,e_w96821783-400_IND,e_w92994753-400_IND,e_w94199110-400_IND,e_w485873968-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_053</t>
+  </si>
+  <si>
+    <t>e_IN218-765_IND,e_w688672798-765_IND,e_w1127651311-765_IND,e_w655683221-765_IND,e_IN194-765_IND,e_w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_036</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND,e_w1206014676-765_IND,e_IN809-765_IND,e_w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_012</t>
+  </si>
+  <si>
+    <t>e_w408924420-765_IND,e_w192782338-765_IND,e_w408924427-765_IND,e_w506461670-765_IND,e_w311933111-765_IND,e_IN539-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_043</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND,e_IN659-765_IND,e_w473902678-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_045</t>
+  </si>
+  <si>
+    <t>e_IN798-765_IND,e_w425401901-765_IND,e_IN801-765_IND,e_IN803-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_031</t>
+  </si>
+  <si>
+    <t>e_w466424134-765_IND,e_w840600239-765_IND,e_w1207477934-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_059</t>
+  </si>
+  <si>
+    <t>e_IN270-765_IND,e_IN277-765_IND,e_IN276-765_IND,e_IN289-765_IND,e_IN288-765_IND,e_IN267-765_IND,e_IN321-765_IND,e_IN323-765_IND,e_IN293-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_027</t>
+  </si>
+  <si>
+    <t>e_w1238123371-400_IND,e_IN286-400_IND,e_w485873934-400_IND,e_IN181-400_IND,e_w1341647644-400_IND,e_IN263-400_IND,e_w93160503-400_IND,e_w526897229-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_052</t>
+  </si>
+  <si>
+    <t>e_IN218-765_IND,e_IN215-765_IND,e_IN187-765_IND,e_IN199-765_IND,e_IN191-765_IND,e_IN194-765_IND,e_w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_037</t>
+  </si>
+  <si>
+    <t>e_IN803-765_IND,e_w545571850-765_IND,e_w751947947-765_IND,e_w342204888-765_IND,e_w910151268-765_IND,e_w315824842-765_IND,e_w1074489047-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_032</t>
+  </si>
+  <si>
+    <t>e_w506461670-765_IND,e_IN684-765_IND,e_w311933111-765_IND,e_IN685-765_IND,e_w409158116-765_IND,e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_018</t>
+  </si>
+  <si>
+    <t>e_w97392607-400_IND,e_w324059200-400_IND,e_IN317-400_IND,e_w923418232-400_IND,e_w577176545-400_IND,e_w1015325412-400_IND,e_IN353-400_IND,e_w209806624-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_065</t>
+  </si>
+  <si>
+    <t>e_w1143180503-765_IND,e_w654736039-765_IND,e_w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_044</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND,e_w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_042</t>
+  </si>
+  <si>
+    <t>e_w492377703-765_IND,e_w355560316-765_IND,e_w386018740-765_IND,e_w315823978-765_IND,e_w386153973-765_IND,e_IN749-765_IND,e_IN748-765_IND,e_w342204888-765_IND,e_w245128370-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_005</t>
+  </si>
+  <si>
+    <t>e_w372701897-765_IND,e_w311176519-765_IND,e_w105373531-765_IND,e_IN42-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_039</t>
+  </si>
+  <si>
+    <t>e_w386153973-765_IND,e_IN803-765_IND,e_w751947947-765_IND,e_w342204888-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_002</t>
+  </si>
+  <si>
+    <t>elc_won_IND_051</t>
+  </si>
+  <si>
+    <t>e_w688672798-765_IND,e_w331275940-765_IND,e_IN529-765_IND,e_IN489-765_IND,e_w655683221-765_IND,e_IN488-765_IND,e_IN486-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_004</t>
+  </si>
+  <si>
+    <t>e_w1341291951-765_IND,e_w105373531-765_IND,e_IN116-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_029</t>
+  </si>
+  <si>
+    <t>e_w1207477934-765_IND,e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_003</t>
+  </si>
+  <si>
+    <t>e_IN275-765_IND,e_w311118424-765_IND,e_w100470285-765_IND,e_IN283-765_IND,e_w311103617-765_IND,e_IN298-765_IND,e_w166692103-400_IND,e_IN300-765_IND,e_IN290-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_055</t>
+  </si>
+  <si>
+    <t>e_IN486-765_IND,e_IN473-765_IND,e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_016</t>
+  </si>
+  <si>
+    <t>e_w166692103-400_IND,e_w1012817818-400_IND,e_w92360278-400_IND,e_w1238123371-400_IND,e_w485873934-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_028</t>
+  </si>
+  <si>
+    <t>e_w324064297-400_IND,e_IN320-400_IND,e_IN259-400_IND,e_IN235-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_066</t>
+  </si>
+  <si>
+    <t>e_IN146-765_IND,e_w654736039-765_IND,e_w1077819664-765_IND,e_w369866141-765_IND,e_IN142-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_040</t>
+  </si>
+  <si>
+    <t>e_w608461884-765_IND,e_w801704865-765_IND,e_w466424134-765_IND,e_w1207477934-765_IND,e_w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_038</t>
+  </si>
+  <si>
+    <t>e_w342204888-765_IND,e_w245128370-765_IND,e_IN742-765_IND,e_w315823978-765_IND,e_w801704865-765_IND,e_w315824842-765_IND,e_w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_061</t>
+  </si>
+  <si>
+    <t>e_w372701897-765_IND,e_w311176519-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_058</t>
+  </si>
+  <si>
+    <t>e_w369866141-765_IND,e_w311571096-765_IND,e_IN230-765_IND,e_IN250-765_IND,e_IN247-765_IND,e_IN233-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_015</t>
+  </si>
+  <si>
+    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN684-765_IND,e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_020</t>
+  </si>
+  <si>
+    <t>e_w354062412-765_IND,e_w248385304-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_021</t>
+  </si>
+  <si>
+    <t>e_w248385304-765_IND,e_w149822703-400_IND,e_IN363-400_IND,e_w209806624-765_IND,e_w209806650-400_IND,e_w485873968-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_023</t>
+  </si>
+  <si>
+    <t>e_w759521252-765_IND,e_w793144832-765_IND</t>
   </si>
   <si>
     <t>elc_won_IND_048</t>
@@ -2515,6 +2788,42 @@
     <t>e_IN440-400_IND</t>
   </si>
   <si>
+    <t>elc_won_IND_009</t>
+  </si>
+  <si>
+    <t>e_IN439-765_IND,e_IN321-765_IND,e_w319423421-765_IND,e_IN343-765_IND,e_IN327-765_IND,e_IN400-765_IND,e_IN370-765_IND,e_w195459361-765_IND,e_IN399-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_013</t>
+  </si>
+  <si>
+    <t>e_w311933111-765_IND,e_w311954703-765_IND,e_IN539-765_IND,e_w1246177377-765_IND,e_IN599-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_050</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w473902678-765_IND,e_w331275940-765_IND,e_w688672798-765_IND,e_w318090288-765_IND,e_IN489-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_064</t>
+  </si>
+  <si>
+    <t>e_w1001700959-765_IND,e_IN218-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_w1143180503-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_011</t>
+  </si>
+  <si>
+    <t>e_IN365-765_IND,e_IN388-765_IND,e_IN373-765_IND,e_w422204218-765_IND,e_IN405-765_IND,e_IN395-765_IND,e_w477691456-765_IND,e_IN375-765_IND,e_w196563905-765_IND,e_w196933682-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_025</t>
+  </si>
+  <si>
+    <t>e_w759521252-765_IND,e_w118228036-400_IND</t>
+  </si>
+  <si>
     <t>elc_won_IND_067</t>
   </si>
   <si>
@@ -2545,34 +2854,22 @@
     <t>e_w118228036-400_IND,e_IN325-400_IND,e_IN315-400_IND,e_IN339-400_IND,e_w205942950-400_IND,e_w793144832-765_IND,e_IN336-400_IND,e_IN320-400_IND</t>
   </si>
   <si>
-    <t>elc_won_IND_009</t>
-  </si>
-  <si>
-    <t>e_IN439-765_IND,e_IN321-765_IND,e_w319423421-765_IND,e_IN343-765_IND,e_IN327-765_IND,e_IN400-765_IND,e_IN370-765_IND,e_w195459361-765_IND,e_IN399-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_013</t>
-  </si>
-  <si>
-    <t>e_w311933111-765_IND,e_w311954703-765_IND,e_IN539-765_IND,e_w1246177377-765_IND,e_IN599-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_066</t>
-  </si>
-  <si>
-    <t>e_IN146-765_IND,e_w654736039-765_IND,e_w1077819664-765_IND,e_w369866141-765_IND,e_IN142-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_040</t>
-  </si>
-  <si>
-    <t>e_w608461884-765_IND,e_w801704865-765_IND,e_w466424134-765_IND,e_w1207477934-765_IND,e_w923365745-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_038</t>
-  </si>
-  <si>
-    <t>e_w342204888-765_IND,e_w245128370-765_IND,e_IN742-765_IND,e_w315823978-765_IND,e_w801704865-765_IND,e_w315824842-765_IND,e_w923365745-765_IND</t>
+    <t>elc_won_IND_057</t>
+  </si>
+  <si>
+    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w369866141-765_IND,e_w311571096-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_041</t>
+  </si>
+  <si>
+    <t>e_w293597835-765_IND,e_w608461884-765_IND,e_w492377703-765_IND,e_w386018740-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_030</t>
+  </si>
+  <si>
+    <t>e_w315824842-765_IND,e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND</t>
   </si>
   <si>
     <t>elc_won_IND_008</t>
@@ -2593,301 +2890,58 @@
     <t>e_IN135-765_IND,e_w420797421-765_IND,e_w1329624553-765_IND,e_IN128-765_IND,e_IN200-765_IND,e_IN196-765_IND,e_w607439318-765_IND,e_IN229-765_IND,e_IN183-765_IND,e_IN160-765_IND,e_IN267-765_IND,e_IN232-765_IND,e_IN180-765_IND,e_IN254-765_IND,e_w100470285-765_IND</t>
   </si>
   <si>
-    <t>elc_won_IND_055</t>
-  </si>
-  <si>
-    <t>e_IN486-765_IND,e_IN473-765_IND,e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_016</t>
-  </si>
-  <si>
-    <t>e_w166692103-400_IND,e_w1012817818-400_IND,e_w92360278-400_IND,e_w1238123371-400_IND,e_w485873934-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_028</t>
-  </si>
-  <si>
-    <t>e_w324064297-400_IND,e_IN320-400_IND,e_IN259-400_IND,e_IN235-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_050</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w473902678-765_IND,e_w331275940-765_IND,e_w688672798-765_IND,e_w318090288-765_IND,e_IN489-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_064</t>
-  </si>
-  <si>
-    <t>e_w1001700959-765_IND,e_IN218-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_011</t>
-  </si>
-  <si>
-    <t>e_IN365-765_IND,e_IN388-765_IND,e_IN373-765_IND,e_w422204218-765_IND,e_IN405-765_IND,e_IN395-765_IND,e_w477691456-765_IND,e_IN375-765_IND,e_w196563905-765_IND,e_w196933682-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_025</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND,e_w118228036-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_065</t>
-  </si>
-  <si>
-    <t>e_w1143180503-765_IND,e_w654736039-765_IND,e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_044</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND,e_w355560316-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_042</t>
-  </si>
-  <si>
-    <t>e_w492377703-765_IND,e_w355560316-765_IND,e_w386018740-765_IND,e_w315823978-765_IND,e_w386153973-765_IND,e_IN749-765_IND,e_IN748-765_IND,e_w342204888-765_IND,e_w245128370-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_005</t>
-  </si>
-  <si>
-    <t>e_w372701897-765_IND,e_w311176519-765_IND,e_w105373531-765_IND,e_IN42-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_039</t>
-  </si>
-  <si>
-    <t>e_w386153973-765_IND,e_IN803-765_IND,e_w751947947-765_IND,e_w342204888-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_002</t>
-  </si>
-  <si>
-    <t>elc_won_IND_056</t>
-  </si>
-  <si>
-    <t>e_w655683221-765_IND,e_IN473-765_IND,e_w311571096-765_IND,e_w209826798-765_IND,e_w360424761-765_IND,e_w193216698-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_054</t>
-  </si>
-  <si>
-    <t>e_w514344408-765_IND,e_w360424761-765_IND,e_w193216698-765_IND,e_IN476-765_IND,e_w192782338-765_IND,e_IN457-765_IND,e_w319423421-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_014</t>
-  </si>
-  <si>
-    <t>e_w408924427-765_IND,e_w506461670-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_061</t>
-  </si>
-  <si>
-    <t>e_w372701897-765_IND,e_w311176519-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_058</t>
-  </si>
-  <si>
-    <t>e_w369866141-765_IND,e_w311571096-765_IND,e_IN230-765_IND,e_IN250-765_IND,e_IN247-765_IND,e_IN233-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_015</t>
-  </si>
-  <si>
-    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN684-765_IND,e_w409112085-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_020</t>
-  </si>
-  <si>
-    <t>e_w354062412-765_IND,e_w248385304-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_021</t>
-  </si>
-  <si>
-    <t>e_w248385304-765_IND,e_w149822703-400_IND,e_IN363-400_IND,e_w209806624-765_IND,e_w209806650-400_IND,e_w485873968-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_023</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND,e_w793144832-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_051</t>
-  </si>
-  <si>
-    <t>e_w688672798-765_IND,e_w331275940-765_IND,e_IN529-765_IND,e_IN489-765_IND,e_w655683221-765_IND,e_IN488-765_IND,e_IN486-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_004</t>
-  </si>
-  <si>
-    <t>e_w1341291951-765_IND,e_w105373531-765_IND,e_IN116-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_029</t>
-  </si>
-  <si>
-    <t>e_w1207477934-765_IND,e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_003</t>
-  </si>
-  <si>
-    <t>e_IN275-765_IND,e_w311118424-765_IND,e_w100470285-765_IND,e_IN283-765_IND,e_w311103617-765_IND,e_IN298-765_IND,e_w166692103-400_IND,e_IN300-765_IND,e_IN290-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_043</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND,e_IN659-765_IND,e_w473902678-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_045</t>
-  </si>
-  <si>
-    <t>e_IN798-765_IND,e_w425401901-765_IND,e_IN801-765_IND,e_IN803-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_031</t>
-  </si>
-  <si>
-    <t>e_w466424134-765_IND,e_w840600239-765_IND,e_w1207477934-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_059</t>
-  </si>
-  <si>
-    <t>e_IN270-765_IND,e_IN277-765_IND,e_IN276-765_IND,e_IN289-765_IND,e_IN288-765_IND,e_IN267-765_IND,e_IN321-765_IND,e_IN323-765_IND,e_IN293-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_027</t>
-  </si>
-  <si>
-    <t>e_w1238123371-400_IND,e_IN286-400_IND,e_w485873934-400_IND,e_IN181-400_IND,e_w1341647644-400_IND,e_IN263-400_IND,e_w93160503-400_IND,e_w526897229-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_057</t>
-  </si>
-  <si>
-    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w369866141-765_IND,e_w311571096-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_041</t>
-  </si>
-  <si>
-    <t>e_w293597835-765_IND,e_w608461884-765_IND,e_w492377703-765_IND,e_w386018740-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_030</t>
-  </si>
-  <si>
-    <t>e_w315824842-765_IND,e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_052</t>
-  </si>
-  <si>
-    <t>e_IN218-765_IND,e_IN215-765_IND,e_IN187-765_IND,e_IN199-765_IND,e_IN191-765_IND,e_IN194-765_IND,e_w631917408-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_037</t>
-  </si>
-  <si>
-    <t>e_IN803-765_IND,e_w545571850-765_IND,e_w751947947-765_IND,e_w342204888-765_IND,e_w910151268-765_IND,e_w315824842-765_IND,e_w1074489047-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_032</t>
-  </si>
-  <si>
-    <t>e_w506461670-765_IND,e_IN684-765_IND,e_w311933111-765_IND,e_IN685-765_IND,e_w409158116-765_IND,e_w409112085-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_018</t>
-  </si>
-  <si>
-    <t>e_w97392607-400_IND,e_w324059200-400_IND,e_IN317-400_IND,e_w923418232-400_IND,e_w577176545-400_IND,e_w1015325412-400_IND,e_IN353-400_IND,e_w209806624-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_053</t>
-  </si>
-  <si>
-    <t>e_IN218-765_IND,e_w688672798-765_IND,e_w1127651311-765_IND,e_w655683221-765_IND,e_IN194-765_IND,e_w631917408-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_036</t>
-  </si>
-  <si>
-    <t>e_w425401901-765_IND,e_w1206014676-765_IND,e_IN809-765_IND,e_w545571850-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_012</t>
-  </si>
-  <si>
-    <t>e_w408924420-765_IND,e_w192782338-765_IND,e_w408924427-765_IND,e_w506461670-765_IND,e_w311933111-765_IND,e_IN539-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_049</t>
-  </si>
-  <si>
-    <t>e_w473902678-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_047</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND,e_w355560316-765_IND,e_w492377703-765_IND,e_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_035</t>
-  </si>
-  <si>
-    <t>e_w318090288-765_IND,e_IN486-765_IND,e_w316463122-765_IND,e_w698045832-765_IND,e_w608461884-765_IND,e_w318050929-765_IND,e_w315477169-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_062</t>
-  </si>
-  <si>
-    <t>e_w369866141-765_IND,e_IN142-765_IND,e_IN107-765_IND,e_IN230-765_IND,e_IN137-765_IND,e_IN140-765_IND,e_IN250-765_IND,e_w274106872-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_033</t>
-  </si>
-  <si>
-    <t>e_w315477169-765_IND,e_w408924420-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_060</t>
-  </si>
-  <si>
-    <t>e_w423702239-765_IND,e_IN250-765_IND,e_w193216698-765_IND,e_IN295-765_IND,e_IN264-765_IND,e_w131484738-765_IND,e_IN272-765_IND,e_IN289-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_010</t>
-  </si>
-  <si>
-    <t>e_IN404-765_IND,e_IN399-765_IND,e_w202980838-765_IND,e_IN390-765_IND,e_IN416-765_IND,e_w477691456-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_019</t>
-  </si>
-  <si>
-    <t>e_w422204218-765_IND,e_IN293-765_IND,e_IN312-765_IND,e_IN302-765_IND,e_IN375-765_IND,e_w409798382-400_IND,e_IN300-765_IND,e_IN290-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_017</t>
-  </si>
-  <si>
-    <t>e_IN290-400_IND,e_w50885643-400_IND,e_w166692103-400_IND,e_w50885643-765_IND,e_w577176545-400_IND,e_w1044735753-400_IND,e_w96821783-400_IND,e_w92994753-400_IND,e_w94199110-400_IND,e_w485873968-400_IND</t>
+    <t>distr_wofelc_wof_IND_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IND_013</t>
@@ -2902,52 +2956,46 @@
     <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_IND_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_IND_022</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 22</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_IND_002</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
+    <t>distr_wofelc_wof_IND_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IND_004</t>
@@ -2974,24 +3022,6 @@
     <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_IND_006</t>
   </si>
   <si>
@@ -3004,34 +3034,49 @@
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
+    <t>elc_wof_IND_021</t>
+  </si>
+  <si>
+    <t>e_w409158116-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_009</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w473902678-765_IND,e_w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_017</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_014</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_010</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>e_w315824842-765_IND,e_w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_001</t>
+  </si>
+  <si>
+    <t>e_IN798-765_IND,e_w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_018</t>
   </si>
   <si>
     <t>elc_wof_IND_013</t>
@@ -3046,40 +3091,31 @@
     <t>e_w323266562-765_IND,e_w759521252-765_IND</t>
   </si>
   <si>
+    <t>elc_wof_IND_015</t>
+  </si>
+  <si>
     <t>elc_wof_IND_022</t>
   </si>
   <si>
-    <t>elc_wof_IND_010</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_009</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w473902678-765_IND,e_w1127651311-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_017</t>
-  </si>
-  <si>
-    <t>e_w425401901-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_014</t>
-  </si>
-  <si>
     <t>elc_wof_IND_002</t>
   </si>
   <si>
-    <t>elc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>e_w315824842-765_IND,e_w923365745-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>e_w409112085-765_IND</t>
+    <t>elc_wof_IND_007</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w688672711-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_008</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_005</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_024</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND,e_IN617-765_IND</t>
   </si>
   <si>
     <t>elc_wof_IND_004</t>
@@ -3103,18 +3139,6 @@
     <t>e_w425401901-765_IND,e_w1206014676-765_IND</t>
   </si>
   <si>
-    <t>elc_wof_IND_015</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_001</t>
-  </si>
-  <si>
-    <t>e_IN798-765_IND,e_w355560316-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_018</t>
-  </si>
-  <si>
     <t>elc_wof_IND_006</t>
   </si>
   <si>
@@ -3122,30 +3146,6 @@
   </si>
   <si>
     <t>elc_wof_IND_012</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_007</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_008</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_005</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_024</t>
-  </si>
-  <si>
-    <t>e_w409112085-765_IND,e_IN617-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_021</t>
-  </si>
-  <si>
-    <t>e_w409158116-765_IND</t>
   </si>
   <si>
     <t>e_won_IND_001</t>
@@ -8576,7 +8576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD42274F-2BD6-42B2-B50D-B5EC04A43574}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B7C108-976C-44A9-AF50-B2241D70CC90}">
   <dimension ref="B9:BD88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8814,16 +8814,16 @@
         <v>415</v>
       </c>
       <c r="Y11" t="s">
-        <v>336</v>
+        <v>396</v>
       </c>
       <c r="Z11" t="s">
         <v>575</v>
       </c>
       <c r="AA11">
-        <v>0.99359748433922845</v>
+        <v>0.99557960200072415</v>
       </c>
       <c r="AB11">
-        <v>117.37945378081078</v>
+        <v>81.040629986723459</v>
       </c>
       <c r="AD11" t="s">
         <v>414</v>
@@ -8856,10 +8856,10 @@
         <v>788</v>
       </c>
       <c r="AO11">
-        <v>0.99660391553167893</v>
+        <v>0.99474825047892679</v>
       </c>
       <c r="AP11">
-        <v>62.261548585886977</v>
+        <v>96.282074553009053</v>
       </c>
       <c r="AR11" t="s">
         <v>414</v>
@@ -8892,10 +8892,10 @@
         <v>969</v>
       </c>
       <c r="BC11">
-        <v>0.99526782804010661</v>
+        <v>0.99308209783432144</v>
       </c>
       <c r="BD11">
-        <v>86.756485931379871</v>
+        <v>126.82820637077275</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8960,16 +8960,16 @@
         <v>419</v>
       </c>
       <c r="Y12" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="Z12" t="s">
         <v>576</v>
       </c>
       <c r="AA12">
-        <v>0.99592552983543692</v>
+        <v>0.99295357769237991</v>
       </c>
       <c r="AB12">
-        <v>74.698619683656872</v>
+        <v>129.18440897303603</v>
       </c>
       <c r="AD12" t="s">
         <v>414</v>
@@ -9002,10 +9002,10 @@
         <v>790</v>
       </c>
       <c r="AO12">
-        <v>0.9959136876641268</v>
+        <v>0.99684527597966854</v>
       </c>
       <c r="AP12">
-        <v>74.915726157675209</v>
+        <v>57.836607039410005</v>
       </c>
       <c r="AR12" t="s">
         <v>414</v>
@@ -9038,10 +9038,10 @@
         <v>971</v>
       </c>
       <c r="BC12">
-        <v>0.98605138538291048</v>
+        <v>0.98137594918937099</v>
       </c>
       <c r="BD12">
-        <v>255.7246013133088</v>
+        <v>341.44093152819772</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -9106,16 +9106,16 @@
         <v>421</v>
       </c>
       <c r="Y13" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="Z13" t="s">
         <v>577</v>
       </c>
       <c r="AA13">
-        <v>0.99463677905825021</v>
+        <v>0.99696751363483405</v>
       </c>
       <c r="AB13">
-        <v>98.325717265413417</v>
+        <v>55.595583361375894</v>
       </c>
       <c r="AD13" t="s">
         <v>414</v>
@@ -9148,10 +9148,10 @@
         <v>792</v>
       </c>
       <c r="AO13">
-        <v>0.9935275292913992</v>
+        <v>0.9943927545810437</v>
       </c>
       <c r="AP13">
-        <v>118.66196299101547</v>
+        <v>102.79949934753229</v>
       </c>
       <c r="AR13" t="s">
         <v>414</v>
@@ -9181,13 +9181,13 @@
         <v>972</v>
       </c>
       <c r="BB13" t="s">
-        <v>863</v>
+        <v>973</v>
       </c>
       <c r="BC13">
-        <v>0.98389167860462323</v>
+        <v>0.9889956676941275</v>
       </c>
       <c r="BD13">
-        <v>295.31922558190735</v>
+        <v>201.74609227432916</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -9252,16 +9252,16 @@
         <v>423</v>
       </c>
       <c r="Y14" t="s">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="Z14" t="s">
         <v>578</v>
       </c>
       <c r="AA14">
-        <v>0.99667564038633161</v>
+        <v>0.98964014500078279</v>
       </c>
       <c r="AB14">
-        <v>60.946592917253042</v>
+        <v>189.93067498564957</v>
       </c>
       <c r="AD14" t="s">
         <v>414</v>
@@ -9294,10 +9294,10 @@
         <v>794</v>
       </c>
       <c r="AO14">
-        <v>0.99687120387267125</v>
+        <v>0.99418244113372889</v>
       </c>
       <c r="AP14">
-        <v>57.361262334360205</v>
+        <v>106.6552458816375</v>
       </c>
       <c r="AR14" t="s">
         <v>414</v>
@@ -9324,16 +9324,16 @@
         <v>926</v>
       </c>
       <c r="BA14" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="BB14" t="s">
-        <v>903</v>
+        <v>650</v>
       </c>
       <c r="BC14">
-        <v>0.98154438143849254</v>
+        <v>0.99193721244794397</v>
       </c>
       <c r="BD14">
-        <v>338.35300696097039</v>
+        <v>147.81777178769397</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9398,16 +9398,16 @@
         <v>425</v>
       </c>
       <c r="Y15" t="s">
-        <v>350</v>
+        <v>386</v>
       </c>
       <c r="Z15" t="s">
         <v>579</v>
       </c>
       <c r="AA15">
-        <v>0.99462937148232844</v>
+        <v>0.9966137462997855</v>
       </c>
       <c r="AB15">
-        <v>98.461522823979266</v>
+        <v>62.081317837266766</v>
       </c>
       <c r="AD15" t="s">
         <v>414</v>
@@ -9440,10 +9440,10 @@
         <v>796</v>
       </c>
       <c r="AO15">
-        <v>0.99584476105827657</v>
+        <v>0.99206751173516827</v>
       </c>
       <c r="AP15">
-        <v>76.179380598263194</v>
+        <v>145.42895152191466</v>
       </c>
       <c r="AR15" t="s">
         <v>414</v>
@@ -9470,16 +9470,16 @@
         <v>928</v>
       </c>
       <c r="BA15" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="BB15" t="s">
-        <v>975</v>
+        <v>794</v>
       </c>
       <c r="BC15">
-        <v>0.98137594918937099</v>
+        <v>0.98154438143849254</v>
       </c>
       <c r="BD15">
-        <v>341.44093152819772</v>
+        <v>338.35300696097039</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9544,16 +9544,16 @@
         <v>427</v>
       </c>
       <c r="Y16" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="Z16" t="s">
         <v>580</v>
       </c>
       <c r="AA16">
-        <v>0.99462643269733408</v>
+        <v>0.99011796851295664</v>
       </c>
       <c r="AB16">
-        <v>98.51540054887441</v>
+        <v>181.17057726246117</v>
       </c>
       <c r="AD16" t="s">
         <v>414</v>
@@ -9586,10 +9586,10 @@
         <v>798</v>
       </c>
       <c r="AO16">
-        <v>0.9961146125371938</v>
+        <v>0.99566554346996428</v>
       </c>
       <c r="AP16">
-        <v>71.232103484781334</v>
+        <v>79.46503638398778</v>
       </c>
       <c r="AR16" t="s">
         <v>414</v>
@@ -9622,10 +9622,10 @@
         <v>977</v>
       </c>
       <c r="BC16">
-        <v>0.9889956676941275</v>
+        <v>0.99307601382667698</v>
       </c>
       <c r="BD16">
-        <v>201.74609227432916</v>
+        <v>126.93974651092147</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9690,16 +9690,16 @@
         <v>429</v>
       </c>
       <c r="Y17" t="s">
-        <v>362</v>
+        <v>391</v>
       </c>
       <c r="Z17" t="s">
         <v>581</v>
       </c>
       <c r="AA17">
-        <v>0.99755789282691543</v>
+        <v>0.99635118654529808</v>
       </c>
       <c r="AB17">
-        <v>44.77196483988353</v>
+        <v>66.894913336202478</v>
       </c>
       <c r="AD17" t="s">
         <v>414</v>
@@ -9732,10 +9732,10 @@
         <v>800</v>
       </c>
       <c r="AO17">
-        <v>0.99607298561021362</v>
+        <v>0.99667664296701652</v>
       </c>
       <c r="AP17">
-        <v>71.995263812749926</v>
+        <v>60.928212271363194</v>
       </c>
       <c r="AR17" t="s">
         <v>414</v>
@@ -9765,13 +9765,13 @@
         <v>978</v>
       </c>
       <c r="BB17" t="s">
-        <v>576</v>
+        <v>979</v>
       </c>
       <c r="BC17">
-        <v>0.99193721244794397</v>
+        <v>0.99275904397179515</v>
       </c>
       <c r="BD17">
-        <v>147.81777178769397</v>
+        <v>132.75086051708826</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9836,16 +9836,16 @@
         <v>431</v>
       </c>
       <c r="Y18" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="Z18" t="s">
         <v>582</v>
       </c>
       <c r="AA18">
-        <v>0.99246356041150996</v>
+        <v>0.99440507690252466</v>
       </c>
       <c r="AB18">
-        <v>138.16805912231732</v>
+        <v>102.57359012038077</v>
       </c>
       <c r="AD18" t="s">
         <v>414</v>
@@ -9878,10 +9878,10 @@
         <v>802</v>
       </c>
       <c r="AO18">
-        <v>0.9929182563937401</v>
+        <v>0.99608442334318104</v>
       </c>
       <c r="AP18">
-        <v>129.83196611476453</v>
+        <v>71.785572041680055</v>
       </c>
       <c r="AR18" t="s">
         <v>414</v>
@@ -9908,16 +9908,16 @@
         <v>934</v>
       </c>
       <c r="BA18" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="BB18" t="s">
-        <v>631</v>
+        <v>981</v>
       </c>
       <c r="BC18">
-        <v>0.97123008268954114</v>
+        <v>0.96206044130113966</v>
       </c>
       <c r="BD18">
-        <v>527.44848402507967</v>
+        <v>695.55857614577315</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9982,16 +9982,16 @@
         <v>433</v>
       </c>
       <c r="Y19" t="s">
-        <v>403</v>
+        <v>363</v>
       </c>
       <c r="Z19" t="s">
         <v>583</v>
       </c>
       <c r="AA19">
-        <v>0.99670408962762203</v>
+        <v>0.99125780375299366</v>
       </c>
       <c r="AB19">
-        <v>60.425023493595695</v>
+        <v>160.27359786178269</v>
       </c>
       <c r="AD19" t="s">
         <v>414</v>
@@ -10024,10 +10024,10 @@
         <v>804</v>
       </c>
       <c r="AO19">
-        <v>0.99628542339510884</v>
+        <v>0.9967907157363165</v>
       </c>
       <c r="AP19">
-        <v>68.100571089671959</v>
+        <v>58.836878167530941</v>
       </c>
       <c r="AR19" t="s">
         <v>414</v>
@@ -10054,16 +10054,16 @@
         <v>936</v>
       </c>
       <c r="BA19" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="BB19" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
       <c r="BC19">
-        <v>0.99307601382667698</v>
+        <v>0.98742179529179352</v>
       </c>
       <c r="BD19">
-        <v>126.93974651092147</v>
+        <v>230.6004196504513</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -10128,16 +10128,16 @@
         <v>435</v>
       </c>
       <c r="Y20" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="Z20" t="s">
         <v>584</v>
       </c>
       <c r="AA20">
-        <v>0.9960389195261472</v>
+        <v>0.99619006668481902</v>
       </c>
       <c r="AB20">
-        <v>72.619808687301173</v>
+        <v>69.848777444984194</v>
       </c>
       <c r="AD20" t="s">
         <v>414</v>
@@ -10170,10 +10170,10 @@
         <v>806</v>
       </c>
       <c r="AO20">
-        <v>0.99720397512579328</v>
+        <v>0.99443964677468366</v>
       </c>
       <c r="AP20">
-        <v>51.260456027123361</v>
+        <v>101.93980913079895</v>
       </c>
       <c r="AR20" t="s">
         <v>414</v>
@@ -10200,16 +10200,16 @@
         <v>938</v>
       </c>
       <c r="BA20" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="BB20" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="BC20">
-        <v>0.99275904397179515</v>
+        <v>0.99526782804010661</v>
       </c>
       <c r="BD20">
-        <v>132.75086051708826</v>
+        <v>86.756485931379871</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -10274,16 +10274,16 @@
         <v>437</v>
       </c>
       <c r="Y21" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="Z21" t="s">
         <v>585</v>
       </c>
       <c r="AA21">
-        <v>0.99707957985864093</v>
+        <v>0.99021813732178554</v>
       </c>
       <c r="AB21">
-        <v>53.541035924916123</v>
+        <v>179.3341491005981</v>
       </c>
       <c r="AD21" t="s">
         <v>414</v>
@@ -10316,10 +10316,10 @@
         <v>808</v>
       </c>
       <c r="AO21">
-        <v>0.99565348329230585</v>
+        <v>0.99761003390352465</v>
       </c>
       <c r="AP21">
-        <v>79.686139641060379</v>
+        <v>43.816045102048356</v>
       </c>
       <c r="AR21" t="s">
         <v>414</v>
@@ -10346,16 +10346,16 @@
         <v>940</v>
       </c>
       <c r="BA21" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="BB21" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="BC21">
-        <v>0.98734896749216872</v>
+        <v>0.98605138538291048</v>
       </c>
       <c r="BD21">
-        <v>231.9355959769062</v>
+        <v>255.7246013133088</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -10420,16 +10420,16 @@
         <v>439</v>
       </c>
       <c r="Y22" t="s">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="Z22" t="s">
         <v>586</v>
       </c>
       <c r="AA22">
-        <v>0.99699505644961572</v>
+        <v>0.99686736582623381</v>
       </c>
       <c r="AB22">
-        <v>55.090631757044932</v>
+        <v>57.431626519047455</v>
       </c>
       <c r="AD22" t="s">
         <v>414</v>
@@ -10462,10 +10462,10 @@
         <v>810</v>
       </c>
       <c r="AO22">
-        <v>0.99618121233373258</v>
+        <v>0.99777413567568085</v>
       </c>
       <c r="AP22">
-        <v>70.011107214903078</v>
+        <v>40.807512612516987</v>
       </c>
       <c r="AR22" t="s">
         <v>414</v>
@@ -10492,16 +10492,16 @@
         <v>942</v>
       </c>
       <c r="BA22" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="BB22" t="s">
-        <v>987</v>
+        <v>650</v>
       </c>
       <c r="BC22">
-        <v>0.98158890816872557</v>
+        <v>0.99603877136023145</v>
       </c>
       <c r="BD22">
-        <v>337.53668357336363</v>
+        <v>72.622525062424401</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10566,16 +10566,16 @@
         <v>441</v>
       </c>
       <c r="Y23" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="Z23" t="s">
         <v>587</v>
       </c>
       <c r="AA23">
-        <v>0.99170691261633115</v>
+        <v>0.99725672762159434</v>
       </c>
       <c r="AB23">
-        <v>152.03993536726261</v>
+        <v>50.29332693743671</v>
       </c>
       <c r="AD23" t="s">
         <v>414</v>
@@ -10608,10 +10608,10 @@
         <v>812</v>
       </c>
       <c r="AO23">
-        <v>0.99592364356186902</v>
+        <v>0.99439150850611324</v>
       </c>
       <c r="AP23">
-        <v>74.733201365734146</v>
+        <v>102.82234405458999</v>
       </c>
       <c r="AR23" t="s">
         <v>414</v>
@@ -10641,13 +10641,13 @@
         <v>988</v>
       </c>
       <c r="BB23" t="s">
-        <v>631</v>
+        <v>877</v>
       </c>
       <c r="BC23">
-        <v>0.98402494782096717</v>
+        <v>0.98389167860462323</v>
       </c>
       <c r="BD23">
-        <v>292.87595661560192</v>
+        <v>295.31922558190735</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10712,16 +10712,16 @@
         <v>443</v>
       </c>
       <c r="Y24" t="s">
-        <v>376</v>
+        <v>349</v>
       </c>
       <c r="Z24" t="s">
         <v>588</v>
       </c>
       <c r="AA24">
-        <v>0.9904035062850528</v>
+        <v>0.99569491323214321</v>
       </c>
       <c r="AB24">
-        <v>175.93571810736526</v>
+        <v>78.926590744041093</v>
       </c>
       <c r="AD24" t="s">
         <v>414</v>
@@ -10754,10 +10754,10 @@
         <v>814</v>
       </c>
       <c r="AO24">
-        <v>0.99641167752379312</v>
+        <v>0.99595416313893737</v>
       </c>
       <c r="AP24">
-        <v>65.785912063792665</v>
+        <v>74.173675786148877</v>
       </c>
       <c r="AR24" t="s">
         <v>414</v>
@@ -10787,13 +10787,13 @@
         <v>989</v>
       </c>
       <c r="BB24" t="s">
-        <v>990</v>
+        <v>604</v>
       </c>
       <c r="BC24">
-        <v>0.99223982078870177</v>
+        <v>0.97123008268954114</v>
       </c>
       <c r="BD24">
-        <v>142.26995220713331</v>
+        <v>527.44848402507967</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10858,16 +10858,16 @@
         <v>445</v>
       </c>
       <c r="Y25" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="Z25" t="s">
         <v>589</v>
       </c>
       <c r="AA25">
-        <v>0.99579357955795456</v>
+        <v>0.99484118006716937</v>
       </c>
       <c r="AB25">
-        <v>77.117708104165573</v>
+        <v>94.578365435227795</v>
       </c>
       <c r="AD25" t="s">
         <v>414</v>
@@ -10900,10 +10900,10 @@
         <v>816</v>
       </c>
       <c r="AO25">
-        <v>0.99784941409648109</v>
+        <v>0.99687821505939955</v>
       </c>
       <c r="AP25">
-        <v>39.427408231180806</v>
+        <v>57.232723911007447</v>
       </c>
       <c r="AR25" t="s">
         <v>414</v>
@@ -10930,16 +10930,16 @@
         <v>948</v>
       </c>
       <c r="BA25" t="s">
+        <v>990</v>
+      </c>
+      <c r="BB25" t="s">
         <v>991</v>
       </c>
-      <c r="BB25" t="s">
-        <v>576</v>
-      </c>
       <c r="BC25">
-        <v>0.99603877136023145</v>
+        <v>0.98838558997012138</v>
       </c>
       <c r="BD25">
-        <v>72.622525062424401</v>
+        <v>212.93085054777492</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -11004,16 +11004,16 @@
         <v>447</v>
       </c>
       <c r="Y26" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="Z26" t="s">
         <v>590</v>
       </c>
       <c r="AA26">
-        <v>0.99066346416517681</v>
+        <v>0.99539558382203508</v>
       </c>
       <c r="AB26">
-        <v>171.16982363842584</v>
+        <v>84.414296596023817</v>
       </c>
       <c r="AD26" t="s">
         <v>414</v>
@@ -11046,10 +11046,10 @@
         <v>818</v>
       </c>
       <c r="AO26">
-        <v>0.99831921281104818</v>
+        <v>0.99368259233234391</v>
       </c>
       <c r="AP26">
-        <v>30.814431797450247</v>
+        <v>115.81914057369519</v>
       </c>
       <c r="AR26" t="s">
         <v>414</v>
@@ -11079,13 +11079,13 @@
         <v>992</v>
       </c>
       <c r="BB26" t="s">
-        <v>993</v>
+        <v>794</v>
       </c>
       <c r="BC26">
-        <v>0.96206044130113966</v>
+        <v>0.98730637899749651</v>
       </c>
       <c r="BD26">
-        <v>695.55857614577315</v>
+        <v>232.71638504589731</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -11150,16 +11150,16 @@
         <v>449</v>
       </c>
       <c r="Y27" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="Z27" t="s">
         <v>591</v>
       </c>
       <c r="AA27">
-        <v>0.99560939477262078</v>
+        <v>0.99579357955795456</v>
       </c>
       <c r="AB27">
-        <v>80.494429168619106</v>
+        <v>77.117708104165573</v>
       </c>
       <c r="AD27" t="s">
         <v>414</v>
@@ -11192,10 +11192,10 @@
         <v>820</v>
       </c>
       <c r="AO27">
-        <v>0.99845356202909108</v>
+        <v>0.9954443722844073</v>
       </c>
       <c r="AP27">
-        <v>28.351362799997673</v>
+        <v>83.519841452532361</v>
       </c>
       <c r="AR27" t="s">
         <v>414</v>
@@ -11222,16 +11222,16 @@
         <v>952</v>
       </c>
       <c r="BA27" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="BB27" t="s">
-        <v>977</v>
+        <v>604</v>
       </c>
       <c r="BC27">
-        <v>0.98742179529179352</v>
+        <v>0.98809190602642238</v>
       </c>
       <c r="BD27">
-        <v>230.6004196504513</v>
+        <v>218.31505618225569</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -11296,16 +11296,16 @@
         <v>451</v>
       </c>
       <c r="Y28" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="Z28" t="s">
         <v>592</v>
       </c>
       <c r="AA28">
-        <v>0.99544039231362502</v>
+        <v>0.99066346416517681</v>
       </c>
       <c r="AB28">
-        <v>83.592807583541571</v>
+        <v>171.16982363842584</v>
       </c>
       <c r="AD28" t="s">
         <v>414</v>
@@ -11338,10 +11338,10 @@
         <v>822</v>
       </c>
       <c r="AO28">
-        <v>0.99611612132862803</v>
+        <v>0.99363040616365128</v>
       </c>
       <c r="AP28">
-        <v>71.204442308486065</v>
+        <v>116.77588699972566</v>
       </c>
       <c r="AR28" t="s">
         <v>414</v>
@@ -11368,16 +11368,16 @@
         <v>954</v>
       </c>
       <c r="BA28" t="s">
+        <v>994</v>
+      </c>
+      <c r="BB28" t="s">
         <v>995</v>
       </c>
-      <c r="BB28" t="s">
-        <v>996</v>
-      </c>
       <c r="BC28">
-        <v>0.98787195157138663</v>
+        <v>0.994208528887633</v>
       </c>
       <c r="BD28">
-        <v>222.34755452457901</v>
+        <v>106.17697039339514</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11442,16 +11442,16 @@
         <v>453</v>
       </c>
       <c r="Y29" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="Z29" t="s">
         <v>593</v>
       </c>
       <c r="AA29">
-        <v>0.99190124970484694</v>
+        <v>0.99560939477262078</v>
       </c>
       <c r="AB29">
-        <v>148.47708874447352</v>
+        <v>80.494429168619106</v>
       </c>
       <c r="AD29" t="s">
         <v>414</v>
@@ -11484,10 +11484,10 @@
         <v>824</v>
       </c>
       <c r="AO29">
-        <v>0.99761105057437038</v>
+        <v>0.99782402570187057</v>
       </c>
       <c r="AP29">
-        <v>43.797406136543607</v>
+        <v>39.892862132373601</v>
       </c>
       <c r="AR29" t="s">
         <v>414</v>
@@ -11514,16 +11514,16 @@
         <v>956</v>
       </c>
       <c r="BA29" t="s">
+        <v>996</v>
+      </c>
+      <c r="BB29" t="s">
         <v>997</v>
       </c>
-      <c r="BB29" t="s">
-        <v>903</v>
-      </c>
       <c r="BC29">
-        <v>0.98853599644984702</v>
+        <v>0.98734896749216872</v>
       </c>
       <c r="BD29">
-        <v>210.17339841947171</v>
+        <v>231.9355959769062</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11588,16 +11588,16 @@
         <v>455</v>
       </c>
       <c r="Y30" t="s">
-        <v>412</v>
+        <v>339</v>
       </c>
       <c r="Z30" t="s">
         <v>594</v>
       </c>
       <c r="AA30">
-        <v>0.9940089461809174</v>
+        <v>0.99544039231362502</v>
       </c>
       <c r="AB30">
-        <v>109.83598668318054</v>
+        <v>83.592807583541571</v>
       </c>
       <c r="AD30" t="s">
         <v>414</v>
@@ -11630,10 +11630,10 @@
         <v>826</v>
       </c>
       <c r="AO30">
-        <v>0.99615289372526561</v>
+        <v>0.99756462867082185</v>
       </c>
       <c r="AP30">
-        <v>70.530281703464368</v>
+        <v>44.648474368267038</v>
       </c>
       <c r="AR30" t="s">
         <v>414</v>
@@ -11666,10 +11666,10 @@
         <v>999</v>
       </c>
       <c r="BC30">
-        <v>0.98838558997012138</v>
+        <v>0.98158890816872557</v>
       </c>
       <c r="BD30">
-        <v>212.93085054777492</v>
+        <v>337.53668357336363</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11734,16 +11734,16 @@
         <v>457</v>
       </c>
       <c r="Y31" t="s">
-        <v>393</v>
+        <v>346</v>
       </c>
       <c r="Z31" t="s">
         <v>595</v>
       </c>
       <c r="AA31">
-        <v>0.99600761890991041</v>
+        <v>0.99190124970484694</v>
       </c>
       <c r="AB31">
-        <v>73.193653318309615</v>
+        <v>148.47708874447352</v>
       </c>
       <c r="AD31" t="s">
         <v>414</v>
@@ -11776,10 +11776,10 @@
         <v>828</v>
       </c>
       <c r="AO31">
-        <v>0.99074948308423383</v>
+        <v>0.99540934349034305</v>
       </c>
       <c r="AP31">
-        <v>169.59281012238051</v>
+        <v>84.162036010377406</v>
       </c>
       <c r="AR31" t="s">
         <v>414</v>
@@ -11809,13 +11809,13 @@
         <v>1000</v>
       </c>
       <c r="BB31" t="s">
-        <v>903</v>
+        <v>604</v>
       </c>
       <c r="BC31">
-        <v>0.98730637899749651</v>
+        <v>0.98402494782096717</v>
       </c>
       <c r="BD31">
-        <v>232.71638504589731</v>
+        <v>292.87595661560192</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11880,16 +11880,16 @@
         <v>459</v>
       </c>
       <c r="Y32" t="s">
-        <v>352</v>
+        <v>412</v>
       </c>
       <c r="Z32" t="s">
         <v>596</v>
       </c>
       <c r="AA32">
-        <v>0.99700029739711071</v>
+        <v>0.9940089461809174</v>
       </c>
       <c r="AB32">
-        <v>54.994547719637801</v>
+        <v>109.83598668318054</v>
       </c>
       <c r="AD32" t="s">
         <v>414</v>
@@ -11922,10 +11922,10 @@
         <v>830</v>
       </c>
       <c r="AO32">
-        <v>0.99270401267208797</v>
+        <v>0.99657664224037934</v>
       </c>
       <c r="AP32">
-        <v>133.75976767838793</v>
+        <v>62.761558926379031</v>
       </c>
       <c r="AR32" t="s">
         <v>414</v>
@@ -11955,13 +11955,13 @@
         <v>1001</v>
       </c>
       <c r="BB32" t="s">
-        <v>631</v>
+        <v>1002</v>
       </c>
       <c r="BC32">
-        <v>0.98809190602642238</v>
+        <v>0.99223982078870177</v>
       </c>
       <c r="BD32">
-        <v>218.31505618225569</v>
+        <v>142.26995220713331</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -12026,16 +12026,16 @@
         <v>461</v>
       </c>
       <c r="Y33" t="s">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="Z33" t="s">
         <v>597</v>
       </c>
       <c r="AA33">
-        <v>0.99408511741207395</v>
+        <v>0.99600761890991041</v>
       </c>
       <c r="AB33">
-        <v>108.43951411197776</v>
+        <v>73.193653318309615</v>
       </c>
       <c r="AD33" t="s">
         <v>414</v>
@@ -12068,10 +12068,10 @@
         <v>832</v>
       </c>
       <c r="AO33">
-        <v>0.99764772442226368</v>
+        <v>0.99091245964276031</v>
       </c>
       <c r="AP33">
-        <v>43.125052258499352</v>
+        <v>166.60490654939525</v>
       </c>
       <c r="AR33" t="s">
         <v>414</v>
@@ -12098,16 +12098,16 @@
         <v>964</v>
       </c>
       <c r="BA33" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="BB33" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="BC33">
-        <v>0.994208528887633</v>
+        <v>0.98787195157138663</v>
       </c>
       <c r="BD33">
-        <v>106.17697039339514</v>
+        <v>222.34755452457901</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -12172,16 +12172,16 @@
         <v>463</v>
       </c>
       <c r="Y34" t="s">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="Z34" t="s">
         <v>598</v>
       </c>
       <c r="AA34">
-        <v>0.99529948277209723</v>
+        <v>0.99700029739711071</v>
       </c>
       <c r="AB34">
-        <v>86.176149178218239</v>
+        <v>54.994547719637801</v>
       </c>
       <c r="AD34" t="s">
         <v>414</v>
@@ -12214,10 +12214,10 @@
         <v>834</v>
       </c>
       <c r="AO34">
-        <v>0.99703044337128366</v>
+        <v>0.99846230399777702</v>
       </c>
       <c r="AP34">
-        <v>54.441871526466279</v>
+        <v>28.191093374087806</v>
       </c>
       <c r="AR34" t="s">
         <v>414</v>
@@ -12244,16 +12244,16 @@
         <v>966</v>
       </c>
       <c r="BA34" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="BB34" t="s">
-        <v>1005</v>
+        <v>794</v>
       </c>
       <c r="BC34">
-        <v>0.99308209783432144</v>
+        <v>0.98853599644984702</v>
       </c>
       <c r="BD34">
-        <v>126.82820637077275</v>
+        <v>210.17339841947171</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -12318,16 +12318,16 @@
         <v>465</v>
       </c>
       <c r="Y35" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="Z35" t="s">
         <v>599</v>
       </c>
       <c r="AA35">
-        <v>0.99551989204648861</v>
+        <v>0.99408511741207395</v>
       </c>
       <c r="AB35">
-        <v>82.135312481041623</v>
+        <v>108.43951411197776</v>
       </c>
       <c r="AD35" t="s">
         <v>414</v>
@@ -12428,16 +12428,16 @@
         <v>467</v>
       </c>
       <c r="Y36" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="Z36" t="s">
         <v>600</v>
       </c>
       <c r="AA36">
-        <v>0.9979392050107273</v>
+        <v>0.99529948277209723</v>
       </c>
       <c r="AB36">
-        <v>37.781241469999252</v>
+        <v>86.176149178218239</v>
       </c>
       <c r="AD36" t="s">
         <v>414</v>
@@ -12538,16 +12538,16 @@
         <v>469</v>
       </c>
       <c r="Y37" t="s">
-        <v>354</v>
+        <v>404</v>
       </c>
       <c r="Z37" t="s">
         <v>601</v>
       </c>
       <c r="AA37">
-        <v>0.9982033297630386</v>
+        <v>0.99675394464629852</v>
       </c>
       <c r="AB37">
-        <v>32.938954344292306</v>
+        <v>59.511014817860868</v>
       </c>
       <c r="AD37" t="s">
         <v>414</v>
@@ -12648,16 +12648,16 @@
         <v>471</v>
       </c>
       <c r="Y38" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="Z38" t="s">
         <v>602</v>
       </c>
       <c r="AA38">
-        <v>0.99769372286934066</v>
+        <v>0.9962437778559039</v>
       </c>
       <c r="AB38">
-        <v>42.281747395421668</v>
+        <v>68.86407264176249</v>
       </c>
       <c r="AD38" t="s">
         <v>414</v>
@@ -12758,16 +12758,16 @@
         <v>473</v>
       </c>
       <c r="Y39" t="s">
-        <v>338</v>
+        <v>371</v>
       </c>
       <c r="Z39" t="s">
         <v>603</v>
       </c>
       <c r="AA39">
-        <v>0.99080344458411729</v>
+        <v>0.99617006411660358</v>
       </c>
       <c r="AB39">
-        <v>168.60351595784994</v>
+        <v>70.215491195600634</v>
       </c>
       <c r="AD39" t="s">
         <v>414</v>
@@ -12868,16 +12868,16 @@
         <v>475</v>
       </c>
       <c r="Y40" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="Z40" t="s">
         <v>604</v>
       </c>
       <c r="AA40">
-        <v>0.98636012609964985</v>
+        <v>0.99282834435956602</v>
       </c>
       <c r="AB40">
-        <v>250.06435483975247</v>
+        <v>131.48035340795542</v>
       </c>
       <c r="AD40" t="s">
         <v>414</v>
@@ -12907,7 +12907,7 @@
         <v>845</v>
       </c>
       <c r="AN40" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AO40">
         <v>0.9950502580620818</v>
@@ -12978,16 +12978,16 @@
         <v>477</v>
       </c>
       <c r="Y41" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Z41" t="s">
         <v>605</v>
       </c>
       <c r="AA41">
-        <v>0.99598850450039844</v>
+        <v>0.99569310304523451</v>
       </c>
       <c r="AB41">
-        <v>73.544084159361034</v>
+        <v>78.959777504033639</v>
       </c>
       <c r="AD41" t="s">
         <v>414</v>
@@ -13020,10 +13020,10 @@
         <v>847</v>
       </c>
       <c r="AO41">
-        <v>0.99474825047892679</v>
+        <v>0.99533901157332205</v>
       </c>
       <c r="AP41">
-        <v>96.282074553009053</v>
+        <v>85.451454489096079</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -13088,16 +13088,16 @@
         <v>479</v>
       </c>
       <c r="Y42" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Z42" t="s">
         <v>606</v>
       </c>
       <c r="AA42">
-        <v>0.99310312827752323</v>
+        <v>0.99502431999137919</v>
       </c>
       <c r="AB42">
-        <v>126.44264824540761</v>
+        <v>91.220800158047325</v>
       </c>
       <c r="AD42" t="s">
         <v>414</v>
@@ -13130,10 +13130,10 @@
         <v>849</v>
       </c>
       <c r="AO42">
-        <v>0.99684527597966854</v>
+        <v>0.99754339130519476</v>
       </c>
       <c r="AP42">
-        <v>57.836607039410005</v>
+        <v>45.037826071429087</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -13198,16 +13198,16 @@
         <v>481</v>
       </c>
       <c r="Y43" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="Z43" t="s">
         <v>607</v>
       </c>
       <c r="AA43">
-        <v>0.99557960200072415</v>
+        <v>0.99584577617815018</v>
       </c>
       <c r="AB43">
-        <v>81.040629986723459</v>
+        <v>76.16077006724673</v>
       </c>
       <c r="AD43" t="s">
         <v>414</v>
@@ -13240,10 +13240,10 @@
         <v>851</v>
       </c>
       <c r="AO43">
-        <v>0.9943927545810437</v>
+        <v>0.99542398891280204</v>
       </c>
       <c r="AP43">
-        <v>102.79949934753229</v>
+        <v>83.893536598629126</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -13308,16 +13308,16 @@
         <v>483</v>
       </c>
       <c r="Y44" t="s">
-        <v>398</v>
+        <v>350</v>
       </c>
       <c r="Z44" t="s">
         <v>608</v>
       </c>
       <c r="AA44">
-        <v>0.99295357769237991</v>
+        <v>0.99462937148232844</v>
       </c>
       <c r="AB44">
-        <v>129.18440897303603</v>
+        <v>98.461522823979266</v>
       </c>
       <c r="AD44" t="s">
         <v>414</v>
@@ -13350,10 +13350,10 @@
         <v>853</v>
       </c>
       <c r="AO44">
-        <v>0.99425851119451991</v>
+        <v>0.99617615910816915</v>
       </c>
       <c r="AP44">
-        <v>105.26062810046888</v>
+        <v>70.103749683564772</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -13418,16 +13418,16 @@
         <v>485</v>
       </c>
       <c r="Y45" t="s">
-        <v>355</v>
+        <v>405</v>
       </c>
       <c r="Z45" t="s">
         <v>609</v>
       </c>
       <c r="AA45">
-        <v>0.99696751363483405</v>
+        <v>0.99462643269733408</v>
       </c>
       <c r="AB45">
-        <v>55.595583361375894</v>
+        <v>98.51540054887441</v>
       </c>
       <c r="AD45" t="s">
         <v>414</v>
@@ -13460,10 +13460,10 @@
         <v>855</v>
       </c>
       <c r="AO45">
-        <v>0.99712282780353001</v>
+        <v>0.99611612132862803</v>
       </c>
       <c r="AP45">
-        <v>52.74815693528295</v>
+        <v>71.204442308486065</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13528,16 +13528,16 @@
         <v>487</v>
       </c>
       <c r="Y46" t="s">
-        <v>408</v>
+        <v>362</v>
       </c>
       <c r="Z46" t="s">
         <v>610</v>
       </c>
       <c r="AA46">
-        <v>0.98964014500078279</v>
+        <v>0.99755789282691543</v>
       </c>
       <c r="AB46">
-        <v>189.93067498564957</v>
+        <v>44.77196483988353</v>
       </c>
       <c r="AD46" t="s">
         <v>414</v>
@@ -13570,10 +13570,10 @@
         <v>857</v>
       </c>
       <c r="AO46">
-        <v>0.99005506097810436</v>
+        <v>0.99761105057437038</v>
       </c>
       <c r="AP46">
-        <v>182.32388206808599</v>
+        <v>43.797406136543607</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13638,16 +13638,16 @@
         <v>489</v>
       </c>
       <c r="Y47" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="Z47" t="s">
         <v>611</v>
       </c>
       <c r="AA47">
-        <v>0.9966137462997855</v>
+        <v>0.99246356041150996</v>
       </c>
       <c r="AB47">
-        <v>62.081317837266766</v>
+        <v>138.16805912231732</v>
       </c>
       <c r="AD47" t="s">
         <v>414</v>
@@ -13680,10 +13680,10 @@
         <v>859</v>
       </c>
       <c r="AO47">
-        <v>0.99631269816920021</v>
+        <v>0.99615289372526561</v>
       </c>
       <c r="AP47">
-        <v>67.600533564663479</v>
+        <v>70.530281703464368</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13748,16 +13748,16 @@
         <v>491</v>
       </c>
       <c r="Y48" t="s">
-        <v>384</v>
+        <v>347</v>
       </c>
       <c r="Z48" t="s">
         <v>612</v>
       </c>
       <c r="AA48">
-        <v>0.99011796851295664</v>
+        <v>0.99478609753984348</v>
       </c>
       <c r="AB48">
-        <v>181.17057726246117</v>
+        <v>95.588211769535249</v>
       </c>
       <c r="AD48" t="s">
         <v>414</v>
@@ -13790,10 +13790,10 @@
         <v>861</v>
       </c>
       <c r="AO48">
-        <v>0.99772400077475298</v>
+        <v>0.99618121233373258</v>
       </c>
       <c r="AP48">
-        <v>41.726652462862774</v>
+        <v>70.011107214903078</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -13858,16 +13858,16 @@
         <v>493</v>
       </c>
       <c r="Y49" t="s">
-        <v>391</v>
+        <v>345</v>
       </c>
       <c r="Z49" t="s">
         <v>613</v>
       </c>
       <c r="AA49">
-        <v>0.99635118654529808</v>
+        <v>0.99568525132868968</v>
       </c>
       <c r="AB49">
-        <v>66.894913336202478</v>
+        <v>79.10372564068922</v>
       </c>
       <c r="AD49" t="s">
         <v>414</v>
@@ -13900,10 +13900,10 @@
         <v>863</v>
       </c>
       <c r="AO49">
-        <v>0.99604673274056554</v>
+        <v>0.99592364356186902</v>
       </c>
       <c r="AP49">
-        <v>72.476566422965192</v>
+        <v>74.733201365734146</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -13968,16 +13968,16 @@
         <v>495</v>
       </c>
       <c r="Y50" t="s">
-        <v>390</v>
+        <v>342</v>
       </c>
       <c r="Z50" t="s">
         <v>614</v>
       </c>
       <c r="AA50">
-        <v>0.99440507690252466</v>
+        <v>0.99590266392783655</v>
       </c>
       <c r="AB50">
-        <v>102.57359012038077</v>
+        <v>75.117827989662302</v>
       </c>
       <c r="AD50" t="s">
         <v>414</v>
@@ -14010,10 +14010,10 @@
         <v>865</v>
       </c>
       <c r="AO50">
-        <v>0.99533901157332205</v>
+        <v>0.99641167752379312</v>
       </c>
       <c r="AP50">
-        <v>85.451454489096079</v>
+        <v>65.785912063792665</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -14078,16 +14078,16 @@
         <v>497</v>
       </c>
       <c r="Y51" t="s">
-        <v>395</v>
+        <v>357</v>
       </c>
       <c r="Z51" t="s">
         <v>615</v>
       </c>
       <c r="AA51">
-        <v>0.99540885392130762</v>
+        <v>0.99449671322390631</v>
       </c>
       <c r="AB51">
-        <v>84.171011442693441</v>
+        <v>100.89359089505045</v>
       </c>
       <c r="AD51" t="s">
         <v>414</v>
@@ -14120,10 +14120,10 @@
         <v>867</v>
       </c>
       <c r="AO51">
-        <v>0.99754339130519476</v>
+        <v>0.99425851119451991</v>
       </c>
       <c r="AP51">
-        <v>45.037826071429087</v>
+        <v>105.26062810046888</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -14188,16 +14188,16 @@
         <v>499</v>
       </c>
       <c r="Y52" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="Z52" t="s">
         <v>616</v>
       </c>
       <c r="AA52">
-        <v>0.99360802526828129</v>
+        <v>0.99701127670202949</v>
       </c>
       <c r="AB52">
-        <v>117.18620341484296</v>
+        <v>54.793260462791778</v>
       </c>
       <c r="AD52" t="s">
         <v>414</v>
@@ -14230,10 +14230,10 @@
         <v>869</v>
       </c>
       <c r="AO52">
-        <v>0.99542398891280204</v>
+        <v>0.99712282780353001</v>
       </c>
       <c r="AP52">
-        <v>83.893536598629126</v>
+        <v>52.74815693528295</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -14298,16 +14298,16 @@
         <v>501</v>
       </c>
       <c r="Y53" t="s">
-        <v>400</v>
+        <v>341</v>
       </c>
       <c r="Z53" t="s">
         <v>617</v>
       </c>
       <c r="AA53">
-        <v>0.99515679011930902</v>
+        <v>0.99571525957109708</v>
       </c>
       <c r="AB53">
-        <v>88.792181146001369</v>
+        <v>78.553574529886689</v>
       </c>
       <c r="AD53" t="s">
         <v>414</v>
@@ -14340,10 +14340,10 @@
         <v>871</v>
       </c>
       <c r="AO53">
-        <v>0.99617615910816915</v>
+        <v>0.99005506097810436</v>
       </c>
       <c r="AP53">
-        <v>70.103749683564772</v>
+        <v>182.32388206808599</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -14408,16 +14408,16 @@
         <v>503</v>
       </c>
       <c r="Y54" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="Z54" t="s">
         <v>618</v>
       </c>
       <c r="AA54">
-        <v>0.99409145347725225</v>
+        <v>0.99553579843385909</v>
       </c>
       <c r="AB54">
-        <v>108.32335291704148</v>
+        <v>81.84369537924907</v>
       </c>
       <c r="AD54" t="s">
         <v>414</v>
@@ -14450,10 +14450,10 @@
         <v>873</v>
       </c>
       <c r="AO54">
-        <v>0.99368259233234391</v>
+        <v>0.99631269816920021</v>
       </c>
       <c r="AP54">
-        <v>115.81914057369519</v>
+        <v>67.600533564663479</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -14518,16 +14518,16 @@
         <v>505</v>
       </c>
       <c r="Y55" t="s">
-        <v>381</v>
+        <v>353</v>
       </c>
       <c r="Z55" t="s">
         <v>619</v>
       </c>
       <c r="AA55">
-        <v>0.99464051280908794</v>
+        <v>0.99734372305564056</v>
       </c>
       <c r="AB55">
-        <v>98.257265166721183</v>
+        <v>48.698410646589842</v>
       </c>
       <c r="AD55" t="s">
         <v>414</v>
@@ -14560,10 +14560,10 @@
         <v>875</v>
       </c>
       <c r="AO55">
-        <v>0.9954443722844073</v>
+        <v>0.99772400077475298</v>
       </c>
       <c r="AP55">
-        <v>83.519841452532361</v>
+        <v>41.726652462862774</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -14628,16 +14628,16 @@
         <v>507</v>
       </c>
       <c r="Y56" t="s">
-        <v>335</v>
+        <v>388</v>
       </c>
       <c r="Z56" t="s">
         <v>620</v>
       </c>
       <c r="AA56">
-        <v>0.99578350963230966</v>
+        <v>0.99662670467221526</v>
       </c>
       <c r="AB56">
-        <v>77.302323407656075</v>
+        <v>61.843747676054292</v>
       </c>
       <c r="AD56" t="s">
         <v>414</v>
@@ -14670,10 +14670,10 @@
         <v>877</v>
       </c>
       <c r="AO56">
-        <v>0.99363040616365128</v>
+        <v>0.99604673274056554</v>
       </c>
       <c r="AP56">
-        <v>116.77588699972566</v>
+        <v>72.476566422965192</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -14738,16 +14738,16 @@
         <v>509</v>
       </c>
       <c r="Y57" t="s">
-        <v>407</v>
+        <v>361</v>
       </c>
       <c r="Z57" t="s">
         <v>621</v>
       </c>
       <c r="AA57">
-        <v>0.99720191150310689</v>
+        <v>0.99740761205901929</v>
       </c>
       <c r="AB57">
-        <v>51.298289109706943</v>
+        <v>47.527112251312907</v>
       </c>
       <c r="AD57" t="s">
         <v>414</v>
@@ -14780,10 +14780,10 @@
         <v>879</v>
       </c>
       <c r="AO57">
-        <v>0.99782402570187057</v>
+        <v>0.99660391553167893</v>
       </c>
       <c r="AP57">
-        <v>39.892862132373601</v>
+        <v>62.261548585886977</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -14848,16 +14848,16 @@
         <v>511</v>
       </c>
       <c r="Y58" t="s">
-        <v>401</v>
+        <v>368</v>
       </c>
       <c r="Z58" t="s">
         <v>622</v>
       </c>
       <c r="AA58">
-        <v>0.9954551465796494</v>
+        <v>0.99730769203227776</v>
       </c>
       <c r="AB58">
-        <v>83.32231270642734</v>
+        <v>49.358979408241737</v>
       </c>
       <c r="AD58" t="s">
         <v>414</v>
@@ -14890,10 +14890,10 @@
         <v>881</v>
       </c>
       <c r="AO58">
-        <v>0.99756462867082185</v>
+        <v>0.9959136876641268</v>
       </c>
       <c r="AP58">
-        <v>44.648474368267038</v>
+        <v>74.915726157675209</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -14958,16 +14958,16 @@
         <v>513</v>
       </c>
       <c r="Y59" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="Z59" t="s">
         <v>623</v>
       </c>
       <c r="AA59">
-        <v>0.99552053983611355</v>
+        <v>0.998073964784436</v>
       </c>
       <c r="AB59">
-        <v>82.123436337918946</v>
+        <v>35.310645618673441</v>
       </c>
       <c r="AD59" t="s">
         <v>414</v>
@@ -15000,10 +15000,10 @@
         <v>883</v>
       </c>
       <c r="AO59">
-        <v>0.99568571110966864</v>
+        <v>0.9935275292913992</v>
       </c>
       <c r="AP59">
-        <v>79.095296322741547</v>
+        <v>118.66196299101547</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -15068,16 +15068,16 @@
         <v>515</v>
       </c>
       <c r="Y60" t="s">
-        <v>385</v>
+        <v>337</v>
       </c>
       <c r="Z60" t="s">
         <v>624</v>
       </c>
       <c r="AA60">
-        <v>0.98935435476104872</v>
+        <v>0.99551989204648861</v>
       </c>
       <c r="AB60">
-        <v>195.1701627141077</v>
+        <v>82.135312481041623</v>
       </c>
       <c r="AD60" t="s">
         <v>414</v>
@@ -15110,10 +15110,10 @@
         <v>885</v>
       </c>
       <c r="AO60">
-        <v>0.99609062270337045</v>
+        <v>0.99687120387267125</v>
       </c>
       <c r="AP60">
-        <v>71.671917104874566</v>
+        <v>57.361262334360205</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -15178,16 +15178,16 @@
         <v>517</v>
       </c>
       <c r="Y61" t="s">
-        <v>392</v>
+        <v>356</v>
       </c>
       <c r="Z61" t="s">
         <v>625</v>
       </c>
       <c r="AA61">
-        <v>0.99775872574768198</v>
+        <v>0.9979392050107273</v>
       </c>
       <c r="AB61">
-        <v>41.090027959164246</v>
+        <v>37.781241469999252</v>
       </c>
       <c r="AD61" t="s">
         <v>414</v>
@@ -15220,10 +15220,10 @@
         <v>887</v>
       </c>
       <c r="AO61">
-        <v>0.99598588086244633</v>
+        <v>0.99720397512579328</v>
       </c>
       <c r="AP61">
-        <v>73.592184188484865</v>
+        <v>51.260456027123361</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -15288,16 +15288,16 @@
         <v>519</v>
       </c>
       <c r="Y62" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="Z62" t="s">
         <v>626</v>
       </c>
       <c r="AA62">
-        <v>0.99125780375299366</v>
+        <v>0.9982033297630386</v>
       </c>
       <c r="AB62">
-        <v>160.27359786178269</v>
+        <v>32.938954344292306</v>
       </c>
       <c r="AD62" t="s">
         <v>414</v>
@@ -15330,10 +15330,10 @@
         <v>889</v>
       </c>
       <c r="AO62">
-        <v>0.99540934349034305</v>
+        <v>0.99565348329230585</v>
       </c>
       <c r="AP62">
-        <v>84.162036010377406</v>
+        <v>79.686139641060379</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -15398,16 +15398,16 @@
         <v>521</v>
       </c>
       <c r="Y63" t="s">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="Z63" t="s">
         <v>627</v>
       </c>
       <c r="AA63">
-        <v>0.99619006668481902</v>
+        <v>0.99769372286934066</v>
       </c>
       <c r="AB63">
-        <v>69.848777444984194</v>
+        <v>42.281747395421668</v>
       </c>
       <c r="AD63" t="s">
         <v>414</v>
@@ -15440,10 +15440,10 @@
         <v>891</v>
       </c>
       <c r="AO63">
-        <v>0.99657664224037934</v>
+        <v>0.99074948308423383</v>
       </c>
       <c r="AP63">
-        <v>62.761558926379031</v>
+        <v>169.59281012238051</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -15508,16 +15508,16 @@
         <v>523</v>
       </c>
       <c r="Y64" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="Z64" t="s">
         <v>628</v>
       </c>
       <c r="AA64">
-        <v>0.99021813732178554</v>
+        <v>0.99540885392130762</v>
       </c>
       <c r="AB64">
-        <v>179.3341491005981</v>
+        <v>84.171011442693441</v>
       </c>
       <c r="AD64" t="s">
         <v>414</v>
@@ -15550,10 +15550,10 @@
         <v>893</v>
       </c>
       <c r="AO64">
-        <v>0.99091245964276031</v>
+        <v>0.99270401267208797</v>
       </c>
       <c r="AP64">
-        <v>166.60490654939525</v>
+        <v>133.75976767838793</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -15618,16 +15618,16 @@
         <v>525</v>
       </c>
       <c r="Y65" t="s">
-        <v>389</v>
+        <v>351</v>
       </c>
       <c r="Z65" t="s">
         <v>629</v>
       </c>
       <c r="AA65">
-        <v>0.99686736582623381</v>
+        <v>0.99360802526828129</v>
       </c>
       <c r="AB65">
-        <v>57.431626519047455</v>
+        <v>117.18620341484296</v>
       </c>
       <c r="AD65" t="s">
         <v>414</v>
@@ -15660,10 +15660,10 @@
         <v>895</v>
       </c>
       <c r="AO65">
-        <v>0.99846230399777702</v>
+        <v>0.99764772442226368</v>
       </c>
       <c r="AP65">
-        <v>28.191093374087806</v>
+        <v>43.125052258499352</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -15728,16 +15728,16 @@
         <v>527</v>
       </c>
       <c r="Y66" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="Z66" t="s">
         <v>630</v>
       </c>
       <c r="AA66">
-        <v>0.99725672762159434</v>
+        <v>0.99515679011930902</v>
       </c>
       <c r="AB66">
-        <v>50.29332693743671</v>
+        <v>88.792181146001369</v>
       </c>
       <c r="AD66" t="s">
         <v>414</v>
@@ -15770,10 +15770,10 @@
         <v>897</v>
       </c>
       <c r="AO66">
-        <v>0.99439150850611324</v>
+        <v>0.99703044337128366</v>
       </c>
       <c r="AP66">
-        <v>102.82234405458999</v>
+        <v>54.441871526466279</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -15838,16 +15838,16 @@
         <v>529</v>
       </c>
       <c r="Y67" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="Z67" t="s">
         <v>631</v>
       </c>
       <c r="AA67">
-        <v>0.99282834435956602</v>
+        <v>0.99409145347725225</v>
       </c>
       <c r="AB67">
-        <v>131.48035340795542</v>
+        <v>108.32335291704148</v>
       </c>
       <c r="AD67" t="s">
         <v>414</v>
@@ -15880,10 +15880,10 @@
         <v>899</v>
       </c>
       <c r="AO67">
-        <v>0.99595416313893737</v>
+        <v>0.99584476105827657</v>
       </c>
       <c r="AP67">
-        <v>74.173675786148877</v>
+        <v>76.179380598263194</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -15948,16 +15948,16 @@
         <v>531</v>
       </c>
       <c r="Y68" t="s">
-        <v>344</v>
+        <v>381</v>
       </c>
       <c r="Z68" t="s">
         <v>632</v>
       </c>
       <c r="AA68">
-        <v>0.99569310304523451</v>
+        <v>0.99464051280908794</v>
       </c>
       <c r="AB68">
-        <v>78.959777504033639</v>
+        <v>98.257265166721183</v>
       </c>
       <c r="AD68" t="s">
         <v>414</v>
@@ -15990,10 +15990,10 @@
         <v>901</v>
       </c>
       <c r="AO68">
-        <v>0.99687821505939955</v>
+        <v>0.9961146125371938</v>
       </c>
       <c r="AP68">
-        <v>57.232723911007447</v>
+        <v>71.232103484781334</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -16058,16 +16058,16 @@
         <v>533</v>
       </c>
       <c r="Y69" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="Z69" t="s">
         <v>633</v>
       </c>
       <c r="AA69">
-        <v>0.99502431999137919</v>
+        <v>0.99670408962762203</v>
       </c>
       <c r="AB69">
-        <v>91.220800158047325</v>
+        <v>60.425023493595695</v>
       </c>
       <c r="AD69" t="s">
         <v>414</v>
@@ -16100,10 +16100,10 @@
         <v>903</v>
       </c>
       <c r="AO69">
-        <v>0.99418244113372889</v>
+        <v>0.99607298561021362</v>
       </c>
       <c r="AP69">
-        <v>106.6552458816375</v>
+        <v>71.995263812749926</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -16168,16 +16168,16 @@
         <v>535</v>
       </c>
       <c r="Y70" t="s">
-        <v>402</v>
+        <v>358</v>
       </c>
       <c r="Z70" t="s">
         <v>634</v>
       </c>
       <c r="AA70">
-        <v>0.99584577617815018</v>
+        <v>0.9960389195261472</v>
       </c>
       <c r="AB70">
-        <v>76.16077006724673</v>
+        <v>72.619808687301173</v>
       </c>
       <c r="AD70" t="s">
         <v>414</v>
@@ -16210,10 +16210,10 @@
         <v>905</v>
       </c>
       <c r="AO70">
-        <v>0.99206751173516827</v>
+        <v>0.9929182563937401</v>
       </c>
       <c r="AP70">
-        <v>145.42895152191466</v>
+        <v>129.83196611476453</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -16278,16 +16278,16 @@
         <v>537</v>
       </c>
       <c r="Y71" t="s">
-        <v>404</v>
+        <v>372</v>
       </c>
       <c r="Z71" t="s">
         <v>635</v>
       </c>
       <c r="AA71">
-        <v>0.99675394464629852</v>
+        <v>0.99707957985864093</v>
       </c>
       <c r="AB71">
-        <v>59.511014817860868</v>
+        <v>53.541035924916123</v>
       </c>
       <c r="AD71" t="s">
         <v>414</v>
@@ -16320,10 +16320,10 @@
         <v>907</v>
       </c>
       <c r="AO71">
-        <v>0.99566554346996428</v>
+        <v>0.99628542339510884</v>
       </c>
       <c r="AP71">
-        <v>79.46503638398778</v>
+        <v>68.100571089671959</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -16388,16 +16388,16 @@
         <v>539</v>
       </c>
       <c r="Y72" t="s">
-        <v>369</v>
+        <v>338</v>
       </c>
       <c r="Z72" t="s">
         <v>636</v>
       </c>
       <c r="AA72">
-        <v>0.9962437778559039</v>
+        <v>0.99080344458411729</v>
       </c>
       <c r="AB72">
-        <v>68.86407264176249</v>
+        <v>168.60351595784994</v>
       </c>
       <c r="AD72" t="s">
         <v>414</v>
@@ -16430,10 +16430,10 @@
         <v>909</v>
       </c>
       <c r="AO72">
-        <v>0.99667664296701652</v>
+        <v>0.99568571110966864</v>
       </c>
       <c r="AP72">
-        <v>60.928212271363194</v>
+        <v>79.095296322741547</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -16498,16 +16498,16 @@
         <v>541</v>
       </c>
       <c r="Y73" t="s">
-        <v>371</v>
+        <v>410</v>
       </c>
       <c r="Z73" t="s">
         <v>637</v>
       </c>
       <c r="AA73">
-        <v>0.99617006411660358</v>
+        <v>0.98636012609964985</v>
       </c>
       <c r="AB73">
-        <v>70.215491195600634</v>
+        <v>250.06435483975247</v>
       </c>
       <c r="AD73" t="s">
         <v>414</v>
@@ -16540,10 +16540,10 @@
         <v>911</v>
       </c>
       <c r="AO73">
-        <v>0.99608442334318104</v>
+        <v>0.99609062270337045</v>
       </c>
       <c r="AP73">
-        <v>71.785572041680055</v>
+        <v>71.671917104874566</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -16608,16 +16608,16 @@
         <v>543</v>
       </c>
       <c r="Y74" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="Z74" t="s">
         <v>638</v>
       </c>
       <c r="AA74">
-        <v>0.99478609753984348</v>
+        <v>0.99598850450039844</v>
       </c>
       <c r="AB74">
-        <v>95.588211769535249</v>
+        <v>73.544084159361034</v>
       </c>
       <c r="AD74" t="s">
         <v>414</v>
@@ -16650,10 +16650,10 @@
         <v>913</v>
       </c>
       <c r="AO74">
-        <v>0.9967907157363165</v>
+        <v>0.99598588086244633</v>
       </c>
       <c r="AP74">
-        <v>58.836878167530941</v>
+        <v>73.592184188484865</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -16718,16 +16718,16 @@
         <v>545</v>
       </c>
       <c r="Y75" t="s">
-        <v>345</v>
+        <v>409</v>
       </c>
       <c r="Z75" t="s">
         <v>639</v>
       </c>
       <c r="AA75">
-        <v>0.99568525132868968</v>
+        <v>0.99310312827752323</v>
       </c>
       <c r="AB75">
-        <v>79.10372564068922</v>
+        <v>126.44264824540761</v>
       </c>
       <c r="AD75" t="s">
         <v>414</v>
@@ -16760,10 +16760,10 @@
         <v>915</v>
       </c>
       <c r="AO75">
-        <v>0.99443964677468366</v>
+        <v>0.99784941409648109</v>
       </c>
       <c r="AP75">
-        <v>101.93980913079895</v>
+        <v>39.427408231180806</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -16828,16 +16828,16 @@
         <v>547</v>
       </c>
       <c r="Y76" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="Z76" t="s">
         <v>640</v>
       </c>
       <c r="AA76">
-        <v>0.99590266392783655</v>
+        <v>0.99578350963230966</v>
       </c>
       <c r="AB76">
-        <v>75.117827989662302</v>
+        <v>77.302323407656075</v>
       </c>
       <c r="AD76" t="s">
         <v>414</v>
@@ -16870,10 +16870,10 @@
         <v>917</v>
       </c>
       <c r="AO76">
-        <v>0.99761003390352465</v>
+        <v>0.99831921281104818</v>
       </c>
       <c r="AP76">
-        <v>43.816045102048356</v>
+        <v>30.814431797450247</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -16938,16 +16938,16 @@
         <v>549</v>
       </c>
       <c r="Y77" t="s">
-        <v>357</v>
+        <v>407</v>
       </c>
       <c r="Z77" t="s">
         <v>641</v>
       </c>
       <c r="AA77">
-        <v>0.99449671322390631</v>
+        <v>0.99720191150310689</v>
       </c>
       <c r="AB77">
-        <v>100.89359089505045</v>
+        <v>51.298289109706943</v>
       </c>
       <c r="AD77" t="s">
         <v>414</v>
@@ -16980,10 +16980,10 @@
         <v>919</v>
       </c>
       <c r="AO77">
-        <v>0.99777413567568085</v>
+        <v>0.99845356202909108</v>
       </c>
       <c r="AP77">
-        <v>40.807512612516987</v>
+        <v>28.351362799997673</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -17048,16 +17048,16 @@
         <v>551</v>
       </c>
       <c r="Y78" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="Z78" t="s">
         <v>642</v>
       </c>
       <c r="AA78">
-        <v>0.99701127670202949</v>
+        <v>0.9954551465796494</v>
       </c>
       <c r="AB78">
-        <v>54.793260462791778</v>
+        <v>83.32231270642734</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -17122,16 +17122,16 @@
         <v>553</v>
       </c>
       <c r="Y79" t="s">
-        <v>349</v>
+        <v>399</v>
       </c>
       <c r="Z79" t="s">
         <v>643</v>
       </c>
       <c r="AA79">
-        <v>0.99569491323214321</v>
+        <v>0.99552053983611355</v>
       </c>
       <c r="AB79">
-        <v>78.926590744041093</v>
+        <v>82.123436337918946</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -17196,16 +17196,16 @@
         <v>555</v>
       </c>
       <c r="Y80" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Z80" t="s">
         <v>644</v>
       </c>
       <c r="AA80">
-        <v>0.99484118006716937</v>
+        <v>0.98935435476104872</v>
       </c>
       <c r="AB80">
-        <v>94.578365435227795</v>
+        <v>195.1701627141077</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -17270,16 +17270,16 @@
         <v>557</v>
       </c>
       <c r="Y81" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="Z81" t="s">
         <v>645</v>
       </c>
       <c r="AA81">
-        <v>0.99539558382203508</v>
+        <v>0.99775872574768198</v>
       </c>
       <c r="AB81">
-        <v>84.414296596023817</v>
+        <v>41.090027959164246</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -17344,16 +17344,16 @@
         <v>559</v>
       </c>
       <c r="Y82" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="Z82" t="s">
         <v>646</v>
       </c>
       <c r="AA82">
-        <v>0.99571525957109708</v>
+        <v>0.99699505644961572</v>
       </c>
       <c r="AB82">
-        <v>78.553574529886689</v>
+        <v>55.090631757044932</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -17418,16 +17418,16 @@
         <v>561</v>
       </c>
       <c r="Y83" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="Z83" t="s">
         <v>647</v>
       </c>
       <c r="AA83">
-        <v>0.99553579843385909</v>
+        <v>0.99170691261633115</v>
       </c>
       <c r="AB83">
-        <v>81.84369537924907</v>
+        <v>152.03993536726261</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -17492,16 +17492,16 @@
         <v>563</v>
       </c>
       <c r="Y84" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="Z84" t="s">
         <v>648</v>
       </c>
       <c r="AA84">
-        <v>0.99734372305564056</v>
+        <v>0.9904035062850528</v>
       </c>
       <c r="AB84">
-        <v>48.698410646589842</v>
+        <v>175.93571810736526</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -17566,16 +17566,16 @@
         <v>565</v>
       </c>
       <c r="Y85" t="s">
-        <v>388</v>
+        <v>336</v>
       </c>
       <c r="Z85" t="s">
         <v>649</v>
       </c>
       <c r="AA85">
-        <v>0.99662670467221526</v>
+        <v>0.99359748433922845</v>
       </c>
       <c r="AB85">
-        <v>61.843747676054292</v>
+        <v>117.37945378081078</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -17640,16 +17640,16 @@
         <v>567</v>
       </c>
       <c r="Y86" t="s">
-        <v>361</v>
+        <v>406</v>
       </c>
       <c r="Z86" t="s">
         <v>650</v>
       </c>
       <c r="AA86">
-        <v>0.99740761205901929</v>
+        <v>0.99592552983543692</v>
       </c>
       <c r="AB86">
-        <v>47.527112251312907</v>
+        <v>74.698619683656872</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -17714,16 +17714,16 @@
         <v>569</v>
       </c>
       <c r="Y87" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="Z87" t="s">
         <v>651</v>
       </c>
       <c r="AA87">
-        <v>0.99730769203227776</v>
+        <v>0.99463677905825021</v>
       </c>
       <c r="AB87">
-        <v>49.358979408241737</v>
+        <v>98.325717265413417</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -17788,16 +17788,16 @@
         <v>571</v>
       </c>
       <c r="Y88" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="Z88" t="s">
         <v>652</v>
       </c>
       <c r="AA88">
-        <v>0.998073964784436</v>
+        <v>0.99667564038633161</v>
       </c>
       <c r="AB88">
-        <v>35.310645618673441</v>
+        <v>60.946592917253042</v>
       </c>
     </row>
   </sheetData>
@@ -17806,7 +17806,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFB20448-A4D2-499B-8A01-753D67DDF0D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{910D7DAB-E951-40C6-9633-3C737EBD2B12}">
   <dimension ref="B9:Z77"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17918,7 +17918,7 @@
         <v>1006</v>
       </c>
       <c r="K11" t="s">
-        <v>799</v>
+        <v>902</v>
       </c>
       <c r="L11">
         <v>29.7146465744454</v>
@@ -17951,7 +17951,7 @@
         <v>1140</v>
       </c>
       <c r="X11" t="s">
-        <v>992</v>
+        <v>980</v>
       </c>
       <c r="Y11">
         <v>0.33825</v>
@@ -18019,7 +18019,7 @@
         <v>1142</v>
       </c>
       <c r="X12" t="s">
-        <v>979</v>
+        <v>989</v>
       </c>
       <c r="Y12">
         <v>10.88325</v>
@@ -18054,7 +18054,7 @@
         <v>1010</v>
       </c>
       <c r="K13" t="s">
-        <v>870</v>
+        <v>852</v>
       </c>
       <c r="L13">
         <v>24.156328337033791</v>
@@ -18087,7 +18087,7 @@
         <v>1144</v>
       </c>
       <c r="X13" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
         <v>26.983499999999999</v>
@@ -18122,7 +18122,7 @@
         <v>1012</v>
       </c>
       <c r="K14" t="s">
-        <v>866</v>
+        <v>848</v>
       </c>
       <c r="L14">
         <v>16.006796560234815</v>
@@ -18155,7 +18155,7 @@
         <v>1146</v>
       </c>
       <c r="X14" t="s">
-        <v>984</v>
+        <v>996</v>
       </c>
       <c r="Y14">
         <v>42.507750000000001</v>
@@ -18223,7 +18223,7 @@
         <v>1148</v>
       </c>
       <c r="X15" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="Y15">
         <v>24.900749999999999</v>
@@ -18258,7 +18258,7 @@
         <v>1016</v>
       </c>
       <c r="K16" t="s">
-        <v>819</v>
+        <v>918</v>
       </c>
       <c r="L16">
         <v>29.492382648463739</v>
@@ -18291,7 +18291,7 @@
         <v>1150</v>
       </c>
       <c r="X16" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="Y16">
         <v>18.545249999999999</v>
@@ -18326,7 +18326,7 @@
         <v>1018</v>
       </c>
       <c r="K17" t="s">
-        <v>817</v>
+        <v>916</v>
       </c>
       <c r="L17">
         <v>8.6778699255653748</v>
@@ -18359,7 +18359,7 @@
         <v>1152</v>
       </c>
       <c r="X17" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="Y17">
         <v>29.838000000000001</v>
@@ -18394,7 +18394,7 @@
         <v>1020</v>
       </c>
       <c r="K18" t="s">
-        <v>815</v>
+        <v>914</v>
       </c>
       <c r="L18">
         <v>12.772248157772113</v>
@@ -18427,7 +18427,7 @@
         <v>1154</v>
       </c>
       <c r="X18" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="Y18">
         <v>58.689</v>
@@ -18462,7 +18462,7 @@
         <v>1022</v>
       </c>
       <c r="K19" t="s">
-        <v>805</v>
+        <v>886</v>
       </c>
       <c r="L19">
         <v>15.217638427037592</v>
@@ -18495,7 +18495,7 @@
         <v>1156</v>
       </c>
       <c r="X19" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="Y19">
         <v>48.432000000000002</v>
@@ -18530,7 +18530,7 @@
         <v>1024</v>
       </c>
       <c r="K20" t="s">
-        <v>914</v>
+        <v>805</v>
       </c>
       <c r="L20">
         <v>3.1385663053565613</v>
@@ -18563,7 +18563,7 @@
         <v>1158</v>
       </c>
       <c r="X20" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="Y20">
         <v>47.794499999999999</v>
@@ -18598,7 +18598,7 @@
         <v>1026</v>
       </c>
       <c r="K21" t="s">
-        <v>831</v>
+        <v>894</v>
       </c>
       <c r="L21">
         <v>4.0628682283884237</v>
@@ -18631,7 +18631,7 @@
         <v>1160</v>
       </c>
       <c r="X21" t="s">
-        <v>986</v>
+        <v>998</v>
       </c>
       <c r="Y21">
         <v>7.1767500000000002</v>
@@ -18666,7 +18666,7 @@
         <v>1028</v>
       </c>
       <c r="K22" t="s">
-        <v>900</v>
+        <v>815</v>
       </c>
       <c r="L22">
         <v>19.408837136062758</v>
@@ -18699,7 +18699,7 @@
         <v>1162</v>
       </c>
       <c r="X22" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="Y22">
         <v>8.1052499999999998</v>
@@ -18734,7 +18734,7 @@
         <v>1030</v>
       </c>
       <c r="K23" t="s">
-        <v>807</v>
+        <v>888</v>
       </c>
       <c r="L23">
         <v>15.054857587707319</v>
@@ -18767,7 +18767,7 @@
         <v>1164</v>
       </c>
       <c r="X23" t="s">
-        <v>968</v>
+        <v>983</v>
       </c>
       <c r="Y23">
         <v>9.3810000000000002</v>
@@ -18802,7 +18802,7 @@
         <v>1032</v>
       </c>
       <c r="K24" t="s">
-        <v>850</v>
+        <v>791</v>
       </c>
       <c r="L24">
         <v>13.019602602156084</v>
@@ -18835,7 +18835,7 @@
         <v>1166</v>
       </c>
       <c r="X24" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="Y24">
         <v>11.47575</v>
@@ -18870,7 +18870,7 @@
         <v>1034</v>
       </c>
       <c r="K25" t="s">
-        <v>856</v>
+        <v>870</v>
       </c>
       <c r="L25">
         <v>25.094411791551167</v>
@@ -18903,7 +18903,7 @@
         <v>1168</v>
       </c>
       <c r="X25" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="Y25">
         <v>6.1372499999999999</v>
@@ -18938,7 +18938,7 @@
         <v>1036</v>
       </c>
       <c r="K26" t="s">
-        <v>823</v>
+        <v>856</v>
       </c>
       <c r="L26">
         <v>18.31221960055294</v>
@@ -18971,7 +18971,7 @@
         <v>1170</v>
       </c>
       <c r="X26" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="Y26">
         <v>14.57325</v>
@@ -19006,7 +19006,7 @@
         <v>1038</v>
       </c>
       <c r="K27" t="s">
-        <v>918</v>
+        <v>809</v>
       </c>
       <c r="L27">
         <v>27.91719839668141</v>
@@ -19039,7 +19039,7 @@
         <v>1172</v>
       </c>
       <c r="X27" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="Y27">
         <v>10.491</v>
@@ -19074,7 +19074,7 @@
         <v>1040</v>
       </c>
       <c r="K28" t="s">
-        <v>894</v>
+        <v>833</v>
       </c>
       <c r="L28">
         <v>8.5144758814389814</v>
@@ -19107,7 +19107,7 @@
         <v>1174</v>
       </c>
       <c r="X28" t="s">
-        <v>994</v>
+        <v>982</v>
       </c>
       <c r="Y28">
         <v>17.414249999999999</v>
@@ -19142,7 +19142,7 @@
         <v>1042</v>
       </c>
       <c r="K29" t="s">
-        <v>916</v>
+        <v>807</v>
       </c>
       <c r="L29">
         <v>12.144708893333986</v>
@@ -19175,7 +19175,7 @@
         <v>1176</v>
       </c>
       <c r="X29" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="Y29">
         <v>10.968</v>
@@ -19210,7 +19210,7 @@
         <v>1044</v>
       </c>
       <c r="K30" t="s">
-        <v>858</v>
+        <v>872</v>
       </c>
       <c r="L30">
         <v>1.6724491767694549</v>
@@ -19243,7 +19243,7 @@
         <v>1178</v>
       </c>
       <c r="X30" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="Y30">
         <v>10.79175</v>
@@ -19278,7 +19278,7 @@
         <v>1046</v>
       </c>
       <c r="K31" t="s">
-        <v>860</v>
+        <v>874</v>
       </c>
       <c r="L31">
         <v>13.894741632015101</v>
@@ -19311,7 +19311,7 @@
         <v>1180</v>
       </c>
       <c r="X31" t="s">
-        <v>1004</v>
+        <v>968</v>
       </c>
       <c r="Y31">
         <v>20.114249999999998</v>
@@ -19346,7 +19346,7 @@
         <v>1048</v>
       </c>
       <c r="K32" t="s">
-        <v>793</v>
+        <v>884</v>
       </c>
       <c r="L32">
         <v>11.876635800692616</v>
@@ -19379,7 +19379,7 @@
         <v>1182</v>
       </c>
       <c r="X32" t="s">
-        <v>972</v>
+        <v>988</v>
       </c>
       <c r="Y32">
         <v>44.373750000000001</v>
@@ -19414,7 +19414,7 @@
         <v>1050</v>
       </c>
       <c r="K33" t="s">
-        <v>862</v>
+        <v>876</v>
       </c>
       <c r="L33">
         <v>27.15579263061009</v>
@@ -19447,7 +19447,7 @@
         <v>1184</v>
       </c>
       <c r="X33" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="Y33">
         <v>18.57525</v>
@@ -19482,7 +19482,7 @@
         <v>1052</v>
       </c>
       <c r="K34" t="s">
-        <v>801</v>
+        <v>904</v>
       </c>
       <c r="L34">
         <v>27.043339674957092</v>
@@ -19515,7 +19515,7 @@
         <v>1186</v>
       </c>
       <c r="X34" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="Y34">
         <v>18.241499999999998</v>
@@ -19550,7 +19550,7 @@
         <v>1054</v>
       </c>
       <c r="K35" t="s">
-        <v>833</v>
+        <v>896</v>
       </c>
       <c r="L35">
         <v>12.170927347824723</v>
@@ -19585,7 +19585,7 @@
         <v>1056</v>
       </c>
       <c r="K36" t="s">
-        <v>803</v>
+        <v>906</v>
       </c>
       <c r="L36">
         <v>26.999240466622091</v>
@@ -19620,7 +19620,7 @@
         <v>1058</v>
       </c>
       <c r="K37" t="s">
-        <v>880</v>
+        <v>825</v>
       </c>
       <c r="L37">
         <v>23.305350986470582</v>
@@ -19655,7 +19655,7 @@
         <v>1060</v>
       </c>
       <c r="K38" t="s">
-        <v>825</v>
+        <v>858</v>
       </c>
       <c r="L38">
         <v>19.293897715957783</v>
@@ -19690,7 +19690,7 @@
         <v>1062</v>
       </c>
       <c r="K39" t="s">
-        <v>868</v>
+        <v>850</v>
       </c>
       <c r="L39">
         <v>34.8352470366899</v>
@@ -19725,7 +19725,7 @@
         <v>1064</v>
       </c>
       <c r="K40" t="s">
-        <v>886</v>
+        <v>912</v>
       </c>
       <c r="L40">
         <v>22.439012549480047</v>
@@ -19760,7 +19760,7 @@
         <v>1066</v>
       </c>
       <c r="K41" t="s">
-        <v>876</v>
+        <v>821</v>
       </c>
       <c r="L41">
         <v>19.571302094407635</v>
@@ -19795,7 +19795,7 @@
         <v>1068</v>
       </c>
       <c r="K42" t="s">
-        <v>892</v>
+        <v>831</v>
       </c>
       <c r="L42">
         <v>16.258507759053195</v>
@@ -19830,7 +19830,7 @@
         <v>1070</v>
       </c>
       <c r="K43" t="s">
-        <v>910</v>
+        <v>801</v>
       </c>
       <c r="L43">
         <v>48.074816212675138</v>
@@ -19865,7 +19865,7 @@
         <v>1072</v>
       </c>
       <c r="K44" t="s">
-        <v>789</v>
+        <v>880</v>
       </c>
       <c r="L44">
         <v>65.59399718970684</v>
@@ -19900,7 +19900,7 @@
         <v>1074</v>
       </c>
       <c r="K45" t="s">
-        <v>906</v>
+        <v>797</v>
       </c>
       <c r="L45">
         <v>65.706815294563484</v>
@@ -19935,7 +19935,7 @@
         <v>1076</v>
       </c>
       <c r="K46" t="s">
-        <v>898</v>
+        <v>813</v>
       </c>
       <c r="L46">
         <v>13.859521883612567</v>
@@ -19970,7 +19970,7 @@
         <v>1078</v>
       </c>
       <c r="K47" t="s">
-        <v>890</v>
+        <v>829</v>
       </c>
       <c r="L47">
         <v>32.682899602232801</v>
@@ -20005,7 +20005,7 @@
         <v>1080</v>
       </c>
       <c r="K48" t="s">
-        <v>813</v>
+        <v>864</v>
       </c>
       <c r="L48">
         <v>39.028686646898073</v>
@@ -20075,7 +20075,7 @@
         <v>1084</v>
       </c>
       <c r="K50" t="s">
-        <v>811</v>
+        <v>862</v>
       </c>
       <c r="L50">
         <v>64.703394190718342</v>
@@ -20110,7 +20110,7 @@
         <v>1086</v>
       </c>
       <c r="K51" t="s">
-        <v>884</v>
+        <v>910</v>
       </c>
       <c r="L51">
         <v>46.777110562179843</v>
@@ -20180,7 +20180,7 @@
         <v>1090</v>
       </c>
       <c r="K53" t="s">
-        <v>872</v>
+        <v>817</v>
       </c>
       <c r="L53">
         <v>8.0718642408500934</v>
@@ -20250,7 +20250,7 @@
         <v>1094</v>
       </c>
       <c r="K55" t="s">
-        <v>874</v>
+        <v>819</v>
       </c>
       <c r="L55">
         <v>26.74310381624198</v>
@@ -20285,7 +20285,7 @@
         <v>1096</v>
       </c>
       <c r="K56" t="s">
-        <v>791</v>
+        <v>882</v>
       </c>
       <c r="L56">
         <v>47.811917655816522</v>
@@ -20320,7 +20320,7 @@
         <v>1098</v>
       </c>
       <c r="K57" t="s">
-        <v>904</v>
+        <v>795</v>
       </c>
       <c r="L57">
         <v>65.898010391046881</v>
@@ -20355,7 +20355,7 @@
         <v>1100</v>
       </c>
       <c r="K58" t="s">
-        <v>787</v>
+        <v>878</v>
       </c>
       <c r="L58">
         <v>49.914822287456737</v>
@@ -20390,7 +20390,7 @@
         <v>1102</v>
       </c>
       <c r="K59" t="s">
-        <v>902</v>
+        <v>793</v>
       </c>
       <c r="L59">
         <v>19.963633091222835</v>
@@ -20425,7 +20425,7 @@
         <v>1104</v>
       </c>
       <c r="K60" t="s">
-        <v>827</v>
+        <v>890</v>
       </c>
       <c r="L60">
         <v>71.04376789192942</v>
@@ -20460,7 +20460,7 @@
         <v>1106</v>
       </c>
       <c r="K61" t="s">
-        <v>864</v>
+        <v>846</v>
       </c>
       <c r="L61">
         <v>43.07229279461999</v>
@@ -20495,7 +20495,7 @@
         <v>1108</v>
       </c>
       <c r="K62" t="s">
-        <v>888</v>
+        <v>827</v>
       </c>
       <c r="L62">
         <v>38.769945374969119</v>
@@ -20530,7 +20530,7 @@
         <v>1110</v>
       </c>
       <c r="K63" t="s">
-        <v>896</v>
+        <v>811</v>
       </c>
       <c r="L63">
         <v>59.009737840109466</v>
@@ -20565,7 +20565,7 @@
         <v>1112</v>
       </c>
       <c r="K64" t="s">
-        <v>848</v>
+        <v>789</v>
       </c>
       <c r="L64">
         <v>28.865927665826828</v>
@@ -20600,7 +20600,7 @@
         <v>1114</v>
       </c>
       <c r="K65" t="s">
-        <v>821</v>
+        <v>854</v>
       </c>
       <c r="L65">
         <v>37.976260419426943</v>
@@ -20635,7 +20635,7 @@
         <v>1116</v>
       </c>
       <c r="K66" t="s">
-        <v>846</v>
+        <v>787</v>
       </c>
       <c r="L66">
         <v>44.88386263672971</v>
@@ -20670,7 +20670,7 @@
         <v>1118</v>
       </c>
       <c r="K67" t="s">
-        <v>882</v>
+        <v>908</v>
       </c>
       <c r="L67">
         <v>23.350121881103082</v>
@@ -20705,7 +20705,7 @@
         <v>1120</v>
       </c>
       <c r="K68" t="s">
-        <v>854</v>
+        <v>868</v>
       </c>
       <c r="L68">
         <v>15.289477961960474</v>
@@ -20740,7 +20740,7 @@
         <v>1122</v>
       </c>
       <c r="K69" t="s">
-        <v>878</v>
+        <v>823</v>
       </c>
       <c r="L69">
         <v>10.395885695189069</v>
@@ -20775,7 +20775,7 @@
         <v>1124</v>
       </c>
       <c r="K70" t="s">
-        <v>912</v>
+        <v>803</v>
       </c>
       <c r="L70">
         <v>23.89105636564183</v>
@@ -20810,7 +20810,7 @@
         <v>1126</v>
       </c>
       <c r="K71" t="s">
-        <v>852</v>
+        <v>866</v>
       </c>
       <c r="L71">
         <v>18.959710131684457</v>
@@ -20845,7 +20845,7 @@
         <v>1128</v>
       </c>
       <c r="K72" t="s">
-        <v>908</v>
+        <v>799</v>
       </c>
       <c r="L72">
         <v>6.6550975614073966</v>
@@ -20880,7 +20880,7 @@
         <v>1130</v>
       </c>
       <c r="K73" t="s">
-        <v>797</v>
+        <v>900</v>
       </c>
       <c r="L73">
         <v>13.961943802326671</v>
@@ -20915,7 +20915,7 @@
         <v>1132</v>
       </c>
       <c r="K74" t="s">
-        <v>829</v>
+        <v>892</v>
       </c>
       <c r="L74">
         <v>51.937776653453852</v>
@@ -20985,7 +20985,7 @@
         <v>1136</v>
       </c>
       <c r="K76" t="s">
-        <v>809</v>
+        <v>860</v>
       </c>
       <c r="L76">
         <v>19.42059121972445</v>
@@ -21020,7 +21020,7 @@
         <v>1138</v>
       </c>
       <c r="K77" t="s">
-        <v>795</v>
+        <v>898</v>
       </c>
       <c r="L77">
         <v>30.063621105864488</v>
@@ -21035,7 +21035,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1156FEA4-D1E4-4558-8239-293DED6806C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35FFF292-143B-4945-BDBE-92DFB43067F3}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22852,7 +22852,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D82F175-9C2A-4C77-B91C-2A7B69BE4775}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24158417-AFCF-4FCE-8D50-5FB1DF86D323}">
   <dimension ref="B2:M11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01960541-079E-4BDD-AC81-3A758C39037F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3959B16F-C97B-48FE-A6D4-BAC6EE1C7E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1375,18 +1375,336 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IND_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IND_062</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 62</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_IND_064</t>
   </si>
   <si>
@@ -1429,208 +1747,64 @@
     <t>connecting solar to buses in cluster 56</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
+    <t>distr_solelc_spv_IND_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
   </si>
   <si>
     <t>distr_solelc_spv_IND_007</t>
@@ -1675,186 +1849,171 @@
     <t>connecting solar to buses in cluster 45</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w372701897-765_IND,e_IN10-765_IND,e_w311176519-765_IND</t>
+  </si>
+  <si>
+    <t>e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND,e_w311571096-765_IND,e_w514344408-765_IND,e_w193216698-765_IND</t>
+  </si>
+  <si>
+    <t>e_w698045832-765_IND,e_w315477169-765_IND,e_w408924420-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN42-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN440-400_IND,e_IN386-400_IND,e_w1072445901-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN10-765_IND,e_w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND,e_w1206014676-765_IND,e_w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN300-765_IND,e_w166692103-400_IND,e_IN290-400_IND,e_w97392607-400_IND,e_w50885643-400_IND,e_w324059200-400_IND,e_IN317-400_IND,e_w50885643-765_IND,e_w577176545-400_IND,e_w209806624-400_IND,e_w1044735753-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN145-400_IND</t>
+  </si>
+  <si>
+    <t>e_w166692103-400_IND,e_w1044735753-400_IND,e_w1012817818-400_IND,e_w92994753-400_IND,e_w92360278-400_IND,e_w1238123371-400_IND,e_w94199110-400_IND,e_w485873934-400_IND,e_IN179-400_IND,e_IN286-400_IND,e_IN181-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1072445901-400_IND</t>
+  </si>
+  <si>
+    <t>e_w375941438-400_IND,e_IN145-400_IND</t>
+  </si>
+  <si>
+    <t>e_w608461884-765_IND,e_w318050929-765_IND,e_w315477169-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311176519-765_IND,e_w372701897-765_IND,e_w105373531-765_IND,e_IN10-765_IND,e_IN42-765_IND,e_w1341291951-765_IND</t>
+  </si>
+  <si>
+    <t>e_w801704865-765_IND,e_w1207477934-765_IND,e_w923365745-765_IND,e_IN684-765_IND</t>
+  </si>
+  <si>
+    <t>e_w840600239-765_IND,e_w408924427-765_IND,e_w506461670-765_IND</t>
+  </si>
+  <si>
+    <t>e_w409158116-765_IND,e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN486-765_IND,e_w655683221-765_IND,e_IN473-765_IND,e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN798-765_IND,e_w386153973-765_IND,e_w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>e_w315823978-765_IND,e_w386018740-765_IND,e_w801704865-765_IND,e_IN742-765_IND,e_w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>e_w688672798-765_IND,e_IN218-765_IND,e_IN215-765_IND,e_IN199-765_IND,e_IN194-765_IND,e_IN191-765_IND,e_w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>e_w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>e_w323266562-765_IND,e_w759521252-765_IND,e_w793144832-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1341647644-400_IND,e_IN263-400_IND,e_w93160503-400_IND,e_w526897229-400_IND,e_IN259-400_IND,e_IN320-400_IND,e_IN235-400_IND</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND,e_w1127651311-765_IND,e_w331275940-765_IND,e_w688672798-765_IND</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND,e_w429459345-765_IND</t>
+  </si>
+  <si>
+    <t>e_w316463122-765_IND,e_w318090288-765_IND,e_w318050929-765_IND,e_w315477169-765_IND,e_w698045832-765_IND</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND,e_IN806-765_IND,e_IN798-765_IND,e_w1206014676-765_IND</t>
+  </si>
+  <si>
+    <t>e_w342204888-765_IND,e_w245128370-765_IND,e_IN742-765_IND,e_w315824842-765_IND,e_w923365745-765_IND,e_w910151268-765_IND,e_w1074489047-765_IND</t>
+  </si>
+  <si>
+    <t>e_w759521252-765_IND,e_w118228036-400_IND,e_w793144832-765_IND,e_IN339-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1099365579-400_IND,e_w375941438-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN163-765_IND,e_w1143180503-765_IND,e_w654736039-765_IND,e_w631917408-765_IND,e_IN146-765_IND,e_w1077819664-765_IND,e_w311176519-765_IND,e_w369866141-765_IND,e_IN142-765_IND,e_IN108-765_IND,e_IN107-765_IND,e_IN94-765_IND</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND,e_IN610-765_IND,e_IN617-765_IND,e_w323266562-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1072445901-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w1336628403-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w688672798-765_IND,e_IN218-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND,e_IN659-765_IND</t>
+  </si>
+  <si>
+    <t>e_w331275940-765_IND,e_IN529-765_IND,e_w688672798-765_IND,e_w655683221-765_IND,e_IN489-765_IND,e_IN488-765_IND,e_IN486-765_IND</t>
+  </si>
+  <si>
+    <t>e_w654736039-765_IND,e_w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>e_w492377703-765_IND,e_w293597835-765_IND,e_w608461884-765_IND,e_w386018740-765_IND,e_w801704865-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311571096-765_IND,e_IN250-765_IND,e_IN247-765_IND,e_IN233-765_IND,e_w193216698-765_IND,e_w423702239-765_IND,e_IN295-765_IND,e_IN264-765_IND,e_w131484738-765_IND,e_IN246-765_IND,e_IN272-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311103617-765_IND,e_w166692103-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN235-400_IND,e_w465787206-400_IND,e_IN265-400_IND,e_w1265489491-400_IND</t>
+  </si>
+  <si>
+    <t>e_w386153973-765_IND,e_w342204888-765_IND,e_w751947947-765_IND,e_w910151268-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN128-765_IND,e_IN116-765_IND,e_w1341291951-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND,e_IN180-765_IND,e_IN206-765_IND,e_w311103617-765_IND</t>
+  </si>
+  <si>
+    <t>e_w374367235-400_IND,e_IN260-400_IND,e_w439006823-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1001700959-765_IND,e_IN218-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN218-765_IND,e_w1001700959-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_IN215-765_IND,e_IN191-765_IND,e_w1143180503-765_IND,e_IN163-765_IND,e_w654736039-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1207477934-765_IND,e_w840600239-765_IND,e_w506461670-765_IND,e_IN684-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311954703-765_IND,e_w1246177377-765_IND,e_IN540-765_IND,e_IN599-765_IND,e_IN586-765_IND,e_w353914761-765_IND,e_IN583-765_IND,e_IN555-765_IND,e_IN578-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN235-400_IND,e_w239498664-400_IND,e_IN265-400_IND,e_w1265489491-400_IND,e_w610646823-400_IND</t>
+  </si>
+  <si>
     <t>e_IN659-765_IND,e_w453513742-765_IND,e_IN642-765_IND,e_w429459345-765_IND,e_w492377703-765_IND,e_w293597835-765_IND,e_w608461884-765_IND,e_w318050929-765_IND,e_w316463122-765_IND</t>
   </si>
   <si>
@@ -1879,106 +2038,34 @@
     <t>e_IN607-765_IND,e_IN578-765_IND,e_w248385304-765_IND,e_w323266562-765_IND,e_w149822703-400_IND,e_w759521252-765_IND</t>
   </si>
   <si>
-    <t>e_w1001700959-765_IND,e_IN218-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN218-765_IND,e_w1001700959-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_IN215-765_IND,e_IN191-765_IND,e_w1143180503-765_IND,e_IN163-765_IND,e_w654736039-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1207477934-765_IND,e_w840600239-765_IND,e_w506461670-765_IND,e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311954703-765_IND,e_w1246177377-765_IND,e_IN540-765_IND,e_IN599-765_IND,e_IN586-765_IND,e_w353914761-765_IND,e_IN583-765_IND,e_IN555-765_IND,e_IN578-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN235-400_IND,e_w239498664-400_IND,e_IN265-400_IND,e_w1265489491-400_IND,e_w610646823-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN163-765_IND,e_w1143180503-765_IND,e_w654736039-765_IND,e_w631917408-765_IND,e_IN146-765_IND,e_w1077819664-765_IND,e_w311176519-765_IND,e_w369866141-765_IND,e_IN142-765_IND,e_IN108-765_IND,e_IN107-765_IND,e_IN94-765_IND</t>
-  </si>
-  <si>
-    <t>e_w409112085-765_IND,e_IN610-765_IND,e_IN617-765_IND,e_w323266562-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1072445901-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w1336628403-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w688672798-765_IND,e_IN218-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND</t>
-  </si>
-  <si>
-    <t>e_w473902678-765_IND,e_IN659-765_IND</t>
-  </si>
-  <si>
-    <t>e_w331275940-765_IND,e_IN529-765_IND,e_w688672798-765_IND,e_w655683221-765_IND,e_IN489-765_IND,e_IN488-765_IND,e_IN486-765_IND</t>
-  </si>
-  <si>
-    <t>e_w654736039-765_IND,e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>e_w355560316-765_IND</t>
-  </si>
-  <si>
-    <t>e_w492377703-765_IND,e_w293597835-765_IND,e_w608461884-765_IND,e_w386018740-765_IND,e_w801704865-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311571096-765_IND,e_IN250-765_IND,e_IN247-765_IND,e_IN233-765_IND,e_w193216698-765_IND,e_w423702239-765_IND,e_IN295-765_IND,e_IN264-765_IND,e_w131484738-765_IND,e_IN246-765_IND,e_IN272-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311103617-765_IND,e_w166692103-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN235-400_IND,e_w465787206-400_IND,e_IN265-400_IND,e_w1265489491-400_IND</t>
-  </si>
-  <si>
-    <t>e_w342204888-765_IND,e_w245128370-765_IND,e_IN742-765_IND,e_w315824842-765_IND,e_w923365745-765_IND,e_w910151268-765_IND,e_w1074489047-765_IND</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND,e_w118228036-400_IND,e_w793144832-765_IND,e_IN339-400_IND</t>
-  </si>
-  <si>
-    <t>e_w1099365579-400_IND,e_w375941438-400_IND</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN486-765_IND,e_w655683221-765_IND,e_IN473-765_IND,e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN798-765_IND,e_w386153973-765_IND,e_w355560316-765_IND</t>
-  </si>
-  <si>
-    <t>e_w315823978-765_IND,e_w386018740-765_IND,e_w801704865-765_IND,e_IN742-765_IND,e_w923365745-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN10-765_IND,e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>e_w425401901-765_IND,e_w1206014676-765_IND,e_w545571850-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN300-765_IND,e_w166692103-400_IND,e_IN290-400_IND,e_w97392607-400_IND,e_w50885643-400_IND,e_w324059200-400_IND,e_IN317-400_IND,e_w50885643-765_IND,e_w577176545-400_IND,e_w209806624-400_IND,e_w1044735753-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN145-400_IND</t>
-  </si>
-  <si>
-    <t>e_w372701897-765_IND,e_IN10-765_IND,e_w311176519-765_IND</t>
-  </si>
-  <si>
-    <t>e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND,e_w311571096-765_IND,e_w514344408-765_IND,e_w193216698-765_IND</t>
-  </si>
-  <si>
-    <t>e_w698045832-765_IND,e_w315477169-765_IND,e_w408924420-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN42-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN440-400_IND,e_IN386-400_IND,e_w1072445901-400_IND</t>
+    <t>e_w1127651311-765_IND,e_w688672798-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN806-765_IND,e_IN801-765_IND,e_IN798-765_IND,e_w425401901-765_IND,e_w1206014676-765_IND,e_IN809-765_IND,e_IN803-765_IND,e_w386153973-765_IND,e_w751947947-765_IND,e_w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND,e_IN749-765_IND,e_IN748-765_IND,e_w342204888-765_IND,e_w245128370-765_IND</t>
+  </si>
+  <si>
+    <t>e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND,e_IN685-765_IND</t>
+  </si>
+  <si>
+    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN684-765_IND,e_w409112085-765_IND,e_IN599-765_IND</t>
+  </si>
+  <si>
+    <t>e_w196933682-765_IND,e_w923418232-400_IND,e_w1015325412-400_IND,e_w248385304-765_IND,e_IN353-400_IND,e_w149822703-400_IND,e_IN363-400_IND,e_w209806624-765_IND,e_w96821783-400_IND,e_w209806650-400_IND,e_w485873968-400_IND</t>
+  </si>
+  <si>
+    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w311571096-765_IND,e_w369866141-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN100-765_IND,e_w247861059-765_IND,e_w311176519-765_IND,e_IN105-765_IND,e_w105373531-765_IND,e_w274106872-765_IND,e_IN136-765_IND,e_w420797421-765_IND,e_w417569420-765_IND,e_IN135-765_IND,e_w1341291951-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN270-765_IND,e_IN196-765_IND,e_IN174-765_IND,e_w1329624553-765_IND,e_IN276-765_IND,e_IN200-765_IND,e_w607439318-765_IND,e_IN229-765_IND,e_IN183-765_IND,e_IN160-765_IND,e_w352619220-765_IND,e_IN267-765_IND,e_IN232-765_IND,e_IN254-765_IND,e_w100470285-765_IND,e_IN275-765_IND,e_w311118424-765_IND,e_IN283-765_IND,e_w311103617-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN260-400_IND,e_w203673991-400_IND,e_w1265496720-400_IND,e_w610646823-400_IND,e_w375084335-400_IND,e_IN177-400_IND,e_IN176-400_IND,e_w375941438-400_IND,e_IN145-400_IND</t>
   </si>
   <si>
     <t>e_w473902678-765_IND,e_w331275940-765_IND,e_IN642-765_IND,e_w318090288-765_IND,e_IN489-765_IND,e_IN486-765_IND,e_w316463122-765_IND,e_w698045832-765_IND</t>
@@ -2002,91 +2089,22 @@
     <t>e_IN155-400_IND,e_w116541259-400_IND,e_IN235-400_IND</t>
   </si>
   <si>
-    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w311571096-765_IND,e_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN100-765_IND,e_w247861059-765_IND,e_w311176519-765_IND,e_IN105-765_IND,e_w105373531-765_IND,e_w274106872-765_IND,e_IN136-765_IND,e_w420797421-765_IND,e_w417569420-765_IND,e_IN135-765_IND,e_w1341291951-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN270-765_IND,e_IN196-765_IND,e_IN174-765_IND,e_w1329624553-765_IND,e_IN276-765_IND,e_IN200-765_IND,e_w607439318-765_IND,e_IN229-765_IND,e_IN183-765_IND,e_IN160-765_IND,e_w352619220-765_IND,e_IN267-765_IND,e_IN232-765_IND,e_IN254-765_IND,e_w100470285-765_IND,e_IN275-765_IND,e_w311118424-765_IND,e_IN283-765_IND,e_w311103617-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN260-400_IND,e_w203673991-400_IND,e_w1265496720-400_IND,e_w610646823-400_IND,e_w375084335-400_IND,e_IN177-400_IND,e_IN176-400_IND,e_w375941438-400_IND,e_IN145-400_IND</t>
-  </si>
-  <si>
-    <t>e_w608461884-765_IND,e_w318050929-765_IND,e_w315477169-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311176519-765_IND,e_w372701897-765_IND,e_w105373531-765_IND,e_IN10-765_IND,e_IN42-765_IND,e_w1341291951-765_IND</t>
-  </si>
-  <si>
-    <t>e_w801704865-765_IND,e_w1207477934-765_IND,e_w923365745-765_IND,e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>e_w840600239-765_IND,e_w408924427-765_IND,e_w506461670-765_IND</t>
-  </si>
-  <si>
-    <t>e_w409158116-765_IND,e_w409112085-765_IND</t>
-  </si>
-  <si>
-    <t>e_w386153973-765_IND,e_w342204888-765_IND,e_w751947947-765_IND,e_w910151268-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN128-765_IND,e_IN116-765_IND,e_w1341291951-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND,e_IN180-765_IND,e_IN206-765_IND,e_w311103617-765_IND</t>
-  </si>
-  <si>
-    <t>e_w374367235-400_IND,e_IN260-400_IND,e_w439006823-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
-  </si>
-  <si>
-    <t>e_w473902678-765_IND,e_w1127651311-765_IND,e_w331275940-765_IND,e_w688672798-765_IND</t>
-  </si>
-  <si>
-    <t>e_w355560316-765_IND,e_w429459345-765_IND</t>
-  </si>
-  <si>
-    <t>e_w316463122-765_IND,e_w318090288-765_IND,e_w318050929-765_IND,e_w315477169-765_IND,e_w698045832-765_IND</t>
-  </si>
-  <si>
-    <t>e_w425401901-765_IND,e_IN806-765_IND,e_IN798-765_IND,e_w1206014676-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1127651311-765_IND,e_w688672798-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN806-765_IND,e_IN801-765_IND,e_IN798-765_IND,e_w425401901-765_IND,e_w1206014676-765_IND,e_IN809-765_IND,e_IN803-765_IND,e_w386153973-765_IND,e_w751947947-765_IND,e_w545571850-765_IND</t>
-  </si>
-  <si>
-    <t>e_w355560316-765_IND,e_IN749-765_IND,e_IN748-765_IND,e_w342204888-765_IND,e_w245128370-765_IND</t>
-  </si>
-  <si>
-    <t>e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND,e_IN685-765_IND</t>
-  </si>
-  <si>
-    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN684-765_IND,e_w409112085-765_IND,e_IN599-765_IND</t>
-  </si>
-  <si>
-    <t>e_w196933682-765_IND,e_w923418232-400_IND,e_w1015325412-400_IND,e_w248385304-765_IND,e_IN353-400_IND,e_w149822703-400_IND,e_IN363-400_IND,e_w209806624-765_IND,e_w96821783-400_IND,e_w209806650-400_IND,e_w485873968-400_IND</t>
-  </si>
-  <si>
-    <t>e_w166692103-400_IND,e_w1044735753-400_IND,e_w1012817818-400_IND,e_w92994753-400_IND,e_w92360278-400_IND,e_w1238123371-400_IND,e_w94199110-400_IND,e_w485873934-400_IND,e_IN179-400_IND,e_IN286-400_IND,e_IN181-400_IND</t>
-  </si>
-  <si>
-    <t>e_w1072445901-400_IND</t>
-  </si>
-  <si>
-    <t>e_w375941438-400_IND,e_IN145-400_IND</t>
-  </si>
-  <si>
-    <t>e_w688672798-765_IND,e_IN218-765_IND,e_IN215-765_IND,e_IN199-765_IND,e_IN194-765_IND,e_IN191-765_IND,e_w631917408-765_IND</t>
-  </si>
-  <si>
-    <t>e_w545571850-765_IND</t>
-  </si>
-  <si>
-    <t>e_w323266562-765_IND,e_w759521252-765_IND,e_w793144832-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1341647644-400_IND,e_IN263-400_IND,e_w93160503-400_IND,e_w526897229-400_IND,e_IN259-400_IND,e_IN320-400_IND,e_IN235-400_IND</t>
+    <t>distr_wonelc_won_IND_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
   </si>
   <si>
     <t>distr_wonelc_won_IND_056</t>
@@ -2107,6 +2125,144 @@
     <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
+    <t>distr_wonelc_won_IND_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_IND_049</t>
   </si>
   <si>
@@ -2161,22 +2317,118 @@
     <t>connecting wind onshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
+    <t>distr_wonelc_won_IND_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wonelc_won_IND_043</t>
@@ -2209,222 +2461,6 @@
     <t>connecting wind onshore to buses in cluster 27</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_IND_067</t>
   </si>
   <si>
@@ -2455,40 +2491,22 @@
     <t>connecting wind onshore to buses in cluster 26</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
+    <t>elc_won_IND_066</t>
+  </si>
+  <si>
+    <t>e_IN146-765_IND,e_w654736039-765_IND,e_w1077819664-765_IND,e_w369866141-765_IND,e_IN142-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_040</t>
+  </si>
+  <si>
+    <t>e_w608461884-765_IND,e_w801704865-765_IND,e_w466424134-765_IND,e_w1207477934-765_IND,e_w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_038</t>
+  </si>
+  <si>
+    <t>e_w342204888-765_IND,e_w245128370-765_IND,e_IN742-765_IND,e_w315823978-765_IND,e_w801704865-765_IND,e_w315824842-765_IND,e_w923365745-765_IND</t>
   </si>
   <si>
     <t>elc_won_IND_056</t>
@@ -2509,6 +2527,141 @@
     <t>e_w408924427-765_IND,e_w506461670-765_IND</t>
   </si>
   <si>
+    <t>elc_won_IND_050</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w473902678-765_IND,e_w331275940-765_IND,e_w688672798-765_IND,e_w318090288-765_IND,e_IN489-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_064</t>
+  </si>
+  <si>
+    <t>e_w1001700959-765_IND,e_IN218-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_w1143180503-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_011</t>
+  </si>
+  <si>
+    <t>e_IN365-765_IND,e_IN388-765_IND,e_IN373-765_IND,e_w422204218-765_IND,e_IN405-765_IND,e_IN395-765_IND,e_w477691456-765_IND,e_IN375-765_IND,e_w196563905-765_IND,e_w196933682-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_025</t>
+  </si>
+  <si>
+    <t>e_w759521252-765_IND,e_w118228036-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_053</t>
+  </si>
+  <si>
+    <t>e_IN218-765_IND,e_w688672798-765_IND,e_w1127651311-765_IND,e_w655683221-765_IND,e_IN194-765_IND,e_w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_036</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND,e_w1206014676-765_IND,e_IN809-765_IND,e_w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_012</t>
+  </si>
+  <si>
+    <t>e_w408924420-765_IND,e_w192782338-765_IND,e_w408924427-765_IND,e_w506461670-765_IND,e_w311933111-765_IND,e_IN539-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_057</t>
+  </si>
+  <si>
+    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w369866141-765_IND,e_w311571096-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_041</t>
+  </si>
+  <si>
+    <t>e_w293597835-765_IND,e_w608461884-765_IND,e_w492377703-765_IND,e_w386018740-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_030</t>
+  </si>
+  <si>
+    <t>e_w315824842-765_IND,e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_052</t>
+  </si>
+  <si>
+    <t>e_IN218-765_IND,e_IN215-765_IND,e_IN187-765_IND,e_IN199-765_IND,e_IN191-765_IND,e_IN194-765_IND,e_w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_037</t>
+  </si>
+  <si>
+    <t>e_IN803-765_IND,e_w545571850-765_IND,e_w751947947-765_IND,e_w342204888-765_IND,e_w910151268-765_IND,e_w315824842-765_IND,e_w1074489047-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_032</t>
+  </si>
+  <si>
+    <t>e_w506461670-765_IND,e_IN684-765_IND,e_w311933111-765_IND,e_IN685-765_IND,e_w409158116-765_IND,e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_018</t>
+  </si>
+  <si>
+    <t>e_w97392607-400_IND,e_w324059200-400_IND,e_IN317-400_IND,e_w923418232-400_IND,e_w577176545-400_IND,e_w1015325412-400_IND,e_IN353-400_IND,e_w209806624-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_055</t>
+  </si>
+  <si>
+    <t>e_IN486-765_IND,e_IN473-765_IND,e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_016</t>
+  </si>
+  <si>
+    <t>e_w166692103-400_IND,e_w1012817818-400_IND,e_w92360278-400_IND,e_w1238123371-400_IND,e_w485873934-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_028</t>
+  </si>
+  <si>
+    <t>e_w324064297-400_IND,e_IN320-400_IND,e_IN259-400_IND,e_IN235-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_065</t>
+  </si>
+  <si>
+    <t>e_w1143180503-765_IND,e_w654736039-765_IND,e_w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_044</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND,e_w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_042</t>
+  </si>
+  <si>
+    <t>e_w492377703-765_IND,e_w355560316-765_IND,e_w386018740-765_IND,e_w315823978-765_IND,e_w386153973-765_IND,e_IN749-765_IND,e_IN748-765_IND,e_w342204888-765_IND,e_w245128370-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_005</t>
+  </si>
+  <si>
+    <t>e_w372701897-765_IND,e_w311176519-765_IND,e_w105373531-765_IND,e_IN42-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_039</t>
+  </si>
+  <si>
+    <t>e_w386153973-765_IND,e_IN803-765_IND,e_w751947947-765_IND,e_w342204888-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_002</t>
+  </si>
+  <si>
     <t>elc_won_IND_049</t>
   </si>
   <si>
@@ -2563,22 +2716,118 @@
     <t>e_IN290-400_IND,e_w50885643-400_IND,e_w166692103-400_IND,e_w50885643-765_IND,e_w577176545-400_IND,e_w1044735753-400_IND,e_w96821783-400_IND,e_w92994753-400_IND,e_w94199110-400_IND,e_w485873968-400_IND</t>
   </si>
   <si>
-    <t>elc_won_IND_053</t>
-  </si>
-  <si>
-    <t>e_IN218-765_IND,e_w688672798-765_IND,e_w1127651311-765_IND,e_w655683221-765_IND,e_IN194-765_IND,e_w631917408-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_036</t>
-  </si>
-  <si>
-    <t>e_w425401901-765_IND,e_w1206014676-765_IND,e_IN809-765_IND,e_w545571850-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_012</t>
-  </si>
-  <si>
-    <t>e_w408924420-765_IND,e_w192782338-765_IND,e_w408924427-765_IND,e_w506461670-765_IND,e_w311933111-765_IND,e_IN539-765_IND</t>
+    <t>elc_won_IND_061</t>
+  </si>
+  <si>
+    <t>e_w372701897-765_IND,e_w311176519-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_058</t>
+  </si>
+  <si>
+    <t>e_w369866141-765_IND,e_w311571096-765_IND,e_IN230-765_IND,e_IN250-765_IND,e_IN247-765_IND,e_IN233-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_015</t>
+  </si>
+  <si>
+    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN684-765_IND,e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_020</t>
+  </si>
+  <si>
+    <t>e_w354062412-765_IND,e_w248385304-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_021</t>
+  </si>
+  <si>
+    <t>e_w248385304-765_IND,e_w149822703-400_IND,e_IN363-400_IND,e_w209806624-765_IND,e_w209806650-400_IND,e_w485873968-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_023</t>
+  </si>
+  <si>
+    <t>e_w759521252-765_IND,e_w793144832-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_051</t>
+  </si>
+  <si>
+    <t>e_w688672798-765_IND,e_w331275940-765_IND,e_IN529-765_IND,e_IN489-765_IND,e_w655683221-765_IND,e_IN488-765_IND,e_IN486-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_004</t>
+  </si>
+  <si>
+    <t>e_w1341291951-765_IND,e_w105373531-765_IND,e_IN116-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_029</t>
+  </si>
+  <si>
+    <t>e_w1207477934-765_IND,e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_003</t>
+  </si>
+  <si>
+    <t>e_IN275-765_IND,e_w311118424-765_IND,e_w100470285-765_IND,e_IN283-765_IND,e_w311103617-765_IND,e_IN298-765_IND,e_w166692103-400_IND,e_IN300-765_IND,e_IN290-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_048</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w1336628403-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_034</t>
+  </si>
+  <si>
+    <t>e_IN659-765_IND,e_w453513742-765_IND,e_IN642-765_IND,e_w318090288-765_IND,e_w429459345-765_IND,e_w316463122-765_IND,e_w318050929-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_046</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND,e_IN798-765_IND,e_w386153973-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_022</t>
+  </si>
+  <si>
+    <t>e_IN440-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_009</t>
+  </si>
+  <si>
+    <t>e_IN439-765_IND,e_IN321-765_IND,e_w319423421-765_IND,e_IN343-765_IND,e_IN327-765_IND,e_IN400-765_IND,e_IN370-765_IND,e_w195459361-765_IND,e_IN399-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_013</t>
+  </si>
+  <si>
+    <t>e_w311933111-765_IND,e_w311954703-765_IND,e_IN539-765_IND,e_w1246177377-765_IND,e_IN599-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_008</t>
+  </si>
+  <si>
+    <t>e_w247861059-765_IND,e_w311176519-765_IND,e_IN140-765_IND,e_IN105-765_IND,e_w105373531-765_IND,e_IN136-765_IND,e_w420797421-765_IND,e_w417569420-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_007</t>
+  </si>
+  <si>
+    <t>e_IN136-765_IND,e_IN246-765_IND,e_w274106872-765_IND,e_IN196-765_IND,e_IN174-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_006</t>
+  </si>
+  <si>
+    <t>e_IN135-765_IND,e_w420797421-765_IND,e_w1329624553-765_IND,e_IN128-765_IND,e_IN200-765_IND,e_IN196-765_IND,e_w607439318-765_IND,e_IN229-765_IND,e_IN183-765_IND,e_IN160-765_IND,e_IN267-765_IND,e_IN232-765_IND,e_IN180-765_IND,e_IN254-765_IND,e_w100470285-765_IND</t>
   </si>
   <si>
     <t>elc_won_IND_043</t>
@@ -2611,219 +2860,6 @@
     <t>e_w1238123371-400_IND,e_IN286-400_IND,e_w485873934-400_IND,e_IN181-400_IND,e_w1341647644-400_IND,e_IN263-400_IND,e_w93160503-400_IND,e_w526897229-400_IND</t>
   </si>
   <si>
-    <t>elc_won_IND_052</t>
-  </si>
-  <si>
-    <t>e_IN218-765_IND,e_IN215-765_IND,e_IN187-765_IND,e_IN199-765_IND,e_IN191-765_IND,e_IN194-765_IND,e_w631917408-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_037</t>
-  </si>
-  <si>
-    <t>e_IN803-765_IND,e_w545571850-765_IND,e_w751947947-765_IND,e_w342204888-765_IND,e_w910151268-765_IND,e_w315824842-765_IND,e_w1074489047-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_032</t>
-  </si>
-  <si>
-    <t>e_w506461670-765_IND,e_IN684-765_IND,e_w311933111-765_IND,e_IN685-765_IND,e_w409158116-765_IND,e_w409112085-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_018</t>
-  </si>
-  <si>
-    <t>e_w97392607-400_IND,e_w324059200-400_IND,e_IN317-400_IND,e_w923418232-400_IND,e_w577176545-400_IND,e_w1015325412-400_IND,e_IN353-400_IND,e_w209806624-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_065</t>
-  </si>
-  <si>
-    <t>e_w1143180503-765_IND,e_w654736039-765_IND,e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_044</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND,e_w355560316-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_042</t>
-  </si>
-  <si>
-    <t>e_w492377703-765_IND,e_w355560316-765_IND,e_w386018740-765_IND,e_w315823978-765_IND,e_w386153973-765_IND,e_IN749-765_IND,e_IN748-765_IND,e_w342204888-765_IND,e_w245128370-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_005</t>
-  </si>
-  <si>
-    <t>e_w372701897-765_IND,e_w311176519-765_IND,e_w105373531-765_IND,e_IN42-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_039</t>
-  </si>
-  <si>
-    <t>e_w386153973-765_IND,e_IN803-765_IND,e_w751947947-765_IND,e_w342204888-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_002</t>
-  </si>
-  <si>
-    <t>elc_won_IND_051</t>
-  </si>
-  <si>
-    <t>e_w688672798-765_IND,e_w331275940-765_IND,e_IN529-765_IND,e_IN489-765_IND,e_w655683221-765_IND,e_IN488-765_IND,e_IN486-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_004</t>
-  </si>
-  <si>
-    <t>e_w1341291951-765_IND,e_w105373531-765_IND,e_IN116-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_029</t>
-  </si>
-  <si>
-    <t>e_w1207477934-765_IND,e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_003</t>
-  </si>
-  <si>
-    <t>e_IN275-765_IND,e_w311118424-765_IND,e_w100470285-765_IND,e_IN283-765_IND,e_w311103617-765_IND,e_IN298-765_IND,e_w166692103-400_IND,e_IN300-765_IND,e_IN290-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_055</t>
-  </si>
-  <si>
-    <t>e_IN486-765_IND,e_IN473-765_IND,e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_016</t>
-  </si>
-  <si>
-    <t>e_w166692103-400_IND,e_w1012817818-400_IND,e_w92360278-400_IND,e_w1238123371-400_IND,e_w485873934-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_028</t>
-  </si>
-  <si>
-    <t>e_w324064297-400_IND,e_IN320-400_IND,e_IN259-400_IND,e_IN235-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_066</t>
-  </si>
-  <si>
-    <t>e_IN146-765_IND,e_w654736039-765_IND,e_w1077819664-765_IND,e_w369866141-765_IND,e_IN142-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_040</t>
-  </si>
-  <si>
-    <t>e_w608461884-765_IND,e_w801704865-765_IND,e_w466424134-765_IND,e_w1207477934-765_IND,e_w923365745-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_038</t>
-  </si>
-  <si>
-    <t>e_w342204888-765_IND,e_w245128370-765_IND,e_IN742-765_IND,e_w315823978-765_IND,e_w801704865-765_IND,e_w315824842-765_IND,e_w923365745-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_061</t>
-  </si>
-  <si>
-    <t>e_w372701897-765_IND,e_w311176519-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_058</t>
-  </si>
-  <si>
-    <t>e_w369866141-765_IND,e_w311571096-765_IND,e_IN230-765_IND,e_IN250-765_IND,e_IN247-765_IND,e_IN233-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_015</t>
-  </si>
-  <si>
-    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN684-765_IND,e_w409112085-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_020</t>
-  </si>
-  <si>
-    <t>e_w354062412-765_IND,e_w248385304-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_021</t>
-  </si>
-  <si>
-    <t>e_w248385304-765_IND,e_w149822703-400_IND,e_IN363-400_IND,e_w209806624-765_IND,e_w209806650-400_IND,e_w485873968-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_023</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND,e_w793144832-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_048</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w1336628403-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_034</t>
-  </si>
-  <si>
-    <t>e_IN659-765_IND,e_w453513742-765_IND,e_IN642-765_IND,e_w318090288-765_IND,e_w429459345-765_IND,e_w316463122-765_IND,e_w318050929-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_046</t>
-  </si>
-  <si>
-    <t>e_w355560316-765_IND,e_IN798-765_IND,e_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_022</t>
-  </si>
-  <si>
-    <t>e_IN440-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_009</t>
-  </si>
-  <si>
-    <t>e_IN439-765_IND,e_IN321-765_IND,e_w319423421-765_IND,e_IN343-765_IND,e_IN327-765_IND,e_IN400-765_IND,e_IN370-765_IND,e_w195459361-765_IND,e_IN399-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_013</t>
-  </si>
-  <si>
-    <t>e_w311933111-765_IND,e_w311954703-765_IND,e_IN539-765_IND,e_w1246177377-765_IND,e_IN599-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_050</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w473902678-765_IND,e_w331275940-765_IND,e_w688672798-765_IND,e_w318090288-765_IND,e_IN489-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_064</t>
-  </si>
-  <si>
-    <t>e_w1001700959-765_IND,e_IN218-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_011</t>
-  </si>
-  <si>
-    <t>e_IN365-765_IND,e_IN388-765_IND,e_IN373-765_IND,e_w422204218-765_IND,e_IN405-765_IND,e_IN395-765_IND,e_w477691456-765_IND,e_IN375-765_IND,e_w196563905-765_IND,e_w196933682-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_025</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND,e_w118228036-400_IND</t>
-  </si>
-  <si>
     <t>elc_won_IND_067</t>
   </si>
   <si>
@@ -2854,40 +2890,28 @@
     <t>e_w118228036-400_IND,e_IN325-400_IND,e_IN315-400_IND,e_IN339-400_IND,e_w205942950-400_IND,e_w793144832-765_IND,e_IN336-400_IND,e_IN320-400_IND</t>
   </si>
   <si>
-    <t>elc_won_IND_057</t>
-  </si>
-  <si>
-    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w369866141-765_IND,e_w311571096-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_041</t>
-  </si>
-  <si>
-    <t>e_w293597835-765_IND,e_w608461884-765_IND,e_w492377703-765_IND,e_w386018740-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_030</t>
-  </si>
-  <si>
-    <t>e_w315824842-765_IND,e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_008</t>
-  </si>
-  <si>
-    <t>e_w247861059-765_IND,e_w311176519-765_IND,e_IN140-765_IND,e_IN105-765_IND,e_w105373531-765_IND,e_IN136-765_IND,e_w420797421-765_IND,e_w417569420-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_007</t>
-  </si>
-  <si>
-    <t>e_IN136-765_IND,e_IN246-765_IND,e_w274106872-765_IND,e_IN196-765_IND,e_IN174-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_006</t>
-  </si>
-  <si>
-    <t>e_IN135-765_IND,e_w420797421-765_IND,e_w1329624553-765_IND,e_IN128-765_IND,e_IN200-765_IND,e_IN196-765_IND,e_w607439318-765_IND,e_IN229-765_IND,e_IN183-765_IND,e_IN160-765_IND,e_IN267-765_IND,e_IN232-765_IND,e_IN180-765_IND,e_IN254-765_IND,e_w100470285-765_IND</t>
+    <t>distr_wofelc_wof_IND_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IND_021</t>
@@ -2896,22 +2920,34 @@
     <t>connecting wind offshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
+    <t>distr_wofelc_wof_IND_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IND_010</t>
@@ -2920,16 +2956,64 @@
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
+    <t>distr_wofelc_wof_IND_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IND_001</t>
@@ -2944,94 +3028,28 @@
     <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_IND_015</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
+    <t>elc_wof_IND_009</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w473902678-765_IND,e_w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_017</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_014</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_022</t>
   </si>
   <si>
     <t>elc_wof_IND_021</t>
@@ -3040,34 +3058,82 @@
     <t>e_w409158116-765_IND</t>
   </si>
   <si>
-    <t>elc_wof_IND_009</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w473902678-765_IND,e_w1127651311-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_017</t>
-  </si>
-  <si>
-    <t>e_w425401901-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_014</t>
+    <t>elc_wof_IND_013</t>
+  </si>
+  <si>
+    <t>e_w545571850-765_IND,e_w910151268-765_IND,e_w1074489047-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_023</t>
+  </si>
+  <si>
+    <t>e_w323266562-765_IND,e_w759521252-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>e_w315824842-765_IND,e_w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_002</t>
   </si>
   <si>
     <t>elc_wof_IND_010</t>
   </si>
   <si>
-    <t>elc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>e_w315824842-765_IND,e_w923365745-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>e_w409112085-765_IND</t>
+    <t>elc_wof_IND_007</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w688672711-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_008</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_005</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_024</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND,e_IN617-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_006</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_012</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_004</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND,e_w473902678-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_011</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND,e_w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_003</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_016</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND,e_w1206014676-765_IND</t>
   </si>
   <si>
     <t>elc_wof_IND_001</t>
@@ -3079,73 +3145,7 @@
     <t>elc_wof_IND_018</t>
   </si>
   <si>
-    <t>elc_wof_IND_013</t>
-  </si>
-  <si>
-    <t>e_w545571850-765_IND,e_w910151268-765_IND,e_w1074489047-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_023</t>
-  </si>
-  <si>
-    <t>e_w323266562-765_IND,e_w759521252-765_IND</t>
-  </si>
-  <si>
     <t>elc_wof_IND_015</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_022</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_002</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_007</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_008</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_005</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_024</t>
-  </si>
-  <si>
-    <t>e_w409112085-765_IND,e_IN617-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_004</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND,e_w473902678-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_011</t>
-  </si>
-  <si>
-    <t>e_w473902678-765_IND,e_w1127651311-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_003</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_016</t>
-  </si>
-  <si>
-    <t>e_w425401901-765_IND,e_w1206014676-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_006</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_012</t>
   </si>
   <si>
     <t>e_won_IND_001</t>
@@ -8576,7 +8576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B7C108-976C-44A9-AF50-B2241D70CC90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03164137-8271-4B45-A140-7E5DAE704C7D}">
   <dimension ref="B9:BD88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8814,16 +8814,16 @@
         <v>415</v>
       </c>
       <c r="Y11" t="s">
-        <v>396</v>
+        <v>347</v>
       </c>
       <c r="Z11" t="s">
         <v>575</v>
       </c>
       <c r="AA11">
-        <v>0.99557960200072415</v>
+        <v>0.99478609753984348</v>
       </c>
       <c r="AB11">
-        <v>81.040629986723459</v>
+        <v>95.588211769535249</v>
       </c>
       <c r="AD11" t="s">
         <v>414</v>
@@ -8856,10 +8856,10 @@
         <v>788</v>
       </c>
       <c r="AO11">
-        <v>0.99474825047892679</v>
+        <v>0.99618121233373258</v>
       </c>
       <c r="AP11">
-        <v>96.282074553009053</v>
+        <v>70.011107214903078</v>
       </c>
       <c r="AR11" t="s">
         <v>414</v>
@@ -8892,10 +8892,10 @@
         <v>969</v>
       </c>
       <c r="BC11">
-        <v>0.99308209783432144</v>
+        <v>0.98137594918937099</v>
       </c>
       <c r="BD11">
-        <v>126.82820637077275</v>
+        <v>341.44093152819772</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8960,16 +8960,16 @@
         <v>419</v>
       </c>
       <c r="Y12" t="s">
-        <v>398</v>
+        <v>345</v>
       </c>
       <c r="Z12" t="s">
         <v>576</v>
       </c>
       <c r="AA12">
-        <v>0.99295357769237991</v>
+        <v>0.99568525132868968</v>
       </c>
       <c r="AB12">
-        <v>129.18440897303603</v>
+        <v>79.10372564068922</v>
       </c>
       <c r="AD12" t="s">
         <v>414</v>
@@ -9002,10 +9002,10 @@
         <v>790</v>
       </c>
       <c r="AO12">
-        <v>0.99684527597966854</v>
+        <v>0.99592364356186902</v>
       </c>
       <c r="AP12">
-        <v>57.836607039410005</v>
+        <v>74.733201365734146</v>
       </c>
       <c r="AR12" t="s">
         <v>414</v>
@@ -9038,10 +9038,10 @@
         <v>971</v>
       </c>
       <c r="BC12">
-        <v>0.98137594918937099</v>
+        <v>0.9889956676941275</v>
       </c>
       <c r="BD12">
-        <v>341.44093152819772</v>
+        <v>201.74609227432916</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -9106,16 +9106,16 @@
         <v>421</v>
       </c>
       <c r="Y13" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="Z13" t="s">
         <v>577</v>
       </c>
       <c r="AA13">
-        <v>0.99696751363483405</v>
+        <v>0.99590266392783655</v>
       </c>
       <c r="AB13">
-        <v>55.595583361375894</v>
+        <v>75.117827989662302</v>
       </c>
       <c r="AD13" t="s">
         <v>414</v>
@@ -9148,10 +9148,10 @@
         <v>792</v>
       </c>
       <c r="AO13">
-        <v>0.9943927545810437</v>
+        <v>0.99641167752379312</v>
       </c>
       <c r="AP13">
-        <v>102.79949934753229</v>
+        <v>65.785912063792665</v>
       </c>
       <c r="AR13" t="s">
         <v>414</v>
@@ -9181,13 +9181,13 @@
         <v>972</v>
       </c>
       <c r="BB13" t="s">
-        <v>973</v>
+        <v>597</v>
       </c>
       <c r="BC13">
-        <v>0.9889956676941275</v>
+        <v>0.99193721244794397</v>
       </c>
       <c r="BD13">
-        <v>201.74609227432916</v>
+        <v>147.81777178769397</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -9252,16 +9252,16 @@
         <v>423</v>
       </c>
       <c r="Y14" t="s">
-        <v>408</v>
+        <v>357</v>
       </c>
       <c r="Z14" t="s">
         <v>578</v>
       </c>
       <c r="AA14">
-        <v>0.98964014500078279</v>
+        <v>0.99449671322390631</v>
       </c>
       <c r="AB14">
-        <v>189.93067498564957</v>
+        <v>100.89359089505045</v>
       </c>
       <c r="AD14" t="s">
         <v>414</v>
@@ -9294,10 +9294,10 @@
         <v>794</v>
       </c>
       <c r="AO14">
-        <v>0.99418244113372889</v>
+        <v>0.99474825047892679</v>
       </c>
       <c r="AP14">
-        <v>106.6552458816375</v>
+        <v>96.282074553009053</v>
       </c>
       <c r="AR14" t="s">
         <v>414</v>
@@ -9324,16 +9324,16 @@
         <v>926</v>
       </c>
       <c r="BA14" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="BB14" t="s">
-        <v>650</v>
+        <v>873</v>
       </c>
       <c r="BC14">
-        <v>0.99193721244794397</v>
+        <v>0.98389167860462323</v>
       </c>
       <c r="BD14">
-        <v>147.81777178769397</v>
+        <v>295.31922558190735</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9398,16 +9398,16 @@
         <v>425</v>
       </c>
       <c r="Y15" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="Z15" t="s">
         <v>579</v>
       </c>
       <c r="AA15">
-        <v>0.9966137462997855</v>
+        <v>0.99701127670202949</v>
       </c>
       <c r="AB15">
-        <v>62.081317837266766</v>
+        <v>54.793260462791778</v>
       </c>
       <c r="AD15" t="s">
         <v>414</v>
@@ -9440,10 +9440,10 @@
         <v>796</v>
       </c>
       <c r="AO15">
-        <v>0.99206751173516827</v>
+        <v>0.99684527597966854</v>
       </c>
       <c r="AP15">
-        <v>145.42895152191466</v>
+        <v>57.836607039410005</v>
       </c>
       <c r="AR15" t="s">
         <v>414</v>
@@ -9470,16 +9470,16 @@
         <v>928</v>
       </c>
       <c r="BA15" t="s">
+        <v>974</v>
+      </c>
+      <c r="BB15" t="s">
         <v>975</v>
       </c>
-      <c r="BB15" t="s">
-        <v>794</v>
-      </c>
       <c r="BC15">
-        <v>0.98154438143849254</v>
+        <v>0.99308209783432144</v>
       </c>
       <c r="BD15">
-        <v>338.35300696097039</v>
+        <v>126.82820637077275</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9544,16 +9544,16 @@
         <v>427</v>
       </c>
       <c r="Y16" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="Z16" t="s">
         <v>580</v>
       </c>
       <c r="AA16">
-        <v>0.99011796851295664</v>
+        <v>0.99462937148232844</v>
       </c>
       <c r="AB16">
-        <v>181.17057726246117</v>
+        <v>98.461522823979266</v>
       </c>
       <c r="AD16" t="s">
         <v>414</v>
@@ -9586,10 +9586,10 @@
         <v>798</v>
       </c>
       <c r="AO16">
-        <v>0.99566554346996428</v>
+        <v>0.9943927545810437</v>
       </c>
       <c r="AP16">
-        <v>79.46503638398778</v>
+        <v>102.79949934753229</v>
       </c>
       <c r="AR16" t="s">
         <v>414</v>
@@ -9622,10 +9622,10 @@
         <v>977</v>
       </c>
       <c r="BC16">
-        <v>0.99307601382667698</v>
+        <v>0.99526782804010661</v>
       </c>
       <c r="BD16">
-        <v>126.93974651092147</v>
+        <v>86.756485931379871</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9690,16 +9690,16 @@
         <v>429</v>
       </c>
       <c r="Y17" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="Z17" t="s">
         <v>581</v>
       </c>
       <c r="AA17">
-        <v>0.99635118654529808</v>
+        <v>0.99462643269733408</v>
       </c>
       <c r="AB17">
-        <v>66.894913336202478</v>
+        <v>98.51540054887441</v>
       </c>
       <c r="AD17" t="s">
         <v>414</v>
@@ -9732,10 +9732,10 @@
         <v>800</v>
       </c>
       <c r="AO17">
-        <v>0.99667664296701652</v>
+        <v>0.99074948308423383</v>
       </c>
       <c r="AP17">
-        <v>60.928212271363194</v>
+        <v>169.59281012238051</v>
       </c>
       <c r="AR17" t="s">
         <v>414</v>
@@ -9768,10 +9768,10 @@
         <v>979</v>
       </c>
       <c r="BC17">
-        <v>0.99275904397179515</v>
+        <v>0.98605138538291048</v>
       </c>
       <c r="BD17">
-        <v>132.75086051708826</v>
+        <v>255.7246013133088</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9836,16 +9836,16 @@
         <v>431</v>
       </c>
       <c r="Y18" t="s">
-        <v>390</v>
+        <v>362</v>
       </c>
       <c r="Z18" t="s">
         <v>582</v>
       </c>
       <c r="AA18">
-        <v>0.99440507690252466</v>
+        <v>0.99755789282691543</v>
       </c>
       <c r="AB18">
-        <v>102.57359012038077</v>
+        <v>44.77196483988353</v>
       </c>
       <c r="AD18" t="s">
         <v>414</v>
@@ -9878,10 +9878,10 @@
         <v>802</v>
       </c>
       <c r="AO18">
-        <v>0.99608442334318104</v>
+        <v>0.99270401267208797</v>
       </c>
       <c r="AP18">
-        <v>71.785572041680055</v>
+        <v>133.75976767838793</v>
       </c>
       <c r="AR18" t="s">
         <v>414</v>
@@ -9914,10 +9914,10 @@
         <v>981</v>
       </c>
       <c r="BC18">
-        <v>0.96206044130113966</v>
+        <v>0.99307601382667698</v>
       </c>
       <c r="BD18">
-        <v>695.55857614577315</v>
+        <v>126.93974651092147</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9982,16 +9982,16 @@
         <v>433</v>
       </c>
       <c r="Y19" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="Z19" t="s">
         <v>583</v>
       </c>
       <c r="AA19">
-        <v>0.99125780375299366</v>
+        <v>0.99246356041150996</v>
       </c>
       <c r="AB19">
-        <v>160.27359786178269</v>
+        <v>138.16805912231732</v>
       </c>
       <c r="AD19" t="s">
         <v>414</v>
@@ -10024,10 +10024,10 @@
         <v>804</v>
       </c>
       <c r="AO19">
-        <v>0.9967907157363165</v>
+        <v>0.99764772442226368</v>
       </c>
       <c r="AP19">
-        <v>58.836878167530941</v>
+        <v>43.125052258499352</v>
       </c>
       <c r="AR19" t="s">
         <v>414</v>
@@ -10057,13 +10057,13 @@
         <v>982</v>
       </c>
       <c r="BB19" t="s">
-        <v>973</v>
+        <v>983</v>
       </c>
       <c r="BC19">
-        <v>0.98742179529179352</v>
+        <v>0.99275904397179515</v>
       </c>
       <c r="BD19">
-        <v>230.6004196504513</v>
+        <v>132.75086051708826</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -10128,16 +10128,16 @@
         <v>435</v>
       </c>
       <c r="Y20" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="Z20" t="s">
         <v>584</v>
       </c>
       <c r="AA20">
-        <v>0.99619006668481902</v>
+        <v>0.99699505644961572</v>
       </c>
       <c r="AB20">
-        <v>69.848777444984194</v>
+        <v>55.090631757044932</v>
       </c>
       <c r="AD20" t="s">
         <v>414</v>
@@ -10170,10 +10170,10 @@
         <v>806</v>
       </c>
       <c r="AO20">
-        <v>0.99443964677468366</v>
+        <v>0.99703044337128366</v>
       </c>
       <c r="AP20">
-        <v>101.93980913079895</v>
+        <v>54.441871526466279</v>
       </c>
       <c r="AR20" t="s">
         <v>414</v>
@@ -10200,16 +10200,16 @@
         <v>938</v>
       </c>
       <c r="BA20" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="BB20" t="s">
-        <v>984</v>
+        <v>592</v>
       </c>
       <c r="BC20">
-        <v>0.99526782804010661</v>
+        <v>0.97123008268954114</v>
       </c>
       <c r="BD20">
-        <v>86.756485931379871</v>
+        <v>527.44848402507967</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -10274,16 +10274,16 @@
         <v>437</v>
       </c>
       <c r="Y21" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="Z21" t="s">
         <v>585</v>
       </c>
       <c r="AA21">
-        <v>0.99021813732178554</v>
+        <v>0.99170691261633115</v>
       </c>
       <c r="AB21">
-        <v>179.3341491005981</v>
+        <v>152.03993536726261</v>
       </c>
       <c r="AD21" t="s">
         <v>414</v>
@@ -10316,10 +10316,10 @@
         <v>808</v>
       </c>
       <c r="AO21">
-        <v>0.99761003390352465</v>
+        <v>0.99439150850611324</v>
       </c>
       <c r="AP21">
-        <v>43.816045102048356</v>
+        <v>102.82234405458999</v>
       </c>
       <c r="AR21" t="s">
         <v>414</v>
@@ -10349,13 +10349,13 @@
         <v>985</v>
       </c>
       <c r="BB21" t="s">
-        <v>986</v>
+        <v>845</v>
       </c>
       <c r="BC21">
-        <v>0.98605138538291048</v>
+        <v>0.98154438143849254</v>
       </c>
       <c r="BD21">
-        <v>255.7246013133088</v>
+        <v>338.35300696097039</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -10420,16 +10420,16 @@
         <v>439</v>
       </c>
       <c r="Y22" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="Z22" t="s">
         <v>586</v>
       </c>
       <c r="AA22">
-        <v>0.99686736582623381</v>
+        <v>0.9904035062850528</v>
       </c>
       <c r="AB22">
-        <v>57.431626519047455</v>
+        <v>175.93571810736526</v>
       </c>
       <c r="AD22" t="s">
         <v>414</v>
@@ -10462,10 +10462,10 @@
         <v>810</v>
       </c>
       <c r="AO22">
-        <v>0.99777413567568085</v>
+        <v>0.99595416313893737</v>
       </c>
       <c r="AP22">
-        <v>40.807512612516987</v>
+        <v>74.173675786148877</v>
       </c>
       <c r="AR22" t="s">
         <v>414</v>
@@ -10492,16 +10492,16 @@
         <v>942</v>
       </c>
       <c r="BA22" t="s">
+        <v>986</v>
+      </c>
+      <c r="BB22" t="s">
         <v>987</v>
       </c>
-      <c r="BB22" t="s">
-        <v>650</v>
-      </c>
       <c r="BC22">
-        <v>0.99603877136023145</v>
+        <v>0.98838558997012138</v>
       </c>
       <c r="BD22">
-        <v>72.622525062424401</v>
+        <v>212.93085054777492</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10566,16 +10566,16 @@
         <v>441</v>
       </c>
       <c r="Y23" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="Z23" t="s">
         <v>587</v>
       </c>
       <c r="AA23">
-        <v>0.99725672762159434</v>
+        <v>0.99540885392130762</v>
       </c>
       <c r="AB23">
-        <v>50.29332693743671</v>
+        <v>84.171011442693441</v>
       </c>
       <c r="AD23" t="s">
         <v>414</v>
@@ -10608,10 +10608,10 @@
         <v>812</v>
       </c>
       <c r="AO23">
-        <v>0.99439150850611324</v>
+        <v>0.99687821505939955</v>
       </c>
       <c r="AP23">
-        <v>102.82234405458999</v>
+        <v>57.232723911007447</v>
       </c>
       <c r="AR23" t="s">
         <v>414</v>
@@ -10641,13 +10641,13 @@
         <v>988</v>
       </c>
       <c r="BB23" t="s">
-        <v>877</v>
+        <v>845</v>
       </c>
       <c r="BC23">
-        <v>0.98389167860462323</v>
+        <v>0.98730637899749651</v>
       </c>
       <c r="BD23">
-        <v>295.31922558190735</v>
+        <v>232.71638504589731</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10712,16 +10712,16 @@
         <v>443</v>
       </c>
       <c r="Y24" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Z24" t="s">
         <v>588</v>
       </c>
       <c r="AA24">
-        <v>0.99569491323214321</v>
+        <v>0.99360802526828129</v>
       </c>
       <c r="AB24">
-        <v>78.926590744041093</v>
+        <v>117.18620341484296</v>
       </c>
       <c r="AD24" t="s">
         <v>414</v>
@@ -10754,10 +10754,10 @@
         <v>814</v>
       </c>
       <c r="AO24">
-        <v>0.99595416313893737</v>
+        <v>0.99568571110966864</v>
       </c>
       <c r="AP24">
-        <v>74.173675786148877</v>
+        <v>79.095296322741547</v>
       </c>
       <c r="AR24" t="s">
         <v>414</v>
@@ -10787,13 +10787,13 @@
         <v>989</v>
       </c>
       <c r="BB24" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="BC24">
-        <v>0.97123008268954114</v>
+        <v>0.98809190602642238</v>
       </c>
       <c r="BD24">
-        <v>527.44848402507967</v>
+        <v>218.31505618225569</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10858,16 +10858,16 @@
         <v>445</v>
       </c>
       <c r="Y25" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="Z25" t="s">
         <v>589</v>
       </c>
       <c r="AA25">
-        <v>0.99484118006716937</v>
+        <v>0.99515679011930902</v>
       </c>
       <c r="AB25">
-        <v>94.578365435227795</v>
+        <v>88.792181146001369</v>
       </c>
       <c r="AD25" t="s">
         <v>414</v>
@@ -10900,10 +10900,10 @@
         <v>816</v>
       </c>
       <c r="AO25">
-        <v>0.99687821505939955</v>
+        <v>0.99609062270337045</v>
       </c>
       <c r="AP25">
-        <v>57.232723911007447</v>
+        <v>71.671917104874566</v>
       </c>
       <c r="AR25" t="s">
         <v>414</v>
@@ -10936,10 +10936,10 @@
         <v>991</v>
       </c>
       <c r="BC25">
-        <v>0.98838558997012138</v>
+        <v>0.994208528887633</v>
       </c>
       <c r="BD25">
-        <v>212.93085054777492</v>
+        <v>106.17697039339514</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -11004,16 +11004,16 @@
         <v>447</v>
       </c>
       <c r="Y26" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="Z26" t="s">
         <v>590</v>
       </c>
       <c r="AA26">
-        <v>0.99539558382203508</v>
+        <v>0.99409145347725225</v>
       </c>
       <c r="AB26">
-        <v>84.414296596023817</v>
+        <v>108.32335291704148</v>
       </c>
       <c r="AD26" t="s">
         <v>414</v>
@@ -11046,10 +11046,10 @@
         <v>818</v>
       </c>
       <c r="AO26">
-        <v>0.99368259233234391</v>
+        <v>0.99598588086244633</v>
       </c>
       <c r="AP26">
-        <v>115.81914057369519</v>
+        <v>73.592184188484865</v>
       </c>
       <c r="AR26" t="s">
         <v>414</v>
@@ -11079,13 +11079,13 @@
         <v>992</v>
       </c>
       <c r="BB26" t="s">
-        <v>794</v>
+        <v>993</v>
       </c>
       <c r="BC26">
-        <v>0.98730637899749651</v>
+        <v>0.98787195157138663</v>
       </c>
       <c r="BD26">
-        <v>232.71638504589731</v>
+        <v>222.34755452457901</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -11150,16 +11150,16 @@
         <v>449</v>
       </c>
       <c r="Y27" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="Z27" t="s">
         <v>591</v>
       </c>
       <c r="AA27">
-        <v>0.99579357955795456</v>
+        <v>0.99464051280908794</v>
       </c>
       <c r="AB27">
-        <v>77.117708104165573</v>
+        <v>98.257265166721183</v>
       </c>
       <c r="AD27" t="s">
         <v>414</v>
@@ -11192,10 +11192,10 @@
         <v>820</v>
       </c>
       <c r="AO27">
-        <v>0.9954443722844073</v>
+        <v>0.99540934349034305</v>
       </c>
       <c r="AP27">
-        <v>83.519841452532361</v>
+        <v>84.162036010377406</v>
       </c>
       <c r="AR27" t="s">
         <v>414</v>
@@ -11222,16 +11222,16 @@
         <v>952</v>
       </c>
       <c r="BA27" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="BB27" t="s">
-        <v>604</v>
+        <v>845</v>
       </c>
       <c r="BC27">
-        <v>0.98809190602642238</v>
+        <v>0.98853599644984702</v>
       </c>
       <c r="BD27">
-        <v>218.31505618225569</v>
+        <v>210.17339841947171</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -11296,16 +11296,16 @@
         <v>451</v>
       </c>
       <c r="Y28" t="s">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="Z28" t="s">
         <v>592</v>
       </c>
       <c r="AA28">
-        <v>0.99066346416517681</v>
+        <v>0.99282834435956602</v>
       </c>
       <c r="AB28">
-        <v>171.16982363842584</v>
+        <v>131.48035340795542</v>
       </c>
       <c r="AD28" t="s">
         <v>414</v>
@@ -11338,10 +11338,10 @@
         <v>822</v>
       </c>
       <c r="AO28">
-        <v>0.99363040616365128</v>
+        <v>0.99657664224037934</v>
       </c>
       <c r="AP28">
-        <v>116.77588699972566</v>
+        <v>62.761558926379031</v>
       </c>
       <c r="AR28" t="s">
         <v>414</v>
@@ -11368,16 +11368,16 @@
         <v>954</v>
       </c>
       <c r="BA28" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="BB28" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="BC28">
-        <v>0.994208528887633</v>
+        <v>0.98734896749216872</v>
       </c>
       <c r="BD28">
-        <v>106.17697039339514</v>
+        <v>231.9355959769062</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11442,16 +11442,16 @@
         <v>453</v>
       </c>
       <c r="Y29" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Z29" t="s">
         <v>593</v>
       </c>
       <c r="AA29">
-        <v>0.99560939477262078</v>
+        <v>0.99569310304523451</v>
       </c>
       <c r="AB29">
-        <v>80.494429168619106</v>
+        <v>78.959777504033639</v>
       </c>
       <c r="AD29" t="s">
         <v>414</v>
@@ -11484,10 +11484,10 @@
         <v>824</v>
       </c>
       <c r="AO29">
-        <v>0.99782402570187057</v>
+        <v>0.99091245964276031</v>
       </c>
       <c r="AP29">
-        <v>39.892862132373601</v>
+        <v>166.60490654939525</v>
       </c>
       <c r="AR29" t="s">
         <v>414</v>
@@ -11514,16 +11514,16 @@
         <v>956</v>
       </c>
       <c r="BA29" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="BB29" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="BC29">
-        <v>0.98734896749216872</v>
+        <v>0.98158890816872557</v>
       </c>
       <c r="BD29">
-        <v>231.9355959769062</v>
+        <v>337.53668357336363</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11588,16 +11588,16 @@
         <v>455</v>
       </c>
       <c r="Y30" t="s">
-        <v>339</v>
+        <v>411</v>
       </c>
       <c r="Z30" t="s">
         <v>594</v>
       </c>
       <c r="AA30">
-        <v>0.99544039231362502</v>
+        <v>0.99502431999137919</v>
       </c>
       <c r="AB30">
-        <v>83.592807583541571</v>
+        <v>91.220800158047325</v>
       </c>
       <c r="AD30" t="s">
         <v>414</v>
@@ -11630,10 +11630,10 @@
         <v>826</v>
       </c>
       <c r="AO30">
-        <v>0.99756462867082185</v>
+        <v>0.99846230399777702</v>
       </c>
       <c r="AP30">
-        <v>44.648474368267038</v>
+        <v>28.191093374087806</v>
       </c>
       <c r="AR30" t="s">
         <v>414</v>
@@ -11660,16 +11660,16 @@
         <v>958</v>
       </c>
       <c r="BA30" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="BB30" t="s">
-        <v>999</v>
+        <v>592</v>
       </c>
       <c r="BC30">
-        <v>0.98158890816872557</v>
+        <v>0.98402494782096717</v>
       </c>
       <c r="BD30">
-        <v>337.53668357336363</v>
+        <v>292.87595661560192</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11734,16 +11734,16 @@
         <v>457</v>
       </c>
       <c r="Y31" t="s">
-        <v>346</v>
+        <v>402</v>
       </c>
       <c r="Z31" t="s">
         <v>595</v>
       </c>
       <c r="AA31">
-        <v>0.99190124970484694</v>
+        <v>0.99584577617815018</v>
       </c>
       <c r="AB31">
-        <v>148.47708874447352</v>
+        <v>76.16077006724673</v>
       </c>
       <c r="AD31" t="s">
         <v>414</v>
@@ -11776,10 +11776,10 @@
         <v>828</v>
       </c>
       <c r="AO31">
-        <v>0.99540934349034305</v>
+        <v>0.99611612132862803</v>
       </c>
       <c r="AP31">
-        <v>84.162036010377406</v>
+        <v>71.204442308486065</v>
       </c>
       <c r="AR31" t="s">
         <v>414</v>
@@ -11809,13 +11809,13 @@
         <v>1000</v>
       </c>
       <c r="BB31" t="s">
-        <v>604</v>
+        <v>1001</v>
       </c>
       <c r="BC31">
-        <v>0.98402494782096717</v>
+        <v>0.99223982078870177</v>
       </c>
       <c r="BD31">
-        <v>292.87595661560192</v>
+        <v>142.26995220713331</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11880,16 +11880,16 @@
         <v>459</v>
       </c>
       <c r="Y32" t="s">
-        <v>412</v>
+        <v>336</v>
       </c>
       <c r="Z32" t="s">
         <v>596</v>
       </c>
       <c r="AA32">
-        <v>0.9940089461809174</v>
+        <v>0.99359748433922845</v>
       </c>
       <c r="AB32">
-        <v>109.83598668318054</v>
+        <v>117.37945378081078</v>
       </c>
       <c r="AD32" t="s">
         <v>414</v>
@@ -11922,10 +11922,10 @@
         <v>830</v>
       </c>
       <c r="AO32">
-        <v>0.99657664224037934</v>
+        <v>0.99761105057437038</v>
       </c>
       <c r="AP32">
-        <v>62.761558926379031</v>
+        <v>43.797406136543607</v>
       </c>
       <c r="AR32" t="s">
         <v>414</v>
@@ -11952,16 +11952,16 @@
         <v>962</v>
       </c>
       <c r="BA32" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="BB32" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="BC32">
-        <v>0.99223982078870177</v>
+        <v>0.96206044130113966</v>
       </c>
       <c r="BD32">
-        <v>142.26995220713331</v>
+        <v>695.55857614577315</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -12026,16 +12026,16 @@
         <v>461</v>
       </c>
       <c r="Y33" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="Z33" t="s">
         <v>597</v>
       </c>
       <c r="AA33">
-        <v>0.99600761890991041</v>
+        <v>0.99592552983543692</v>
       </c>
       <c r="AB33">
-        <v>73.193653318309615</v>
+        <v>74.698619683656872</v>
       </c>
       <c r="AD33" t="s">
         <v>414</v>
@@ -12068,10 +12068,10 @@
         <v>832</v>
       </c>
       <c r="AO33">
-        <v>0.99091245964276031</v>
+        <v>0.99615289372526561</v>
       </c>
       <c r="AP33">
-        <v>166.60490654939525</v>
+        <v>70.530281703464368</v>
       </c>
       <c r="AR33" t="s">
         <v>414</v>
@@ -12098,16 +12098,16 @@
         <v>964</v>
       </c>
       <c r="BA33" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="BB33" t="s">
-        <v>1004</v>
+        <v>971</v>
       </c>
       <c r="BC33">
-        <v>0.98787195157138663</v>
+        <v>0.98742179529179352</v>
       </c>
       <c r="BD33">
-        <v>222.34755452457901</v>
+        <v>230.6004196504513</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -12172,16 +12172,16 @@
         <v>463</v>
       </c>
       <c r="Y34" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="Z34" t="s">
         <v>598</v>
       </c>
       <c r="AA34">
-        <v>0.99700029739711071</v>
+        <v>0.99463677905825021</v>
       </c>
       <c r="AB34">
-        <v>54.994547719637801</v>
+        <v>98.325717265413417</v>
       </c>
       <c r="AD34" t="s">
         <v>414</v>
@@ -12214,10 +12214,10 @@
         <v>834</v>
       </c>
       <c r="AO34">
-        <v>0.99846230399777702</v>
+        <v>0.99245794727704639</v>
       </c>
       <c r="AP34">
-        <v>28.191093374087806</v>
+        <v>138.27096658748206</v>
       </c>
       <c r="AR34" t="s">
         <v>414</v>
@@ -12247,13 +12247,13 @@
         <v>1005</v>
       </c>
       <c r="BB34" t="s">
-        <v>794</v>
+        <v>597</v>
       </c>
       <c r="BC34">
-        <v>0.98853599644984702</v>
+        <v>0.99603877136023145</v>
       </c>
       <c r="BD34">
-        <v>210.17339841947171</v>
+        <v>72.622525062424401</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -12318,16 +12318,16 @@
         <v>465</v>
       </c>
       <c r="Y35" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="Z35" t="s">
         <v>599</v>
       </c>
       <c r="AA35">
-        <v>0.99408511741207395</v>
+        <v>0.99667564038633161</v>
       </c>
       <c r="AB35">
-        <v>108.43951411197776</v>
+        <v>60.946592917253042</v>
       </c>
       <c r="AD35" t="s">
         <v>414</v>
@@ -12360,10 +12360,10 @@
         <v>836</v>
       </c>
       <c r="AO35">
-        <v>0.99245794727704639</v>
+        <v>0.99381230463557813</v>
       </c>
       <c r="AP35">
-        <v>138.27096658748206</v>
+        <v>113.44108168106689</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -12428,16 +12428,16 @@
         <v>467</v>
       </c>
       <c r="Y36" t="s">
-        <v>378</v>
+        <v>338</v>
       </c>
       <c r="Z36" t="s">
         <v>600</v>
       </c>
       <c r="AA36">
-        <v>0.99529948277209723</v>
+        <v>0.99080344458411729</v>
       </c>
       <c r="AB36">
-        <v>86.176149178218239</v>
+        <v>168.60351595784994</v>
       </c>
       <c r="AD36" t="s">
         <v>414</v>
@@ -12470,10 +12470,10 @@
         <v>838</v>
       </c>
       <c r="AO36">
-        <v>0.99381230463557813</v>
+        <v>0.99534539864304916</v>
       </c>
       <c r="AP36">
-        <v>113.44108168106689</v>
+        <v>85.3343582107656</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -12538,16 +12538,16 @@
         <v>469</v>
       </c>
       <c r="Y37" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="Z37" t="s">
         <v>601</v>
       </c>
       <c r="AA37">
-        <v>0.99675394464629852</v>
+        <v>0.98636012609964985</v>
       </c>
       <c r="AB37">
-        <v>59.511014817860868</v>
+        <v>250.06435483975247</v>
       </c>
       <c r="AD37" t="s">
         <v>414</v>
@@ -12580,10 +12580,10 @@
         <v>840</v>
       </c>
       <c r="AO37">
-        <v>0.99534539864304916</v>
+        <v>0.99310873310996184</v>
       </c>
       <c r="AP37">
-        <v>85.3343582107656</v>
+        <v>126.33989298403215</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12648,16 +12648,16 @@
         <v>471</v>
       </c>
       <c r="Y38" t="s">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="Z38" t="s">
         <v>602</v>
       </c>
       <c r="AA38">
-        <v>0.9962437778559039</v>
+        <v>0.99598850450039844</v>
       </c>
       <c r="AB38">
-        <v>68.86407264176249</v>
+        <v>73.544084159361034</v>
       </c>
       <c r="AD38" t="s">
         <v>414</v>
@@ -12690,10 +12690,10 @@
         <v>842</v>
       </c>
       <c r="AO38">
-        <v>0.99310873310996184</v>
+        <v>0.99715437961127318</v>
       </c>
       <c r="AP38">
-        <v>126.33989298403215</v>
+        <v>52.169707126657627</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12758,16 +12758,16 @@
         <v>473</v>
       </c>
       <c r="Y39" t="s">
-        <v>371</v>
+        <v>409</v>
       </c>
       <c r="Z39" t="s">
         <v>603</v>
       </c>
       <c r="AA39">
-        <v>0.99617006411660358</v>
+        <v>0.99310312827752323</v>
       </c>
       <c r="AB39">
-        <v>70.215491195600634</v>
+        <v>126.44264824540761</v>
       </c>
       <c r="AD39" t="s">
         <v>414</v>
@@ -12797,13 +12797,13 @@
         <v>843</v>
       </c>
       <c r="AN39" t="s">
-        <v>844</v>
+        <v>618</v>
       </c>
       <c r="AO39">
-        <v>0.99715437961127318</v>
+        <v>0.9950502580620818</v>
       </c>
       <c r="AP39">
-        <v>52.169707126657627</v>
+        <v>90.745268861833736</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12868,16 +12868,16 @@
         <v>475</v>
       </c>
       <c r="Y40" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="Z40" t="s">
         <v>604</v>
       </c>
       <c r="AA40">
-        <v>0.99282834435956602</v>
+        <v>0.99675394464629852</v>
       </c>
       <c r="AB40">
-        <v>131.48035340795542</v>
+        <v>59.511014817860868</v>
       </c>
       <c r="AD40" t="s">
         <v>414</v>
@@ -12904,16 +12904,16 @@
         <v>711</v>
       </c>
       <c r="AM40" t="s">
+        <v>844</v>
+      </c>
+      <c r="AN40" t="s">
         <v>845</v>
       </c>
-      <c r="AN40" t="s">
-        <v>599</v>
-      </c>
       <c r="AO40">
-        <v>0.9950502580620818</v>
+        <v>0.99418244113372889</v>
       </c>
       <c r="AP40">
-        <v>90.745268861833736</v>
+        <v>106.6552458816375</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12978,16 +12978,16 @@
         <v>477</v>
       </c>
       <c r="Y41" t="s">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="Z41" t="s">
         <v>605</v>
       </c>
       <c r="AA41">
-        <v>0.99569310304523451</v>
+        <v>0.9962437778559039</v>
       </c>
       <c r="AB41">
-        <v>78.959777504033639</v>
+        <v>68.86407264176249</v>
       </c>
       <c r="AD41" t="s">
         <v>414</v>
@@ -13020,10 +13020,10 @@
         <v>847</v>
       </c>
       <c r="AO41">
-        <v>0.99533901157332205</v>
+        <v>0.99206751173516827</v>
       </c>
       <c r="AP41">
-        <v>85.451454489096079</v>
+        <v>145.42895152191466</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -13088,16 +13088,16 @@
         <v>479</v>
       </c>
       <c r="Y42" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="Z42" t="s">
         <v>606</v>
       </c>
       <c r="AA42">
-        <v>0.99502431999137919</v>
+        <v>0.99617006411660358</v>
       </c>
       <c r="AB42">
-        <v>91.220800158047325</v>
+        <v>70.215491195600634</v>
       </c>
       <c r="AD42" t="s">
         <v>414</v>
@@ -13130,10 +13130,10 @@
         <v>849</v>
       </c>
       <c r="AO42">
-        <v>0.99754339130519476</v>
+        <v>0.99566554346996428</v>
       </c>
       <c r="AP42">
-        <v>45.037826071429087</v>
+        <v>79.46503638398778</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -13198,16 +13198,16 @@
         <v>481</v>
       </c>
       <c r="Y43" t="s">
-        <v>402</v>
+        <v>349</v>
       </c>
       <c r="Z43" t="s">
         <v>607</v>
       </c>
       <c r="AA43">
-        <v>0.99584577617815018</v>
+        <v>0.99569491323214321</v>
       </c>
       <c r="AB43">
-        <v>76.16077006724673</v>
+        <v>78.926590744041093</v>
       </c>
       <c r="AD43" t="s">
         <v>414</v>
@@ -13240,10 +13240,10 @@
         <v>851</v>
       </c>
       <c r="AO43">
-        <v>0.99542398891280204</v>
+        <v>0.99667664296701652</v>
       </c>
       <c r="AP43">
-        <v>83.893536598629126</v>
+        <v>60.928212271363194</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -13308,16 +13308,16 @@
         <v>483</v>
       </c>
       <c r="Y44" t="s">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="Z44" t="s">
         <v>608</v>
       </c>
       <c r="AA44">
-        <v>0.99462937148232844</v>
+        <v>0.99484118006716937</v>
       </c>
       <c r="AB44">
-        <v>98.461522823979266</v>
+        <v>94.578365435227795</v>
       </c>
       <c r="AD44" t="s">
         <v>414</v>
@@ -13350,10 +13350,10 @@
         <v>853</v>
       </c>
       <c r="AO44">
-        <v>0.99617615910816915</v>
+        <v>0.99608442334318104</v>
       </c>
       <c r="AP44">
-        <v>70.103749683564772</v>
+        <v>71.785572041680055</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -13418,16 +13418,16 @@
         <v>485</v>
       </c>
       <c r="Y45" t="s">
-        <v>405</v>
+        <v>370</v>
       </c>
       <c r="Z45" t="s">
         <v>609</v>
       </c>
       <c r="AA45">
-        <v>0.99462643269733408</v>
+        <v>0.99539558382203508</v>
       </c>
       <c r="AB45">
-        <v>98.51540054887441</v>
+        <v>84.414296596023817</v>
       </c>
       <c r="AD45" t="s">
         <v>414</v>
@@ -13460,10 +13460,10 @@
         <v>855</v>
       </c>
       <c r="AO45">
-        <v>0.99611612132862803</v>
+        <v>0.9967907157363165</v>
       </c>
       <c r="AP45">
-        <v>71.204442308486065</v>
+        <v>58.836878167530941</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13528,16 +13528,16 @@
         <v>487</v>
       </c>
       <c r="Y46" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Z46" t="s">
         <v>610</v>
       </c>
       <c r="AA46">
-        <v>0.99755789282691543</v>
+        <v>0.99579357955795456</v>
       </c>
       <c r="AB46">
-        <v>44.77196483988353</v>
+        <v>77.117708104165573</v>
       </c>
       <c r="AD46" t="s">
         <v>414</v>
@@ -13570,10 +13570,10 @@
         <v>857</v>
       </c>
       <c r="AO46">
-        <v>0.99761105057437038</v>
+        <v>0.99443964677468366</v>
       </c>
       <c r="AP46">
-        <v>43.797406136543607</v>
+        <v>101.93980913079895</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13638,16 +13638,16 @@
         <v>489</v>
       </c>
       <c r="Y47" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="Z47" t="s">
         <v>611</v>
       </c>
       <c r="AA47">
-        <v>0.99246356041150996</v>
+        <v>0.99066346416517681</v>
       </c>
       <c r="AB47">
-        <v>138.16805912231732</v>
+        <v>171.16982363842584</v>
       </c>
       <c r="AD47" t="s">
         <v>414</v>
@@ -13680,10 +13680,10 @@
         <v>859</v>
       </c>
       <c r="AO47">
-        <v>0.99615289372526561</v>
+        <v>0.99761003390352465</v>
       </c>
       <c r="AP47">
-        <v>70.530281703464368</v>
+        <v>43.816045102048356</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13748,16 +13748,16 @@
         <v>491</v>
       </c>
       <c r="Y48" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="Z48" t="s">
         <v>612</v>
       </c>
       <c r="AA48">
-        <v>0.99478609753984348</v>
+        <v>0.99560939477262078</v>
       </c>
       <c r="AB48">
-        <v>95.588211769535249</v>
+        <v>80.494429168619106</v>
       </c>
       <c r="AD48" t="s">
         <v>414</v>
@@ -13790,10 +13790,10 @@
         <v>861</v>
       </c>
       <c r="AO48">
-        <v>0.99618121233373258</v>
+        <v>0.99777413567568085</v>
       </c>
       <c r="AP48">
-        <v>70.011107214903078</v>
+        <v>40.807512612516987</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -13858,16 +13858,16 @@
         <v>493</v>
       </c>
       <c r="Y49" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="Z49" t="s">
         <v>613</v>
       </c>
       <c r="AA49">
-        <v>0.99568525132868968</v>
+        <v>0.99544039231362502</v>
       </c>
       <c r="AB49">
-        <v>79.10372564068922</v>
+        <v>83.592807583541571</v>
       </c>
       <c r="AD49" t="s">
         <v>414</v>
@@ -13900,10 +13900,10 @@
         <v>863</v>
       </c>
       <c r="AO49">
-        <v>0.99592364356186902</v>
+        <v>0.99425851119451991</v>
       </c>
       <c r="AP49">
-        <v>74.733201365734146</v>
+        <v>105.26062810046888</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -13968,16 +13968,16 @@
         <v>495</v>
       </c>
       <c r="Y50" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Z50" t="s">
         <v>614</v>
       </c>
       <c r="AA50">
-        <v>0.99590266392783655</v>
+        <v>0.99190124970484694</v>
       </c>
       <c r="AB50">
-        <v>75.117827989662302</v>
+        <v>148.47708874447352</v>
       </c>
       <c r="AD50" t="s">
         <v>414</v>
@@ -14010,10 +14010,10 @@
         <v>865</v>
       </c>
       <c r="AO50">
-        <v>0.99641167752379312</v>
+        <v>0.99712282780353001</v>
       </c>
       <c r="AP50">
-        <v>65.785912063792665</v>
+        <v>52.74815693528295</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -14078,16 +14078,16 @@
         <v>497</v>
       </c>
       <c r="Y51" t="s">
-        <v>357</v>
+        <v>412</v>
       </c>
       <c r="Z51" t="s">
         <v>615</v>
       </c>
       <c r="AA51">
-        <v>0.99449671322390631</v>
+        <v>0.9940089461809174</v>
       </c>
       <c r="AB51">
-        <v>100.89359089505045</v>
+        <v>109.83598668318054</v>
       </c>
       <c r="AD51" t="s">
         <v>414</v>
@@ -14120,10 +14120,10 @@
         <v>867</v>
       </c>
       <c r="AO51">
-        <v>0.99425851119451991</v>
+        <v>0.99005506097810436</v>
       </c>
       <c r="AP51">
-        <v>105.26062810046888</v>
+        <v>182.32388206808599</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -14188,16 +14188,16 @@
         <v>499</v>
       </c>
       <c r="Y52" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="Z52" t="s">
         <v>616</v>
       </c>
       <c r="AA52">
-        <v>0.99701127670202949</v>
+        <v>0.99600761890991041</v>
       </c>
       <c r="AB52">
-        <v>54.793260462791778</v>
+        <v>73.193653318309615</v>
       </c>
       <c r="AD52" t="s">
         <v>414</v>
@@ -14230,10 +14230,10 @@
         <v>869</v>
       </c>
       <c r="AO52">
-        <v>0.99712282780353001</v>
+        <v>0.99631269816920021</v>
       </c>
       <c r="AP52">
-        <v>52.74815693528295</v>
+        <v>67.600533564663479</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -14298,16 +14298,16 @@
         <v>501</v>
       </c>
       <c r="Y53" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="Z53" t="s">
         <v>617</v>
       </c>
       <c r="AA53">
-        <v>0.99571525957109708</v>
+        <v>0.99700029739711071</v>
       </c>
       <c r="AB53">
-        <v>78.553574529886689</v>
+        <v>54.994547719637801</v>
       </c>
       <c r="AD53" t="s">
         <v>414</v>
@@ -14340,10 +14340,10 @@
         <v>871</v>
       </c>
       <c r="AO53">
-        <v>0.99005506097810436</v>
+        <v>0.99772400077475298</v>
       </c>
       <c r="AP53">
-        <v>182.32388206808599</v>
+        <v>41.726652462862774</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -14408,16 +14408,16 @@
         <v>503</v>
       </c>
       <c r="Y54" t="s">
-        <v>394</v>
+        <v>360</v>
       </c>
       <c r="Z54" t="s">
         <v>618</v>
       </c>
       <c r="AA54">
-        <v>0.99553579843385909</v>
+        <v>0.99408511741207395</v>
       </c>
       <c r="AB54">
-        <v>81.84369537924907</v>
+        <v>108.43951411197776</v>
       </c>
       <c r="AD54" t="s">
         <v>414</v>
@@ -14450,10 +14450,10 @@
         <v>873</v>
       </c>
       <c r="AO54">
-        <v>0.99631269816920021</v>
+        <v>0.99604673274056554</v>
       </c>
       <c r="AP54">
-        <v>67.600533564663479</v>
+        <v>72.476566422965192</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -14518,16 +14518,16 @@
         <v>505</v>
       </c>
       <c r="Y55" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="Z55" t="s">
         <v>619</v>
       </c>
       <c r="AA55">
-        <v>0.99734372305564056</v>
+        <v>0.99529948277209723</v>
       </c>
       <c r="AB55">
-        <v>48.698410646589842</v>
+        <v>86.176149178218239</v>
       </c>
       <c r="AD55" t="s">
         <v>414</v>
@@ -14560,10 +14560,10 @@
         <v>875</v>
       </c>
       <c r="AO55">
-        <v>0.99772400077475298</v>
+        <v>0.99533901157332205</v>
       </c>
       <c r="AP55">
-        <v>41.726652462862774</v>
+        <v>85.451454489096079</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -14628,16 +14628,16 @@
         <v>507</v>
       </c>
       <c r="Y56" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="Z56" t="s">
         <v>620</v>
       </c>
       <c r="AA56">
-        <v>0.99662670467221526</v>
+        <v>0.99670408962762203</v>
       </c>
       <c r="AB56">
-        <v>61.843747676054292</v>
+        <v>60.425023493595695</v>
       </c>
       <c r="AD56" t="s">
         <v>414</v>
@@ -14670,10 +14670,10 @@
         <v>877</v>
       </c>
       <c r="AO56">
-        <v>0.99604673274056554</v>
+        <v>0.99754339130519476</v>
       </c>
       <c r="AP56">
-        <v>72.476566422965192</v>
+        <v>45.037826071429087</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -14738,16 +14738,16 @@
         <v>509</v>
       </c>
       <c r="Y57" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="Z57" t="s">
         <v>621</v>
       </c>
       <c r="AA57">
-        <v>0.99740761205901929</v>
+        <v>0.9960389195261472</v>
       </c>
       <c r="AB57">
-        <v>47.527112251312907</v>
+        <v>72.619808687301173</v>
       </c>
       <c r="AD57" t="s">
         <v>414</v>
@@ -14780,10 +14780,10 @@
         <v>879</v>
       </c>
       <c r="AO57">
-        <v>0.99660391553167893</v>
+        <v>0.99542398891280204</v>
       </c>
       <c r="AP57">
-        <v>62.261548585886977</v>
+        <v>83.893536598629126</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -14848,16 +14848,16 @@
         <v>511</v>
       </c>
       <c r="Y58" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="Z58" t="s">
         <v>622</v>
       </c>
       <c r="AA58">
-        <v>0.99730769203227776</v>
+        <v>0.99707957985864093</v>
       </c>
       <c r="AB58">
-        <v>49.358979408241737</v>
+        <v>53.541035924916123</v>
       </c>
       <c r="AD58" t="s">
         <v>414</v>
@@ -14890,10 +14890,10 @@
         <v>881</v>
       </c>
       <c r="AO58">
-        <v>0.9959136876641268</v>
+        <v>0.99617615910816915</v>
       </c>
       <c r="AP58">
-        <v>74.915726157675209</v>
+        <v>70.103749683564772</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -14958,16 +14958,16 @@
         <v>513</v>
       </c>
       <c r="Y59" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="Z59" t="s">
         <v>623</v>
       </c>
       <c r="AA59">
-        <v>0.998073964784436</v>
+        <v>0.99125780375299366</v>
       </c>
       <c r="AB59">
-        <v>35.310645618673441</v>
+        <v>160.27359786178269</v>
       </c>
       <c r="AD59" t="s">
         <v>414</v>
@@ -15000,10 +15000,10 @@
         <v>883</v>
       </c>
       <c r="AO59">
-        <v>0.9935275292913992</v>
+        <v>0.99660391553167893</v>
       </c>
       <c r="AP59">
-        <v>118.66196299101547</v>
+        <v>62.261548585886977</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -15068,16 +15068,16 @@
         <v>515</v>
       </c>
       <c r="Y60" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="Z60" t="s">
         <v>624</v>
       </c>
       <c r="AA60">
-        <v>0.99551989204648861</v>
+        <v>0.99619006668481902</v>
       </c>
       <c r="AB60">
-        <v>82.135312481041623</v>
+        <v>69.848777444984194</v>
       </c>
       <c r="AD60" t="s">
         <v>414</v>
@@ -15110,10 +15110,10 @@
         <v>885</v>
       </c>
       <c r="AO60">
-        <v>0.99687120387267125</v>
+        <v>0.9959136876641268</v>
       </c>
       <c r="AP60">
-        <v>57.361262334360205</v>
+        <v>74.915726157675209</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -15178,16 +15178,16 @@
         <v>517</v>
       </c>
       <c r="Y61" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="Z61" t="s">
         <v>625</v>
       </c>
       <c r="AA61">
-        <v>0.9979392050107273</v>
+        <v>0.99021813732178554</v>
       </c>
       <c r="AB61">
-        <v>37.781241469999252</v>
+        <v>179.3341491005981</v>
       </c>
       <c r="AD61" t="s">
         <v>414</v>
@@ -15220,10 +15220,10 @@
         <v>887</v>
       </c>
       <c r="AO61">
-        <v>0.99720397512579328</v>
+        <v>0.9935275292913992</v>
       </c>
       <c r="AP61">
-        <v>51.260456027123361</v>
+        <v>118.66196299101547</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -15288,16 +15288,16 @@
         <v>519</v>
       </c>
       <c r="Y62" t="s">
-        <v>354</v>
+        <v>389</v>
       </c>
       <c r="Z62" t="s">
         <v>626</v>
       </c>
       <c r="AA62">
-        <v>0.9982033297630386</v>
+        <v>0.99686736582623381</v>
       </c>
       <c r="AB62">
-        <v>32.938954344292306</v>
+        <v>57.431626519047455</v>
       </c>
       <c r="AD62" t="s">
         <v>414</v>
@@ -15330,10 +15330,10 @@
         <v>889</v>
       </c>
       <c r="AO62">
-        <v>0.99565348329230585</v>
+        <v>0.99687120387267125</v>
       </c>
       <c r="AP62">
-        <v>79.686139641060379</v>
+        <v>57.361262334360205</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -15398,16 +15398,16 @@
         <v>521</v>
       </c>
       <c r="Y63" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="Z63" t="s">
         <v>627</v>
       </c>
       <c r="AA63">
-        <v>0.99769372286934066</v>
+        <v>0.99725672762159434</v>
       </c>
       <c r="AB63">
-        <v>42.281747395421668</v>
+        <v>50.29332693743671</v>
       </c>
       <c r="AD63" t="s">
         <v>414</v>
@@ -15440,10 +15440,10 @@
         <v>891</v>
       </c>
       <c r="AO63">
-        <v>0.99074948308423383</v>
+        <v>0.99720397512579328</v>
       </c>
       <c r="AP63">
-        <v>169.59281012238051</v>
+        <v>51.260456027123361</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -15508,16 +15508,16 @@
         <v>523</v>
       </c>
       <c r="Y64" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Z64" t="s">
         <v>628</v>
       </c>
       <c r="AA64">
-        <v>0.99540885392130762</v>
+        <v>0.99557960200072415</v>
       </c>
       <c r="AB64">
-        <v>84.171011442693441</v>
+        <v>81.040629986723459</v>
       </c>
       <c r="AD64" t="s">
         <v>414</v>
@@ -15550,10 +15550,10 @@
         <v>893</v>
       </c>
       <c r="AO64">
-        <v>0.99270401267208797</v>
+        <v>0.99565348329230585</v>
       </c>
       <c r="AP64">
-        <v>133.75976767838793</v>
+        <v>79.686139641060379</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -15618,16 +15618,16 @@
         <v>525</v>
       </c>
       <c r="Y65" t="s">
-        <v>351</v>
+        <v>398</v>
       </c>
       <c r="Z65" t="s">
         <v>629</v>
       </c>
       <c r="AA65">
-        <v>0.99360802526828129</v>
+        <v>0.99295357769237991</v>
       </c>
       <c r="AB65">
-        <v>117.18620341484296</v>
+        <v>129.18440897303603</v>
       </c>
       <c r="AD65" t="s">
         <v>414</v>
@@ -15660,10 +15660,10 @@
         <v>895</v>
       </c>
       <c r="AO65">
-        <v>0.99764772442226368</v>
+        <v>0.99784941409648109</v>
       </c>
       <c r="AP65">
-        <v>43.125052258499352</v>
+        <v>39.427408231180806</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -15728,16 +15728,16 @@
         <v>527</v>
       </c>
       <c r="Y66" t="s">
-        <v>400</v>
+        <v>355</v>
       </c>
       <c r="Z66" t="s">
         <v>630</v>
       </c>
       <c r="AA66">
-        <v>0.99515679011930902</v>
+        <v>0.99696751363483405</v>
       </c>
       <c r="AB66">
-        <v>88.792181146001369</v>
+        <v>55.595583361375894</v>
       </c>
       <c r="AD66" t="s">
         <v>414</v>
@@ -15770,10 +15770,10 @@
         <v>897</v>
       </c>
       <c r="AO66">
-        <v>0.99703044337128366</v>
+        <v>0.99831921281104818</v>
       </c>
       <c r="AP66">
-        <v>54.441871526466279</v>
+        <v>30.814431797450247</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -15838,16 +15838,16 @@
         <v>529</v>
       </c>
       <c r="Y67" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="Z67" t="s">
         <v>631</v>
       </c>
       <c r="AA67">
-        <v>0.99409145347725225</v>
+        <v>0.98964014500078279</v>
       </c>
       <c r="AB67">
-        <v>108.32335291704148</v>
+        <v>189.93067498564957</v>
       </c>
       <c r="AD67" t="s">
         <v>414</v>
@@ -15880,10 +15880,10 @@
         <v>899</v>
       </c>
       <c r="AO67">
-        <v>0.99584476105827657</v>
+        <v>0.99845356202909108</v>
       </c>
       <c r="AP67">
-        <v>76.179380598263194</v>
+        <v>28.351362799997673</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -15948,16 +15948,16 @@
         <v>531</v>
       </c>
       <c r="Y68" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="Z68" t="s">
         <v>632</v>
       </c>
       <c r="AA68">
-        <v>0.99464051280908794</v>
+        <v>0.9966137462997855</v>
       </c>
       <c r="AB68">
-        <v>98.257265166721183</v>
+        <v>62.081317837266766</v>
       </c>
       <c r="AD68" t="s">
         <v>414</v>
@@ -15990,10 +15990,10 @@
         <v>901</v>
       </c>
       <c r="AO68">
-        <v>0.9961146125371938</v>
+        <v>0.99368259233234391</v>
       </c>
       <c r="AP68">
-        <v>71.232103484781334</v>
+        <v>115.81914057369519</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -16058,16 +16058,16 @@
         <v>533</v>
       </c>
       <c r="Y69" t="s">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="Z69" t="s">
         <v>633</v>
       </c>
       <c r="AA69">
-        <v>0.99670408962762203</v>
+        <v>0.99011796851295664</v>
       </c>
       <c r="AB69">
-        <v>60.425023493595695</v>
+        <v>181.17057726246117</v>
       </c>
       <c r="AD69" t="s">
         <v>414</v>
@@ -16100,10 +16100,10 @@
         <v>903</v>
       </c>
       <c r="AO69">
-        <v>0.99607298561021362</v>
+        <v>0.9954443722844073</v>
       </c>
       <c r="AP69">
-        <v>71.995263812749926</v>
+        <v>83.519841452532361</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -16168,16 +16168,16 @@
         <v>535</v>
       </c>
       <c r="Y70" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="Z70" t="s">
         <v>634</v>
       </c>
       <c r="AA70">
-        <v>0.9960389195261472</v>
+        <v>0.99635118654529808</v>
       </c>
       <c r="AB70">
-        <v>72.619808687301173</v>
+        <v>66.894913336202478</v>
       </c>
       <c r="AD70" t="s">
         <v>414</v>
@@ -16210,10 +16210,10 @@
         <v>905</v>
       </c>
       <c r="AO70">
-        <v>0.9929182563937401</v>
+        <v>0.99363040616365128</v>
       </c>
       <c r="AP70">
-        <v>129.83196611476453</v>
+        <v>116.77588699972566</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -16278,16 +16278,16 @@
         <v>537</v>
       </c>
       <c r="Y71" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="Z71" t="s">
         <v>635</v>
       </c>
       <c r="AA71">
-        <v>0.99707957985864093</v>
+        <v>0.99440507690252466</v>
       </c>
       <c r="AB71">
-        <v>53.541035924916123</v>
+        <v>102.57359012038077</v>
       </c>
       <c r="AD71" t="s">
         <v>414</v>
@@ -16320,10 +16320,10 @@
         <v>907</v>
       </c>
       <c r="AO71">
-        <v>0.99628542339510884</v>
+        <v>0.99782402570187057</v>
       </c>
       <c r="AP71">
-        <v>68.100571089671959</v>
+        <v>39.892862132373601</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -16388,16 +16388,16 @@
         <v>539</v>
       </c>
       <c r="Y72" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="Z72" t="s">
         <v>636</v>
       </c>
       <c r="AA72">
-        <v>0.99080344458411729</v>
+        <v>0.99578350963230966</v>
       </c>
       <c r="AB72">
-        <v>168.60351595784994</v>
+        <v>77.302323407656075</v>
       </c>
       <c r="AD72" t="s">
         <v>414</v>
@@ -16430,10 +16430,10 @@
         <v>909</v>
       </c>
       <c r="AO72">
-        <v>0.99568571110966864</v>
+        <v>0.99756462867082185</v>
       </c>
       <c r="AP72">
-        <v>79.095296322741547</v>
+        <v>44.648474368267038</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -16498,16 +16498,16 @@
         <v>541</v>
       </c>
       <c r="Y73" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="Z73" t="s">
         <v>637</v>
       </c>
       <c r="AA73">
-        <v>0.98636012609964985</v>
+        <v>0.99720191150310689</v>
       </c>
       <c r="AB73">
-        <v>250.06435483975247</v>
+        <v>51.298289109706943</v>
       </c>
       <c r="AD73" t="s">
         <v>414</v>
@@ -16540,10 +16540,10 @@
         <v>911</v>
       </c>
       <c r="AO73">
-        <v>0.99609062270337045</v>
+        <v>0.99584476105827657</v>
       </c>
       <c r="AP73">
-        <v>71.671917104874566</v>
+        <v>76.179380598263194</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -16608,16 +16608,16 @@
         <v>543</v>
       </c>
       <c r="Y74" t="s">
-        <v>343</v>
+        <v>401</v>
       </c>
       <c r="Z74" t="s">
         <v>638</v>
       </c>
       <c r="AA74">
-        <v>0.99598850450039844</v>
+        <v>0.9954551465796494</v>
       </c>
       <c r="AB74">
-        <v>73.544084159361034</v>
+        <v>83.32231270642734</v>
       </c>
       <c r="AD74" t="s">
         <v>414</v>
@@ -16650,10 +16650,10 @@
         <v>913</v>
       </c>
       <c r="AO74">
-        <v>0.99598588086244633</v>
+        <v>0.9961146125371938</v>
       </c>
       <c r="AP74">
-        <v>73.592184188484865</v>
+        <v>71.232103484781334</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -16718,16 +16718,16 @@
         <v>545</v>
       </c>
       <c r="Y75" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="Z75" t="s">
         <v>639</v>
       </c>
       <c r="AA75">
-        <v>0.99310312827752323</v>
+        <v>0.99552053983611355</v>
       </c>
       <c r="AB75">
-        <v>126.44264824540761</v>
+        <v>82.123436337918946</v>
       </c>
       <c r="AD75" t="s">
         <v>414</v>
@@ -16760,10 +16760,10 @@
         <v>915</v>
       </c>
       <c r="AO75">
-        <v>0.99784941409648109</v>
+        <v>0.99607298561021362</v>
       </c>
       <c r="AP75">
-        <v>39.427408231180806</v>
+        <v>71.995263812749926</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -16828,16 +16828,16 @@
         <v>547</v>
       </c>
       <c r="Y76" t="s">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="Z76" t="s">
         <v>640</v>
       </c>
       <c r="AA76">
-        <v>0.99578350963230966</v>
+        <v>0.98935435476104872</v>
       </c>
       <c r="AB76">
-        <v>77.302323407656075</v>
+        <v>195.1701627141077</v>
       </c>
       <c r="AD76" t="s">
         <v>414</v>
@@ -16870,10 +16870,10 @@
         <v>917</v>
       </c>
       <c r="AO76">
-        <v>0.99831921281104818</v>
+        <v>0.9929182563937401</v>
       </c>
       <c r="AP76">
-        <v>30.814431797450247</v>
+        <v>129.83196611476453</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -16938,16 +16938,16 @@
         <v>549</v>
       </c>
       <c r="Y77" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="Z77" t="s">
         <v>641</v>
       </c>
       <c r="AA77">
-        <v>0.99720191150310689</v>
+        <v>0.99775872574768198</v>
       </c>
       <c r="AB77">
-        <v>51.298289109706943</v>
+        <v>41.090027959164246</v>
       </c>
       <c r="AD77" t="s">
         <v>414</v>
@@ -16980,10 +16980,10 @@
         <v>919</v>
       </c>
       <c r="AO77">
-        <v>0.99845356202909108</v>
+        <v>0.99628542339510884</v>
       </c>
       <c r="AP77">
-        <v>28.351362799997673</v>
+        <v>68.100571089671959</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -17048,16 +17048,16 @@
         <v>551</v>
       </c>
       <c r="Y78" t="s">
-        <v>401</v>
+        <v>337</v>
       </c>
       <c r="Z78" t="s">
         <v>642</v>
       </c>
       <c r="AA78">
-        <v>0.9954551465796494</v>
+        <v>0.99551989204648861</v>
       </c>
       <c r="AB78">
-        <v>83.32231270642734</v>
+        <v>82.135312481041623</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -17122,16 +17122,16 @@
         <v>553</v>
       </c>
       <c r="Y79" t="s">
-        <v>399</v>
+        <v>356</v>
       </c>
       <c r="Z79" t="s">
         <v>643</v>
       </c>
       <c r="AA79">
-        <v>0.99552053983611355</v>
+        <v>0.9979392050107273</v>
       </c>
       <c r="AB79">
-        <v>82.123436337918946</v>
+        <v>37.781241469999252</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -17196,16 +17196,16 @@
         <v>555</v>
       </c>
       <c r="Y80" t="s">
-        <v>385</v>
+        <v>354</v>
       </c>
       <c r="Z80" t="s">
         <v>644</v>
       </c>
       <c r="AA80">
-        <v>0.98935435476104872</v>
+        <v>0.9982033297630386</v>
       </c>
       <c r="AB80">
-        <v>195.1701627141077</v>
+        <v>32.938954344292306</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -17270,16 +17270,16 @@
         <v>557</v>
       </c>
       <c r="Y81" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="Z81" t="s">
         <v>645</v>
       </c>
       <c r="AA81">
-        <v>0.99775872574768198</v>
+        <v>0.99769372286934066</v>
       </c>
       <c r="AB81">
-        <v>41.090027959164246</v>
+        <v>42.281747395421668</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -17344,16 +17344,16 @@
         <v>559</v>
       </c>
       <c r="Y82" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="Z82" t="s">
         <v>646</v>
       </c>
       <c r="AA82">
-        <v>0.99699505644961572</v>
+        <v>0.99571525957109708</v>
       </c>
       <c r="AB82">
-        <v>55.090631757044932</v>
+        <v>78.553574529886689</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -17418,16 +17418,16 @@
         <v>561</v>
       </c>
       <c r="Y83" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="Z83" t="s">
         <v>647</v>
       </c>
       <c r="AA83">
-        <v>0.99170691261633115</v>
+        <v>0.99553579843385909</v>
       </c>
       <c r="AB83">
-        <v>152.03993536726261</v>
+        <v>81.84369537924907</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -17492,16 +17492,16 @@
         <v>563</v>
       </c>
       <c r="Y84" t="s">
-        <v>376</v>
+        <v>353</v>
       </c>
       <c r="Z84" t="s">
         <v>648</v>
       </c>
       <c r="AA84">
-        <v>0.9904035062850528</v>
+        <v>0.99734372305564056</v>
       </c>
       <c r="AB84">
-        <v>175.93571810736526</v>
+        <v>48.698410646589842</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -17566,16 +17566,16 @@
         <v>565</v>
       </c>
       <c r="Y85" t="s">
-        <v>336</v>
+        <v>388</v>
       </c>
       <c r="Z85" t="s">
         <v>649</v>
       </c>
       <c r="AA85">
-        <v>0.99359748433922845</v>
+        <v>0.99662670467221526</v>
       </c>
       <c r="AB85">
-        <v>117.37945378081078</v>
+        <v>61.843747676054292</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -17640,16 +17640,16 @@
         <v>567</v>
       </c>
       <c r="Y86" t="s">
-        <v>406</v>
+        <v>361</v>
       </c>
       <c r="Z86" t="s">
         <v>650</v>
       </c>
       <c r="AA86">
-        <v>0.99592552983543692</v>
+        <v>0.99740761205901929</v>
       </c>
       <c r="AB86">
-        <v>74.698619683656872</v>
+        <v>47.527112251312907</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -17714,16 +17714,16 @@
         <v>569</v>
       </c>
       <c r="Y87" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Z87" t="s">
         <v>651</v>
       </c>
       <c r="AA87">
-        <v>0.99463677905825021</v>
+        <v>0.99730769203227776</v>
       </c>
       <c r="AB87">
-        <v>98.325717265413417</v>
+        <v>49.358979408241737</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -17788,16 +17788,16 @@
         <v>571</v>
       </c>
       <c r="Y88" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="Z88" t="s">
         <v>652</v>
       </c>
       <c r="AA88">
-        <v>0.99667564038633161</v>
+        <v>0.998073964784436</v>
       </c>
       <c r="AB88">
-        <v>60.946592917253042</v>
+        <v>35.310645618673441</v>
       </c>
     </row>
   </sheetData>
@@ -17806,7 +17806,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{910D7DAB-E951-40C6-9633-3C737EBD2B12}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05D3A8FD-E351-40B3-BF57-E93E6CF16270}">
   <dimension ref="B9:Z77"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17918,7 +17918,7 @@
         <v>1006</v>
       </c>
       <c r="K11" t="s">
-        <v>902</v>
+        <v>914</v>
       </c>
       <c r="L11">
         <v>29.7146465744454</v>
@@ -17951,7 +17951,7 @@
         <v>1140</v>
       </c>
       <c r="X11" t="s">
-        <v>980</v>
+        <v>1002</v>
       </c>
       <c r="Y11">
         <v>0.33825</v>
@@ -17986,7 +17986,7 @@
         <v>1008</v>
       </c>
       <c r="K12" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="L12">
         <v>13.367096811591049</v>
@@ -18019,7 +18019,7 @@
         <v>1142</v>
       </c>
       <c r="X12" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="Y12">
         <v>10.88325</v>
@@ -18054,7 +18054,7 @@
         <v>1010</v>
       </c>
       <c r="K13" t="s">
-        <v>852</v>
+        <v>880</v>
       </c>
       <c r="L13">
         <v>24.156328337033791</v>
@@ -18087,7 +18087,7 @@
         <v>1144</v>
       </c>
       <c r="X13" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="Y13">
         <v>26.983499999999999</v>
@@ -18122,7 +18122,7 @@
         <v>1012</v>
       </c>
       <c r="K14" t="s">
-        <v>848</v>
+        <v>876</v>
       </c>
       <c r="L14">
         <v>16.006796560234815</v>
@@ -18155,7 +18155,7 @@
         <v>1146</v>
       </c>
       <c r="X14" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Y14">
         <v>42.507750000000001</v>
@@ -18190,7 +18190,7 @@
         <v>1014</v>
       </c>
       <c r="K15" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="L15">
         <v>17.682358378036344</v>
@@ -18223,7 +18223,7 @@
         <v>1148</v>
       </c>
       <c r="X15" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="Y15">
         <v>24.900749999999999</v>
@@ -18258,7 +18258,7 @@
         <v>1016</v>
       </c>
       <c r="K16" t="s">
-        <v>918</v>
+        <v>898</v>
       </c>
       <c r="L16">
         <v>29.492382648463739</v>
@@ -18291,7 +18291,7 @@
         <v>1150</v>
       </c>
       <c r="X16" t="s">
-        <v>1003</v>
+        <v>992</v>
       </c>
       <c r="Y16">
         <v>18.545249999999999</v>
@@ -18326,7 +18326,7 @@
         <v>1018</v>
       </c>
       <c r="K17" t="s">
-        <v>916</v>
+        <v>896</v>
       </c>
       <c r="L17">
         <v>8.6778699255653748</v>
@@ -18359,7 +18359,7 @@
         <v>1152</v>
       </c>
       <c r="X17" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="Y17">
         <v>29.838000000000001</v>
@@ -18394,7 +18394,7 @@
         <v>1020</v>
       </c>
       <c r="K18" t="s">
-        <v>914</v>
+        <v>894</v>
       </c>
       <c r="L18">
         <v>12.772248157772113</v>
@@ -18427,7 +18427,7 @@
         <v>1154</v>
       </c>
       <c r="X18" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="Y18">
         <v>58.689</v>
@@ -18462,7 +18462,7 @@
         <v>1022</v>
       </c>
       <c r="K19" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="L19">
         <v>15.217638427037592</v>
@@ -18495,7 +18495,7 @@
         <v>1156</v>
       </c>
       <c r="X19" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="Y19">
         <v>48.432000000000002</v>
@@ -18530,7 +18530,7 @@
         <v>1024</v>
       </c>
       <c r="K20" t="s">
-        <v>805</v>
+        <v>856</v>
       </c>
       <c r="L20">
         <v>3.1385663053565613</v>
@@ -18563,7 +18563,7 @@
         <v>1158</v>
       </c>
       <c r="X20" t="s">
-        <v>975</v>
+        <v>985</v>
       </c>
       <c r="Y20">
         <v>47.794499999999999</v>
@@ -18598,7 +18598,7 @@
         <v>1026</v>
       </c>
       <c r="K21" t="s">
-        <v>894</v>
+        <v>803</v>
       </c>
       <c r="L21">
         <v>4.0628682283884237</v>
@@ -18631,7 +18631,7 @@
         <v>1160</v>
       </c>
       <c r="X21" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="Y21">
         <v>7.1767500000000002</v>
@@ -18666,7 +18666,7 @@
         <v>1028</v>
       </c>
       <c r="K22" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="L22">
         <v>19.408837136062758</v>
@@ -18699,7 +18699,7 @@
         <v>1162</v>
       </c>
       <c r="X22" t="s">
-        <v>1005</v>
+        <v>994</v>
       </c>
       <c r="Y22">
         <v>8.1052499999999998</v>
@@ -18734,7 +18734,7 @@
         <v>1030</v>
       </c>
       <c r="K23" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="L23">
         <v>15.054857587707319</v>
@@ -18767,7 +18767,7 @@
         <v>1164</v>
       </c>
       <c r="X23" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="Y23">
         <v>9.3810000000000002</v>
@@ -18802,7 +18802,7 @@
         <v>1032</v>
       </c>
       <c r="K24" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="L24">
         <v>13.019602602156084</v>
@@ -18835,7 +18835,7 @@
         <v>1166</v>
       </c>
       <c r="X24" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="Y24">
         <v>11.47575</v>
@@ -18870,7 +18870,7 @@
         <v>1034</v>
       </c>
       <c r="K25" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="L25">
         <v>25.094411791551167</v>
@@ -18903,7 +18903,7 @@
         <v>1168</v>
       </c>
       <c r="X25" t="s">
-        <v>987</v>
+        <v>1005</v>
       </c>
       <c r="Y25">
         <v>6.1372499999999999</v>
@@ -18938,7 +18938,7 @@
         <v>1036</v>
       </c>
       <c r="K26" t="s">
-        <v>856</v>
+        <v>829</v>
       </c>
       <c r="L26">
         <v>18.31221960055294</v>
@@ -18971,7 +18971,7 @@
         <v>1170</v>
       </c>
       <c r="X26" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
         <v>14.57325</v>
@@ -19006,7 +19006,7 @@
         <v>1038</v>
       </c>
       <c r="K27" t="s">
-        <v>809</v>
+        <v>860</v>
       </c>
       <c r="L27">
         <v>27.91719839668141</v>
@@ -19039,7 +19039,7 @@
         <v>1172</v>
       </c>
       <c r="X27" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="Y27">
         <v>10.491</v>
@@ -19074,7 +19074,7 @@
         <v>1040</v>
       </c>
       <c r="K28" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="L28">
         <v>8.5144758814389814</v>
@@ -19107,7 +19107,7 @@
         <v>1174</v>
       </c>
       <c r="X28" t="s">
-        <v>982</v>
+        <v>1004</v>
       </c>
       <c r="Y28">
         <v>17.414249999999999</v>
@@ -19142,7 +19142,7 @@
         <v>1042</v>
       </c>
       <c r="K29" t="s">
-        <v>807</v>
+        <v>858</v>
       </c>
       <c r="L29">
         <v>12.144708893333986</v>
@@ -19175,7 +19175,7 @@
         <v>1176</v>
       </c>
       <c r="X29" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="Y29">
         <v>10.968</v>
@@ -19210,7 +19210,7 @@
         <v>1044</v>
       </c>
       <c r="K30" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="L30">
         <v>1.6724491767694549</v>
@@ -19243,7 +19243,7 @@
         <v>1178</v>
       </c>
       <c r="X30" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="Y30">
         <v>10.79175</v>
@@ -19278,7 +19278,7 @@
         <v>1046</v>
       </c>
       <c r="K31" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="L31">
         <v>13.894741632015101</v>
@@ -19311,7 +19311,7 @@
         <v>1180</v>
       </c>
       <c r="X31" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="Y31">
         <v>20.114249999999998</v>
@@ -19346,7 +19346,7 @@
         <v>1048</v>
       </c>
       <c r="K32" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="L32">
         <v>11.876635800692616</v>
@@ -19379,7 +19379,7 @@
         <v>1182</v>
       </c>
       <c r="X32" t="s">
-        <v>988</v>
+        <v>973</v>
       </c>
       <c r="Y32">
         <v>44.373750000000001</v>
@@ -19414,7 +19414,7 @@
         <v>1050</v>
       </c>
       <c r="K33" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="L33">
         <v>27.15579263061009</v>
@@ -19447,7 +19447,7 @@
         <v>1184</v>
       </c>
       <c r="X33" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="Y33">
         <v>18.57525</v>
@@ -19482,7 +19482,7 @@
         <v>1052</v>
       </c>
       <c r="K34" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="L34">
         <v>27.043339674957092</v>
@@ -19515,7 +19515,7 @@
         <v>1186</v>
       </c>
       <c r="X34" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="Y34">
         <v>18.241499999999998</v>
@@ -19550,7 +19550,7 @@
         <v>1054</v>
       </c>
       <c r="K35" t="s">
-        <v>896</v>
+        <v>805</v>
       </c>
       <c r="L35">
         <v>12.170927347824723</v>
@@ -19585,7 +19585,7 @@
         <v>1056</v>
       </c>
       <c r="K36" t="s">
-        <v>906</v>
+        <v>918</v>
       </c>
       <c r="L36">
         <v>26.999240466622091</v>
@@ -19620,7 +19620,7 @@
         <v>1058</v>
       </c>
       <c r="K37" t="s">
-        <v>825</v>
+        <v>908</v>
       </c>
       <c r="L37">
         <v>23.305350986470582</v>
@@ -19655,7 +19655,7 @@
         <v>1060</v>
       </c>
       <c r="K38" t="s">
-        <v>858</v>
+        <v>831</v>
       </c>
       <c r="L38">
         <v>19.293897715957783</v>
@@ -19690,7 +19690,7 @@
         <v>1062</v>
       </c>
       <c r="K39" t="s">
-        <v>850</v>
+        <v>878</v>
       </c>
       <c r="L39">
         <v>34.8352470366899</v>
@@ -19725,7 +19725,7 @@
         <v>1064</v>
       </c>
       <c r="K40" t="s">
-        <v>912</v>
+        <v>817</v>
       </c>
       <c r="L40">
         <v>22.439012549480047</v>
@@ -19760,7 +19760,7 @@
         <v>1066</v>
       </c>
       <c r="K41" t="s">
-        <v>821</v>
+        <v>904</v>
       </c>
       <c r="L41">
         <v>19.571302094407635</v>
@@ -19795,7 +19795,7 @@
         <v>1068</v>
       </c>
       <c r="K42" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="L42">
         <v>16.258507759053195</v>
@@ -19830,7 +19830,7 @@
         <v>1070</v>
       </c>
       <c r="K43" t="s">
-        <v>801</v>
+        <v>852</v>
       </c>
       <c r="L43">
         <v>48.074816212675138</v>
@@ -19865,7 +19865,7 @@
         <v>1072</v>
       </c>
       <c r="K44" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="L44">
         <v>65.59399718970684</v>
@@ -19900,7 +19900,7 @@
         <v>1074</v>
       </c>
       <c r="K45" t="s">
-        <v>797</v>
+        <v>848</v>
       </c>
       <c r="L45">
         <v>65.706815294563484</v>
@@ -19935,7 +19935,7 @@
         <v>1076</v>
       </c>
       <c r="K46" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="L46">
         <v>13.859521883612567</v>
@@ -19970,7 +19970,7 @@
         <v>1078</v>
       </c>
       <c r="K47" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="L47">
         <v>32.682899602232801</v>
@@ -20005,7 +20005,7 @@
         <v>1080</v>
       </c>
       <c r="K48" t="s">
-        <v>864</v>
+        <v>791</v>
       </c>
       <c r="L48">
         <v>39.028686646898073</v>
@@ -20040,7 +20040,7 @@
         <v>1082</v>
       </c>
       <c r="K49" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="L49">
         <v>25.808486809088087</v>
@@ -20075,7 +20075,7 @@
         <v>1084</v>
       </c>
       <c r="K50" t="s">
-        <v>862</v>
+        <v>789</v>
       </c>
       <c r="L50">
         <v>64.703394190718342</v>
@@ -20110,7 +20110,7 @@
         <v>1086</v>
       </c>
       <c r="K51" t="s">
-        <v>910</v>
+        <v>815</v>
       </c>
       <c r="L51">
         <v>46.777110562179843</v>
@@ -20145,7 +20145,7 @@
         <v>1088</v>
       </c>
       <c r="K52" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="L52">
         <v>83.307298494129057</v>
@@ -20180,7 +20180,7 @@
         <v>1090</v>
       </c>
       <c r="K53" t="s">
-        <v>817</v>
+        <v>900</v>
       </c>
       <c r="L53">
         <v>8.0718642408500934</v>
@@ -20215,7 +20215,7 @@
         <v>1092</v>
       </c>
       <c r="K54" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="L54">
         <v>25.555956589747868</v>
@@ -20250,7 +20250,7 @@
         <v>1094</v>
       </c>
       <c r="K55" t="s">
-        <v>819</v>
+        <v>902</v>
       </c>
       <c r="L55">
         <v>26.74310381624198</v>
@@ -20285,7 +20285,7 @@
         <v>1096</v>
       </c>
       <c r="K56" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="L56">
         <v>47.811917655816522</v>
@@ -20320,7 +20320,7 @@
         <v>1098</v>
       </c>
       <c r="K57" t="s">
-        <v>795</v>
+        <v>846</v>
       </c>
       <c r="L57">
         <v>65.898010391046881</v>
@@ -20355,7 +20355,7 @@
         <v>1100</v>
       </c>
       <c r="K58" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="L58">
         <v>49.914822287456737</v>
@@ -20390,7 +20390,7 @@
         <v>1102</v>
       </c>
       <c r="K59" t="s">
-        <v>793</v>
+        <v>844</v>
       </c>
       <c r="L59">
         <v>19.963633091222835</v>
@@ -20425,7 +20425,7 @@
         <v>1104</v>
       </c>
       <c r="K60" t="s">
-        <v>890</v>
+        <v>799</v>
       </c>
       <c r="L60">
         <v>71.04376789192942</v>
@@ -20460,7 +20460,7 @@
         <v>1106</v>
       </c>
       <c r="K61" t="s">
-        <v>846</v>
+        <v>874</v>
       </c>
       <c r="L61">
         <v>43.07229279461999</v>
@@ -20495,7 +20495,7 @@
         <v>1108</v>
       </c>
       <c r="K62" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="L62">
         <v>38.769945374969119</v>
@@ -20530,7 +20530,7 @@
         <v>1110</v>
       </c>
       <c r="K63" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L63">
         <v>59.009737840109466</v>
@@ -20565,7 +20565,7 @@
         <v>1112</v>
       </c>
       <c r="K64" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="L64">
         <v>28.865927665826828</v>
@@ -20600,7 +20600,7 @@
         <v>1114</v>
       </c>
       <c r="K65" t="s">
-        <v>854</v>
+        <v>827</v>
       </c>
       <c r="L65">
         <v>37.976260419426943</v>
@@ -20635,7 +20635,7 @@
         <v>1116</v>
       </c>
       <c r="K66" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="L66">
         <v>44.88386263672971</v>
@@ -20670,7 +20670,7 @@
         <v>1118</v>
       </c>
       <c r="K67" t="s">
-        <v>908</v>
+        <v>813</v>
       </c>
       <c r="L67">
         <v>23.350121881103082</v>
@@ -20705,7 +20705,7 @@
         <v>1120</v>
       </c>
       <c r="K68" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="L68">
         <v>15.289477961960474</v>
@@ -20740,7 +20740,7 @@
         <v>1122</v>
       </c>
       <c r="K69" t="s">
-        <v>823</v>
+        <v>906</v>
       </c>
       <c r="L69">
         <v>10.395885695189069</v>
@@ -20775,7 +20775,7 @@
         <v>1124</v>
       </c>
       <c r="K70" t="s">
-        <v>803</v>
+        <v>854</v>
       </c>
       <c r="L70">
         <v>23.89105636564183</v>
@@ -20810,7 +20810,7 @@
         <v>1126</v>
       </c>
       <c r="K71" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="L71">
         <v>18.959710131684457</v>
@@ -20845,7 +20845,7 @@
         <v>1128</v>
       </c>
       <c r="K72" t="s">
-        <v>799</v>
+        <v>850</v>
       </c>
       <c r="L72">
         <v>6.6550975614073966</v>
@@ -20880,7 +20880,7 @@
         <v>1130</v>
       </c>
       <c r="K73" t="s">
-        <v>900</v>
+        <v>912</v>
       </c>
       <c r="L73">
         <v>13.961943802326671</v>
@@ -20915,7 +20915,7 @@
         <v>1132</v>
       </c>
       <c r="K74" t="s">
-        <v>892</v>
+        <v>801</v>
       </c>
       <c r="L74">
         <v>51.937776653453852</v>
@@ -20950,7 +20950,7 @@
         <v>1134</v>
       </c>
       <c r="K75" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="L75">
         <v>21.246092446368579</v>
@@ -20985,7 +20985,7 @@
         <v>1136</v>
       </c>
       <c r="K76" t="s">
-        <v>860</v>
+        <v>787</v>
       </c>
       <c r="L76">
         <v>19.42059121972445</v>
@@ -21020,7 +21020,7 @@
         <v>1138</v>
       </c>
       <c r="K77" t="s">
-        <v>898</v>
+        <v>910</v>
       </c>
       <c r="L77">
         <v>30.063621105864488</v>
@@ -21035,7 +21035,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35FFF292-143B-4945-BDBE-92DFB43067F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40B53B39-C9E7-4C7A-9921-93FE7E7CF57C}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22852,7 +22852,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24158417-AFCF-4FCE-8D50-5FB1DF86D323}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9994004-CF4B-401B-BE6B-69FFE683715D}">
   <dimension ref="B2:M11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3959B16F-C97B-48FE-A6D4-BAC6EE1C7E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4472C7E-6598-41AE-BB9A-F563FE323D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1375,18 +1375,96 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IND_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IND_013</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_IND_011</t>
   </si>
   <si>
@@ -1411,6 +1489,120 @@
     <t>connecting solar to buses in cluster 40</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IND_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IND_016</t>
   </si>
   <si>
@@ -1435,22 +1627,136 @@
     <t>connecting solar to buses in cluster 43</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
+    <t>distr_solelc_spv_IND_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
   </si>
   <si>
     <t>distr_solelc_spv_IND_061</t>
@@ -1507,246 +1813,6 @@
     <t>connecting solar to buses in cluster 68</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_IND_001</t>
   </si>
   <si>
@@ -1783,78 +1849,51 @@
     <t>connecting solar to buses in cluster 58</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w166692103-400_IND,e_w1044735753-400_IND,e_w1012817818-400_IND,e_w92994753-400_IND,e_w92360278-400_IND,e_w1238123371-400_IND,e_w94199110-400_IND,e_w485873934-400_IND,e_IN179-400_IND,e_IN286-400_IND,e_IN181-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1072445901-400_IND</t>
+  </si>
+  <si>
+    <t>e_w375941438-400_IND,e_IN145-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w1336628403-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w688672798-765_IND,e_IN218-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND,e_IN659-765_IND</t>
+  </si>
+  <si>
+    <t>e_w331275940-765_IND,e_IN529-765_IND,e_w688672798-765_IND,e_w655683221-765_IND,e_IN489-765_IND,e_IN488-765_IND,e_IN486-765_IND</t>
+  </si>
+  <si>
+    <t>e_w654736039-765_IND,e_w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>e_w492377703-765_IND,e_w293597835-765_IND,e_w608461884-765_IND,e_w386018740-765_IND,e_w801704865-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311571096-765_IND,e_IN250-765_IND,e_IN247-765_IND,e_IN233-765_IND,e_w193216698-765_IND,e_w423702239-765_IND,e_IN295-765_IND,e_IN264-765_IND,e_w131484738-765_IND,e_IN246-765_IND,e_IN272-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311103617-765_IND,e_w166692103-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN235-400_IND,e_w465787206-400_IND,e_IN265-400_IND,e_w1265489491-400_IND</t>
+  </si>
+  <si>
     <t>e_w372701897-765_IND,e_IN10-765_IND,e_w311176519-765_IND</t>
   </si>
   <si>
@@ -1870,6 +1909,63 @@
     <t>e_IN440-400_IND,e_IN386-400_IND,e_w1072445901-400_IND</t>
   </si>
   <si>
+    <t>e_w1001700959-765_IND,e_IN218-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN218-765_IND,e_w1001700959-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_IN215-765_IND,e_IN191-765_IND,e_w1143180503-765_IND,e_IN163-765_IND,e_w654736039-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1207477934-765_IND,e_w840600239-765_IND,e_w506461670-765_IND,e_IN684-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311954703-765_IND,e_w1246177377-765_IND,e_IN540-765_IND,e_IN599-765_IND,e_IN586-765_IND,e_w353914761-765_IND,e_IN583-765_IND,e_IN555-765_IND,e_IN578-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN235-400_IND,e_w239498664-400_IND,e_IN265-400_IND,e_w1265489491-400_IND,e_w610646823-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN163-765_IND,e_w1143180503-765_IND,e_w654736039-765_IND,e_w631917408-765_IND,e_IN146-765_IND,e_w1077819664-765_IND,e_w311176519-765_IND,e_w369866141-765_IND,e_IN142-765_IND,e_IN108-765_IND,e_IN107-765_IND,e_IN94-765_IND</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND,e_IN610-765_IND,e_IN617-765_IND,e_w323266562-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1072445901-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN659-765_IND,e_w453513742-765_IND,e_IN642-765_IND,e_w429459345-765_IND,e_w492377703-765_IND,e_w293597835-765_IND,e_w608461884-765_IND,e_w318050929-765_IND,e_w316463122-765_IND</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND,e_w355560316-765_IND,e_w492377703-765_IND,e_w386018740-765_IND</t>
+  </si>
+  <si>
+    <t>e_w369866141-765_IND,e_IN146-765_IND,e_IN142-765_IND,e_IN230-765_IND,e_IN137-765_IND,e_IN140-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN798-765_IND</t>
+  </si>
+  <si>
+    <t>e_w408924420-765_IND,e_w192782338-765_IND,e_IN476-765_IND,e_IN457-765_IND,e_w408924427-765_IND,e_w319423421-765_IND,e_IN439-765_IND,e_w506461670-765_IND,e_IN400-765_IND,e_IN539-765_IND,e_IN404-765_IND,e_IN399-765_IND,e_IN390-765_IND,e_IN388-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN684-765_IND,e_w409158116-765_IND,e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN539-765_IND,e_w202980838-765_IND,e_IN416-765_IND,e_IN405-765_IND,e_w353914865-765_IND,e_w477691456-765_IND,e_IN540-765_IND,e_w196563905-765_IND,e_w353914761-765_IND,e_IN548-765_IND,e_w354062412-765_IND,e_w248385304-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN607-765_IND,e_IN578-765_IND,e_w248385304-765_IND,e_w323266562-765_IND,e_w149822703-400_IND,e_w759521252-765_IND</t>
+  </si>
+  <si>
+    <t>e_w342204888-765_IND,e_w245128370-765_IND,e_IN742-765_IND,e_w315824842-765_IND,e_w923365745-765_IND,e_w910151268-765_IND,e_w1074489047-765_IND</t>
+  </si>
+  <si>
+    <t>e_w759521252-765_IND,e_w118228036-400_IND,e_w793144832-765_IND,e_IN339-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1099365579-400_IND,e_w375941438-400_IND</t>
+  </si>
+  <si>
     <t>e_IN10-765_IND,e_w372701897-765_IND</t>
   </si>
   <si>
@@ -1882,13 +1978,70 @@
     <t>e_IN145-400_IND</t>
   </si>
   <si>
-    <t>e_w166692103-400_IND,e_w1044735753-400_IND,e_w1012817818-400_IND,e_w92994753-400_IND,e_w92360278-400_IND,e_w1238123371-400_IND,e_w94199110-400_IND,e_w485873934-400_IND,e_IN179-400_IND,e_IN286-400_IND,e_IN181-400_IND</t>
-  </si>
-  <si>
-    <t>e_w1072445901-400_IND</t>
-  </si>
-  <si>
-    <t>e_w375941438-400_IND,e_IN145-400_IND</t>
+    <t>e_w473902678-765_IND,e_w331275940-765_IND,e_IN642-765_IND,e_w318090288-765_IND,e_IN489-765_IND,e_IN486-765_IND,e_w316463122-765_IND,e_w698045832-765_IND</t>
+  </si>
+  <si>
+    <t>e_w466424134-765_IND,e_w1207477934-765_IND,e_w840600239-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN295-765_IND,e_IN277-765_IND,e_IN457-765_IND,e_w423702239-765_IND,e_IN289-765_IND,e_IN288-765_IND,e_IN439-765_IND,e_IN321-765_IND,e_IN343-765_IND,e_IN327-765_IND,e_IN400-765_IND,e_IN370-765_IND,e_w195459361-765_IND,e_IN323-765_IND</t>
+  </si>
+  <si>
+    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN539-765_IND,e_w311954703-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN365-765_IND,e_IN293-765_IND,e_IN373-765_IND,e_w422204218-765_IND,e_IN283-765_IND,e_IN395-765_IND,e_IN312-765_IND,e_IN302-765_IND,e_IN298-765_IND,e_IN375-765_IND,e_w409798382-400_IND,e_IN300-765_IND,e_w196933682-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN325-400_IND,e_IN315-400_IND,e_IN339-400_IND,e_w205942950-400_IND,e_w324064297-400_IND,e_IN320-400_IND,e_IN336-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN155-400_IND,e_w116541259-400_IND,e_IN235-400_IND</t>
+  </si>
+  <si>
+    <t>e_w386153973-765_IND,e_w342204888-765_IND,e_w751947947-765_IND,e_w910151268-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN128-765_IND,e_IN116-765_IND,e_w1341291951-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND,e_IN180-765_IND,e_IN206-765_IND,e_w311103617-765_IND</t>
+  </si>
+  <si>
+    <t>e_w374367235-400_IND,e_IN260-400_IND,e_w439006823-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
+  </si>
+  <si>
+    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w311571096-765_IND,e_w369866141-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN100-765_IND,e_w247861059-765_IND,e_w311176519-765_IND,e_IN105-765_IND,e_w105373531-765_IND,e_w274106872-765_IND,e_IN136-765_IND,e_w420797421-765_IND,e_w417569420-765_IND,e_IN135-765_IND,e_w1341291951-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN270-765_IND,e_IN196-765_IND,e_IN174-765_IND,e_w1329624553-765_IND,e_IN276-765_IND,e_IN200-765_IND,e_w607439318-765_IND,e_IN229-765_IND,e_IN183-765_IND,e_IN160-765_IND,e_w352619220-765_IND,e_IN267-765_IND,e_IN232-765_IND,e_IN254-765_IND,e_w100470285-765_IND,e_IN275-765_IND,e_w311118424-765_IND,e_IN283-765_IND,e_w311103617-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN260-400_IND,e_w203673991-400_IND,e_w1265496720-400_IND,e_w610646823-400_IND,e_w375084335-400_IND,e_IN177-400_IND,e_IN176-400_IND,e_w375941438-400_IND,e_IN145-400_IND</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND,e_w1127651311-765_IND,e_w331275940-765_IND,e_w688672798-765_IND</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND,e_w429459345-765_IND</t>
+  </si>
+  <si>
+    <t>e_w316463122-765_IND,e_w318090288-765_IND,e_w318050929-765_IND,e_w315477169-765_IND,e_w698045832-765_IND</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND,e_IN806-765_IND,e_IN798-765_IND,e_w1206014676-765_IND</t>
+  </si>
+  <si>
+    <t>e_w688672798-765_IND,e_IN218-765_IND,e_IN215-765_IND,e_IN199-765_IND,e_IN194-765_IND,e_IN191-765_IND,e_w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>e_w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>e_w323266562-765_IND,e_w759521252-765_IND,e_w793144832-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1341647644-400_IND,e_IN263-400_IND,e_w93160503-400_IND,e_w526897229-400_IND,e_IN259-400_IND,e_IN320-400_IND,e_IN235-400_IND</t>
   </si>
   <si>
     <t>e_w608461884-765_IND,e_w318050929-765_IND,e_w315477169-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
@@ -1918,126 +2071,6 @@
     <t>e_w315823978-765_IND,e_w386018740-765_IND,e_w801704865-765_IND,e_IN742-765_IND,e_w923365745-765_IND</t>
   </si>
   <si>
-    <t>e_w688672798-765_IND,e_IN218-765_IND,e_IN215-765_IND,e_IN199-765_IND,e_IN194-765_IND,e_IN191-765_IND,e_w631917408-765_IND</t>
-  </si>
-  <si>
-    <t>e_w545571850-765_IND</t>
-  </si>
-  <si>
-    <t>e_w323266562-765_IND,e_w759521252-765_IND,e_w793144832-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1341647644-400_IND,e_IN263-400_IND,e_w93160503-400_IND,e_w526897229-400_IND,e_IN259-400_IND,e_IN320-400_IND,e_IN235-400_IND</t>
-  </si>
-  <si>
-    <t>e_w473902678-765_IND,e_w1127651311-765_IND,e_w331275940-765_IND,e_w688672798-765_IND</t>
-  </si>
-  <si>
-    <t>e_w355560316-765_IND,e_w429459345-765_IND</t>
-  </si>
-  <si>
-    <t>e_w316463122-765_IND,e_w318090288-765_IND,e_w318050929-765_IND,e_w315477169-765_IND,e_w698045832-765_IND</t>
-  </si>
-  <si>
-    <t>e_w425401901-765_IND,e_IN806-765_IND,e_IN798-765_IND,e_w1206014676-765_IND</t>
-  </si>
-  <si>
-    <t>e_w342204888-765_IND,e_w245128370-765_IND,e_IN742-765_IND,e_w315824842-765_IND,e_w923365745-765_IND,e_w910151268-765_IND,e_w1074489047-765_IND</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND,e_w118228036-400_IND,e_w793144832-765_IND,e_IN339-400_IND</t>
-  </si>
-  <si>
-    <t>e_w1099365579-400_IND,e_w375941438-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN163-765_IND,e_w1143180503-765_IND,e_w654736039-765_IND,e_w631917408-765_IND,e_IN146-765_IND,e_w1077819664-765_IND,e_w311176519-765_IND,e_w369866141-765_IND,e_IN142-765_IND,e_IN108-765_IND,e_IN107-765_IND,e_IN94-765_IND</t>
-  </si>
-  <si>
-    <t>e_w409112085-765_IND,e_IN610-765_IND,e_IN617-765_IND,e_w323266562-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1072445901-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w1336628403-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w688672798-765_IND,e_IN218-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND</t>
-  </si>
-  <si>
-    <t>e_w473902678-765_IND,e_IN659-765_IND</t>
-  </si>
-  <si>
-    <t>e_w331275940-765_IND,e_IN529-765_IND,e_w688672798-765_IND,e_w655683221-765_IND,e_IN489-765_IND,e_IN488-765_IND,e_IN486-765_IND</t>
-  </si>
-  <si>
-    <t>e_w654736039-765_IND,e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>e_w355560316-765_IND</t>
-  </si>
-  <si>
-    <t>e_w492377703-765_IND,e_w293597835-765_IND,e_w608461884-765_IND,e_w386018740-765_IND,e_w801704865-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311571096-765_IND,e_IN250-765_IND,e_IN247-765_IND,e_IN233-765_IND,e_w193216698-765_IND,e_w423702239-765_IND,e_IN295-765_IND,e_IN264-765_IND,e_w131484738-765_IND,e_IN246-765_IND,e_IN272-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311103617-765_IND,e_w166692103-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN235-400_IND,e_w465787206-400_IND,e_IN265-400_IND,e_w1265489491-400_IND</t>
-  </si>
-  <si>
-    <t>e_w386153973-765_IND,e_w342204888-765_IND,e_w751947947-765_IND,e_w910151268-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN128-765_IND,e_IN116-765_IND,e_w1341291951-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND,e_IN180-765_IND,e_IN206-765_IND,e_w311103617-765_IND</t>
-  </si>
-  <si>
-    <t>e_w374367235-400_IND,e_IN260-400_IND,e_w439006823-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
-  </si>
-  <si>
-    <t>e_w1001700959-765_IND,e_IN218-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN218-765_IND,e_w1001700959-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_IN215-765_IND,e_IN191-765_IND,e_w1143180503-765_IND,e_IN163-765_IND,e_w654736039-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1207477934-765_IND,e_w840600239-765_IND,e_w506461670-765_IND,e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311954703-765_IND,e_w1246177377-765_IND,e_IN540-765_IND,e_IN599-765_IND,e_IN586-765_IND,e_w353914761-765_IND,e_IN583-765_IND,e_IN555-765_IND,e_IN578-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN235-400_IND,e_w239498664-400_IND,e_IN265-400_IND,e_w1265489491-400_IND,e_w610646823-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN659-765_IND,e_w453513742-765_IND,e_IN642-765_IND,e_w429459345-765_IND,e_w492377703-765_IND,e_w293597835-765_IND,e_w608461884-765_IND,e_w318050929-765_IND,e_w316463122-765_IND</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND,e_w355560316-765_IND,e_w492377703-765_IND,e_w386018740-765_IND</t>
-  </si>
-  <si>
-    <t>e_w369866141-765_IND,e_IN146-765_IND,e_IN142-765_IND,e_IN230-765_IND,e_IN137-765_IND,e_IN140-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN798-765_IND</t>
-  </si>
-  <si>
-    <t>e_w408924420-765_IND,e_w192782338-765_IND,e_IN476-765_IND,e_IN457-765_IND,e_w408924427-765_IND,e_w319423421-765_IND,e_IN439-765_IND,e_w506461670-765_IND,e_IN400-765_IND,e_IN539-765_IND,e_IN404-765_IND,e_IN399-765_IND,e_IN390-765_IND,e_IN388-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN684-765_IND,e_w409158116-765_IND,e_w409112085-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN539-765_IND,e_w202980838-765_IND,e_IN416-765_IND,e_IN405-765_IND,e_w353914865-765_IND,e_w477691456-765_IND,e_IN540-765_IND,e_w196563905-765_IND,e_w353914761-765_IND,e_IN548-765_IND,e_w354062412-765_IND,e_w248385304-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN607-765_IND,e_IN578-765_IND,e_w248385304-765_IND,e_w323266562-765_IND,e_w149822703-400_IND,e_w759521252-765_IND</t>
-  </si>
-  <si>
     <t>e_w1127651311-765_IND,e_w688672798-765_IND</t>
   </si>
   <si>
@@ -2056,37 +2089,220 @@
     <t>e_w196933682-765_IND,e_w923418232-400_IND,e_w1015325412-400_IND,e_w248385304-765_IND,e_IN353-400_IND,e_w149822703-400_IND,e_IN363-400_IND,e_w209806624-765_IND,e_w96821783-400_IND,e_w209806650-400_IND,e_w485873968-400_IND</t>
   </si>
   <si>
-    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w311571096-765_IND,e_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN100-765_IND,e_w247861059-765_IND,e_w311176519-765_IND,e_IN105-765_IND,e_w105373531-765_IND,e_w274106872-765_IND,e_IN136-765_IND,e_w420797421-765_IND,e_w417569420-765_IND,e_IN135-765_IND,e_w1341291951-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN270-765_IND,e_IN196-765_IND,e_IN174-765_IND,e_w1329624553-765_IND,e_IN276-765_IND,e_IN200-765_IND,e_w607439318-765_IND,e_IN229-765_IND,e_IN183-765_IND,e_IN160-765_IND,e_w352619220-765_IND,e_IN267-765_IND,e_IN232-765_IND,e_IN254-765_IND,e_w100470285-765_IND,e_IN275-765_IND,e_w311118424-765_IND,e_IN283-765_IND,e_w311103617-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN260-400_IND,e_w203673991-400_IND,e_w1265496720-400_IND,e_w610646823-400_IND,e_w375084335-400_IND,e_IN177-400_IND,e_IN176-400_IND,e_w375941438-400_IND,e_IN145-400_IND</t>
-  </si>
-  <si>
-    <t>e_w473902678-765_IND,e_w331275940-765_IND,e_IN642-765_IND,e_w318090288-765_IND,e_IN489-765_IND,e_IN486-765_IND,e_w316463122-765_IND,e_w698045832-765_IND</t>
-  </si>
-  <si>
-    <t>e_w466424134-765_IND,e_w1207477934-765_IND,e_w840600239-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN295-765_IND,e_IN277-765_IND,e_IN457-765_IND,e_w423702239-765_IND,e_IN289-765_IND,e_IN288-765_IND,e_IN439-765_IND,e_IN321-765_IND,e_IN343-765_IND,e_IN327-765_IND,e_IN400-765_IND,e_IN370-765_IND,e_w195459361-765_IND,e_IN323-765_IND</t>
-  </si>
-  <si>
-    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN539-765_IND,e_w311954703-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN365-765_IND,e_IN293-765_IND,e_IN373-765_IND,e_w422204218-765_IND,e_IN283-765_IND,e_IN395-765_IND,e_IN312-765_IND,e_IN302-765_IND,e_IN298-765_IND,e_IN375-765_IND,e_w409798382-400_IND,e_IN300-765_IND,e_w196933682-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN325-400_IND,e_IN315-400_IND,e_IN339-400_IND,e_w205942950-400_IND,e_w324064297-400_IND,e_IN320-400_IND,e_IN336-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN155-400_IND,e_w116541259-400_IND,e_IN235-400_IND</t>
+    <t>distr_wonelc_won_IND_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
   </si>
   <si>
     <t>distr_wonelc_won_IND_066</t>
@@ -2107,6 +2323,120 @@
     <t>connecting wind onshore to buses in cluster 38</t>
   </si>
   <si>
+    <t>distr_wonelc_won_IND_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_IND_056</t>
   </si>
   <si>
@@ -2125,28 +2455,22 @@
     <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
+    <t>distr_wonelc_won_IND_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wonelc_won_IND_053</t>
@@ -2167,328 +2491,217 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
+    <t>elc_won_IND_065</t>
+  </si>
+  <si>
+    <t>e_w1143180503-765_IND,e_w654736039-765_IND,e_w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_044</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND,e_w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_042</t>
+  </si>
+  <si>
+    <t>e_w492377703-765_IND,e_w355560316-765_IND,e_w386018740-765_IND,e_w315823978-765_IND,e_w386153973-765_IND,e_IN749-765_IND,e_IN748-765_IND,e_w342204888-765_IND,e_w245128370-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_005</t>
+  </si>
+  <si>
+    <t>e_w372701897-765_IND,e_w311176519-765_IND,e_w105373531-765_IND,e_IN42-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_039</t>
+  </si>
+  <si>
+    <t>e_w386153973-765_IND,e_IN803-765_IND,e_w751947947-765_IND,e_w342204888-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_002</t>
+  </si>
+  <si>
+    <t>elc_won_IND_049</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_047</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND,e_w355560316-765_IND,e_w492377703-765_IND,e_w293597835-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_035</t>
+  </si>
+  <si>
+    <t>e_w318090288-765_IND,e_IN486-765_IND,e_w316463122-765_IND,e_w698045832-765_IND,e_w608461884-765_IND,e_w318050929-765_IND,e_w315477169-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_062</t>
+  </si>
+  <si>
+    <t>e_w369866141-765_IND,e_IN142-765_IND,e_IN107-765_IND,e_IN230-765_IND,e_IN137-765_IND,e_IN140-765_IND,e_IN250-765_IND,e_w274106872-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_033</t>
+  </si>
+  <si>
+    <t>e_w315477169-765_IND,e_w408924420-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_060</t>
+  </si>
+  <si>
+    <t>e_w423702239-765_IND,e_IN250-765_IND,e_w193216698-765_IND,e_IN295-765_IND,e_IN264-765_IND,e_w131484738-765_IND,e_IN272-765_IND,e_IN289-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_010</t>
+  </si>
+  <si>
+    <t>e_IN404-765_IND,e_IN399-765_IND,e_w202980838-765_IND,e_IN390-765_IND,e_IN416-765_IND,e_w477691456-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_019</t>
+  </si>
+  <si>
+    <t>e_w422204218-765_IND,e_IN293-765_IND,e_IN312-765_IND,e_IN302-765_IND,e_IN375-765_IND,e_w409798382-400_IND,e_IN300-765_IND,e_IN290-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_017</t>
+  </si>
+  <si>
+    <t>e_IN290-400_IND,e_w50885643-400_IND,e_w166692103-400_IND,e_w50885643-765_IND,e_w577176545-400_IND,e_w1044735753-400_IND,e_w96821783-400_IND,e_w92994753-400_IND,e_w94199110-400_IND,e_w485873968-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_061</t>
+  </si>
+  <si>
+    <t>e_w372701897-765_IND,e_w311176519-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_058</t>
+  </si>
+  <si>
+    <t>e_w369866141-765_IND,e_w311571096-765_IND,e_IN230-765_IND,e_IN250-765_IND,e_IN247-765_IND,e_IN233-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_015</t>
+  </si>
+  <si>
+    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN684-765_IND,e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_020</t>
+  </si>
+  <si>
+    <t>e_w354062412-765_IND,e_w248385304-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_021</t>
+  </si>
+  <si>
+    <t>e_w248385304-765_IND,e_w149822703-400_IND,e_IN363-400_IND,e_w209806624-765_IND,e_w209806650-400_IND,e_w485873968-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_023</t>
+  </si>
+  <si>
+    <t>e_w759521252-765_IND,e_w793144832-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_051</t>
+  </si>
+  <si>
+    <t>e_w688672798-765_IND,e_w331275940-765_IND,e_IN529-765_IND,e_IN489-765_IND,e_w655683221-765_IND,e_IN488-765_IND,e_IN486-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_004</t>
+  </si>
+  <si>
+    <t>e_w1341291951-765_IND,e_w105373531-765_IND,e_IN116-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_029</t>
+  </si>
+  <si>
+    <t>e_w1207477934-765_IND,e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_003</t>
+  </si>
+  <si>
+    <t>e_IN275-765_IND,e_w311118424-765_IND,e_w100470285-765_IND,e_IN283-765_IND,e_w311103617-765_IND,e_IN298-765_IND,e_w166692103-400_IND,e_IN300-765_IND,e_IN290-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_048</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w1336628403-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_034</t>
+  </si>
+  <si>
+    <t>e_IN659-765_IND,e_w453513742-765_IND,e_IN642-765_IND,e_w318090288-765_IND,e_w429459345-765_IND,e_w316463122-765_IND,e_w318050929-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_046</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND,e_IN798-765_IND,e_w386153973-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_022</t>
+  </si>
+  <si>
+    <t>e_IN440-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_057</t>
+  </si>
+  <si>
+    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w369866141-765_IND,e_w311571096-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_041</t>
+  </si>
+  <si>
+    <t>e_w293597835-765_IND,e_w608461884-765_IND,e_w492377703-765_IND,e_w386018740-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_030</t>
+  </si>
+  <si>
+    <t>e_w315824842-765_IND,e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_050</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w473902678-765_IND,e_w331275940-765_IND,e_w688672798-765_IND,e_w318090288-765_IND,e_IN489-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_064</t>
+  </si>
+  <si>
+    <t>e_w1001700959-765_IND,e_IN218-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_w1143180503-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_011</t>
+  </si>
+  <si>
+    <t>e_IN365-765_IND,e_IN388-765_IND,e_IN373-765_IND,e_w422204218-765_IND,e_IN405-765_IND,e_IN395-765_IND,e_w477691456-765_IND,e_IN375-765_IND,e_w196563905-765_IND,e_w196933682-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_025</t>
+  </si>
+  <si>
+    <t>e_w759521252-765_IND,e_w118228036-400_IND</t>
   </si>
   <si>
     <t>elc_won_IND_066</t>
@@ -2509,6 +2722,120 @@
     <t>e_w342204888-765_IND,e_w245128370-765_IND,e_IN742-765_IND,e_w315823978-765_IND,e_w801704865-765_IND,e_w315824842-765_IND,e_w923365745-765_IND</t>
   </si>
   <si>
+    <t>elc_won_IND_055</t>
+  </si>
+  <si>
+    <t>e_IN486-765_IND,e_IN473-765_IND,e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_016</t>
+  </si>
+  <si>
+    <t>e_w166692103-400_IND,e_w1012817818-400_IND,e_w92360278-400_IND,e_w1238123371-400_IND,e_w485873934-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_028</t>
+  </si>
+  <si>
+    <t>e_w324064297-400_IND,e_IN320-400_IND,e_IN259-400_IND,e_IN235-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_009</t>
+  </si>
+  <si>
+    <t>e_IN439-765_IND,e_IN321-765_IND,e_w319423421-765_IND,e_IN343-765_IND,e_IN327-765_IND,e_IN400-765_IND,e_IN370-765_IND,e_w195459361-765_IND,e_IN399-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_013</t>
+  </si>
+  <si>
+    <t>e_w311933111-765_IND,e_w311954703-765_IND,e_IN539-765_IND,e_w1246177377-765_IND,e_IN599-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_043</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND,e_IN659-765_IND,e_w473902678-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_045</t>
+  </si>
+  <si>
+    <t>e_IN798-765_IND,e_w425401901-765_IND,e_IN801-765_IND,e_IN803-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_031</t>
+  </si>
+  <si>
+    <t>e_w466424134-765_IND,e_w840600239-765_IND,e_w1207477934-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_059</t>
+  </si>
+  <si>
+    <t>e_IN270-765_IND,e_IN277-765_IND,e_IN276-765_IND,e_IN289-765_IND,e_IN288-765_IND,e_IN267-765_IND,e_IN321-765_IND,e_IN323-765_IND,e_IN293-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_027</t>
+  </si>
+  <si>
+    <t>e_w1238123371-400_IND,e_IN286-400_IND,e_w485873934-400_IND,e_IN181-400_IND,e_w1341647644-400_IND,e_IN263-400_IND,e_w93160503-400_IND,e_w526897229-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_052</t>
+  </si>
+  <si>
+    <t>e_IN218-765_IND,e_IN215-765_IND,e_IN187-765_IND,e_IN199-765_IND,e_IN191-765_IND,e_IN194-765_IND,e_w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_037</t>
+  </si>
+  <si>
+    <t>e_IN803-765_IND,e_w545571850-765_IND,e_w751947947-765_IND,e_w342204888-765_IND,e_w910151268-765_IND,e_w315824842-765_IND,e_w1074489047-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_032</t>
+  </si>
+  <si>
+    <t>e_w506461670-765_IND,e_IN684-765_IND,e_w311933111-765_IND,e_IN685-765_IND,e_w409158116-765_IND,e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_018</t>
+  </si>
+  <si>
+    <t>e_w97392607-400_IND,e_w324059200-400_IND,e_IN317-400_IND,e_w923418232-400_IND,e_w577176545-400_IND,e_w1015325412-400_IND,e_IN353-400_IND,e_w209806624-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_067</t>
+  </si>
+  <si>
+    <t>e_IN163-765_IND,e_w1143180503-765_IND,e_w654736039-765_IND,e_w631917408-765_IND,e_IN146-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_063</t>
+  </si>
+  <si>
+    <t>e_w1077819664-765_IND,e_w311176519-765_IND,e_IN108-765_IND,e_IN94-765_IND,e_IN137-765_IND,e_IN100-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_001</t>
+  </si>
+  <si>
+    <t>e_w352619220-765_IND,e_IN180-765_IND,e_IN206-765_IND,e_w311103617-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_024</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND,e_IN617-765_IND,e_w323266562-765_IND,e_w759521252-765_IND,e_w793144832-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_026</t>
+  </si>
+  <si>
+    <t>e_w118228036-400_IND,e_IN325-400_IND,e_IN315-400_IND,e_IN339-400_IND,e_w205942950-400_IND,e_w793144832-765_IND,e_IN336-400_IND,e_IN320-400_IND</t>
+  </si>
+  <si>
     <t>elc_won_IND_056</t>
   </si>
   <si>
@@ -2527,28 +2854,22 @@
     <t>e_w408924427-765_IND,e_w506461670-765_IND</t>
   </si>
   <si>
-    <t>elc_won_IND_050</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w473902678-765_IND,e_w331275940-765_IND,e_w688672798-765_IND,e_w318090288-765_IND,e_IN489-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_064</t>
-  </si>
-  <si>
-    <t>e_w1001700959-765_IND,e_IN218-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_011</t>
-  </si>
-  <si>
-    <t>e_IN365-765_IND,e_IN388-765_IND,e_IN373-765_IND,e_w422204218-765_IND,e_IN405-765_IND,e_IN395-765_IND,e_w477691456-765_IND,e_IN375-765_IND,e_w196563905-765_IND,e_w196933682-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_025</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND,e_w118228036-400_IND</t>
+    <t>elc_won_IND_008</t>
+  </si>
+  <si>
+    <t>e_w247861059-765_IND,e_w311176519-765_IND,e_IN140-765_IND,e_IN105-765_IND,e_w105373531-765_IND,e_IN136-765_IND,e_w420797421-765_IND,e_w417569420-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_007</t>
+  </si>
+  <si>
+    <t>e_IN136-765_IND,e_IN246-765_IND,e_w274106872-765_IND,e_IN196-765_IND,e_IN174-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_006</t>
+  </si>
+  <si>
+    <t>e_IN135-765_IND,e_w420797421-765_IND,e_w1329624553-765_IND,e_IN128-765_IND,e_IN200-765_IND,e_IN196-765_IND,e_w607439318-765_IND,e_IN229-765_IND,e_IN183-765_IND,e_IN160-765_IND,e_IN267-765_IND,e_IN232-765_IND,e_IN180-765_IND,e_IN254-765_IND,e_w100470285-765_IND</t>
   </si>
   <si>
     <t>elc_won_IND_053</t>
@@ -2569,325 +2890,100 @@
     <t>e_w408924420-765_IND,e_w192782338-765_IND,e_w408924427-765_IND,e_w506461670-765_IND,e_w311933111-765_IND,e_IN539-765_IND</t>
   </si>
   <si>
-    <t>elc_won_IND_057</t>
-  </si>
-  <si>
-    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w369866141-765_IND,e_w311571096-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_041</t>
-  </si>
-  <si>
-    <t>e_w293597835-765_IND,e_w608461884-765_IND,e_w492377703-765_IND,e_w386018740-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_030</t>
-  </si>
-  <si>
-    <t>e_w315824842-765_IND,e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_052</t>
-  </si>
-  <si>
-    <t>e_IN218-765_IND,e_IN215-765_IND,e_IN187-765_IND,e_IN199-765_IND,e_IN191-765_IND,e_IN194-765_IND,e_w631917408-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_037</t>
-  </si>
-  <si>
-    <t>e_IN803-765_IND,e_w545571850-765_IND,e_w751947947-765_IND,e_w342204888-765_IND,e_w910151268-765_IND,e_w315824842-765_IND,e_w1074489047-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_032</t>
-  </si>
-  <si>
-    <t>e_w506461670-765_IND,e_IN684-765_IND,e_w311933111-765_IND,e_IN685-765_IND,e_w409158116-765_IND,e_w409112085-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_018</t>
-  </si>
-  <si>
-    <t>e_w97392607-400_IND,e_w324059200-400_IND,e_IN317-400_IND,e_w923418232-400_IND,e_w577176545-400_IND,e_w1015325412-400_IND,e_IN353-400_IND,e_w209806624-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_055</t>
-  </si>
-  <si>
-    <t>e_IN486-765_IND,e_IN473-765_IND,e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_016</t>
-  </si>
-  <si>
-    <t>e_w166692103-400_IND,e_w1012817818-400_IND,e_w92360278-400_IND,e_w1238123371-400_IND,e_w485873934-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_028</t>
-  </si>
-  <si>
-    <t>e_w324064297-400_IND,e_IN320-400_IND,e_IN259-400_IND,e_IN235-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_065</t>
-  </si>
-  <si>
-    <t>e_w1143180503-765_IND,e_w654736039-765_IND,e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_044</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND,e_w355560316-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_042</t>
-  </si>
-  <si>
-    <t>e_w492377703-765_IND,e_w355560316-765_IND,e_w386018740-765_IND,e_w315823978-765_IND,e_w386153973-765_IND,e_IN749-765_IND,e_IN748-765_IND,e_w342204888-765_IND,e_w245128370-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_005</t>
-  </si>
-  <si>
-    <t>e_w372701897-765_IND,e_w311176519-765_IND,e_w105373531-765_IND,e_IN42-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_039</t>
-  </si>
-  <si>
-    <t>e_w386153973-765_IND,e_IN803-765_IND,e_w751947947-765_IND,e_w342204888-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_002</t>
-  </si>
-  <si>
-    <t>elc_won_IND_049</t>
-  </si>
-  <si>
-    <t>e_w473902678-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_047</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND,e_w355560316-765_IND,e_w492377703-765_IND,e_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_035</t>
-  </si>
-  <si>
-    <t>e_w318090288-765_IND,e_IN486-765_IND,e_w316463122-765_IND,e_w698045832-765_IND,e_w608461884-765_IND,e_w318050929-765_IND,e_w315477169-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_062</t>
-  </si>
-  <si>
-    <t>e_w369866141-765_IND,e_IN142-765_IND,e_IN107-765_IND,e_IN230-765_IND,e_IN137-765_IND,e_IN140-765_IND,e_IN250-765_IND,e_w274106872-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_033</t>
-  </si>
-  <si>
-    <t>e_w315477169-765_IND,e_w408924420-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_060</t>
-  </si>
-  <si>
-    <t>e_w423702239-765_IND,e_IN250-765_IND,e_w193216698-765_IND,e_IN295-765_IND,e_IN264-765_IND,e_w131484738-765_IND,e_IN272-765_IND,e_IN289-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_010</t>
-  </si>
-  <si>
-    <t>e_IN404-765_IND,e_IN399-765_IND,e_w202980838-765_IND,e_IN390-765_IND,e_IN416-765_IND,e_w477691456-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_019</t>
-  </si>
-  <si>
-    <t>e_w422204218-765_IND,e_IN293-765_IND,e_IN312-765_IND,e_IN302-765_IND,e_IN375-765_IND,e_w409798382-400_IND,e_IN300-765_IND,e_IN290-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_017</t>
-  </si>
-  <si>
-    <t>e_IN290-400_IND,e_w50885643-400_IND,e_w166692103-400_IND,e_w50885643-765_IND,e_w577176545-400_IND,e_w1044735753-400_IND,e_w96821783-400_IND,e_w92994753-400_IND,e_w94199110-400_IND,e_w485873968-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_061</t>
-  </si>
-  <si>
-    <t>e_w372701897-765_IND,e_w311176519-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_058</t>
-  </si>
-  <si>
-    <t>e_w369866141-765_IND,e_w311571096-765_IND,e_IN230-765_IND,e_IN250-765_IND,e_IN247-765_IND,e_IN233-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_015</t>
-  </si>
-  <si>
-    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN684-765_IND,e_w409112085-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_020</t>
-  </si>
-  <si>
-    <t>e_w354062412-765_IND,e_w248385304-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_021</t>
-  </si>
-  <si>
-    <t>e_w248385304-765_IND,e_w149822703-400_IND,e_IN363-400_IND,e_w209806624-765_IND,e_w209806650-400_IND,e_w485873968-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_023</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND,e_w793144832-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_051</t>
-  </si>
-  <si>
-    <t>e_w688672798-765_IND,e_w331275940-765_IND,e_IN529-765_IND,e_IN489-765_IND,e_w655683221-765_IND,e_IN488-765_IND,e_IN486-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_004</t>
-  </si>
-  <si>
-    <t>e_w1341291951-765_IND,e_w105373531-765_IND,e_IN116-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_029</t>
-  </si>
-  <si>
-    <t>e_w1207477934-765_IND,e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_003</t>
-  </si>
-  <si>
-    <t>e_IN275-765_IND,e_w311118424-765_IND,e_w100470285-765_IND,e_IN283-765_IND,e_w311103617-765_IND,e_IN298-765_IND,e_w166692103-400_IND,e_IN300-765_IND,e_IN290-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_048</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w1336628403-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_034</t>
-  </si>
-  <si>
-    <t>e_IN659-765_IND,e_w453513742-765_IND,e_IN642-765_IND,e_w318090288-765_IND,e_w429459345-765_IND,e_w316463122-765_IND,e_w318050929-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_046</t>
-  </si>
-  <si>
-    <t>e_w355560316-765_IND,e_IN798-765_IND,e_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_022</t>
-  </si>
-  <si>
-    <t>e_IN440-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_009</t>
-  </si>
-  <si>
-    <t>e_IN439-765_IND,e_IN321-765_IND,e_w319423421-765_IND,e_IN343-765_IND,e_IN327-765_IND,e_IN400-765_IND,e_IN370-765_IND,e_w195459361-765_IND,e_IN399-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_013</t>
-  </si>
-  <si>
-    <t>e_w311933111-765_IND,e_w311954703-765_IND,e_IN539-765_IND,e_w1246177377-765_IND,e_IN599-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_008</t>
-  </si>
-  <si>
-    <t>e_w247861059-765_IND,e_w311176519-765_IND,e_IN140-765_IND,e_IN105-765_IND,e_w105373531-765_IND,e_IN136-765_IND,e_w420797421-765_IND,e_w417569420-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_007</t>
-  </si>
-  <si>
-    <t>e_IN136-765_IND,e_IN246-765_IND,e_w274106872-765_IND,e_IN196-765_IND,e_IN174-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_006</t>
-  </si>
-  <si>
-    <t>e_IN135-765_IND,e_w420797421-765_IND,e_w1329624553-765_IND,e_IN128-765_IND,e_IN200-765_IND,e_IN196-765_IND,e_w607439318-765_IND,e_IN229-765_IND,e_IN183-765_IND,e_IN160-765_IND,e_IN267-765_IND,e_IN232-765_IND,e_IN180-765_IND,e_IN254-765_IND,e_w100470285-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_043</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND,e_IN659-765_IND,e_w473902678-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_045</t>
-  </si>
-  <si>
-    <t>e_IN798-765_IND,e_w425401901-765_IND,e_IN801-765_IND,e_IN803-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_031</t>
-  </si>
-  <si>
-    <t>e_w466424134-765_IND,e_w840600239-765_IND,e_w1207477934-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_059</t>
-  </si>
-  <si>
-    <t>e_IN270-765_IND,e_IN277-765_IND,e_IN276-765_IND,e_IN289-765_IND,e_IN288-765_IND,e_IN267-765_IND,e_IN321-765_IND,e_IN323-765_IND,e_IN293-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_027</t>
-  </si>
-  <si>
-    <t>e_w1238123371-400_IND,e_IN286-400_IND,e_w485873934-400_IND,e_IN181-400_IND,e_w1341647644-400_IND,e_IN263-400_IND,e_w93160503-400_IND,e_w526897229-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_067</t>
-  </si>
-  <si>
-    <t>e_IN163-765_IND,e_w1143180503-765_IND,e_w654736039-765_IND,e_w631917408-765_IND,e_IN146-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_063</t>
-  </si>
-  <si>
-    <t>e_w1077819664-765_IND,e_w311176519-765_IND,e_IN108-765_IND,e_IN94-765_IND,e_IN137-765_IND,e_IN100-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_001</t>
-  </si>
-  <si>
-    <t>e_w352619220-765_IND,e_IN180-765_IND,e_IN206-765_IND,e_w311103617-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_024</t>
-  </si>
-  <si>
-    <t>e_w409112085-765_IND,e_IN617-765_IND,e_w323266562-765_IND,e_w759521252-765_IND,e_w793144832-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_026</t>
-  </si>
-  <si>
-    <t>e_w118228036-400_IND,e_IN325-400_IND,e_IN315-400_IND,e_IN339-400_IND,e_w205942950-400_IND,e_w793144832-765_IND,e_IN336-400_IND,e_IN320-400_IND</t>
+    <t>distr_wofelc_wof_IND_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IND_009</t>
@@ -2908,10 +3004,28 @@
     <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
+    <t>distr_wofelc_wof_IND_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IND_021</t>
@@ -2920,118 +3034,79 @@
     <t>connecting wind offshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
+    <t>elc_wof_IND_010</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_013</t>
+  </si>
+  <si>
+    <t>e_w545571850-765_IND,e_w910151268-765_IND,e_w1074489047-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_023</t>
+  </si>
+  <si>
+    <t>e_w323266562-765_IND,e_w759521252-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_002</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_007</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w688672711-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_008</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_005</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_024</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND,e_IN617-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_015</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_001</t>
+  </si>
+  <si>
+    <t>e_IN798-765_IND,e_w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_018</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_022</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_006</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_012</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>e_w315824842-765_IND,e_w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND</t>
   </si>
   <si>
     <t>elc_wof_IND_009</t>
@@ -3043,109 +3118,34 @@
     <t>elc_wof_IND_017</t>
   </si>
   <si>
-    <t>e_w425401901-765_IND</t>
-  </si>
-  <si>
     <t>elc_wof_IND_014</t>
   </si>
   <si>
-    <t>elc_wof_IND_022</t>
+    <t>elc_wof_IND_011</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND,e_w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_003</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_016</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND,e_w1206014676-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_004</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND,e_w473902678-765_IND</t>
   </si>
   <si>
     <t>elc_wof_IND_021</t>
   </si>
   <si>
     <t>e_w409158116-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_013</t>
-  </si>
-  <si>
-    <t>e_w545571850-765_IND,e_w910151268-765_IND,e_w1074489047-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_023</t>
-  </si>
-  <si>
-    <t>e_w323266562-765_IND,e_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>e_w315824842-765_IND,e_w923365745-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>e_w409112085-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_002</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_010</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_007</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_008</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_005</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_024</t>
-  </si>
-  <si>
-    <t>e_w409112085-765_IND,e_IN617-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_006</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_012</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_004</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND,e_w473902678-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_011</t>
-  </si>
-  <si>
-    <t>e_w473902678-765_IND,e_w1127651311-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_003</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_016</t>
-  </si>
-  <si>
-    <t>e_w425401901-765_IND,e_w1206014676-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_001</t>
-  </si>
-  <si>
-    <t>e_IN798-765_IND,e_w355560316-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_018</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_015</t>
   </si>
   <si>
     <t>e_won_IND_001</t>
@@ -8576,7 +8576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03164137-8271-4B45-A140-7E5DAE704C7D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EFF6EBC-81FB-4AAF-A68D-6C2FADB019F7}">
   <dimension ref="B9:BD88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8814,16 +8814,16 @@
         <v>415</v>
       </c>
       <c r="Y11" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="Z11" t="s">
         <v>575</v>
       </c>
       <c r="AA11">
-        <v>0.99478609753984348</v>
+        <v>0.99699505644961572</v>
       </c>
       <c r="AB11">
-        <v>95.588211769535249</v>
+        <v>55.090631757044932</v>
       </c>
       <c r="AD11" t="s">
         <v>414</v>
@@ -8856,10 +8856,10 @@
         <v>788</v>
       </c>
       <c r="AO11">
-        <v>0.99618121233373258</v>
+        <v>0.99245794727704639</v>
       </c>
       <c r="AP11">
-        <v>70.011107214903078</v>
+        <v>138.27096658748206</v>
       </c>
       <c r="AR11" t="s">
         <v>414</v>
@@ -8889,13 +8889,13 @@
         <v>968</v>
       </c>
       <c r="BB11" t="s">
-        <v>969</v>
+        <v>799</v>
       </c>
       <c r="BC11">
-        <v>0.98137594918937099</v>
+        <v>0.98154438143849254</v>
       </c>
       <c r="BD11">
-        <v>341.44093152819772</v>
+        <v>338.35300696097039</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8960,16 +8960,16 @@
         <v>419</v>
       </c>
       <c r="Y12" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="Z12" t="s">
         <v>576</v>
       </c>
       <c r="AA12">
-        <v>0.99568525132868968</v>
+        <v>0.99170691261633115</v>
       </c>
       <c r="AB12">
-        <v>79.10372564068922</v>
+        <v>152.03993536726261</v>
       </c>
       <c r="AD12" t="s">
         <v>414</v>
@@ -9002,10 +9002,10 @@
         <v>790</v>
       </c>
       <c r="AO12">
-        <v>0.99592364356186902</v>
+        <v>0.99381230463557813</v>
       </c>
       <c r="AP12">
-        <v>74.733201365734146</v>
+        <v>113.44108168106689</v>
       </c>
       <c r="AR12" t="s">
         <v>414</v>
@@ -9032,16 +9032,16 @@
         <v>922</v>
       </c>
       <c r="BA12" t="s">
+        <v>969</v>
+      </c>
+      <c r="BB12" t="s">
         <v>970</v>
       </c>
-      <c r="BB12" t="s">
-        <v>971</v>
-      </c>
       <c r="BC12">
-        <v>0.9889956676941275</v>
+        <v>0.99526782804010661</v>
       </c>
       <c r="BD12">
-        <v>201.74609227432916</v>
+        <v>86.756485931379871</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -9106,16 +9106,16 @@
         <v>421</v>
       </c>
       <c r="Y13" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="Z13" t="s">
         <v>577</v>
       </c>
       <c r="AA13">
-        <v>0.99590266392783655</v>
+        <v>0.9904035062850528</v>
       </c>
       <c r="AB13">
-        <v>75.117827989662302</v>
+        <v>175.93571810736526</v>
       </c>
       <c r="AD13" t="s">
         <v>414</v>
@@ -9148,10 +9148,10 @@
         <v>792</v>
       </c>
       <c r="AO13">
-        <v>0.99641167752379312</v>
+        <v>0.99534539864304916</v>
       </c>
       <c r="AP13">
-        <v>65.785912063792665</v>
+        <v>85.3343582107656</v>
       </c>
       <c r="AR13" t="s">
         <v>414</v>
@@ -9178,16 +9178,16 @@
         <v>924</v>
       </c>
       <c r="BA13" t="s">
+        <v>971</v>
+      </c>
+      <c r="BB13" t="s">
         <v>972</v>
       </c>
-      <c r="BB13" t="s">
-        <v>597</v>
-      </c>
       <c r="BC13">
-        <v>0.99193721244794397</v>
+        <v>0.98605138538291048</v>
       </c>
       <c r="BD13">
-        <v>147.81777178769397</v>
+        <v>255.7246013133088</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -9252,16 +9252,16 @@
         <v>423</v>
       </c>
       <c r="Y14" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="Z14" t="s">
         <v>578</v>
       </c>
       <c r="AA14">
-        <v>0.99449671322390631</v>
+        <v>0.99579357955795456</v>
       </c>
       <c r="AB14">
-        <v>100.89359089505045</v>
+        <v>77.117708104165573</v>
       </c>
       <c r="AD14" t="s">
         <v>414</v>
@@ -9294,10 +9294,10 @@
         <v>794</v>
       </c>
       <c r="AO14">
-        <v>0.99474825047892679</v>
+        <v>0.99310873310996184</v>
       </c>
       <c r="AP14">
-        <v>96.282074553009053</v>
+        <v>126.33989298403215</v>
       </c>
       <c r="AR14" t="s">
         <v>414</v>
@@ -9327,13 +9327,13 @@
         <v>973</v>
       </c>
       <c r="BB14" t="s">
-        <v>873</v>
+        <v>643</v>
       </c>
       <c r="BC14">
-        <v>0.98389167860462323</v>
+        <v>0.97123008268954114</v>
       </c>
       <c r="BD14">
-        <v>295.31922558190735</v>
+        <v>527.44848402507967</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9398,16 +9398,16 @@
         <v>425</v>
       </c>
       <c r="Y15" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="Z15" t="s">
         <v>579</v>
       </c>
       <c r="AA15">
-        <v>0.99701127670202949</v>
+        <v>0.99066346416517681</v>
       </c>
       <c r="AB15">
-        <v>54.793260462791778</v>
+        <v>171.16982363842584</v>
       </c>
       <c r="AD15" t="s">
         <v>414</v>
@@ -9440,10 +9440,10 @@
         <v>796</v>
       </c>
       <c r="AO15">
-        <v>0.99684527597966854</v>
+        <v>0.99715437961127318</v>
       </c>
       <c r="AP15">
-        <v>57.836607039410005</v>
+        <v>52.169707126657627</v>
       </c>
       <c r="AR15" t="s">
         <v>414</v>
@@ -9476,10 +9476,10 @@
         <v>975</v>
       </c>
       <c r="BC15">
-        <v>0.99308209783432144</v>
+        <v>0.98838558997012138</v>
       </c>
       <c r="BD15">
-        <v>126.82820637077275</v>
+        <v>212.93085054777492</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9544,16 +9544,16 @@
         <v>427</v>
       </c>
       <c r="Y16" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="Z16" t="s">
         <v>580</v>
       </c>
       <c r="AA16">
-        <v>0.99462937148232844</v>
+        <v>0.99560939477262078</v>
       </c>
       <c r="AB16">
-        <v>98.461522823979266</v>
+        <v>80.494429168619106</v>
       </c>
       <c r="AD16" t="s">
         <v>414</v>
@@ -9583,13 +9583,13 @@
         <v>797</v>
       </c>
       <c r="AN16" t="s">
-        <v>798</v>
+        <v>586</v>
       </c>
       <c r="AO16">
-        <v>0.9943927545810437</v>
+        <v>0.9950502580620818</v>
       </c>
       <c r="AP16">
-        <v>102.79949934753229</v>
+        <v>90.745268861833736</v>
       </c>
       <c r="AR16" t="s">
         <v>414</v>
@@ -9619,13 +9619,13 @@
         <v>976</v>
       </c>
       <c r="BB16" t="s">
-        <v>977</v>
+        <v>799</v>
       </c>
       <c r="BC16">
-        <v>0.99526782804010661</v>
+        <v>0.98730637899749651</v>
       </c>
       <c r="BD16">
-        <v>86.756485931379871</v>
+        <v>232.71638504589731</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9690,16 +9690,16 @@
         <v>429</v>
       </c>
       <c r="Y17" t="s">
-        <v>405</v>
+        <v>339</v>
       </c>
       <c r="Z17" t="s">
         <v>581</v>
       </c>
       <c r="AA17">
-        <v>0.99462643269733408</v>
+        <v>0.99544039231362502</v>
       </c>
       <c r="AB17">
-        <v>98.51540054887441</v>
+        <v>83.592807583541571</v>
       </c>
       <c r="AD17" t="s">
         <v>414</v>
@@ -9726,16 +9726,16 @@
         <v>665</v>
       </c>
       <c r="AM17" t="s">
+        <v>798</v>
+      </c>
+      <c r="AN17" t="s">
         <v>799</v>
       </c>
-      <c r="AN17" t="s">
-        <v>800</v>
-      </c>
       <c r="AO17">
-        <v>0.99074948308423383</v>
+        <v>0.99418244113372889</v>
       </c>
       <c r="AP17">
-        <v>169.59281012238051</v>
+        <v>106.6552458816375</v>
       </c>
       <c r="AR17" t="s">
         <v>414</v>
@@ -9762,16 +9762,16 @@
         <v>932</v>
       </c>
       <c r="BA17" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="BB17" t="s">
-        <v>979</v>
+        <v>643</v>
       </c>
       <c r="BC17">
-        <v>0.98605138538291048</v>
+        <v>0.98809190602642238</v>
       </c>
       <c r="BD17">
-        <v>255.7246013133088</v>
+        <v>218.31505618225569</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9836,16 +9836,16 @@
         <v>431</v>
       </c>
       <c r="Y18" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="Z18" t="s">
         <v>582</v>
       </c>
       <c r="AA18">
-        <v>0.99755789282691543</v>
+        <v>0.99190124970484694</v>
       </c>
       <c r="AB18">
-        <v>44.77196483988353</v>
+        <v>148.47708874447352</v>
       </c>
       <c r="AD18" t="s">
         <v>414</v>
@@ -9872,16 +9872,16 @@
         <v>667</v>
       </c>
       <c r="AM18" t="s">
+        <v>800</v>
+      </c>
+      <c r="AN18" t="s">
         <v>801</v>
       </c>
-      <c r="AN18" t="s">
-        <v>802</v>
-      </c>
       <c r="AO18">
-        <v>0.99270401267208797</v>
+        <v>0.99206751173516827</v>
       </c>
       <c r="AP18">
-        <v>133.75976767838793</v>
+        <v>145.42895152191466</v>
       </c>
       <c r="AR18" t="s">
         <v>414</v>
@@ -9908,16 +9908,16 @@
         <v>934</v>
       </c>
       <c r="BA18" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="BB18" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="BC18">
-        <v>0.99307601382667698</v>
+        <v>0.994208528887633</v>
       </c>
       <c r="BD18">
-        <v>126.93974651092147</v>
+        <v>106.17697039339514</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9982,16 +9982,16 @@
         <v>433</v>
       </c>
       <c r="Y19" t="s">
-        <v>377</v>
+        <v>412</v>
       </c>
       <c r="Z19" t="s">
         <v>583</v>
       </c>
       <c r="AA19">
-        <v>0.99246356041150996</v>
+        <v>0.9940089461809174</v>
       </c>
       <c r="AB19">
-        <v>138.16805912231732</v>
+        <v>109.83598668318054</v>
       </c>
       <c r="AD19" t="s">
         <v>414</v>
@@ -10018,16 +10018,16 @@
         <v>669</v>
       </c>
       <c r="AM19" t="s">
+        <v>802</v>
+      </c>
+      <c r="AN19" t="s">
         <v>803</v>
       </c>
-      <c r="AN19" t="s">
-        <v>804</v>
-      </c>
       <c r="AO19">
-        <v>0.99764772442226368</v>
+        <v>0.99566554346996428</v>
       </c>
       <c r="AP19">
-        <v>43.125052258499352</v>
+        <v>79.46503638398778</v>
       </c>
       <c r="AR19" t="s">
         <v>414</v>
@@ -10054,16 +10054,16 @@
         <v>936</v>
       </c>
       <c r="BA19" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="BB19" t="s">
-        <v>983</v>
+        <v>635</v>
       </c>
       <c r="BC19">
-        <v>0.99275904397179515</v>
+        <v>0.99603877136023145</v>
       </c>
       <c r="BD19">
-        <v>132.75086051708826</v>
+        <v>72.622525062424401</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -10128,16 +10128,16 @@
         <v>435</v>
       </c>
       <c r="Y20" t="s">
-        <v>359</v>
+        <v>393</v>
       </c>
       <c r="Z20" t="s">
         <v>584</v>
       </c>
       <c r="AA20">
-        <v>0.99699505644961572</v>
+        <v>0.99600761890991041</v>
       </c>
       <c r="AB20">
-        <v>55.090631757044932</v>
+        <v>73.193653318309615</v>
       </c>
       <c r="AD20" t="s">
         <v>414</v>
@@ -10164,16 +10164,16 @@
         <v>671</v>
       </c>
       <c r="AM20" t="s">
+        <v>804</v>
+      </c>
+      <c r="AN20" t="s">
         <v>805</v>
       </c>
-      <c r="AN20" t="s">
-        <v>806</v>
-      </c>
       <c r="AO20">
-        <v>0.99703044337128366</v>
+        <v>0.99667664296701652</v>
       </c>
       <c r="AP20">
-        <v>54.441871526466279</v>
+        <v>60.928212271363194</v>
       </c>
       <c r="AR20" t="s">
         <v>414</v>
@@ -10200,16 +10200,16 @@
         <v>938</v>
       </c>
       <c r="BA20" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="BB20" t="s">
-        <v>592</v>
+        <v>982</v>
       </c>
       <c r="BC20">
-        <v>0.97123008268954114</v>
+        <v>0.96206044130113966</v>
       </c>
       <c r="BD20">
-        <v>527.44848402507967</v>
+        <v>695.55857614577315</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -10274,16 +10274,16 @@
         <v>437</v>
       </c>
       <c r="Y21" t="s">
-        <v>373</v>
+        <v>352</v>
       </c>
       <c r="Z21" t="s">
         <v>585</v>
       </c>
       <c r="AA21">
-        <v>0.99170691261633115</v>
+        <v>0.99700029739711071</v>
       </c>
       <c r="AB21">
-        <v>152.03993536726261</v>
+        <v>54.994547719637801</v>
       </c>
       <c r="AD21" t="s">
         <v>414</v>
@@ -10310,16 +10310,16 @@
         <v>673</v>
       </c>
       <c r="AM21" t="s">
+        <v>806</v>
+      </c>
+      <c r="AN21" t="s">
         <v>807</v>
       </c>
-      <c r="AN21" t="s">
-        <v>808</v>
-      </c>
       <c r="AO21">
-        <v>0.99439150850611324</v>
+        <v>0.99608442334318104</v>
       </c>
       <c r="AP21">
-        <v>102.82234405458999</v>
+        <v>71.785572041680055</v>
       </c>
       <c r="AR21" t="s">
         <v>414</v>
@@ -10346,16 +10346,16 @@
         <v>940</v>
       </c>
       <c r="BA21" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="BB21" t="s">
-        <v>845</v>
+        <v>984</v>
       </c>
       <c r="BC21">
-        <v>0.98154438143849254</v>
+        <v>0.98742179529179352</v>
       </c>
       <c r="BD21">
-        <v>338.35300696097039</v>
+        <v>230.6004196504513</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -10420,16 +10420,16 @@
         <v>439</v>
       </c>
       <c r="Y22" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="Z22" t="s">
         <v>586</v>
       </c>
       <c r="AA22">
-        <v>0.9904035062850528</v>
+        <v>0.99408511741207395</v>
       </c>
       <c r="AB22">
-        <v>175.93571810736526</v>
+        <v>108.43951411197776</v>
       </c>
       <c r="AD22" t="s">
         <v>414</v>
@@ -10456,16 +10456,16 @@
         <v>675</v>
       </c>
       <c r="AM22" t="s">
+        <v>808</v>
+      </c>
+      <c r="AN22" t="s">
         <v>809</v>
       </c>
-      <c r="AN22" t="s">
-        <v>810</v>
-      </c>
       <c r="AO22">
-        <v>0.99595416313893737</v>
+        <v>0.9967907157363165</v>
       </c>
       <c r="AP22">
-        <v>74.173675786148877</v>
+        <v>58.836878167530941</v>
       </c>
       <c r="AR22" t="s">
         <v>414</v>
@@ -10492,16 +10492,16 @@
         <v>942</v>
       </c>
       <c r="BA22" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="BB22" t="s">
-        <v>987</v>
+        <v>827</v>
       </c>
       <c r="BC22">
-        <v>0.98838558997012138</v>
+        <v>0.98389167860462323</v>
       </c>
       <c r="BD22">
-        <v>212.93085054777492</v>
+        <v>295.31922558190735</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10566,16 +10566,16 @@
         <v>441</v>
       </c>
       <c r="Y23" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="Z23" t="s">
         <v>587</v>
       </c>
       <c r="AA23">
-        <v>0.99540885392130762</v>
+        <v>0.99529948277209723</v>
       </c>
       <c r="AB23">
-        <v>84.171011442693441</v>
+        <v>86.176149178218239</v>
       </c>
       <c r="AD23" t="s">
         <v>414</v>
@@ -10602,16 +10602,16 @@
         <v>677</v>
       </c>
       <c r="AM23" t="s">
+        <v>810</v>
+      </c>
+      <c r="AN23" t="s">
         <v>811</v>
       </c>
-      <c r="AN23" t="s">
-        <v>812</v>
-      </c>
       <c r="AO23">
-        <v>0.99687821505939955</v>
+        <v>0.99443964677468366</v>
       </c>
       <c r="AP23">
-        <v>57.232723911007447</v>
+        <v>101.93980913079895</v>
       </c>
       <c r="AR23" t="s">
         <v>414</v>
@@ -10638,16 +10638,16 @@
         <v>944</v>
       </c>
       <c r="BA23" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="BB23" t="s">
-        <v>845</v>
+        <v>987</v>
       </c>
       <c r="BC23">
-        <v>0.98730637899749651</v>
+        <v>0.98787195157138663</v>
       </c>
       <c r="BD23">
-        <v>232.71638504589731</v>
+        <v>222.34755452457901</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10712,16 +10712,16 @@
         <v>443</v>
       </c>
       <c r="Y24" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="Z24" t="s">
         <v>588</v>
       </c>
       <c r="AA24">
-        <v>0.99360802526828129</v>
+        <v>0.99478609753984348</v>
       </c>
       <c r="AB24">
-        <v>117.18620341484296</v>
+        <v>95.588211769535249</v>
       </c>
       <c r="AD24" t="s">
         <v>414</v>
@@ -10748,16 +10748,16 @@
         <v>679</v>
       </c>
       <c r="AM24" t="s">
+        <v>812</v>
+      </c>
+      <c r="AN24" t="s">
         <v>813</v>
       </c>
-      <c r="AN24" t="s">
-        <v>814</v>
-      </c>
       <c r="AO24">
-        <v>0.99568571110966864</v>
+        <v>0.99761003390352465</v>
       </c>
       <c r="AP24">
-        <v>79.095296322741547</v>
+        <v>43.816045102048356</v>
       </c>
       <c r="AR24" t="s">
         <v>414</v>
@@ -10784,16 +10784,16 @@
         <v>946</v>
       </c>
       <c r="BA24" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="BB24" t="s">
-        <v>592</v>
+        <v>799</v>
       </c>
       <c r="BC24">
-        <v>0.98809190602642238</v>
+        <v>0.98853599644984702</v>
       </c>
       <c r="BD24">
-        <v>218.31505618225569</v>
+        <v>210.17339841947171</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10858,16 +10858,16 @@
         <v>445</v>
       </c>
       <c r="Y25" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
       <c r="Z25" t="s">
         <v>589</v>
       </c>
       <c r="AA25">
-        <v>0.99515679011930902</v>
+        <v>0.99568525132868968</v>
       </c>
       <c r="AB25">
-        <v>88.792181146001369</v>
+        <v>79.10372564068922</v>
       </c>
       <c r="AD25" t="s">
         <v>414</v>
@@ -10894,16 +10894,16 @@
         <v>681</v>
       </c>
       <c r="AM25" t="s">
+        <v>814</v>
+      </c>
+      <c r="AN25" t="s">
         <v>815</v>
       </c>
-      <c r="AN25" t="s">
-        <v>816</v>
-      </c>
       <c r="AO25">
-        <v>0.99609062270337045</v>
+        <v>0.99777413567568085</v>
       </c>
       <c r="AP25">
-        <v>71.671917104874566</v>
+        <v>40.807512612516987</v>
       </c>
       <c r="AR25" t="s">
         <v>414</v>
@@ -10930,16 +10930,16 @@
         <v>948</v>
       </c>
       <c r="BA25" t="s">
+        <v>989</v>
+      </c>
+      <c r="BB25" t="s">
         <v>990</v>
       </c>
-      <c r="BB25" t="s">
-        <v>991</v>
-      </c>
       <c r="BC25">
-        <v>0.994208528887633</v>
+        <v>0.99307601382667698</v>
       </c>
       <c r="BD25">
-        <v>106.17697039339514</v>
+        <v>126.93974651092147</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -11004,16 +11004,16 @@
         <v>447</v>
       </c>
       <c r="Y26" t="s">
-        <v>387</v>
+        <v>342</v>
       </c>
       <c r="Z26" t="s">
         <v>590</v>
       </c>
       <c r="AA26">
-        <v>0.99409145347725225</v>
+        <v>0.99590266392783655</v>
       </c>
       <c r="AB26">
-        <v>108.32335291704148</v>
+        <v>75.117827989662302</v>
       </c>
       <c r="AD26" t="s">
         <v>414</v>
@@ -11040,16 +11040,16 @@
         <v>683</v>
       </c>
       <c r="AM26" t="s">
+        <v>816</v>
+      </c>
+      <c r="AN26" t="s">
         <v>817</v>
       </c>
-      <c r="AN26" t="s">
-        <v>818</v>
-      </c>
       <c r="AO26">
-        <v>0.99598588086244633</v>
+        <v>0.99425851119451991</v>
       </c>
       <c r="AP26">
-        <v>73.592184188484865</v>
+        <v>105.26062810046888</v>
       </c>
       <c r="AR26" t="s">
         <v>414</v>
@@ -11076,16 +11076,16 @@
         <v>950</v>
       </c>
       <c r="BA26" t="s">
+        <v>991</v>
+      </c>
+      <c r="BB26" t="s">
         <v>992</v>
       </c>
-      <c r="BB26" t="s">
-        <v>993</v>
-      </c>
       <c r="BC26">
-        <v>0.98787195157138663</v>
+        <v>0.99275904397179515</v>
       </c>
       <c r="BD26">
-        <v>222.34755452457901</v>
+        <v>132.75086051708826</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -11150,16 +11150,16 @@
         <v>449</v>
       </c>
       <c r="Y27" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="Z27" t="s">
         <v>591</v>
       </c>
       <c r="AA27">
-        <v>0.99464051280908794</v>
+        <v>0.99449671322390631</v>
       </c>
       <c r="AB27">
-        <v>98.257265166721183</v>
+        <v>100.89359089505045</v>
       </c>
       <c r="AD27" t="s">
         <v>414</v>
@@ -11186,16 +11186,16 @@
         <v>685</v>
       </c>
       <c r="AM27" t="s">
+        <v>818</v>
+      </c>
+      <c r="AN27" t="s">
         <v>819</v>
       </c>
-      <c r="AN27" t="s">
-        <v>820</v>
-      </c>
       <c r="AO27">
-        <v>0.99540934349034305</v>
+        <v>0.99712282780353001</v>
       </c>
       <c r="AP27">
-        <v>84.162036010377406</v>
+        <v>52.74815693528295</v>
       </c>
       <c r="AR27" t="s">
         <v>414</v>
@@ -11222,16 +11222,16 @@
         <v>952</v>
       </c>
       <c r="BA27" t="s">
+        <v>993</v>
+      </c>
+      <c r="BB27" t="s">
         <v>994</v>
       </c>
-      <c r="BB27" t="s">
-        <v>845</v>
-      </c>
       <c r="BC27">
-        <v>0.98853599644984702</v>
+        <v>0.98137594918937099</v>
       </c>
       <c r="BD27">
-        <v>210.17339841947171</v>
+        <v>341.44093152819772</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -11296,16 +11296,16 @@
         <v>451</v>
       </c>
       <c r="Y28" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
       <c r="Z28" t="s">
         <v>592</v>
       </c>
       <c r="AA28">
-        <v>0.99282834435956602</v>
+        <v>0.99701127670202949</v>
       </c>
       <c r="AB28">
-        <v>131.48035340795542</v>
+        <v>54.793260462791778</v>
       </c>
       <c r="AD28" t="s">
         <v>414</v>
@@ -11332,16 +11332,16 @@
         <v>687</v>
       </c>
       <c r="AM28" t="s">
+        <v>820</v>
+      </c>
+      <c r="AN28" t="s">
         <v>821</v>
       </c>
-      <c r="AN28" t="s">
-        <v>822</v>
-      </c>
       <c r="AO28">
-        <v>0.99657664224037934</v>
+        <v>0.99005506097810436</v>
       </c>
       <c r="AP28">
-        <v>62.761558926379031</v>
+        <v>182.32388206808599</v>
       </c>
       <c r="AR28" t="s">
         <v>414</v>
@@ -11371,13 +11371,13 @@
         <v>995</v>
       </c>
       <c r="BB28" t="s">
-        <v>996</v>
+        <v>984</v>
       </c>
       <c r="BC28">
-        <v>0.98734896749216872</v>
+        <v>0.9889956676941275</v>
       </c>
       <c r="BD28">
-        <v>231.9355959769062</v>
+        <v>201.74609227432916</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11442,16 +11442,16 @@
         <v>453</v>
       </c>
       <c r="Y29" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="Z29" t="s">
         <v>593</v>
       </c>
       <c r="AA29">
-        <v>0.99569310304523451</v>
+        <v>0.99125780375299366</v>
       </c>
       <c r="AB29">
-        <v>78.959777504033639</v>
+        <v>160.27359786178269</v>
       </c>
       <c r="AD29" t="s">
         <v>414</v>
@@ -11478,16 +11478,16 @@
         <v>689</v>
       </c>
       <c r="AM29" t="s">
+        <v>822</v>
+      </c>
+      <c r="AN29" t="s">
         <v>823</v>
       </c>
-      <c r="AN29" t="s">
-        <v>824</v>
-      </c>
       <c r="AO29">
-        <v>0.99091245964276031</v>
+        <v>0.99631269816920021</v>
       </c>
       <c r="AP29">
-        <v>166.60490654939525</v>
+        <v>67.600533564663479</v>
       </c>
       <c r="AR29" t="s">
         <v>414</v>
@@ -11514,16 +11514,16 @@
         <v>956</v>
       </c>
       <c r="BA29" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="BB29" t="s">
-        <v>998</v>
+        <v>635</v>
       </c>
       <c r="BC29">
-        <v>0.98158890816872557</v>
+        <v>0.99193721244794397</v>
       </c>
       <c r="BD29">
-        <v>337.53668357336363</v>
+        <v>147.81777178769397</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11588,16 +11588,16 @@
         <v>455</v>
       </c>
       <c r="Y30" t="s">
-        <v>411</v>
+        <v>348</v>
       </c>
       <c r="Z30" t="s">
         <v>594</v>
       </c>
       <c r="AA30">
-        <v>0.99502431999137919</v>
+        <v>0.99619006668481902</v>
       </c>
       <c r="AB30">
-        <v>91.220800158047325</v>
+        <v>69.848777444984194</v>
       </c>
       <c r="AD30" t="s">
         <v>414</v>
@@ -11624,16 +11624,16 @@
         <v>691</v>
       </c>
       <c r="AM30" t="s">
+        <v>824</v>
+      </c>
+      <c r="AN30" t="s">
         <v>825</v>
       </c>
-      <c r="AN30" t="s">
-        <v>826</v>
-      </c>
       <c r="AO30">
-        <v>0.99846230399777702</v>
+        <v>0.99772400077475298</v>
       </c>
       <c r="AP30">
-        <v>28.191093374087806</v>
+        <v>41.726652462862774</v>
       </c>
       <c r="AR30" t="s">
         <v>414</v>
@@ -11660,16 +11660,16 @@
         <v>958</v>
       </c>
       <c r="BA30" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="BB30" t="s">
-        <v>592</v>
+        <v>998</v>
       </c>
       <c r="BC30">
-        <v>0.98402494782096717</v>
+        <v>0.98158890816872557</v>
       </c>
       <c r="BD30">
-        <v>292.87595661560192</v>
+        <v>337.53668357336363</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11734,16 +11734,16 @@
         <v>457</v>
       </c>
       <c r="Y31" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="Z31" t="s">
         <v>595</v>
       </c>
       <c r="AA31">
-        <v>0.99584577617815018</v>
+        <v>0.99021813732178554</v>
       </c>
       <c r="AB31">
-        <v>76.16077006724673</v>
+        <v>179.3341491005981</v>
       </c>
       <c r="AD31" t="s">
         <v>414</v>
@@ -11770,16 +11770,16 @@
         <v>693</v>
       </c>
       <c r="AM31" t="s">
+        <v>826</v>
+      </c>
+      <c r="AN31" t="s">
         <v>827</v>
       </c>
-      <c r="AN31" t="s">
-        <v>828</v>
-      </c>
       <c r="AO31">
-        <v>0.99611612132862803</v>
+        <v>0.99604673274056554</v>
       </c>
       <c r="AP31">
-        <v>71.204442308486065</v>
+        <v>72.476566422965192</v>
       </c>
       <c r="AR31" t="s">
         <v>414</v>
@@ -11806,16 +11806,16 @@
         <v>960</v>
       </c>
       <c r="BA31" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="BB31" t="s">
-        <v>1001</v>
+        <v>643</v>
       </c>
       <c r="BC31">
-        <v>0.99223982078870177</v>
+        <v>0.98402494782096717</v>
       </c>
       <c r="BD31">
-        <v>142.26995220713331</v>
+        <v>292.87595661560192</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11880,16 +11880,16 @@
         <v>459</v>
       </c>
       <c r="Y32" t="s">
-        <v>336</v>
+        <v>389</v>
       </c>
       <c r="Z32" t="s">
         <v>596</v>
       </c>
       <c r="AA32">
-        <v>0.99359748433922845</v>
+        <v>0.99686736582623381</v>
       </c>
       <c r="AB32">
-        <v>117.37945378081078</v>
+        <v>57.431626519047455</v>
       </c>
       <c r="AD32" t="s">
         <v>414</v>
@@ -11916,16 +11916,16 @@
         <v>695</v>
       </c>
       <c r="AM32" t="s">
+        <v>828</v>
+      </c>
+      <c r="AN32" t="s">
         <v>829</v>
       </c>
-      <c r="AN32" t="s">
-        <v>830</v>
-      </c>
       <c r="AO32">
-        <v>0.99761105057437038</v>
+        <v>0.99533901157332205</v>
       </c>
       <c r="AP32">
-        <v>43.797406136543607</v>
+        <v>85.451454489096079</v>
       </c>
       <c r="AR32" t="s">
         <v>414</v>
@@ -11952,16 +11952,16 @@
         <v>962</v>
       </c>
       <c r="BA32" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="BB32" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="BC32">
-        <v>0.96206044130113966</v>
+        <v>0.99223982078870177</v>
       </c>
       <c r="BD32">
-        <v>695.55857614577315</v>
+        <v>142.26995220713331</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -12026,16 +12026,16 @@
         <v>461</v>
       </c>
       <c r="Y33" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="Z33" t="s">
         <v>597</v>
       </c>
       <c r="AA33">
-        <v>0.99592552983543692</v>
+        <v>0.99725672762159434</v>
       </c>
       <c r="AB33">
-        <v>74.698619683656872</v>
+        <v>50.29332693743671</v>
       </c>
       <c r="AD33" t="s">
         <v>414</v>
@@ -12062,16 +12062,16 @@
         <v>697</v>
       </c>
       <c r="AM33" t="s">
+        <v>830</v>
+      </c>
+      <c r="AN33" t="s">
         <v>831</v>
       </c>
-      <c r="AN33" t="s">
-        <v>832</v>
-      </c>
       <c r="AO33">
-        <v>0.99615289372526561</v>
+        <v>0.99754339130519476</v>
       </c>
       <c r="AP33">
-        <v>70.530281703464368</v>
+        <v>45.037826071429087</v>
       </c>
       <c r="AR33" t="s">
         <v>414</v>
@@ -12098,16 +12098,16 @@
         <v>964</v>
       </c>
       <c r="BA33" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="BB33" t="s">
-        <v>971</v>
+        <v>1003</v>
       </c>
       <c r="BC33">
-        <v>0.98742179529179352</v>
+        <v>0.98734896749216872</v>
       </c>
       <c r="BD33">
-        <v>230.6004196504513</v>
+        <v>231.9355959769062</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -12172,16 +12172,16 @@
         <v>463</v>
       </c>
       <c r="Y34" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="Z34" t="s">
         <v>598</v>
       </c>
       <c r="AA34">
-        <v>0.99463677905825021</v>
+        <v>0.99569491323214321</v>
       </c>
       <c r="AB34">
-        <v>98.325717265413417</v>
+        <v>78.926590744041093</v>
       </c>
       <c r="AD34" t="s">
         <v>414</v>
@@ -12208,16 +12208,16 @@
         <v>699</v>
       </c>
       <c r="AM34" t="s">
+        <v>832</v>
+      </c>
+      <c r="AN34" t="s">
         <v>833</v>
       </c>
-      <c r="AN34" t="s">
-        <v>834</v>
-      </c>
       <c r="AO34">
-        <v>0.99245794727704639</v>
+        <v>0.99542398891280204</v>
       </c>
       <c r="AP34">
-        <v>138.27096658748206</v>
+        <v>83.893536598629126</v>
       </c>
       <c r="AR34" t="s">
         <v>414</v>
@@ -12244,16 +12244,16 @@
         <v>966</v>
       </c>
       <c r="BA34" t="s">
+        <v>1004</v>
+      </c>
+      <c r="BB34" t="s">
         <v>1005</v>
       </c>
-      <c r="BB34" t="s">
-        <v>597</v>
-      </c>
       <c r="BC34">
-        <v>0.99603877136023145</v>
+        <v>0.99308209783432144</v>
       </c>
       <c r="BD34">
-        <v>72.622525062424401</v>
+        <v>126.82820637077275</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -12318,16 +12318,16 @@
         <v>465</v>
       </c>
       <c r="Y35" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="Z35" t="s">
         <v>599</v>
       </c>
       <c r="AA35">
-        <v>0.99667564038633161</v>
+        <v>0.99484118006716937</v>
       </c>
       <c r="AB35">
-        <v>60.946592917253042</v>
+        <v>94.578365435227795</v>
       </c>
       <c r="AD35" t="s">
         <v>414</v>
@@ -12354,16 +12354,16 @@
         <v>701</v>
       </c>
       <c r="AM35" t="s">
+        <v>834</v>
+      </c>
+      <c r="AN35" t="s">
         <v>835</v>
       </c>
-      <c r="AN35" t="s">
-        <v>836</v>
-      </c>
       <c r="AO35">
-        <v>0.99381230463557813</v>
+        <v>0.99617615910816915</v>
       </c>
       <c r="AP35">
-        <v>113.44108168106689</v>
+        <v>70.103749683564772</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -12428,16 +12428,16 @@
         <v>467</v>
       </c>
       <c r="Y36" t="s">
-        <v>338</v>
+        <v>370</v>
       </c>
       <c r="Z36" t="s">
         <v>600</v>
       </c>
       <c r="AA36">
-        <v>0.99080344458411729</v>
+        <v>0.99539558382203508</v>
       </c>
       <c r="AB36">
-        <v>168.60351595784994</v>
+        <v>84.414296596023817</v>
       </c>
       <c r="AD36" t="s">
         <v>414</v>
@@ -12464,16 +12464,16 @@
         <v>703</v>
       </c>
       <c r="AM36" t="s">
+        <v>836</v>
+      </c>
+      <c r="AN36" t="s">
         <v>837</v>
       </c>
-      <c r="AN36" t="s">
-        <v>838</v>
-      </c>
       <c r="AO36">
-        <v>0.99534539864304916</v>
+        <v>0.99660391553167893</v>
       </c>
       <c r="AP36">
-        <v>85.3343582107656</v>
+        <v>62.261548585886977</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -12538,16 +12538,16 @@
         <v>469</v>
       </c>
       <c r="Y37" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="Z37" t="s">
         <v>601</v>
       </c>
       <c r="AA37">
-        <v>0.98636012609964985</v>
+        <v>0.99557960200072415</v>
       </c>
       <c r="AB37">
-        <v>250.06435483975247</v>
+        <v>81.040629986723459</v>
       </c>
       <c r="AD37" t="s">
         <v>414</v>
@@ -12574,16 +12574,16 @@
         <v>705</v>
       </c>
       <c r="AM37" t="s">
+        <v>838</v>
+      </c>
+      <c r="AN37" t="s">
         <v>839</v>
       </c>
-      <c r="AN37" t="s">
-        <v>840</v>
-      </c>
       <c r="AO37">
-        <v>0.99310873310996184</v>
+        <v>0.9959136876641268</v>
       </c>
       <c r="AP37">
-        <v>126.33989298403215</v>
+        <v>74.915726157675209</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12648,16 +12648,16 @@
         <v>471</v>
       </c>
       <c r="Y38" t="s">
-        <v>343</v>
+        <v>398</v>
       </c>
       <c r="Z38" t="s">
         <v>602</v>
       </c>
       <c r="AA38">
-        <v>0.99598850450039844</v>
+        <v>0.99295357769237991</v>
       </c>
       <c r="AB38">
-        <v>73.544084159361034</v>
+        <v>129.18440897303603</v>
       </c>
       <c r="AD38" t="s">
         <v>414</v>
@@ -12684,16 +12684,16 @@
         <v>707</v>
       </c>
       <c r="AM38" t="s">
+        <v>840</v>
+      </c>
+      <c r="AN38" t="s">
         <v>841</v>
       </c>
-      <c r="AN38" t="s">
-        <v>842</v>
-      </c>
       <c r="AO38">
-        <v>0.99715437961127318</v>
+        <v>0.9935275292913992</v>
       </c>
       <c r="AP38">
-        <v>52.169707126657627</v>
+        <v>118.66196299101547</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12758,16 +12758,16 @@
         <v>473</v>
       </c>
       <c r="Y39" t="s">
-        <v>409</v>
+        <v>355</v>
       </c>
       <c r="Z39" t="s">
         <v>603</v>
       </c>
       <c r="AA39">
-        <v>0.99310312827752323</v>
+        <v>0.99696751363483405</v>
       </c>
       <c r="AB39">
-        <v>126.44264824540761</v>
+        <v>55.595583361375894</v>
       </c>
       <c r="AD39" t="s">
         <v>414</v>
@@ -12794,16 +12794,16 @@
         <v>709</v>
       </c>
       <c r="AM39" t="s">
+        <v>842</v>
+      </c>
+      <c r="AN39" t="s">
         <v>843</v>
       </c>
-      <c r="AN39" t="s">
-        <v>618</v>
-      </c>
       <c r="AO39">
-        <v>0.9950502580620818</v>
+        <v>0.99687120387267125</v>
       </c>
       <c r="AP39">
-        <v>90.745268861833736</v>
+        <v>57.361262334360205</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12868,16 +12868,16 @@
         <v>475</v>
       </c>
       <c r="Y40" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="Z40" t="s">
         <v>604</v>
       </c>
       <c r="AA40">
-        <v>0.99675394464629852</v>
+        <v>0.98964014500078279</v>
       </c>
       <c r="AB40">
-        <v>59.511014817860868</v>
+        <v>189.93067498564957</v>
       </c>
       <c r="AD40" t="s">
         <v>414</v>
@@ -12910,10 +12910,10 @@
         <v>845</v>
       </c>
       <c r="AO40">
-        <v>0.99418244113372889</v>
+        <v>0.99568571110966864</v>
       </c>
       <c r="AP40">
-        <v>106.6552458816375</v>
+        <v>79.095296322741547</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12978,16 +12978,16 @@
         <v>477</v>
       </c>
       <c r="Y41" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="Z41" t="s">
         <v>605</v>
       </c>
       <c r="AA41">
-        <v>0.9962437778559039</v>
+        <v>0.9966137462997855</v>
       </c>
       <c r="AB41">
-        <v>68.86407264176249</v>
+        <v>62.081317837266766</v>
       </c>
       <c r="AD41" t="s">
         <v>414</v>
@@ -13020,10 +13020,10 @@
         <v>847</v>
       </c>
       <c r="AO41">
-        <v>0.99206751173516827</v>
+        <v>0.99609062270337045</v>
       </c>
       <c r="AP41">
-        <v>145.42895152191466</v>
+        <v>71.671917104874566</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -13088,16 +13088,16 @@
         <v>479</v>
       </c>
       <c r="Y42" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="Z42" t="s">
         <v>606</v>
       </c>
       <c r="AA42">
-        <v>0.99617006411660358</v>
+        <v>0.99011796851295664</v>
       </c>
       <c r="AB42">
-        <v>70.215491195600634</v>
+        <v>181.17057726246117</v>
       </c>
       <c r="AD42" t="s">
         <v>414</v>
@@ -13130,10 +13130,10 @@
         <v>849</v>
       </c>
       <c r="AO42">
-        <v>0.99566554346996428</v>
+        <v>0.99598588086244633</v>
       </c>
       <c r="AP42">
-        <v>79.46503638398778</v>
+        <v>73.592184188484865</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -13198,16 +13198,16 @@
         <v>481</v>
       </c>
       <c r="Y43" t="s">
-        <v>349</v>
+        <v>391</v>
       </c>
       <c r="Z43" t="s">
         <v>607</v>
       </c>
       <c r="AA43">
-        <v>0.99569491323214321</v>
+        <v>0.99635118654529808</v>
       </c>
       <c r="AB43">
-        <v>78.926590744041093</v>
+        <v>66.894913336202478</v>
       </c>
       <c r="AD43" t="s">
         <v>414</v>
@@ -13240,10 +13240,10 @@
         <v>851</v>
       </c>
       <c r="AO43">
-        <v>0.99667664296701652</v>
+        <v>0.99074948308423383</v>
       </c>
       <c r="AP43">
-        <v>60.928212271363194</v>
+        <v>169.59281012238051</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -13308,16 +13308,16 @@
         <v>483</v>
       </c>
       <c r="Y44" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="Z44" t="s">
         <v>608</v>
       </c>
       <c r="AA44">
-        <v>0.99484118006716937</v>
+        <v>0.99440507690252466</v>
       </c>
       <c r="AB44">
-        <v>94.578365435227795</v>
+        <v>102.57359012038077</v>
       </c>
       <c r="AD44" t="s">
         <v>414</v>
@@ -13350,10 +13350,10 @@
         <v>853</v>
       </c>
       <c r="AO44">
-        <v>0.99608442334318104</v>
+        <v>0.99270401267208797</v>
       </c>
       <c r="AP44">
-        <v>71.785572041680055</v>
+        <v>133.75976767838793</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -13418,16 +13418,16 @@
         <v>485</v>
       </c>
       <c r="Y45" t="s">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="Z45" t="s">
         <v>609</v>
       </c>
       <c r="AA45">
-        <v>0.99539558382203508</v>
+        <v>0.99675394464629852</v>
       </c>
       <c r="AB45">
-        <v>84.414296596023817</v>
+        <v>59.511014817860868</v>
       </c>
       <c r="AD45" t="s">
         <v>414</v>
@@ -13460,10 +13460,10 @@
         <v>855</v>
       </c>
       <c r="AO45">
-        <v>0.9967907157363165</v>
+        <v>0.99764772442226368</v>
       </c>
       <c r="AP45">
-        <v>58.836878167530941</v>
+        <v>43.125052258499352</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13528,16 +13528,16 @@
         <v>487</v>
       </c>
       <c r="Y46" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="Z46" t="s">
         <v>610</v>
       </c>
       <c r="AA46">
-        <v>0.99579357955795456</v>
+        <v>0.9962437778559039</v>
       </c>
       <c r="AB46">
-        <v>77.117708104165573</v>
+        <v>68.86407264176249</v>
       </c>
       <c r="AD46" t="s">
         <v>414</v>
@@ -13570,10 +13570,10 @@
         <v>857</v>
       </c>
       <c r="AO46">
-        <v>0.99443964677468366</v>
+        <v>0.99703044337128366</v>
       </c>
       <c r="AP46">
-        <v>101.93980913079895</v>
+        <v>54.441871526466279</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13638,16 +13638,16 @@
         <v>489</v>
       </c>
       <c r="Y47" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="Z47" t="s">
         <v>611</v>
       </c>
       <c r="AA47">
-        <v>0.99066346416517681</v>
+        <v>0.99617006411660358</v>
       </c>
       <c r="AB47">
-        <v>171.16982363842584</v>
+        <v>70.215491195600634</v>
       </c>
       <c r="AD47" t="s">
         <v>414</v>
@@ -13680,10 +13680,10 @@
         <v>859</v>
       </c>
       <c r="AO47">
-        <v>0.99761003390352465</v>
+        <v>0.99618121233373258</v>
       </c>
       <c r="AP47">
-        <v>43.816045102048356</v>
+        <v>70.011107214903078</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13748,16 +13748,16 @@
         <v>491</v>
       </c>
       <c r="Y48" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="Z48" t="s">
         <v>612</v>
       </c>
       <c r="AA48">
-        <v>0.99560939477262078</v>
+        <v>0.99462937148232844</v>
       </c>
       <c r="AB48">
-        <v>80.494429168619106</v>
+        <v>98.461522823979266</v>
       </c>
       <c r="AD48" t="s">
         <v>414</v>
@@ -13790,10 +13790,10 @@
         <v>861</v>
       </c>
       <c r="AO48">
-        <v>0.99777413567568085</v>
+        <v>0.99592364356186902</v>
       </c>
       <c r="AP48">
-        <v>40.807512612516987</v>
+        <v>74.733201365734146</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -13858,16 +13858,16 @@
         <v>493</v>
       </c>
       <c r="Y49" t="s">
-        <v>339</v>
+        <v>405</v>
       </c>
       <c r="Z49" t="s">
         <v>613</v>
       </c>
       <c r="AA49">
-        <v>0.99544039231362502</v>
+        <v>0.99462643269733408</v>
       </c>
       <c r="AB49">
-        <v>83.592807583541571</v>
+        <v>98.51540054887441</v>
       </c>
       <c r="AD49" t="s">
         <v>414</v>
@@ -13900,10 +13900,10 @@
         <v>863</v>
       </c>
       <c r="AO49">
-        <v>0.99425851119451991</v>
+        <v>0.99641167752379312</v>
       </c>
       <c r="AP49">
-        <v>105.26062810046888</v>
+        <v>65.785912063792665</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -13968,16 +13968,16 @@
         <v>495</v>
       </c>
       <c r="Y50" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="Z50" t="s">
         <v>614</v>
       </c>
       <c r="AA50">
-        <v>0.99190124970484694</v>
+        <v>0.99755789282691543</v>
       </c>
       <c r="AB50">
-        <v>148.47708874447352</v>
+        <v>44.77196483988353</v>
       </c>
       <c r="AD50" t="s">
         <v>414</v>
@@ -14010,10 +14010,10 @@
         <v>865</v>
       </c>
       <c r="AO50">
-        <v>0.99712282780353001</v>
+        <v>0.99611612132862803</v>
       </c>
       <c r="AP50">
-        <v>52.74815693528295</v>
+        <v>71.204442308486065</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -14078,16 +14078,16 @@
         <v>497</v>
       </c>
       <c r="Y51" t="s">
-        <v>412</v>
+        <v>377</v>
       </c>
       <c r="Z51" t="s">
         <v>615</v>
       </c>
       <c r="AA51">
-        <v>0.9940089461809174</v>
+        <v>0.99246356041150996</v>
       </c>
       <c r="AB51">
-        <v>109.83598668318054</v>
+        <v>138.16805912231732</v>
       </c>
       <c r="AD51" t="s">
         <v>414</v>
@@ -14120,10 +14120,10 @@
         <v>867</v>
       </c>
       <c r="AO51">
-        <v>0.99005506097810436</v>
+        <v>0.99761105057437038</v>
       </c>
       <c r="AP51">
-        <v>182.32388206808599</v>
+        <v>43.797406136543607</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -14188,16 +14188,16 @@
         <v>499</v>
       </c>
       <c r="Y52" t="s">
-        <v>393</v>
+        <v>341</v>
       </c>
       <c r="Z52" t="s">
         <v>616</v>
       </c>
       <c r="AA52">
-        <v>0.99600761890991041</v>
+        <v>0.99571525957109708</v>
       </c>
       <c r="AB52">
-        <v>73.193653318309615</v>
+        <v>78.553574529886689</v>
       </c>
       <c r="AD52" t="s">
         <v>414</v>
@@ -14230,10 +14230,10 @@
         <v>869</v>
       </c>
       <c r="AO52">
-        <v>0.99631269816920021</v>
+        <v>0.99615289372526561</v>
       </c>
       <c r="AP52">
-        <v>67.600533564663479</v>
+        <v>70.530281703464368</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -14298,16 +14298,16 @@
         <v>501</v>
       </c>
       <c r="Y53" t="s">
-        <v>352</v>
+        <v>394</v>
       </c>
       <c r="Z53" t="s">
         <v>617</v>
       </c>
       <c r="AA53">
-        <v>0.99700029739711071</v>
+        <v>0.99553579843385909</v>
       </c>
       <c r="AB53">
-        <v>54.994547719637801</v>
+        <v>81.84369537924907</v>
       </c>
       <c r="AD53" t="s">
         <v>414</v>
@@ -14340,10 +14340,10 @@
         <v>871</v>
       </c>
       <c r="AO53">
-        <v>0.99772400077475298</v>
+        <v>0.99720397512579328</v>
       </c>
       <c r="AP53">
-        <v>41.726652462862774</v>
+        <v>51.260456027123361</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -14408,16 +14408,16 @@
         <v>503</v>
       </c>
       <c r="Y54" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="Z54" t="s">
         <v>618</v>
       </c>
       <c r="AA54">
-        <v>0.99408511741207395</v>
+        <v>0.99734372305564056</v>
       </c>
       <c r="AB54">
-        <v>108.43951411197776</v>
+        <v>48.698410646589842</v>
       </c>
       <c r="AD54" t="s">
         <v>414</v>
@@ -14450,10 +14450,10 @@
         <v>873</v>
       </c>
       <c r="AO54">
-        <v>0.99604673274056554</v>
+        <v>0.99565348329230585</v>
       </c>
       <c r="AP54">
-        <v>72.476566422965192</v>
+        <v>79.686139641060379</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -14518,16 +14518,16 @@
         <v>505</v>
       </c>
       <c r="Y55" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="Z55" t="s">
         <v>619</v>
       </c>
       <c r="AA55">
-        <v>0.99529948277209723</v>
+        <v>0.99662670467221526</v>
       </c>
       <c r="AB55">
-        <v>86.176149178218239</v>
+        <v>61.843747676054292</v>
       </c>
       <c r="AD55" t="s">
         <v>414</v>
@@ -14560,10 +14560,10 @@
         <v>875</v>
       </c>
       <c r="AO55">
-        <v>0.99533901157332205</v>
+        <v>0.99368259233234391</v>
       </c>
       <c r="AP55">
-        <v>85.451454489096079</v>
+        <v>115.81914057369519</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -14628,16 +14628,16 @@
         <v>507</v>
       </c>
       <c r="Y56" t="s">
-        <v>403</v>
+        <v>361</v>
       </c>
       <c r="Z56" t="s">
         <v>620</v>
       </c>
       <c r="AA56">
-        <v>0.99670408962762203</v>
+        <v>0.99740761205901929</v>
       </c>
       <c r="AB56">
-        <v>60.425023493595695</v>
+        <v>47.527112251312907</v>
       </c>
       <c r="AD56" t="s">
         <v>414</v>
@@ -14670,10 +14670,10 @@
         <v>877</v>
       </c>
       <c r="AO56">
-        <v>0.99754339130519476</v>
+        <v>0.9954443722844073</v>
       </c>
       <c r="AP56">
-        <v>45.037826071429087</v>
+        <v>83.519841452532361</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -14738,16 +14738,16 @@
         <v>509</v>
       </c>
       <c r="Y57" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="Z57" t="s">
         <v>621</v>
       </c>
       <c r="AA57">
-        <v>0.9960389195261472</v>
+        <v>0.99730769203227776</v>
       </c>
       <c r="AB57">
-        <v>72.619808687301173</v>
+        <v>49.358979408241737</v>
       </c>
       <c r="AD57" t="s">
         <v>414</v>
@@ -14780,10 +14780,10 @@
         <v>879</v>
       </c>
       <c r="AO57">
-        <v>0.99542398891280204</v>
+        <v>0.99363040616365128</v>
       </c>
       <c r="AP57">
-        <v>83.893536598629126</v>
+        <v>116.77588699972566</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -14848,16 +14848,16 @@
         <v>511</v>
       </c>
       <c r="Y58" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="Z58" t="s">
         <v>622</v>
       </c>
       <c r="AA58">
-        <v>0.99707957985864093</v>
+        <v>0.998073964784436</v>
       </c>
       <c r="AB58">
-        <v>53.541035924916123</v>
+        <v>35.310645618673441</v>
       </c>
       <c r="AD58" t="s">
         <v>414</v>
@@ -14890,10 +14890,10 @@
         <v>881</v>
       </c>
       <c r="AO58">
-        <v>0.99617615910816915</v>
+        <v>0.99782402570187057</v>
       </c>
       <c r="AP58">
-        <v>70.103749683564772</v>
+        <v>39.892862132373601</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -14958,16 +14958,16 @@
         <v>513</v>
       </c>
       <c r="Y59" t="s">
-        <v>363</v>
+        <v>403</v>
       </c>
       <c r="Z59" t="s">
         <v>623</v>
       </c>
       <c r="AA59">
-        <v>0.99125780375299366</v>
+        <v>0.99670408962762203</v>
       </c>
       <c r="AB59">
-        <v>160.27359786178269</v>
+        <v>60.425023493595695</v>
       </c>
       <c r="AD59" t="s">
         <v>414</v>
@@ -15000,10 +15000,10 @@
         <v>883</v>
       </c>
       <c r="AO59">
-        <v>0.99660391553167893</v>
+        <v>0.99756462867082185</v>
       </c>
       <c r="AP59">
-        <v>62.261548585886977</v>
+        <v>44.648474368267038</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -15068,16 +15068,16 @@
         <v>515</v>
       </c>
       <c r="Y60" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="Z60" t="s">
         <v>624</v>
       </c>
       <c r="AA60">
-        <v>0.99619006668481902</v>
+        <v>0.9960389195261472</v>
       </c>
       <c r="AB60">
-        <v>69.848777444984194</v>
+        <v>72.619808687301173</v>
       </c>
       <c r="AD60" t="s">
         <v>414</v>
@@ -15110,10 +15110,10 @@
         <v>885</v>
       </c>
       <c r="AO60">
-        <v>0.9959136876641268</v>
+        <v>0.99540934349034305</v>
       </c>
       <c r="AP60">
-        <v>74.915726157675209</v>
+        <v>84.162036010377406</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -15178,16 +15178,16 @@
         <v>517</v>
       </c>
       <c r="Y61" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="Z61" t="s">
         <v>625</v>
       </c>
       <c r="AA61">
-        <v>0.99021813732178554</v>
+        <v>0.99707957985864093</v>
       </c>
       <c r="AB61">
-        <v>179.3341491005981</v>
+        <v>53.541035924916123</v>
       </c>
       <c r="AD61" t="s">
         <v>414</v>
@@ -15220,10 +15220,10 @@
         <v>887</v>
       </c>
       <c r="AO61">
-        <v>0.9935275292913992</v>
+        <v>0.99657664224037934</v>
       </c>
       <c r="AP61">
-        <v>118.66196299101547</v>
+        <v>62.761558926379031</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -15288,16 +15288,16 @@
         <v>519</v>
       </c>
       <c r="Y62" t="s">
-        <v>389</v>
+        <v>337</v>
       </c>
       <c r="Z62" t="s">
         <v>626</v>
       </c>
       <c r="AA62">
-        <v>0.99686736582623381</v>
+        <v>0.99551989204648861</v>
       </c>
       <c r="AB62">
-        <v>57.431626519047455</v>
+        <v>82.135312481041623</v>
       </c>
       <c r="AD62" t="s">
         <v>414</v>
@@ -15330,10 +15330,10 @@
         <v>889</v>
       </c>
       <c r="AO62">
-        <v>0.99687120387267125</v>
+        <v>0.99091245964276031</v>
       </c>
       <c r="AP62">
-        <v>57.361262334360205</v>
+        <v>166.60490654939525</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -15398,16 +15398,16 @@
         <v>521</v>
       </c>
       <c r="Y63" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="Z63" t="s">
         <v>627</v>
       </c>
       <c r="AA63">
-        <v>0.99725672762159434</v>
+        <v>0.9979392050107273</v>
       </c>
       <c r="AB63">
-        <v>50.29332693743671</v>
+        <v>37.781241469999252</v>
       </c>
       <c r="AD63" t="s">
         <v>414</v>
@@ -15440,10 +15440,10 @@
         <v>891</v>
       </c>
       <c r="AO63">
-        <v>0.99720397512579328</v>
+        <v>0.99846230399777702</v>
       </c>
       <c r="AP63">
-        <v>51.260456027123361</v>
+        <v>28.191093374087806</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -15508,16 +15508,16 @@
         <v>523</v>
       </c>
       <c r="Y64" t="s">
-        <v>396</v>
+        <v>354</v>
       </c>
       <c r="Z64" t="s">
         <v>628</v>
       </c>
       <c r="AA64">
-        <v>0.99557960200072415</v>
+        <v>0.9982033297630386</v>
       </c>
       <c r="AB64">
-        <v>81.040629986723459</v>
+        <v>32.938954344292306</v>
       </c>
       <c r="AD64" t="s">
         <v>414</v>
@@ -15550,10 +15550,10 @@
         <v>893</v>
       </c>
       <c r="AO64">
-        <v>0.99565348329230585</v>
+        <v>0.99584476105827657</v>
       </c>
       <c r="AP64">
-        <v>79.686139641060379</v>
+        <v>76.179380598263194</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -15618,16 +15618,16 @@
         <v>525</v>
       </c>
       <c r="Y65" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
       <c r="Z65" t="s">
         <v>629</v>
       </c>
       <c r="AA65">
-        <v>0.99295357769237991</v>
+        <v>0.99769372286934066</v>
       </c>
       <c r="AB65">
-        <v>129.18440897303603</v>
+        <v>42.281747395421668</v>
       </c>
       <c r="AD65" t="s">
         <v>414</v>
@@ -15660,10 +15660,10 @@
         <v>895</v>
       </c>
       <c r="AO65">
-        <v>0.99784941409648109</v>
+        <v>0.9961146125371938</v>
       </c>
       <c r="AP65">
-        <v>39.427408231180806</v>
+        <v>71.232103484781334</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -15728,16 +15728,16 @@
         <v>527</v>
       </c>
       <c r="Y66" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="Z66" t="s">
         <v>630</v>
       </c>
       <c r="AA66">
-        <v>0.99696751363483405</v>
+        <v>0.99080344458411729</v>
       </c>
       <c r="AB66">
-        <v>55.595583361375894</v>
+        <v>168.60351595784994</v>
       </c>
       <c r="AD66" t="s">
         <v>414</v>
@@ -15770,10 +15770,10 @@
         <v>897</v>
       </c>
       <c r="AO66">
-        <v>0.99831921281104818</v>
+        <v>0.99607298561021362</v>
       </c>
       <c r="AP66">
-        <v>30.814431797450247</v>
+        <v>71.995263812749926</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -15838,16 +15838,16 @@
         <v>529</v>
       </c>
       <c r="Y67" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Z67" t="s">
         <v>631</v>
       </c>
       <c r="AA67">
-        <v>0.98964014500078279</v>
+        <v>0.98636012609964985</v>
       </c>
       <c r="AB67">
-        <v>189.93067498564957</v>
+        <v>250.06435483975247</v>
       </c>
       <c r="AD67" t="s">
         <v>414</v>
@@ -15880,10 +15880,10 @@
         <v>899</v>
       </c>
       <c r="AO67">
-        <v>0.99845356202909108</v>
+        <v>0.9929182563937401</v>
       </c>
       <c r="AP67">
-        <v>28.351362799997673</v>
+        <v>129.83196611476453</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -15948,16 +15948,16 @@
         <v>531</v>
       </c>
       <c r="Y68" t="s">
-        <v>386</v>
+        <v>343</v>
       </c>
       <c r="Z68" t="s">
         <v>632</v>
       </c>
       <c r="AA68">
-        <v>0.9966137462997855</v>
+        <v>0.99598850450039844</v>
       </c>
       <c r="AB68">
-        <v>62.081317837266766</v>
+        <v>73.544084159361034</v>
       </c>
       <c r="AD68" t="s">
         <v>414</v>
@@ -15990,10 +15990,10 @@
         <v>901</v>
       </c>
       <c r="AO68">
-        <v>0.99368259233234391</v>
+        <v>0.99628542339510884</v>
       </c>
       <c r="AP68">
-        <v>115.81914057369519</v>
+        <v>68.100571089671959</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -16058,16 +16058,16 @@
         <v>533</v>
       </c>
       <c r="Y69" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="Z69" t="s">
         <v>633</v>
       </c>
       <c r="AA69">
-        <v>0.99011796851295664</v>
+        <v>0.99310312827752323</v>
       </c>
       <c r="AB69">
-        <v>181.17057726246117</v>
+        <v>126.44264824540761</v>
       </c>
       <c r="AD69" t="s">
         <v>414</v>
@@ -16100,10 +16100,10 @@
         <v>903</v>
       </c>
       <c r="AO69">
-        <v>0.9954443722844073</v>
+        <v>0.99474825047892679</v>
       </c>
       <c r="AP69">
-        <v>83.519841452532361</v>
+        <v>96.282074553009053</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -16168,16 +16168,16 @@
         <v>535</v>
       </c>
       <c r="Y70" t="s">
-        <v>391</v>
+        <v>336</v>
       </c>
       <c r="Z70" t="s">
         <v>634</v>
       </c>
       <c r="AA70">
-        <v>0.99635118654529808</v>
+        <v>0.99359748433922845</v>
       </c>
       <c r="AB70">
-        <v>66.894913336202478</v>
+        <v>117.37945378081078</v>
       </c>
       <c r="AD70" t="s">
         <v>414</v>
@@ -16210,10 +16210,10 @@
         <v>905</v>
       </c>
       <c r="AO70">
-        <v>0.99363040616365128</v>
+        <v>0.99684527597966854</v>
       </c>
       <c r="AP70">
-        <v>116.77588699972566</v>
+        <v>57.836607039410005</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -16278,16 +16278,16 @@
         <v>537</v>
       </c>
       <c r="Y71" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="Z71" t="s">
         <v>635</v>
       </c>
       <c r="AA71">
-        <v>0.99440507690252466</v>
+        <v>0.99592552983543692</v>
       </c>
       <c r="AB71">
-        <v>102.57359012038077</v>
+        <v>74.698619683656872</v>
       </c>
       <c r="AD71" t="s">
         <v>414</v>
@@ -16320,10 +16320,10 @@
         <v>907</v>
       </c>
       <c r="AO71">
-        <v>0.99782402570187057</v>
+        <v>0.9943927545810437</v>
       </c>
       <c r="AP71">
-        <v>39.892862132373601</v>
+        <v>102.79949934753229</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -16388,16 +16388,16 @@
         <v>539</v>
       </c>
       <c r="Y72" t="s">
-        <v>335</v>
+        <v>366</v>
       </c>
       <c r="Z72" t="s">
         <v>636</v>
       </c>
       <c r="AA72">
-        <v>0.99578350963230966</v>
+        <v>0.99463677905825021</v>
       </c>
       <c r="AB72">
-        <v>77.302323407656075</v>
+        <v>98.325717265413417</v>
       </c>
       <c r="AD72" t="s">
         <v>414</v>
@@ -16430,10 +16430,10 @@
         <v>909</v>
       </c>
       <c r="AO72">
-        <v>0.99756462867082185</v>
+        <v>0.99784941409648109</v>
       </c>
       <c r="AP72">
-        <v>44.648474368267038</v>
+        <v>39.427408231180806</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -16498,16 +16498,16 @@
         <v>541</v>
       </c>
       <c r="Y73" t="s">
-        <v>407</v>
+        <v>367</v>
       </c>
       <c r="Z73" t="s">
         <v>637</v>
       </c>
       <c r="AA73">
-        <v>0.99720191150310689</v>
+        <v>0.99667564038633161</v>
       </c>
       <c r="AB73">
-        <v>51.298289109706943</v>
+        <v>60.946592917253042</v>
       </c>
       <c r="AD73" t="s">
         <v>414</v>
@@ -16540,10 +16540,10 @@
         <v>911</v>
       </c>
       <c r="AO73">
-        <v>0.99584476105827657</v>
+        <v>0.99831921281104818</v>
       </c>
       <c r="AP73">
-        <v>76.179380598263194</v>
+        <v>30.814431797450247</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -16608,16 +16608,16 @@
         <v>543</v>
       </c>
       <c r="Y74" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="Z74" t="s">
         <v>638</v>
       </c>
       <c r="AA74">
-        <v>0.9954551465796494</v>
+        <v>0.99540885392130762</v>
       </c>
       <c r="AB74">
-        <v>83.32231270642734</v>
+        <v>84.171011442693441</v>
       </c>
       <c r="AD74" t="s">
         <v>414</v>
@@ -16650,10 +16650,10 @@
         <v>913</v>
       </c>
       <c r="AO74">
-        <v>0.9961146125371938</v>
+        <v>0.99845356202909108</v>
       </c>
       <c r="AP74">
-        <v>71.232103484781334</v>
+        <v>28.351362799997673</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -16718,16 +16718,16 @@
         <v>545</v>
       </c>
       <c r="Y75" t="s">
-        <v>399</v>
+        <v>351</v>
       </c>
       <c r="Z75" t="s">
         <v>639</v>
       </c>
       <c r="AA75">
-        <v>0.99552053983611355</v>
+        <v>0.99360802526828129</v>
       </c>
       <c r="AB75">
-        <v>82.123436337918946</v>
+        <v>117.18620341484296</v>
       </c>
       <c r="AD75" t="s">
         <v>414</v>
@@ -16760,10 +16760,10 @@
         <v>915</v>
       </c>
       <c r="AO75">
-        <v>0.99607298561021362</v>
+        <v>0.99439150850611324</v>
       </c>
       <c r="AP75">
-        <v>71.995263812749926</v>
+        <v>102.82234405458999</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -16828,16 +16828,16 @@
         <v>547</v>
       </c>
       <c r="Y76" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="Z76" t="s">
         <v>640</v>
       </c>
       <c r="AA76">
-        <v>0.98935435476104872</v>
+        <v>0.99515679011930902</v>
       </c>
       <c r="AB76">
-        <v>195.1701627141077</v>
+        <v>88.792181146001369</v>
       </c>
       <c r="AD76" t="s">
         <v>414</v>
@@ -16870,10 +16870,10 @@
         <v>917</v>
       </c>
       <c r="AO76">
-        <v>0.9929182563937401</v>
+        <v>0.99595416313893737</v>
       </c>
       <c r="AP76">
-        <v>129.83196611476453</v>
+        <v>74.173675786148877</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -16938,16 +16938,16 @@
         <v>549</v>
       </c>
       <c r="Y77" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="Z77" t="s">
         <v>641</v>
       </c>
       <c r="AA77">
-        <v>0.99775872574768198</v>
+        <v>0.99409145347725225</v>
       </c>
       <c r="AB77">
-        <v>41.090027959164246</v>
+        <v>108.32335291704148</v>
       </c>
       <c r="AD77" t="s">
         <v>414</v>
@@ -16980,10 +16980,10 @@
         <v>919</v>
       </c>
       <c r="AO77">
-        <v>0.99628542339510884</v>
+        <v>0.99687821505939955</v>
       </c>
       <c r="AP77">
-        <v>68.100571089671959</v>
+        <v>57.232723911007447</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -17048,16 +17048,16 @@
         <v>551</v>
       </c>
       <c r="Y78" t="s">
-        <v>337</v>
+        <v>381</v>
       </c>
       <c r="Z78" t="s">
         <v>642</v>
       </c>
       <c r="AA78">
-        <v>0.99551989204648861</v>
+        <v>0.99464051280908794</v>
       </c>
       <c r="AB78">
-        <v>82.135312481041623</v>
+        <v>98.257265166721183</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -17122,16 +17122,16 @@
         <v>553</v>
       </c>
       <c r="Y79" t="s">
-        <v>356</v>
+        <v>397</v>
       </c>
       <c r="Z79" t="s">
         <v>643</v>
       </c>
       <c r="AA79">
-        <v>0.9979392050107273</v>
+        <v>0.99282834435956602</v>
       </c>
       <c r="AB79">
-        <v>37.781241469999252</v>
+        <v>131.48035340795542</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -17196,16 +17196,16 @@
         <v>555</v>
       </c>
       <c r="Y80" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="Z80" t="s">
         <v>644</v>
       </c>
       <c r="AA80">
-        <v>0.9982033297630386</v>
+        <v>0.99569310304523451</v>
       </c>
       <c r="AB80">
-        <v>32.938954344292306</v>
+        <v>78.959777504033639</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -17270,16 +17270,16 @@
         <v>557</v>
       </c>
       <c r="Y81" t="s">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="Z81" t="s">
         <v>645</v>
       </c>
       <c r="AA81">
-        <v>0.99769372286934066</v>
+        <v>0.99502431999137919</v>
       </c>
       <c r="AB81">
-        <v>42.281747395421668</v>
+        <v>91.220800158047325</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -17344,16 +17344,16 @@
         <v>559</v>
       </c>
       <c r="Y82" t="s">
-        <v>341</v>
+        <v>402</v>
       </c>
       <c r="Z82" t="s">
         <v>646</v>
       </c>
       <c r="AA82">
-        <v>0.99571525957109708</v>
+        <v>0.99584577617815018</v>
       </c>
       <c r="AB82">
-        <v>78.553574529886689</v>
+        <v>76.16077006724673</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -17418,16 +17418,16 @@
         <v>561</v>
       </c>
       <c r="Y83" t="s">
-        <v>394</v>
+        <v>335</v>
       </c>
       <c r="Z83" t="s">
         <v>647</v>
       </c>
       <c r="AA83">
-        <v>0.99553579843385909</v>
+        <v>0.99578350963230966</v>
       </c>
       <c r="AB83">
-        <v>81.84369537924907</v>
+        <v>77.302323407656075</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -17492,16 +17492,16 @@
         <v>563</v>
       </c>
       <c r="Y84" t="s">
-        <v>353</v>
+        <v>407</v>
       </c>
       <c r="Z84" t="s">
         <v>648</v>
       </c>
       <c r="AA84">
-        <v>0.99734372305564056</v>
+        <v>0.99720191150310689</v>
       </c>
       <c r="AB84">
-        <v>48.698410646589842</v>
+        <v>51.298289109706943</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -17566,16 +17566,16 @@
         <v>565</v>
       </c>
       <c r="Y85" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="Z85" t="s">
         <v>649</v>
       </c>
       <c r="AA85">
-        <v>0.99662670467221526</v>
+        <v>0.9954551465796494</v>
       </c>
       <c r="AB85">
-        <v>61.843747676054292</v>
+        <v>83.32231270642734</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -17640,16 +17640,16 @@
         <v>567</v>
       </c>
       <c r="Y86" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="Z86" t="s">
         <v>650</v>
       </c>
       <c r="AA86">
-        <v>0.99740761205901929</v>
+        <v>0.99552053983611355</v>
       </c>
       <c r="AB86">
-        <v>47.527112251312907</v>
+        <v>82.123436337918946</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -17714,16 +17714,16 @@
         <v>569</v>
       </c>
       <c r="Y87" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="Z87" t="s">
         <v>651</v>
       </c>
       <c r="AA87">
-        <v>0.99730769203227776</v>
+        <v>0.98935435476104872</v>
       </c>
       <c r="AB87">
-        <v>49.358979408241737</v>
+        <v>195.1701627141077</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -17788,16 +17788,16 @@
         <v>571</v>
       </c>
       <c r="Y88" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="Z88" t="s">
         <v>652</v>
       </c>
       <c r="AA88">
-        <v>0.998073964784436</v>
+        <v>0.99775872574768198</v>
       </c>
       <c r="AB88">
-        <v>35.310645618673441</v>
+        <v>41.090027959164246</v>
       </c>
     </row>
   </sheetData>
@@ -17806,7 +17806,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05D3A8FD-E351-40B3-BF57-E93E6CF16270}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC7E37C-B954-44A0-A03C-328FC0A82B0A}">
   <dimension ref="B9:Z77"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17918,7 +17918,7 @@
         <v>1006</v>
       </c>
       <c r="K11" t="s">
-        <v>914</v>
+        <v>896</v>
       </c>
       <c r="L11">
         <v>29.7146465744454</v>
@@ -17951,7 +17951,7 @@
         <v>1140</v>
       </c>
       <c r="X11" t="s">
-        <v>1002</v>
+        <v>981</v>
       </c>
       <c r="Y11">
         <v>0.33825</v>
@@ -17986,7 +17986,7 @@
         <v>1008</v>
       </c>
       <c r="K12" t="s">
-        <v>843</v>
+        <v>797</v>
       </c>
       <c r="L12">
         <v>13.367096811591049</v>
@@ -18019,7 +18019,7 @@
         <v>1142</v>
       </c>
       <c r="X12" t="s">
-        <v>984</v>
+        <v>973</v>
       </c>
       <c r="Y12">
         <v>10.88325</v>
@@ -18054,7 +18054,7 @@
         <v>1010</v>
       </c>
       <c r="K13" t="s">
-        <v>880</v>
+        <v>834</v>
       </c>
       <c r="L13">
         <v>24.156328337033791</v>
@@ -18122,7 +18122,7 @@
         <v>1012</v>
       </c>
       <c r="K14" t="s">
-        <v>876</v>
+        <v>830</v>
       </c>
       <c r="L14">
         <v>16.006796560234815</v>
@@ -18155,7 +18155,7 @@
         <v>1146</v>
       </c>
       <c r="X14" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
       <c r="Y14">
         <v>42.507750000000001</v>
@@ -18190,7 +18190,7 @@
         <v>1014</v>
       </c>
       <c r="K15" t="s">
-        <v>839</v>
+        <v>793</v>
       </c>
       <c r="L15">
         <v>17.682358378036344</v>
@@ -18223,7 +18223,7 @@
         <v>1148</v>
       </c>
       <c r="X15" t="s">
-        <v>989</v>
+        <v>977</v>
       </c>
       <c r="Y15">
         <v>24.900749999999999</v>
@@ -18258,7 +18258,7 @@
         <v>1016</v>
       </c>
       <c r="K16" t="s">
-        <v>898</v>
+        <v>912</v>
       </c>
       <c r="L16">
         <v>29.492382648463739</v>
@@ -18291,7 +18291,7 @@
         <v>1150</v>
       </c>
       <c r="X16" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="Y16">
         <v>18.545249999999999</v>
@@ -18326,7 +18326,7 @@
         <v>1018</v>
       </c>
       <c r="K17" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="L17">
         <v>8.6778699255653748</v>
@@ -18359,7 +18359,7 @@
         <v>1152</v>
       </c>
       <c r="X17" t="s">
-        <v>986</v>
+        <v>974</v>
       </c>
       <c r="Y17">
         <v>29.838000000000001</v>
@@ -18394,7 +18394,7 @@
         <v>1020</v>
       </c>
       <c r="K18" t="s">
-        <v>894</v>
+        <v>908</v>
       </c>
       <c r="L18">
         <v>12.772248157772113</v>
@@ -18427,7 +18427,7 @@
         <v>1154</v>
       </c>
       <c r="X18" t="s">
-        <v>988</v>
+        <v>976</v>
       </c>
       <c r="Y18">
         <v>58.689</v>
@@ -18462,7 +18462,7 @@
         <v>1022</v>
       </c>
       <c r="K19" t="s">
-        <v>890</v>
+        <v>870</v>
       </c>
       <c r="L19">
         <v>15.217638427037592</v>
@@ -18495,7 +18495,7 @@
         <v>1156</v>
       </c>
       <c r="X19" t="s">
-        <v>968</v>
+        <v>993</v>
       </c>
       <c r="Y19">
         <v>48.432000000000002</v>
@@ -18530,7 +18530,7 @@
         <v>1024</v>
       </c>
       <c r="K20" t="s">
-        <v>856</v>
+        <v>810</v>
       </c>
       <c r="L20">
         <v>3.1385663053565613</v>
@@ -18563,7 +18563,7 @@
         <v>1158</v>
       </c>
       <c r="X20" t="s">
-        <v>985</v>
+        <v>968</v>
       </c>
       <c r="Y20">
         <v>47.794499999999999</v>
@@ -18598,7 +18598,7 @@
         <v>1026</v>
       </c>
       <c r="K21" t="s">
-        <v>803</v>
+        <v>854</v>
       </c>
       <c r="L21">
         <v>4.0628682283884237</v>
@@ -18666,7 +18666,7 @@
         <v>1028</v>
       </c>
       <c r="K22" t="s">
-        <v>811</v>
+        <v>918</v>
       </c>
       <c r="L22">
         <v>19.408837136062758</v>
@@ -18699,7 +18699,7 @@
         <v>1162</v>
       </c>
       <c r="X22" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="Y22">
         <v>8.1052499999999998</v>
@@ -18734,7 +18734,7 @@
         <v>1030</v>
       </c>
       <c r="K23" t="s">
-        <v>892</v>
+        <v>872</v>
       </c>
       <c r="L23">
         <v>15.054857587707319</v>
@@ -18767,7 +18767,7 @@
         <v>1164</v>
       </c>
       <c r="X23" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="Y23">
         <v>9.3810000000000002</v>
@@ -18802,7 +18802,7 @@
         <v>1032</v>
       </c>
       <c r="K24" t="s">
-        <v>797</v>
+        <v>906</v>
       </c>
       <c r="L24">
         <v>13.019602602156084</v>
@@ -18835,7 +18835,7 @@
         <v>1166</v>
       </c>
       <c r="X24" t="s">
-        <v>972</v>
+        <v>996</v>
       </c>
       <c r="Y24">
         <v>11.47575</v>
@@ -18870,7 +18870,7 @@
         <v>1034</v>
       </c>
       <c r="K25" t="s">
-        <v>866</v>
+        <v>820</v>
       </c>
       <c r="L25">
         <v>25.094411791551167</v>
@@ -18903,7 +18903,7 @@
         <v>1168</v>
       </c>
       <c r="X25" t="s">
-        <v>1005</v>
+        <v>980</v>
       </c>
       <c r="Y25">
         <v>6.1372499999999999</v>
@@ -18938,7 +18938,7 @@
         <v>1036</v>
       </c>
       <c r="K26" t="s">
-        <v>829</v>
+        <v>866</v>
       </c>
       <c r="L26">
         <v>18.31221960055294</v>
@@ -19006,7 +19006,7 @@
         <v>1038</v>
       </c>
       <c r="K27" t="s">
-        <v>860</v>
+        <v>814</v>
       </c>
       <c r="L27">
         <v>27.91719839668141</v>
@@ -19039,7 +19039,7 @@
         <v>1172</v>
       </c>
       <c r="X27" t="s">
-        <v>970</v>
+        <v>995</v>
       </c>
       <c r="Y27">
         <v>10.491</v>
@@ -19074,7 +19074,7 @@
         <v>1040</v>
       </c>
       <c r="K28" t="s">
-        <v>825</v>
+        <v>890</v>
       </c>
       <c r="L28">
         <v>8.5144758814389814</v>
@@ -19107,7 +19107,7 @@
         <v>1174</v>
       </c>
       <c r="X28" t="s">
-        <v>1004</v>
+        <v>983</v>
       </c>
       <c r="Y28">
         <v>17.414249999999999</v>
@@ -19142,7 +19142,7 @@
         <v>1042</v>
       </c>
       <c r="K29" t="s">
-        <v>858</v>
+        <v>812</v>
       </c>
       <c r="L29">
         <v>12.144708893333986</v>
@@ -19175,7 +19175,7 @@
         <v>1176</v>
       </c>
       <c r="X29" t="s">
-        <v>980</v>
+        <v>989</v>
       </c>
       <c r="Y29">
         <v>10.968</v>
@@ -19210,7 +19210,7 @@
         <v>1044</v>
       </c>
       <c r="K30" t="s">
-        <v>868</v>
+        <v>822</v>
       </c>
       <c r="L30">
         <v>1.6724491767694549</v>
@@ -19243,7 +19243,7 @@
         <v>1178</v>
       </c>
       <c r="X30" t="s">
-        <v>982</v>
+        <v>991</v>
       </c>
       <c r="Y30">
         <v>10.79175</v>
@@ -19278,7 +19278,7 @@
         <v>1046</v>
       </c>
       <c r="K31" t="s">
-        <v>870</v>
+        <v>824</v>
       </c>
       <c r="L31">
         <v>13.894741632015101</v>
@@ -19311,7 +19311,7 @@
         <v>1180</v>
       </c>
       <c r="X31" t="s">
-        <v>974</v>
+        <v>1004</v>
       </c>
       <c r="Y31">
         <v>20.114249999999998</v>
@@ -19346,7 +19346,7 @@
         <v>1048</v>
       </c>
       <c r="K32" t="s">
-        <v>888</v>
+        <v>842</v>
       </c>
       <c r="L32">
         <v>11.876635800692616</v>
@@ -19379,7 +19379,7 @@
         <v>1182</v>
       </c>
       <c r="X32" t="s">
-        <v>973</v>
+        <v>985</v>
       </c>
       <c r="Y32">
         <v>44.373750000000001</v>
@@ -19414,7 +19414,7 @@
         <v>1050</v>
       </c>
       <c r="K33" t="s">
-        <v>872</v>
+        <v>826</v>
       </c>
       <c r="L33">
         <v>27.15579263061009</v>
@@ -19447,7 +19447,7 @@
         <v>1184</v>
       </c>
       <c r="X33" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="Y33">
         <v>18.57525</v>
@@ -19482,7 +19482,7 @@
         <v>1052</v>
       </c>
       <c r="K34" t="s">
-        <v>916</v>
+        <v>898</v>
       </c>
       <c r="L34">
         <v>27.043339674957092</v>
@@ -19515,7 +19515,7 @@
         <v>1186</v>
       </c>
       <c r="X34" t="s">
-        <v>990</v>
+        <v>978</v>
       </c>
       <c r="Y34">
         <v>18.241499999999998</v>
@@ -19550,7 +19550,7 @@
         <v>1054</v>
       </c>
       <c r="K35" t="s">
-        <v>805</v>
+        <v>856</v>
       </c>
       <c r="L35">
         <v>12.170927347824723</v>
@@ -19585,7 +19585,7 @@
         <v>1056</v>
       </c>
       <c r="K36" t="s">
-        <v>918</v>
+        <v>900</v>
       </c>
       <c r="L36">
         <v>26.999240466622091</v>
@@ -19620,7 +19620,7 @@
         <v>1058</v>
       </c>
       <c r="K37" t="s">
-        <v>908</v>
+        <v>882</v>
       </c>
       <c r="L37">
         <v>23.305350986470582</v>
@@ -19655,7 +19655,7 @@
         <v>1060</v>
       </c>
       <c r="K38" t="s">
-        <v>831</v>
+        <v>868</v>
       </c>
       <c r="L38">
         <v>19.293897715957783</v>
@@ -19690,7 +19690,7 @@
         <v>1062</v>
       </c>
       <c r="K39" t="s">
-        <v>878</v>
+        <v>832</v>
       </c>
       <c r="L39">
         <v>34.8352470366899</v>
@@ -19725,7 +19725,7 @@
         <v>1064</v>
       </c>
       <c r="K40" t="s">
-        <v>817</v>
+        <v>848</v>
       </c>
       <c r="L40">
         <v>22.439012549480047</v>
@@ -19760,7 +19760,7 @@
         <v>1066</v>
       </c>
       <c r="K41" t="s">
-        <v>904</v>
+        <v>878</v>
       </c>
       <c r="L41">
         <v>19.571302094407635</v>
@@ -19795,7 +19795,7 @@
         <v>1068</v>
       </c>
       <c r="K42" t="s">
-        <v>823</v>
+        <v>888</v>
       </c>
       <c r="L42">
         <v>16.258507759053195</v>
@@ -19830,7 +19830,7 @@
         <v>1070</v>
       </c>
       <c r="K43" t="s">
-        <v>852</v>
+        <v>806</v>
       </c>
       <c r="L43">
         <v>48.074816212675138</v>
@@ -19865,7 +19865,7 @@
         <v>1072</v>
       </c>
       <c r="K44" t="s">
-        <v>884</v>
+        <v>838</v>
       </c>
       <c r="L44">
         <v>65.59399718970684</v>
@@ -19900,7 +19900,7 @@
         <v>1074</v>
       </c>
       <c r="K45" t="s">
-        <v>848</v>
+        <v>802</v>
       </c>
       <c r="L45">
         <v>65.706815294563484</v>
@@ -19935,7 +19935,7 @@
         <v>1076</v>
       </c>
       <c r="K46" t="s">
-        <v>809</v>
+        <v>916</v>
       </c>
       <c r="L46">
         <v>13.859521883612567</v>
@@ -19970,7 +19970,7 @@
         <v>1078</v>
       </c>
       <c r="K47" t="s">
-        <v>821</v>
+        <v>886</v>
       </c>
       <c r="L47">
         <v>32.682899602232801</v>
@@ -20005,7 +20005,7 @@
         <v>1080</v>
       </c>
       <c r="K48" t="s">
-        <v>791</v>
+        <v>862</v>
       </c>
       <c r="L48">
         <v>39.028686646898073</v>
@@ -20040,7 +20040,7 @@
         <v>1082</v>
       </c>
       <c r="K49" t="s">
-        <v>841</v>
+        <v>795</v>
       </c>
       <c r="L49">
         <v>25.808486809088087</v>
@@ -20075,7 +20075,7 @@
         <v>1084</v>
       </c>
       <c r="K50" t="s">
-        <v>789</v>
+        <v>860</v>
       </c>
       <c r="L50">
         <v>64.703394190718342</v>
@@ -20110,7 +20110,7 @@
         <v>1086</v>
       </c>
       <c r="K51" t="s">
-        <v>815</v>
+        <v>846</v>
       </c>
       <c r="L51">
         <v>46.777110562179843</v>
@@ -20145,7 +20145,7 @@
         <v>1088</v>
       </c>
       <c r="K52" t="s">
-        <v>837</v>
+        <v>791</v>
       </c>
       <c r="L52">
         <v>83.307298494129057</v>
@@ -20180,7 +20180,7 @@
         <v>1090</v>
       </c>
       <c r="K53" t="s">
-        <v>900</v>
+        <v>874</v>
       </c>
       <c r="L53">
         <v>8.0718642408500934</v>
@@ -20215,7 +20215,7 @@
         <v>1092</v>
       </c>
       <c r="K54" t="s">
-        <v>835</v>
+        <v>789</v>
       </c>
       <c r="L54">
         <v>25.555956589747868</v>
@@ -20250,7 +20250,7 @@
         <v>1094</v>
       </c>
       <c r="K55" t="s">
-        <v>902</v>
+        <v>876</v>
       </c>
       <c r="L55">
         <v>26.74310381624198</v>
@@ -20285,7 +20285,7 @@
         <v>1096</v>
       </c>
       <c r="K56" t="s">
-        <v>886</v>
+        <v>840</v>
       </c>
       <c r="L56">
         <v>47.811917655816522</v>
@@ -20320,7 +20320,7 @@
         <v>1098</v>
       </c>
       <c r="K57" t="s">
-        <v>846</v>
+        <v>800</v>
       </c>
       <c r="L57">
         <v>65.898010391046881</v>
@@ -20355,7 +20355,7 @@
         <v>1100</v>
       </c>
       <c r="K58" t="s">
-        <v>882</v>
+        <v>836</v>
       </c>
       <c r="L58">
         <v>49.914822287456737</v>
@@ -20390,7 +20390,7 @@
         <v>1102</v>
       </c>
       <c r="K59" t="s">
-        <v>844</v>
+        <v>798</v>
       </c>
       <c r="L59">
         <v>19.963633091222835</v>
@@ -20425,7 +20425,7 @@
         <v>1104</v>
       </c>
       <c r="K60" t="s">
-        <v>799</v>
+        <v>850</v>
       </c>
       <c r="L60">
         <v>71.04376789192942</v>
@@ -20460,7 +20460,7 @@
         <v>1106</v>
       </c>
       <c r="K61" t="s">
-        <v>874</v>
+        <v>828</v>
       </c>
       <c r="L61">
         <v>43.07229279461999</v>
@@ -20495,7 +20495,7 @@
         <v>1108</v>
       </c>
       <c r="K62" t="s">
-        <v>819</v>
+        <v>884</v>
       </c>
       <c r="L62">
         <v>38.769945374969119</v>
@@ -20530,7 +20530,7 @@
         <v>1110</v>
       </c>
       <c r="K63" t="s">
-        <v>807</v>
+        <v>914</v>
       </c>
       <c r="L63">
         <v>59.009737840109466</v>
@@ -20565,7 +20565,7 @@
         <v>1112</v>
       </c>
       <c r="K64" t="s">
-        <v>795</v>
+        <v>904</v>
       </c>
       <c r="L64">
         <v>28.865927665826828</v>
@@ -20600,7 +20600,7 @@
         <v>1114</v>
       </c>
       <c r="K65" t="s">
-        <v>827</v>
+        <v>864</v>
       </c>
       <c r="L65">
         <v>37.976260419426943</v>
@@ -20635,7 +20635,7 @@
         <v>1116</v>
       </c>
       <c r="K66" t="s">
-        <v>793</v>
+        <v>902</v>
       </c>
       <c r="L66">
         <v>44.88386263672971</v>
@@ -20670,7 +20670,7 @@
         <v>1118</v>
       </c>
       <c r="K67" t="s">
-        <v>813</v>
+        <v>844</v>
       </c>
       <c r="L67">
         <v>23.350121881103082</v>
@@ -20705,7 +20705,7 @@
         <v>1120</v>
       </c>
       <c r="K68" t="s">
-        <v>864</v>
+        <v>818</v>
       </c>
       <c r="L68">
         <v>15.289477961960474</v>
@@ -20740,7 +20740,7 @@
         <v>1122</v>
       </c>
       <c r="K69" t="s">
-        <v>906</v>
+        <v>880</v>
       </c>
       <c r="L69">
         <v>10.395885695189069</v>
@@ -20775,7 +20775,7 @@
         <v>1124</v>
       </c>
       <c r="K70" t="s">
-        <v>854</v>
+        <v>808</v>
       </c>
       <c r="L70">
         <v>23.89105636564183</v>
@@ -20810,7 +20810,7 @@
         <v>1126</v>
       </c>
       <c r="K71" t="s">
-        <v>862</v>
+        <v>816</v>
       </c>
       <c r="L71">
         <v>18.959710131684457</v>
@@ -20845,7 +20845,7 @@
         <v>1128</v>
       </c>
       <c r="K72" t="s">
-        <v>850</v>
+        <v>804</v>
       </c>
       <c r="L72">
         <v>6.6550975614073966</v>
@@ -20880,7 +20880,7 @@
         <v>1130</v>
       </c>
       <c r="K73" t="s">
-        <v>912</v>
+        <v>894</v>
       </c>
       <c r="L73">
         <v>13.961943802326671</v>
@@ -20915,7 +20915,7 @@
         <v>1132</v>
       </c>
       <c r="K74" t="s">
-        <v>801</v>
+        <v>852</v>
       </c>
       <c r="L74">
         <v>51.937776653453852</v>
@@ -20950,7 +20950,7 @@
         <v>1134</v>
       </c>
       <c r="K75" t="s">
-        <v>833</v>
+        <v>787</v>
       </c>
       <c r="L75">
         <v>21.246092446368579</v>
@@ -20985,7 +20985,7 @@
         <v>1136</v>
       </c>
       <c r="K76" t="s">
-        <v>787</v>
+        <v>858</v>
       </c>
       <c r="L76">
         <v>19.42059121972445</v>
@@ -21020,7 +21020,7 @@
         <v>1138</v>
       </c>
       <c r="K77" t="s">
-        <v>910</v>
+        <v>892</v>
       </c>
       <c r="L77">
         <v>30.063621105864488</v>
@@ -21035,7 +21035,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40B53B39-C9E7-4C7A-9921-93FE7E7CF57C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36EED67B-AEF5-4BFD-82A0-17AB65921C61}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22852,7 +22852,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9994004-CF4B-401B-BE6B-69FFE683715D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACBE7FF5-C7AF-41F8-9328-726EB9DD8AC5}">
   <dimension ref="B2:M11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4472C7E-6598-41AE-BB9A-F563FE323D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F120257-5FA1-49A1-830A-7B01CF326B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1375,18 +1375,468 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IND_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IND_025</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 25</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_IND_039</t>
   </si>
   <si>
@@ -1399,462 +1849,237 @@
     <t>connecting solar to buses in cluster 42</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_IN659-765_IND,e_w453513742-765_IND,e_IN642-765_IND,e_w429459345-765_IND,e_w492377703-765_IND,e_w293597835-765_IND,e_w608461884-765_IND,e_w318050929-765_IND,e_w316463122-765_IND</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND,e_w355560316-765_IND,e_w492377703-765_IND,e_w386018740-765_IND</t>
+  </si>
+  <si>
+    <t>e_w369866141-765_IND,e_IN146-765_IND,e_IN142-765_IND,e_IN230-765_IND,e_IN137-765_IND,e_IN140-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN798-765_IND</t>
+  </si>
+  <si>
+    <t>e_w408924420-765_IND,e_w192782338-765_IND,e_IN476-765_IND,e_IN457-765_IND,e_w408924427-765_IND,e_w319423421-765_IND,e_IN439-765_IND,e_w506461670-765_IND,e_IN400-765_IND,e_IN539-765_IND,e_IN404-765_IND,e_IN399-765_IND,e_IN390-765_IND,e_IN388-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN684-765_IND,e_w409158116-765_IND,e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN539-765_IND,e_w202980838-765_IND,e_IN416-765_IND,e_IN405-765_IND,e_w353914865-765_IND,e_w477691456-765_IND,e_IN540-765_IND,e_w196563905-765_IND,e_w353914761-765_IND,e_IN548-765_IND,e_w354062412-765_IND,e_w248385304-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN607-765_IND,e_IN578-765_IND,e_w248385304-765_IND,e_w323266562-765_IND,e_w149822703-400_IND,e_w759521252-765_IND</t>
+  </si>
+  <si>
+    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w311571096-765_IND,e_w369866141-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN100-765_IND,e_w247861059-765_IND,e_w311176519-765_IND,e_IN105-765_IND,e_w105373531-765_IND,e_w274106872-765_IND,e_IN136-765_IND,e_w420797421-765_IND,e_w417569420-765_IND,e_IN135-765_IND,e_w1341291951-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN270-765_IND,e_IN196-765_IND,e_IN174-765_IND,e_w1329624553-765_IND,e_IN276-765_IND,e_IN200-765_IND,e_w607439318-765_IND,e_IN229-765_IND,e_IN183-765_IND,e_IN160-765_IND,e_w352619220-765_IND,e_IN267-765_IND,e_IN232-765_IND,e_IN254-765_IND,e_w100470285-765_IND,e_IN275-765_IND,e_w311118424-765_IND,e_IN283-765_IND,e_w311103617-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN260-400_IND,e_w203673991-400_IND,e_w1265496720-400_IND,e_w610646823-400_IND,e_w375084335-400_IND,e_IN177-400_IND,e_IN176-400_IND,e_w375941438-400_IND,e_IN145-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w1336628403-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w688672798-765_IND,e_IN218-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND,e_IN659-765_IND</t>
+  </si>
+  <si>
+    <t>e_w331275940-765_IND,e_IN529-765_IND,e_w688672798-765_IND,e_w655683221-765_IND,e_IN489-765_IND,e_IN488-765_IND,e_IN486-765_IND</t>
+  </si>
+  <si>
+    <t>e_w654736039-765_IND,e_w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>e_w492377703-765_IND,e_w293597835-765_IND,e_w608461884-765_IND,e_w386018740-765_IND,e_w801704865-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311571096-765_IND,e_IN250-765_IND,e_IN247-765_IND,e_IN233-765_IND,e_w193216698-765_IND,e_w423702239-765_IND,e_IN295-765_IND,e_IN264-765_IND,e_w131484738-765_IND,e_IN246-765_IND,e_IN272-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311103617-765_IND,e_w166692103-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN235-400_IND,e_w465787206-400_IND,e_IN265-400_IND,e_w1265489491-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN10-765_IND,e_w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND,e_w1206014676-765_IND,e_w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN300-765_IND,e_w166692103-400_IND,e_IN290-400_IND,e_w97392607-400_IND,e_w50885643-400_IND,e_w324059200-400_IND,e_IN317-400_IND,e_w50885643-765_IND,e_w577176545-400_IND,e_w209806624-400_IND,e_w1044735753-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN145-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1001700959-765_IND,e_IN218-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN218-765_IND,e_w1001700959-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_IN215-765_IND,e_IN191-765_IND,e_w1143180503-765_IND,e_IN163-765_IND,e_w654736039-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1207477934-765_IND,e_w840600239-765_IND,e_w506461670-765_IND,e_IN684-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311954703-765_IND,e_w1246177377-765_IND,e_IN540-765_IND,e_IN599-765_IND,e_IN586-765_IND,e_w353914761-765_IND,e_IN583-765_IND,e_IN555-765_IND,e_IN578-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN235-400_IND,e_w239498664-400_IND,e_IN265-400_IND,e_w1265489491-400_IND,e_w610646823-400_IND</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN486-765_IND,e_w655683221-765_IND,e_IN473-765_IND,e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN798-765_IND,e_w386153973-765_IND,e_w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>e_w315823978-765_IND,e_w386018740-765_IND,e_w801704865-765_IND,e_IN742-765_IND,e_w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND,e_w1127651311-765_IND,e_w331275940-765_IND,e_w688672798-765_IND</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND,e_w429459345-765_IND</t>
+  </si>
+  <si>
+    <t>e_w316463122-765_IND,e_w318090288-765_IND,e_w318050929-765_IND,e_w315477169-765_IND,e_w698045832-765_IND</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND,e_IN806-765_IND,e_IN798-765_IND,e_w1206014676-765_IND</t>
+  </si>
+  <si>
+    <t>e_w372701897-765_IND,e_IN10-765_IND,e_w311176519-765_IND</t>
+  </si>
+  <si>
+    <t>e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND,e_w311571096-765_IND,e_w514344408-765_IND,e_w193216698-765_IND</t>
+  </si>
+  <si>
+    <t>e_w698045832-765_IND,e_w315477169-765_IND,e_w408924420-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN42-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN440-400_IND,e_IN386-400_IND,e_w1072445901-400_IND</t>
+  </si>
+  <si>
+    <t>e_w608461884-765_IND,e_w318050929-765_IND,e_w315477169-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311176519-765_IND,e_w372701897-765_IND,e_w105373531-765_IND,e_IN10-765_IND,e_IN42-765_IND,e_w1341291951-765_IND</t>
+  </si>
+  <si>
+    <t>e_w801704865-765_IND,e_w1207477934-765_IND,e_w923365745-765_IND,e_IN684-765_IND</t>
+  </si>
+  <si>
+    <t>e_w840600239-765_IND,e_w408924427-765_IND,e_w506461670-765_IND</t>
+  </si>
+  <si>
+    <t>e_w409158116-765_IND,e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>e_w386153973-765_IND,e_w342204888-765_IND,e_w751947947-765_IND,e_w910151268-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN128-765_IND,e_IN116-765_IND,e_w1341291951-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND,e_IN180-765_IND,e_IN206-765_IND,e_w311103617-765_IND</t>
+  </si>
+  <si>
+    <t>e_w374367235-400_IND,e_IN260-400_IND,e_w439006823-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1127651311-765_IND,e_w688672798-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN806-765_IND,e_IN801-765_IND,e_IN798-765_IND,e_w425401901-765_IND,e_w1206014676-765_IND,e_IN809-765_IND,e_IN803-765_IND,e_w386153973-765_IND,e_w751947947-765_IND,e_w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND,e_IN749-765_IND,e_IN748-765_IND,e_w342204888-765_IND,e_w245128370-765_IND</t>
+  </si>
+  <si>
+    <t>e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND,e_IN685-765_IND</t>
+  </si>
+  <si>
+    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN684-765_IND,e_w409112085-765_IND,e_IN599-765_IND</t>
+  </si>
+  <si>
+    <t>e_w196933682-765_IND,e_w923418232-400_IND,e_w1015325412-400_IND,e_w248385304-765_IND,e_IN353-400_IND,e_w149822703-400_IND,e_IN363-400_IND,e_w209806624-765_IND,e_w96821783-400_IND,e_w209806650-400_IND,e_w485873968-400_IND</t>
+  </si>
+  <si>
+    <t>e_w688672798-765_IND,e_IN218-765_IND,e_IN215-765_IND,e_IN199-765_IND,e_IN194-765_IND,e_IN191-765_IND,e_w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>e_w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>e_w323266562-765_IND,e_w759521252-765_IND,e_w793144832-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1341647644-400_IND,e_IN263-400_IND,e_w93160503-400_IND,e_w526897229-400_IND,e_IN259-400_IND,e_IN320-400_IND,e_IN235-400_IND</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND,e_w331275940-765_IND,e_IN642-765_IND,e_w318090288-765_IND,e_IN489-765_IND,e_IN486-765_IND,e_w316463122-765_IND,e_w698045832-765_IND</t>
+  </si>
+  <si>
+    <t>e_w466424134-765_IND,e_w1207477934-765_IND,e_w840600239-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN295-765_IND,e_IN277-765_IND,e_IN457-765_IND,e_w423702239-765_IND,e_IN289-765_IND,e_IN288-765_IND,e_IN439-765_IND,e_IN321-765_IND,e_IN343-765_IND,e_IN327-765_IND,e_IN400-765_IND,e_IN370-765_IND,e_w195459361-765_IND,e_IN323-765_IND</t>
+  </si>
+  <si>
+    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN539-765_IND,e_w311954703-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN365-765_IND,e_IN293-765_IND,e_IN373-765_IND,e_w422204218-765_IND,e_IN283-765_IND,e_IN395-765_IND,e_IN312-765_IND,e_IN302-765_IND,e_IN298-765_IND,e_IN375-765_IND,e_w409798382-400_IND,e_IN300-765_IND,e_w196933682-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN325-400_IND,e_IN315-400_IND,e_IN339-400_IND,e_w205942950-400_IND,e_w324064297-400_IND,e_IN320-400_IND,e_IN336-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN155-400_IND,e_w116541259-400_IND,e_IN235-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN163-765_IND,e_w1143180503-765_IND,e_w654736039-765_IND,e_w631917408-765_IND,e_IN146-765_IND,e_w1077819664-765_IND,e_w311176519-765_IND,e_w369866141-765_IND,e_IN142-765_IND,e_IN108-765_IND,e_IN107-765_IND,e_IN94-765_IND</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND,e_IN610-765_IND,e_IN617-765_IND,e_w323266562-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1072445901-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
+  </si>
+  <si>
+    <t>e_w342204888-765_IND,e_w245128370-765_IND,e_IN742-765_IND,e_w315824842-765_IND,e_w923365745-765_IND,e_w910151268-765_IND,e_w1074489047-765_IND</t>
+  </si>
+  <si>
+    <t>e_w759521252-765_IND,e_w118228036-400_IND,e_w793144832-765_IND,e_IN339-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1099365579-400_IND,e_w375941438-400_IND</t>
+  </si>
+  <si>
     <t>e_w166692103-400_IND,e_w1044735753-400_IND,e_w1012817818-400_IND,e_w92994753-400_IND,e_w92360278-400_IND,e_w1238123371-400_IND,e_w94199110-400_IND,e_w485873934-400_IND,e_IN179-400_IND,e_IN286-400_IND,e_IN181-400_IND</t>
   </si>
   <si>
@@ -1864,229 +2089,88 @@
     <t>e_w375941438-400_IND,e_IN145-400_IND</t>
   </si>
   <si>
-    <t>e_w1078426593-765_IND,e_w1336628403-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w688672798-765_IND,e_IN218-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND</t>
-  </si>
-  <si>
-    <t>e_w473902678-765_IND,e_IN659-765_IND</t>
-  </si>
-  <si>
-    <t>e_w331275940-765_IND,e_IN529-765_IND,e_w688672798-765_IND,e_w655683221-765_IND,e_IN489-765_IND,e_IN488-765_IND,e_IN486-765_IND</t>
-  </si>
-  <si>
-    <t>e_w654736039-765_IND,e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>e_w355560316-765_IND</t>
-  </si>
-  <si>
-    <t>e_w492377703-765_IND,e_w293597835-765_IND,e_w608461884-765_IND,e_w386018740-765_IND,e_w801704865-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311571096-765_IND,e_IN250-765_IND,e_IN247-765_IND,e_IN233-765_IND,e_w193216698-765_IND,e_w423702239-765_IND,e_IN295-765_IND,e_IN264-765_IND,e_w131484738-765_IND,e_IN246-765_IND,e_IN272-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311103617-765_IND,e_w166692103-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN235-400_IND,e_w465787206-400_IND,e_IN265-400_IND,e_w1265489491-400_IND</t>
-  </si>
-  <si>
-    <t>e_w372701897-765_IND,e_IN10-765_IND,e_w311176519-765_IND</t>
-  </si>
-  <si>
-    <t>e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND,e_w311571096-765_IND,e_w514344408-765_IND,e_w193216698-765_IND</t>
-  </si>
-  <si>
-    <t>e_w698045832-765_IND,e_w315477169-765_IND,e_w408924420-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN42-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN440-400_IND,e_IN386-400_IND,e_w1072445901-400_IND</t>
-  </si>
-  <si>
-    <t>e_w1001700959-765_IND,e_IN218-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN218-765_IND,e_w1001700959-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_IN215-765_IND,e_IN191-765_IND,e_w1143180503-765_IND,e_IN163-765_IND,e_w654736039-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1207477934-765_IND,e_w840600239-765_IND,e_w506461670-765_IND,e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311954703-765_IND,e_w1246177377-765_IND,e_IN540-765_IND,e_IN599-765_IND,e_IN586-765_IND,e_w353914761-765_IND,e_IN583-765_IND,e_IN555-765_IND,e_IN578-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN235-400_IND,e_w239498664-400_IND,e_IN265-400_IND,e_w1265489491-400_IND,e_w610646823-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN163-765_IND,e_w1143180503-765_IND,e_w654736039-765_IND,e_w631917408-765_IND,e_IN146-765_IND,e_w1077819664-765_IND,e_w311176519-765_IND,e_w369866141-765_IND,e_IN142-765_IND,e_IN108-765_IND,e_IN107-765_IND,e_IN94-765_IND</t>
-  </si>
-  <si>
-    <t>e_w409112085-765_IND,e_IN610-765_IND,e_IN617-765_IND,e_w323266562-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1072445901-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN659-765_IND,e_w453513742-765_IND,e_IN642-765_IND,e_w429459345-765_IND,e_w492377703-765_IND,e_w293597835-765_IND,e_w608461884-765_IND,e_w318050929-765_IND,e_w316463122-765_IND</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND,e_w355560316-765_IND,e_w492377703-765_IND,e_w386018740-765_IND</t>
-  </si>
-  <si>
-    <t>e_w369866141-765_IND,e_IN146-765_IND,e_IN142-765_IND,e_IN230-765_IND,e_IN137-765_IND,e_IN140-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN798-765_IND</t>
-  </si>
-  <si>
-    <t>e_w408924420-765_IND,e_w192782338-765_IND,e_IN476-765_IND,e_IN457-765_IND,e_w408924427-765_IND,e_w319423421-765_IND,e_IN439-765_IND,e_w506461670-765_IND,e_IN400-765_IND,e_IN539-765_IND,e_IN404-765_IND,e_IN399-765_IND,e_IN390-765_IND,e_IN388-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN684-765_IND,e_w409158116-765_IND,e_w409112085-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN539-765_IND,e_w202980838-765_IND,e_IN416-765_IND,e_IN405-765_IND,e_w353914865-765_IND,e_w477691456-765_IND,e_IN540-765_IND,e_w196563905-765_IND,e_w353914761-765_IND,e_IN548-765_IND,e_w354062412-765_IND,e_w248385304-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN607-765_IND,e_IN578-765_IND,e_w248385304-765_IND,e_w323266562-765_IND,e_w149822703-400_IND,e_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>e_w342204888-765_IND,e_w245128370-765_IND,e_IN742-765_IND,e_w315824842-765_IND,e_w923365745-765_IND,e_w910151268-765_IND,e_w1074489047-765_IND</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND,e_w118228036-400_IND,e_w793144832-765_IND,e_IN339-400_IND</t>
-  </si>
-  <si>
-    <t>e_w1099365579-400_IND,e_w375941438-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN10-765_IND,e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>e_w425401901-765_IND,e_w1206014676-765_IND,e_w545571850-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN300-765_IND,e_w166692103-400_IND,e_IN290-400_IND,e_w97392607-400_IND,e_w50885643-400_IND,e_w324059200-400_IND,e_IN317-400_IND,e_w50885643-765_IND,e_w577176545-400_IND,e_w209806624-400_IND,e_w1044735753-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN145-400_IND</t>
-  </si>
-  <si>
-    <t>e_w473902678-765_IND,e_w331275940-765_IND,e_IN642-765_IND,e_w318090288-765_IND,e_IN489-765_IND,e_IN486-765_IND,e_w316463122-765_IND,e_w698045832-765_IND</t>
-  </si>
-  <si>
-    <t>e_w466424134-765_IND,e_w1207477934-765_IND,e_w840600239-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN295-765_IND,e_IN277-765_IND,e_IN457-765_IND,e_w423702239-765_IND,e_IN289-765_IND,e_IN288-765_IND,e_IN439-765_IND,e_IN321-765_IND,e_IN343-765_IND,e_IN327-765_IND,e_IN400-765_IND,e_IN370-765_IND,e_w195459361-765_IND,e_IN323-765_IND</t>
-  </si>
-  <si>
-    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN539-765_IND,e_w311954703-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN365-765_IND,e_IN293-765_IND,e_IN373-765_IND,e_w422204218-765_IND,e_IN283-765_IND,e_IN395-765_IND,e_IN312-765_IND,e_IN302-765_IND,e_IN298-765_IND,e_IN375-765_IND,e_w409798382-400_IND,e_IN300-765_IND,e_w196933682-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN325-400_IND,e_IN315-400_IND,e_IN339-400_IND,e_w205942950-400_IND,e_w324064297-400_IND,e_IN320-400_IND,e_IN336-400_IND</t>
-  </si>
-  <si>
-    <t>e_IN155-400_IND,e_w116541259-400_IND,e_IN235-400_IND</t>
-  </si>
-  <si>
-    <t>e_w386153973-765_IND,e_w342204888-765_IND,e_w751947947-765_IND,e_w910151268-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN128-765_IND,e_IN116-765_IND,e_w1341291951-765_IND,e_w1415199647-765_IND,e_w352619220-765_IND,e_IN180-765_IND,e_IN206-765_IND,e_w311103617-765_IND</t>
-  </si>
-  <si>
-    <t>e_w374367235-400_IND,e_IN260-400_IND,e_w439006823-400_IND,e_w1099365556-400_IND,e_w1099365579-400_IND</t>
-  </si>
-  <si>
-    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w311571096-765_IND,e_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN100-765_IND,e_w247861059-765_IND,e_w311176519-765_IND,e_IN105-765_IND,e_w105373531-765_IND,e_w274106872-765_IND,e_IN136-765_IND,e_w420797421-765_IND,e_w417569420-765_IND,e_IN135-765_IND,e_w1341291951-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN270-765_IND,e_IN196-765_IND,e_IN174-765_IND,e_w1329624553-765_IND,e_IN276-765_IND,e_IN200-765_IND,e_w607439318-765_IND,e_IN229-765_IND,e_IN183-765_IND,e_IN160-765_IND,e_w352619220-765_IND,e_IN267-765_IND,e_IN232-765_IND,e_IN254-765_IND,e_w100470285-765_IND,e_IN275-765_IND,e_w311118424-765_IND,e_IN283-765_IND,e_w311103617-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN260-400_IND,e_w203673991-400_IND,e_w1265496720-400_IND,e_w610646823-400_IND,e_w375084335-400_IND,e_IN177-400_IND,e_IN176-400_IND,e_w375941438-400_IND,e_IN145-400_IND</t>
-  </si>
-  <si>
-    <t>e_w473902678-765_IND,e_w1127651311-765_IND,e_w331275940-765_IND,e_w688672798-765_IND</t>
-  </si>
-  <si>
-    <t>e_w355560316-765_IND,e_w429459345-765_IND</t>
-  </si>
-  <si>
-    <t>e_w316463122-765_IND,e_w318090288-765_IND,e_w318050929-765_IND,e_w315477169-765_IND,e_w698045832-765_IND</t>
-  </si>
-  <si>
-    <t>e_w425401901-765_IND,e_IN806-765_IND,e_IN798-765_IND,e_w1206014676-765_IND</t>
-  </si>
-  <si>
-    <t>e_w688672798-765_IND,e_IN218-765_IND,e_IN215-765_IND,e_IN199-765_IND,e_IN194-765_IND,e_IN191-765_IND,e_w631917408-765_IND</t>
-  </si>
-  <si>
-    <t>e_w545571850-765_IND</t>
-  </si>
-  <si>
-    <t>e_w323266562-765_IND,e_w759521252-765_IND,e_w793144832-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1341647644-400_IND,e_IN263-400_IND,e_w93160503-400_IND,e_w526897229-400_IND,e_IN259-400_IND,e_IN320-400_IND,e_IN235-400_IND</t>
-  </si>
-  <si>
-    <t>e_w608461884-765_IND,e_w318050929-765_IND,e_w315477169-765_IND,e_w201845280-765_IND,e_w840600239-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311176519-765_IND,e_w372701897-765_IND,e_w105373531-765_IND,e_IN10-765_IND,e_IN42-765_IND,e_w1341291951-765_IND</t>
-  </si>
-  <si>
-    <t>e_w801704865-765_IND,e_w1207477934-765_IND,e_w923365745-765_IND,e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>e_w840600239-765_IND,e_w408924427-765_IND,e_w506461670-765_IND</t>
-  </si>
-  <si>
-    <t>e_w409158116-765_IND,e_w409112085-765_IND</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN486-765_IND,e_w655683221-765_IND,e_IN473-765_IND,e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN798-765_IND,e_w386153973-765_IND,e_w355560316-765_IND</t>
-  </si>
-  <si>
-    <t>e_w315823978-765_IND,e_w386018740-765_IND,e_w801704865-765_IND,e_IN742-765_IND,e_w923365745-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1127651311-765_IND,e_w688672798-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN806-765_IND,e_IN801-765_IND,e_IN798-765_IND,e_w425401901-765_IND,e_w1206014676-765_IND,e_IN809-765_IND,e_IN803-765_IND,e_w386153973-765_IND,e_w751947947-765_IND,e_w545571850-765_IND</t>
-  </si>
-  <si>
-    <t>e_w355560316-765_IND,e_IN749-765_IND,e_IN748-765_IND,e_w342204888-765_IND,e_w245128370-765_IND</t>
-  </si>
-  <si>
-    <t>e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND,e_IN685-765_IND</t>
-  </si>
-  <si>
-    <t>e_w506461670-765_IND,e_w311933111-765_IND,e_IN684-765_IND,e_w409112085-765_IND,e_IN599-765_IND</t>
-  </si>
-  <si>
-    <t>e_w196933682-765_IND,e_w923418232-400_IND,e_w1015325412-400_IND,e_w248385304-765_IND,e_IN353-400_IND,e_w149822703-400_IND,e_IN363-400_IND,e_w209806624-765_IND,e_w96821783-400_IND,e_w209806650-400_IND,e_w485873968-400_IND</t>
+    <t>distr_wonelc_won_IND_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
   </si>
   <si>
     <t>distr_wonelc_won_IND_065</t>
@@ -2125,6 +2209,174 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wonelc_won_IND_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_IND_049</t>
   </si>
   <si>
@@ -2239,256 +2491,88 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
+    <t>elc_won_IND_056</t>
+  </si>
+  <si>
+    <t>e_w655683221-765_IND,e_IN473-765_IND,e_w311571096-765_IND,e_w209826798-765_IND,e_w360424761-765_IND,e_w193216698-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_054</t>
+  </si>
+  <si>
+    <t>e_w514344408-765_IND,e_w360424761-765_IND,e_w193216698-765_IND,e_IN476-765_IND,e_w192782338-765_IND,e_IN457-765_IND,e_w319423421-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_014</t>
+  </si>
+  <si>
+    <t>e_w408924427-765_IND,e_w506461670-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_048</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w1336628403-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_034</t>
+  </si>
+  <si>
+    <t>e_IN659-765_IND,e_w453513742-765_IND,e_IN642-765_IND,e_w318090288-765_IND,e_w429459345-765_IND,e_w316463122-765_IND,e_w318050929-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_046</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND,e_IN798-765_IND,e_w386153973-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_022</t>
+  </si>
+  <si>
+    <t>e_IN440-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_055</t>
+  </si>
+  <si>
+    <t>e_IN486-765_IND,e_IN473-765_IND,e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_016</t>
+  </si>
+  <si>
+    <t>e_w166692103-400_IND,e_w1012817818-400_IND,e_w92360278-400_IND,e_w1238123371-400_IND,e_w485873934-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_028</t>
+  </si>
+  <si>
+    <t>e_w324064297-400_IND,e_IN320-400_IND,e_IN259-400_IND,e_IN235-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_050</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w473902678-765_IND,e_w331275940-765_IND,e_w688672798-765_IND,e_w318090288-765_IND,e_IN489-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_064</t>
+  </si>
+  <si>
+    <t>e_w1001700959-765_IND,e_IN218-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_w1143180503-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_011</t>
+  </si>
+  <si>
+    <t>e_IN365-765_IND,e_IN388-765_IND,e_IN373-765_IND,e_w422204218-765_IND,e_IN405-765_IND,e_IN395-765_IND,e_w477691456-765_IND,e_IN375-765_IND,e_w196563905-765_IND,e_w196933682-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_025</t>
+  </si>
+  <si>
+    <t>e_w759521252-765_IND,e_w118228036-400_IND</t>
   </si>
   <si>
     <t>elc_won_IND_065</t>
@@ -2524,6 +2608,174 @@
     <t>elc_won_IND_002</t>
   </si>
   <si>
+    <t>elc_won_IND_066</t>
+  </si>
+  <si>
+    <t>e_IN146-765_IND,e_w654736039-765_IND,e_w1077819664-765_IND,e_w369866141-765_IND,e_IN142-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_040</t>
+  </si>
+  <si>
+    <t>e_w608461884-765_IND,e_w801704865-765_IND,e_w466424134-765_IND,e_w1207477934-765_IND,e_w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_038</t>
+  </si>
+  <si>
+    <t>e_w342204888-765_IND,e_w245128370-765_IND,e_IN742-765_IND,e_w315823978-765_IND,e_w801704865-765_IND,e_w315824842-765_IND,e_w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_067</t>
+  </si>
+  <si>
+    <t>e_IN163-765_IND,e_w1143180503-765_IND,e_w654736039-765_IND,e_w631917408-765_IND,e_IN146-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_063</t>
+  </si>
+  <si>
+    <t>e_w1077819664-765_IND,e_w311176519-765_IND,e_IN108-765_IND,e_IN94-765_IND,e_IN137-765_IND,e_IN100-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_001</t>
+  </si>
+  <si>
+    <t>e_w352619220-765_IND,e_IN180-765_IND,e_IN206-765_IND,e_w311103617-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_024</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND,e_IN617-765_IND,e_w323266562-765_IND,e_w759521252-765_IND,e_w793144832-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_026</t>
+  </si>
+  <si>
+    <t>e_w118228036-400_IND,e_IN325-400_IND,e_IN315-400_IND,e_IN339-400_IND,e_w205942950-400_IND,e_w793144832-765_IND,e_IN336-400_IND,e_IN320-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_043</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND,e_IN659-765_IND,e_w473902678-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_045</t>
+  </si>
+  <si>
+    <t>e_IN798-765_IND,e_w425401901-765_IND,e_IN801-765_IND,e_IN803-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_031</t>
+  </si>
+  <si>
+    <t>e_w466424134-765_IND,e_w840600239-765_IND,e_w1207477934-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_059</t>
+  </si>
+  <si>
+    <t>e_IN270-765_IND,e_IN277-765_IND,e_IN276-765_IND,e_IN289-765_IND,e_IN288-765_IND,e_IN267-765_IND,e_IN321-765_IND,e_IN323-765_IND,e_IN293-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_027</t>
+  </si>
+  <si>
+    <t>e_w1238123371-400_IND,e_IN286-400_IND,e_w485873934-400_IND,e_IN181-400_IND,e_w1341647644-400_IND,e_IN263-400_IND,e_w93160503-400_IND,e_w526897229-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_053</t>
+  </si>
+  <si>
+    <t>e_IN218-765_IND,e_w688672798-765_IND,e_w1127651311-765_IND,e_w655683221-765_IND,e_IN194-765_IND,e_w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_036</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND,e_w1206014676-765_IND,e_IN809-765_IND,e_w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_012</t>
+  </si>
+  <si>
+    <t>e_w408924420-765_IND,e_w192782338-765_IND,e_w408924427-765_IND,e_w506461670-765_IND,e_w311933111-765_IND,e_IN539-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_057</t>
+  </si>
+  <si>
+    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w369866141-765_IND,e_w311571096-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_041</t>
+  </si>
+  <si>
+    <t>e_w293597835-765_IND,e_w608461884-765_IND,e_w492377703-765_IND,e_w386018740-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_030</t>
+  </si>
+  <si>
+    <t>e_w315824842-765_IND,e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_052</t>
+  </si>
+  <si>
+    <t>e_IN218-765_IND,e_IN215-765_IND,e_IN187-765_IND,e_IN199-765_IND,e_IN191-765_IND,e_IN194-765_IND,e_w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_037</t>
+  </si>
+  <si>
+    <t>e_IN803-765_IND,e_w545571850-765_IND,e_w751947947-765_IND,e_w342204888-765_IND,e_w910151268-765_IND,e_w315824842-765_IND,e_w1074489047-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_032</t>
+  </si>
+  <si>
+    <t>e_w506461670-765_IND,e_IN684-765_IND,e_w311933111-765_IND,e_IN685-765_IND,e_w409158116-765_IND,e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_018</t>
+  </si>
+  <si>
+    <t>e_w97392607-400_IND,e_w324059200-400_IND,e_IN317-400_IND,e_w923418232-400_IND,e_w577176545-400_IND,e_w1015325412-400_IND,e_IN353-400_IND,e_w209806624-400_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_009</t>
+  </si>
+  <si>
+    <t>e_IN439-765_IND,e_IN321-765_IND,e_w319423421-765_IND,e_IN343-765_IND,e_IN327-765_IND,e_IN400-765_IND,e_IN370-765_IND,e_w195459361-765_IND,e_IN399-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_013</t>
+  </si>
+  <si>
+    <t>e_w311933111-765_IND,e_w311954703-765_IND,e_IN539-765_IND,e_w1246177377-765_IND,e_IN599-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_008</t>
+  </si>
+  <si>
+    <t>e_w247861059-765_IND,e_w311176519-765_IND,e_IN140-765_IND,e_IN105-765_IND,e_w105373531-765_IND,e_IN136-765_IND,e_w420797421-765_IND,e_w417569420-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_007</t>
+  </si>
+  <si>
+    <t>e_IN136-765_IND,e_IN246-765_IND,e_w274106872-765_IND,e_IN196-765_IND,e_IN174-765_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_006</t>
+  </si>
+  <si>
+    <t>e_IN135-765_IND,e_w420797421-765_IND,e_w1329624553-765_IND,e_IN128-765_IND,e_IN200-765_IND,e_IN196-765_IND,e_w607439318-765_IND,e_IN229-765_IND,e_IN183-765_IND,e_IN160-765_IND,e_IN267-765_IND,e_IN232-765_IND,e_IN180-765_IND,e_IN254-765_IND,e_w100470285-765_IND</t>
+  </si>
+  <si>
     <t>elc_won_IND_049</t>
   </si>
   <si>
@@ -2638,256 +2890,88 @@
     <t>e_IN275-765_IND,e_w311118424-765_IND,e_w100470285-765_IND,e_IN283-765_IND,e_w311103617-765_IND,e_IN298-765_IND,e_w166692103-400_IND,e_IN300-765_IND,e_IN290-400_IND</t>
   </si>
   <si>
-    <t>elc_won_IND_048</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w1336628403-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_034</t>
-  </si>
-  <si>
-    <t>e_IN659-765_IND,e_w453513742-765_IND,e_IN642-765_IND,e_w318090288-765_IND,e_w429459345-765_IND,e_w316463122-765_IND,e_w318050929-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_046</t>
-  </si>
-  <si>
-    <t>e_w355560316-765_IND,e_IN798-765_IND,e_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_022</t>
-  </si>
-  <si>
-    <t>e_IN440-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_057</t>
-  </si>
-  <si>
-    <t>e_w655683221-765_IND,e_w631917408-765_IND,e_w369866141-765_IND,e_w311571096-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_041</t>
-  </si>
-  <si>
-    <t>e_w293597835-765_IND,e_w608461884-765_IND,e_w492377703-765_IND,e_w386018740-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_030</t>
-  </si>
-  <si>
-    <t>e_w315824842-765_IND,e_w923365745-765_IND,e_IN684-765_IND,e_w409158116-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_050</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w688672711-765_IND,e_w1127651311-765_IND,e_w473902678-765_IND,e_w331275940-765_IND,e_w688672798-765_IND,e_w318090288-765_IND,e_IN489-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_064</t>
-  </si>
-  <si>
-    <t>e_w1001700959-765_IND,e_IN218-765_IND,e_IN187-765_IND,e_w686891085-765_IND,e_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_011</t>
-  </si>
-  <si>
-    <t>e_IN365-765_IND,e_IN388-765_IND,e_IN373-765_IND,e_w422204218-765_IND,e_IN405-765_IND,e_IN395-765_IND,e_w477691456-765_IND,e_IN375-765_IND,e_w196563905-765_IND,e_w196933682-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_025</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND,e_w118228036-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_066</t>
-  </si>
-  <si>
-    <t>e_IN146-765_IND,e_w654736039-765_IND,e_w1077819664-765_IND,e_w369866141-765_IND,e_IN142-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_040</t>
-  </si>
-  <si>
-    <t>e_w608461884-765_IND,e_w801704865-765_IND,e_w466424134-765_IND,e_w1207477934-765_IND,e_w923365745-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_038</t>
-  </si>
-  <si>
-    <t>e_w342204888-765_IND,e_w245128370-765_IND,e_IN742-765_IND,e_w315823978-765_IND,e_w801704865-765_IND,e_w315824842-765_IND,e_w923365745-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_055</t>
-  </si>
-  <si>
-    <t>e_IN486-765_IND,e_IN473-765_IND,e_w698045832-765_IND,e_w209826798-765_IND,e_w360424761-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_016</t>
-  </si>
-  <si>
-    <t>e_w166692103-400_IND,e_w1012817818-400_IND,e_w92360278-400_IND,e_w1238123371-400_IND,e_w485873934-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_028</t>
-  </si>
-  <si>
-    <t>e_w324064297-400_IND,e_IN320-400_IND,e_IN259-400_IND,e_IN235-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_009</t>
-  </si>
-  <si>
-    <t>e_IN439-765_IND,e_IN321-765_IND,e_w319423421-765_IND,e_IN343-765_IND,e_IN327-765_IND,e_IN400-765_IND,e_IN370-765_IND,e_w195459361-765_IND,e_IN399-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_013</t>
-  </si>
-  <si>
-    <t>e_w311933111-765_IND,e_w311954703-765_IND,e_IN539-765_IND,e_w1246177377-765_IND,e_IN599-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_043</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND,e_IN659-765_IND,e_w473902678-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_045</t>
-  </si>
-  <si>
-    <t>e_IN798-765_IND,e_w425401901-765_IND,e_IN801-765_IND,e_IN803-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_031</t>
-  </si>
-  <si>
-    <t>e_w466424134-765_IND,e_w840600239-765_IND,e_w1207477934-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_059</t>
-  </si>
-  <si>
-    <t>e_IN270-765_IND,e_IN277-765_IND,e_IN276-765_IND,e_IN289-765_IND,e_IN288-765_IND,e_IN267-765_IND,e_IN321-765_IND,e_IN323-765_IND,e_IN293-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_027</t>
-  </si>
-  <si>
-    <t>e_w1238123371-400_IND,e_IN286-400_IND,e_w485873934-400_IND,e_IN181-400_IND,e_w1341647644-400_IND,e_IN263-400_IND,e_w93160503-400_IND,e_w526897229-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_052</t>
-  </si>
-  <si>
-    <t>e_IN218-765_IND,e_IN215-765_IND,e_IN187-765_IND,e_IN199-765_IND,e_IN191-765_IND,e_IN194-765_IND,e_w631917408-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_037</t>
-  </si>
-  <si>
-    <t>e_IN803-765_IND,e_w545571850-765_IND,e_w751947947-765_IND,e_w342204888-765_IND,e_w910151268-765_IND,e_w315824842-765_IND,e_w1074489047-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_032</t>
-  </si>
-  <si>
-    <t>e_w506461670-765_IND,e_IN684-765_IND,e_w311933111-765_IND,e_IN685-765_IND,e_w409158116-765_IND,e_w409112085-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_018</t>
-  </si>
-  <si>
-    <t>e_w97392607-400_IND,e_w324059200-400_IND,e_IN317-400_IND,e_w923418232-400_IND,e_w577176545-400_IND,e_w1015325412-400_IND,e_IN353-400_IND,e_w209806624-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_067</t>
-  </si>
-  <si>
-    <t>e_IN163-765_IND,e_w1143180503-765_IND,e_w654736039-765_IND,e_w631917408-765_IND,e_IN146-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_063</t>
-  </si>
-  <si>
-    <t>e_w1077819664-765_IND,e_w311176519-765_IND,e_IN108-765_IND,e_IN94-765_IND,e_IN137-765_IND,e_IN100-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_001</t>
-  </si>
-  <si>
-    <t>e_w352619220-765_IND,e_IN180-765_IND,e_IN206-765_IND,e_w311103617-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_024</t>
-  </si>
-  <si>
-    <t>e_w409112085-765_IND,e_IN617-765_IND,e_w323266562-765_IND,e_w759521252-765_IND,e_w793144832-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_026</t>
-  </si>
-  <si>
-    <t>e_w118228036-400_IND,e_IN325-400_IND,e_IN315-400_IND,e_IN339-400_IND,e_w205942950-400_IND,e_w793144832-765_IND,e_IN336-400_IND,e_IN320-400_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_056</t>
-  </si>
-  <si>
-    <t>e_w655683221-765_IND,e_IN473-765_IND,e_w311571096-765_IND,e_w209826798-765_IND,e_w360424761-765_IND,e_w193216698-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_054</t>
-  </si>
-  <si>
-    <t>e_w514344408-765_IND,e_w360424761-765_IND,e_w193216698-765_IND,e_IN476-765_IND,e_w192782338-765_IND,e_IN457-765_IND,e_w319423421-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_014</t>
-  </si>
-  <si>
-    <t>e_w408924427-765_IND,e_w506461670-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_008</t>
-  </si>
-  <si>
-    <t>e_w247861059-765_IND,e_w311176519-765_IND,e_IN140-765_IND,e_IN105-765_IND,e_w105373531-765_IND,e_IN136-765_IND,e_w420797421-765_IND,e_w417569420-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_007</t>
-  </si>
-  <si>
-    <t>e_IN136-765_IND,e_IN246-765_IND,e_w274106872-765_IND,e_IN196-765_IND,e_IN174-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_006</t>
-  </si>
-  <si>
-    <t>e_IN135-765_IND,e_w420797421-765_IND,e_w1329624553-765_IND,e_IN128-765_IND,e_IN200-765_IND,e_IN196-765_IND,e_w607439318-765_IND,e_IN229-765_IND,e_IN183-765_IND,e_IN160-765_IND,e_IN267-765_IND,e_IN232-765_IND,e_IN180-765_IND,e_IN254-765_IND,e_w100470285-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_053</t>
-  </si>
-  <si>
-    <t>e_IN218-765_IND,e_w688672798-765_IND,e_w1127651311-765_IND,e_w655683221-765_IND,e_IN194-765_IND,e_w631917408-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_036</t>
-  </si>
-  <si>
-    <t>e_w425401901-765_IND,e_w1206014676-765_IND,e_IN809-765_IND,e_w545571850-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_012</t>
-  </si>
-  <si>
-    <t>e_w408924420-765_IND,e_w192782338-765_IND,e_w408924427-765_IND,e_w506461670-765_IND,e_w311933111-765_IND,e_IN539-765_IND</t>
+    <t>distr_wofelc_wof_IND_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IND_010</t>
@@ -2896,6 +2980,30 @@
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_IND_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_IND_013</t>
   </si>
   <si>
@@ -2908,102 +3016,6 @@
     <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_IND_011</t>
   </si>
   <si>
@@ -3022,21 +3034,93 @@
     <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
+    <t>elc_wof_IND_009</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w473902678-765_IND,e_w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_017</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_014</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>e_w315824842-765_IND,e_w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_002</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_015</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_006</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_012</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_007</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND,e_w688672711-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_008</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_005</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_024</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND,e_IN617-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_004</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND,e_w473902678-765_IND</t>
   </si>
   <si>
     <t>elc_wof_IND_010</t>
   </si>
   <si>
+    <t>elc_wof_IND_021</t>
+  </si>
+  <si>
+    <t>e_w409158116-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_001</t>
+  </si>
+  <si>
+    <t>e_IN798-765_IND,e_w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_018</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_022</t>
+  </si>
+  <si>
     <t>elc_wof_IND_013</t>
   </si>
   <si>
@@ -3049,78 +3133,6 @@
     <t>e_w323266562-765_IND,e_w759521252-765_IND</t>
   </si>
   <si>
-    <t>elc_wof_IND_002</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_007</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_008</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_005</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_024</t>
-  </si>
-  <si>
-    <t>e_w409112085-765_IND,e_IN617-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_015</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_001</t>
-  </si>
-  <si>
-    <t>e_IN798-765_IND,e_w355560316-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_018</t>
-  </si>
-  <si>
-    <t>e_w425401901-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_022</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_006</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_012</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>e_w315824842-765_IND,e_w923365745-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>e_w409112085-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_009</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765_IND,e_w473902678-765_IND,e_w1127651311-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_017</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_014</t>
-  </si>
-  <si>
     <t>elc_wof_IND_011</t>
   </si>
   <si>
@@ -3136,18 +3148,6 @@
     <t>e_w425401901-765_IND,e_w1206014676-765_IND</t>
   </si>
   <si>
-    <t>elc_wof_IND_004</t>
-  </si>
-  <si>
-    <t>e_w429459345-765_IND,e_w473902678-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_021</t>
-  </si>
-  <si>
-    <t>e_w409158116-765_IND</t>
-  </si>
-  <si>
     <t>e_won_IND_001</t>
   </si>
   <si>
@@ -3841,7 +3841,7 @@
     <t>Transformer: e_w97392607-400_IND → e_w97392607-765_IND</t>
   </si>
   <si>
-    <t>e_w1074489047-765_IND,e_w116541259-400_IND,e_w409112085-765_IND,e_w910151268-765_IND</t>
+    <t>e_w116541259-400_IND</t>
   </si>
 </sst>
 </file>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>e_w1074489047-765_IND,e_w116541259-400_IND,e_w409112085-765_IND,e_w910151268-765_IND</v>
+        <v>e_w116541259-400_IND</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>e_w1074489047-765_IND,e_w116541259-400_IND,e_w409112085-765_IND,e_w910151268-765_IND</v>
+        <v>e_w116541259-400_IND</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -8576,7 +8576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EFF6EBC-81FB-4AAF-A68D-6C2FADB019F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B497F833-838D-40E4-857E-8CB92FD8E58D}">
   <dimension ref="B9:BD88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8814,16 +8814,16 @@
         <v>415</v>
       </c>
       <c r="Y11" t="s">
-        <v>359</v>
+        <v>396</v>
       </c>
       <c r="Z11" t="s">
         <v>575</v>
       </c>
       <c r="AA11">
-        <v>0.99699505644961572</v>
+        <v>0.99557960200072415</v>
       </c>
       <c r="AB11">
-        <v>55.090631757044932</v>
+        <v>81.040629986723459</v>
       </c>
       <c r="AD11" t="s">
         <v>414</v>
@@ -8856,10 +8856,10 @@
         <v>788</v>
       </c>
       <c r="AO11">
-        <v>0.99245794727704639</v>
+        <v>0.99474825047892679</v>
       </c>
       <c r="AP11">
-        <v>138.27096658748206</v>
+        <v>96.282074553009053</v>
       </c>
       <c r="AR11" t="s">
         <v>414</v>
@@ -8889,13 +8889,13 @@
         <v>968</v>
       </c>
       <c r="BB11" t="s">
-        <v>799</v>
+        <v>969</v>
       </c>
       <c r="BC11">
-        <v>0.98154438143849254</v>
+        <v>0.98137594918937099</v>
       </c>
       <c r="BD11">
-        <v>338.35300696097039</v>
+        <v>341.44093152819772</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8960,16 +8960,16 @@
         <v>419</v>
       </c>
       <c r="Y12" t="s">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="Z12" t="s">
         <v>576</v>
       </c>
       <c r="AA12">
-        <v>0.99170691261633115</v>
+        <v>0.99295357769237991</v>
       </c>
       <c r="AB12">
-        <v>152.03993536726261</v>
+        <v>129.18440897303603</v>
       </c>
       <c r="AD12" t="s">
         <v>414</v>
@@ -9002,10 +9002,10 @@
         <v>790</v>
       </c>
       <c r="AO12">
-        <v>0.99381230463557813</v>
+        <v>0.99684527597966854</v>
       </c>
       <c r="AP12">
-        <v>113.44108168106689</v>
+        <v>57.836607039410005</v>
       </c>
       <c r="AR12" t="s">
         <v>414</v>
@@ -9032,16 +9032,16 @@
         <v>922</v>
       </c>
       <c r="BA12" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="BB12" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="BC12">
-        <v>0.99526782804010661</v>
+        <v>0.9889956676941275</v>
       </c>
       <c r="BD12">
-        <v>86.756485931379871</v>
+        <v>201.74609227432916</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -9106,16 +9106,16 @@
         <v>421</v>
       </c>
       <c r="Y13" t="s">
-        <v>376</v>
+        <v>355</v>
       </c>
       <c r="Z13" t="s">
         <v>577</v>
       </c>
       <c r="AA13">
-        <v>0.9904035062850528</v>
+        <v>0.99696751363483405</v>
       </c>
       <c r="AB13">
-        <v>175.93571810736526</v>
+        <v>55.595583361375894</v>
       </c>
       <c r="AD13" t="s">
         <v>414</v>
@@ -9148,10 +9148,10 @@
         <v>792</v>
       </c>
       <c r="AO13">
-        <v>0.99534539864304916</v>
+        <v>0.9943927545810437</v>
       </c>
       <c r="AP13">
-        <v>85.3343582107656</v>
+        <v>102.79949934753229</v>
       </c>
       <c r="AR13" t="s">
         <v>414</v>
@@ -9178,16 +9178,16 @@
         <v>924</v>
       </c>
       <c r="BA13" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="BB13" t="s">
-        <v>972</v>
+        <v>634</v>
       </c>
       <c r="BC13">
-        <v>0.98605138538291048</v>
+        <v>0.99193721244794397</v>
       </c>
       <c r="BD13">
-        <v>255.7246013133088</v>
+        <v>147.81777178769397</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -9252,16 +9252,16 @@
         <v>423</v>
       </c>
       <c r="Y14" t="s">
-        <v>364</v>
+        <v>408</v>
       </c>
       <c r="Z14" t="s">
         <v>578</v>
       </c>
       <c r="AA14">
-        <v>0.99579357955795456</v>
+        <v>0.98964014500078279</v>
       </c>
       <c r="AB14">
-        <v>77.117708104165573</v>
+        <v>189.93067498564957</v>
       </c>
       <c r="AD14" t="s">
         <v>414</v>
@@ -9294,10 +9294,10 @@
         <v>794</v>
       </c>
       <c r="AO14">
-        <v>0.99310873310996184</v>
+        <v>0.99660391553167893</v>
       </c>
       <c r="AP14">
-        <v>126.33989298403215</v>
+        <v>62.261548585886977</v>
       </c>
       <c r="AR14" t="s">
         <v>414</v>
@@ -9327,13 +9327,13 @@
         <v>973</v>
       </c>
       <c r="BB14" t="s">
-        <v>643</v>
+        <v>974</v>
       </c>
       <c r="BC14">
-        <v>0.97123008268954114</v>
+        <v>0.99307601382667698</v>
       </c>
       <c r="BD14">
-        <v>527.44848402507967</v>
+        <v>126.93974651092147</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9398,16 +9398,16 @@
         <v>425</v>
       </c>
       <c r="Y15" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="Z15" t="s">
         <v>579</v>
       </c>
       <c r="AA15">
-        <v>0.99066346416517681</v>
+        <v>0.9966137462997855</v>
       </c>
       <c r="AB15">
-        <v>171.16982363842584</v>
+        <v>62.081317837266766</v>
       </c>
       <c r="AD15" t="s">
         <v>414</v>
@@ -9440,10 +9440,10 @@
         <v>796</v>
       </c>
       <c r="AO15">
-        <v>0.99715437961127318</v>
+        <v>0.9959136876641268</v>
       </c>
       <c r="AP15">
-        <v>52.169707126657627</v>
+        <v>74.915726157675209</v>
       </c>
       <c r="AR15" t="s">
         <v>414</v>
@@ -9470,16 +9470,16 @@
         <v>928</v>
       </c>
       <c r="BA15" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="BB15" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="BC15">
-        <v>0.98838558997012138</v>
+        <v>0.99275904397179515</v>
       </c>
       <c r="BD15">
-        <v>212.93085054777492</v>
+        <v>132.75086051708826</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9544,16 +9544,16 @@
         <v>427</v>
       </c>
       <c r="Y16" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="Z16" t="s">
         <v>580</v>
       </c>
       <c r="AA16">
-        <v>0.99560939477262078</v>
+        <v>0.99011796851295664</v>
       </c>
       <c r="AB16">
-        <v>80.494429168619106</v>
+        <v>181.17057726246117</v>
       </c>
       <c r="AD16" t="s">
         <v>414</v>
@@ -9583,13 +9583,13 @@
         <v>797</v>
       </c>
       <c r="AN16" t="s">
-        <v>586</v>
+        <v>798</v>
       </c>
       <c r="AO16">
-        <v>0.9950502580620818</v>
+        <v>0.9935275292913992</v>
       </c>
       <c r="AP16">
-        <v>90.745268861833736</v>
+        <v>118.66196299101547</v>
       </c>
       <c r="AR16" t="s">
         <v>414</v>
@@ -9616,16 +9616,16 @@
         <v>930</v>
       </c>
       <c r="BA16" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="BB16" t="s">
-        <v>799</v>
+        <v>606</v>
       </c>
       <c r="BC16">
-        <v>0.98730637899749651</v>
+        <v>0.97123008268954114</v>
       </c>
       <c r="BD16">
-        <v>232.71638504589731</v>
+        <v>527.44848402507967</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9690,16 +9690,16 @@
         <v>429</v>
       </c>
       <c r="Y17" t="s">
-        <v>339</v>
+        <v>391</v>
       </c>
       <c r="Z17" t="s">
         <v>581</v>
       </c>
       <c r="AA17">
-        <v>0.99544039231362502</v>
+        <v>0.99635118654529808</v>
       </c>
       <c r="AB17">
-        <v>83.592807583541571</v>
+        <v>66.894913336202478</v>
       </c>
       <c r="AD17" t="s">
         <v>414</v>
@@ -9726,16 +9726,16 @@
         <v>665</v>
       </c>
       <c r="AM17" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AN17" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AO17">
-        <v>0.99418244113372889</v>
+        <v>0.99687120387267125</v>
       </c>
       <c r="AP17">
-        <v>106.6552458816375</v>
+        <v>57.361262334360205</v>
       </c>
       <c r="AR17" t="s">
         <v>414</v>
@@ -9762,16 +9762,16 @@
         <v>932</v>
       </c>
       <c r="BA17" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="BB17" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="BC17">
-        <v>0.98809190602642238</v>
+        <v>0.99603877136023145</v>
       </c>
       <c r="BD17">
-        <v>218.31505618225569</v>
+        <v>72.622525062424401</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9836,16 +9836,16 @@
         <v>431</v>
       </c>
       <c r="Y18" t="s">
-        <v>346</v>
+        <v>390</v>
       </c>
       <c r="Z18" t="s">
         <v>582</v>
       </c>
       <c r="AA18">
-        <v>0.99190124970484694</v>
+        <v>0.99440507690252466</v>
       </c>
       <c r="AB18">
-        <v>148.47708874447352</v>
+        <v>102.57359012038077</v>
       </c>
       <c r="AD18" t="s">
         <v>414</v>
@@ -9872,16 +9872,16 @@
         <v>667</v>
       </c>
       <c r="AM18" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AN18" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AO18">
-        <v>0.99206751173516827</v>
+        <v>0.99611612132862803</v>
       </c>
       <c r="AP18">
-        <v>145.42895152191466</v>
+        <v>71.204442308486065</v>
       </c>
       <c r="AR18" t="s">
         <v>414</v>
@@ -9908,16 +9908,16 @@
         <v>934</v>
       </c>
       <c r="BA18" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="BB18" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="BC18">
-        <v>0.994208528887633</v>
+        <v>0.98787195157138663</v>
       </c>
       <c r="BD18">
-        <v>106.17697039339514</v>
+        <v>222.34755452457901</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9982,16 +9982,16 @@
         <v>433</v>
       </c>
       <c r="Y19" t="s">
-        <v>412</v>
+        <v>337</v>
       </c>
       <c r="Z19" t="s">
         <v>583</v>
       </c>
       <c r="AA19">
-        <v>0.9940089461809174</v>
+        <v>0.99551989204648861</v>
       </c>
       <c r="AB19">
-        <v>109.83598668318054</v>
+        <v>82.135312481041623</v>
       </c>
       <c r="AD19" t="s">
         <v>414</v>
@@ -10018,16 +10018,16 @@
         <v>669</v>
       </c>
       <c r="AM19" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AN19" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AO19">
-        <v>0.99566554346996428</v>
+        <v>0.99761105057437038</v>
       </c>
       <c r="AP19">
-        <v>79.46503638398778</v>
+        <v>43.797406136543607</v>
       </c>
       <c r="AR19" t="s">
         <v>414</v>
@@ -10054,16 +10054,16 @@
         <v>936</v>
       </c>
       <c r="BA19" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="BB19" t="s">
-        <v>635</v>
+        <v>883</v>
       </c>
       <c r="BC19">
-        <v>0.99603877136023145</v>
+        <v>0.98853599644984702</v>
       </c>
       <c r="BD19">
-        <v>72.622525062424401</v>
+        <v>210.17339841947171</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -10128,16 +10128,16 @@
         <v>435</v>
       </c>
       <c r="Y20" t="s">
-        <v>393</v>
+        <v>356</v>
       </c>
       <c r="Z20" t="s">
         <v>584</v>
       </c>
       <c r="AA20">
-        <v>0.99600761890991041</v>
+        <v>0.9979392050107273</v>
       </c>
       <c r="AB20">
-        <v>73.193653318309615</v>
+        <v>37.781241469999252</v>
       </c>
       <c r="AD20" t="s">
         <v>414</v>
@@ -10164,16 +10164,16 @@
         <v>671</v>
       </c>
       <c r="AM20" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AN20" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AO20">
-        <v>0.99667664296701652</v>
+        <v>0.99615289372526561</v>
       </c>
       <c r="AP20">
-        <v>60.928212271363194</v>
+        <v>70.530281703464368</v>
       </c>
       <c r="AR20" t="s">
         <v>414</v>
@@ -10200,16 +10200,16 @@
         <v>938</v>
       </c>
       <c r="BA20" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="BB20" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="BC20">
-        <v>0.96206044130113966</v>
+        <v>0.98838558997012138</v>
       </c>
       <c r="BD20">
-        <v>695.55857614577315</v>
+        <v>212.93085054777492</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -10274,16 +10274,16 @@
         <v>437</v>
       </c>
       <c r="Y21" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Z21" t="s">
         <v>585</v>
       </c>
       <c r="AA21">
-        <v>0.99700029739711071</v>
+        <v>0.9982033297630386</v>
       </c>
       <c r="AB21">
-        <v>54.994547719637801</v>
+        <v>32.938954344292306</v>
       </c>
       <c r="AD21" t="s">
         <v>414</v>
@@ -10310,16 +10310,16 @@
         <v>673</v>
       </c>
       <c r="AM21" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AN21" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AO21">
-        <v>0.99608442334318104</v>
+        <v>0.99074948308423383</v>
       </c>
       <c r="AP21">
-        <v>71.785572041680055</v>
+        <v>169.59281012238051</v>
       </c>
       <c r="AR21" t="s">
         <v>414</v>
@@ -10346,16 +10346,16 @@
         <v>940</v>
       </c>
       <c r="BA21" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="BB21" t="s">
-        <v>984</v>
+        <v>883</v>
       </c>
       <c r="BC21">
-        <v>0.98742179529179352</v>
+        <v>0.98730637899749651</v>
       </c>
       <c r="BD21">
-        <v>230.6004196504513</v>
+        <v>232.71638504589731</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -10420,16 +10420,16 @@
         <v>439</v>
       </c>
       <c r="Y22" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="Z22" t="s">
         <v>586</v>
       </c>
       <c r="AA22">
-        <v>0.99408511741207395</v>
+        <v>0.99769372286934066</v>
       </c>
       <c r="AB22">
-        <v>108.43951411197776</v>
+        <v>42.281747395421668</v>
       </c>
       <c r="AD22" t="s">
         <v>414</v>
@@ -10456,16 +10456,16 @@
         <v>675</v>
       </c>
       <c r="AM22" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AN22" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AO22">
-        <v>0.9967907157363165</v>
+        <v>0.99270401267208797</v>
       </c>
       <c r="AP22">
-        <v>58.836878167530941</v>
+        <v>133.75976767838793</v>
       </c>
       <c r="AR22" t="s">
         <v>414</v>
@@ -10495,13 +10495,13 @@
         <v>985</v>
       </c>
       <c r="BB22" t="s">
-        <v>827</v>
+        <v>606</v>
       </c>
       <c r="BC22">
-        <v>0.98389167860462323</v>
+        <v>0.98809190602642238</v>
       </c>
       <c r="BD22">
-        <v>295.31922558190735</v>
+        <v>218.31505618225569</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10566,16 +10566,16 @@
         <v>441</v>
       </c>
       <c r="Y23" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="Z23" t="s">
         <v>587</v>
       </c>
       <c r="AA23">
-        <v>0.99529948277209723</v>
+        <v>0.99579357955795456</v>
       </c>
       <c r="AB23">
-        <v>86.176149178218239</v>
+        <v>77.117708104165573</v>
       </c>
       <c r="AD23" t="s">
         <v>414</v>
@@ -10602,16 +10602,16 @@
         <v>677</v>
       </c>
       <c r="AM23" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AN23" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AO23">
-        <v>0.99443964677468366</v>
+        <v>0.99764772442226368</v>
       </c>
       <c r="AP23">
-        <v>101.93980913079895</v>
+        <v>43.125052258499352</v>
       </c>
       <c r="AR23" t="s">
         <v>414</v>
@@ -10644,10 +10644,10 @@
         <v>987</v>
       </c>
       <c r="BC23">
-        <v>0.98787195157138663</v>
+        <v>0.994208528887633</v>
       </c>
       <c r="BD23">
-        <v>222.34755452457901</v>
+        <v>106.17697039339514</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10712,16 +10712,16 @@
         <v>443</v>
       </c>
       <c r="Y24" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="Z24" t="s">
         <v>588</v>
       </c>
       <c r="AA24">
-        <v>0.99478609753984348</v>
+        <v>0.99066346416517681</v>
       </c>
       <c r="AB24">
-        <v>95.588211769535249</v>
+        <v>171.16982363842584</v>
       </c>
       <c r="AD24" t="s">
         <v>414</v>
@@ -10748,16 +10748,16 @@
         <v>679</v>
       </c>
       <c r="AM24" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AN24" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AO24">
-        <v>0.99761003390352465</v>
+        <v>0.99703044337128366</v>
       </c>
       <c r="AP24">
-        <v>43.816045102048356</v>
+        <v>54.441871526466279</v>
       </c>
       <c r="AR24" t="s">
         <v>414</v>
@@ -10787,13 +10787,13 @@
         <v>988</v>
       </c>
       <c r="BB24" t="s">
-        <v>799</v>
+        <v>989</v>
       </c>
       <c r="BC24">
-        <v>0.98853599644984702</v>
+        <v>0.98734896749216872</v>
       </c>
       <c r="BD24">
-        <v>210.17339841947171</v>
+        <v>231.9355959769062</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10858,16 +10858,16 @@
         <v>445</v>
       </c>
       <c r="Y25" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="Z25" t="s">
         <v>589</v>
       </c>
       <c r="AA25">
-        <v>0.99568525132868968</v>
+        <v>0.99560939477262078</v>
       </c>
       <c r="AB25">
-        <v>79.10372564068922</v>
+        <v>80.494429168619106</v>
       </c>
       <c r="AD25" t="s">
         <v>414</v>
@@ -10894,16 +10894,16 @@
         <v>681</v>
       </c>
       <c r="AM25" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AN25" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AO25">
-        <v>0.99777413567568085</v>
+        <v>0.99245794727704639</v>
       </c>
       <c r="AP25">
-        <v>40.807512612516987</v>
+        <v>138.27096658748206</v>
       </c>
       <c r="AR25" t="s">
         <v>414</v>
@@ -10930,16 +10930,16 @@
         <v>948</v>
       </c>
       <c r="BA25" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="BB25" t="s">
-        <v>990</v>
+        <v>883</v>
       </c>
       <c r="BC25">
-        <v>0.99307601382667698</v>
+        <v>0.98154438143849254</v>
       </c>
       <c r="BD25">
-        <v>126.93974651092147</v>
+        <v>338.35300696097039</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -11004,16 +11004,16 @@
         <v>447</v>
       </c>
       <c r="Y26" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="Z26" t="s">
         <v>590</v>
       </c>
       <c r="AA26">
-        <v>0.99590266392783655</v>
+        <v>0.99544039231362502</v>
       </c>
       <c r="AB26">
-        <v>75.117827989662302</v>
+        <v>83.592807583541571</v>
       </c>
       <c r="AD26" t="s">
         <v>414</v>
@@ -11040,16 +11040,16 @@
         <v>683</v>
       </c>
       <c r="AM26" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AN26" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AO26">
-        <v>0.99425851119451991</v>
+        <v>0.99381230463557813</v>
       </c>
       <c r="AP26">
-        <v>105.26062810046888</v>
+        <v>113.44108168106689</v>
       </c>
       <c r="AR26" t="s">
         <v>414</v>
@@ -11082,10 +11082,10 @@
         <v>992</v>
       </c>
       <c r="BC26">
-        <v>0.99275904397179515</v>
+        <v>0.99308209783432144</v>
       </c>
       <c r="BD26">
-        <v>132.75086051708826</v>
+        <v>126.82820637077275</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -11150,16 +11150,16 @@
         <v>449</v>
       </c>
       <c r="Y27" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="Z27" t="s">
         <v>591</v>
       </c>
       <c r="AA27">
-        <v>0.99449671322390631</v>
+        <v>0.99190124970484694</v>
       </c>
       <c r="AB27">
-        <v>100.89359089505045</v>
+        <v>148.47708874447352</v>
       </c>
       <c r="AD27" t="s">
         <v>414</v>
@@ -11186,16 +11186,16 @@
         <v>685</v>
       </c>
       <c r="AM27" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AN27" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AO27">
-        <v>0.99712282780353001</v>
+        <v>0.99534539864304916</v>
       </c>
       <c r="AP27">
-        <v>52.74815693528295</v>
+        <v>85.3343582107656</v>
       </c>
       <c r="AR27" t="s">
         <v>414</v>
@@ -11228,10 +11228,10 @@
         <v>994</v>
       </c>
       <c r="BC27">
-        <v>0.98137594918937099</v>
+        <v>0.96206044130113966</v>
       </c>
       <c r="BD27">
-        <v>341.44093152819772</v>
+        <v>695.55857614577315</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -11296,16 +11296,16 @@
         <v>451</v>
       </c>
       <c r="Y28" t="s">
-        <v>374</v>
+        <v>412</v>
       </c>
       <c r="Z28" t="s">
         <v>592</v>
       </c>
       <c r="AA28">
-        <v>0.99701127670202949</v>
+        <v>0.9940089461809174</v>
       </c>
       <c r="AB28">
-        <v>54.793260462791778</v>
+        <v>109.83598668318054</v>
       </c>
       <c r="AD28" t="s">
         <v>414</v>
@@ -11332,16 +11332,16 @@
         <v>687</v>
       </c>
       <c r="AM28" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AN28" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AO28">
-        <v>0.99005506097810436</v>
+        <v>0.99310873310996184</v>
       </c>
       <c r="AP28">
-        <v>182.32388206808599</v>
+        <v>126.33989298403215</v>
       </c>
       <c r="AR28" t="s">
         <v>414</v>
@@ -11371,13 +11371,13 @@
         <v>995</v>
       </c>
       <c r="BB28" t="s">
-        <v>984</v>
+        <v>971</v>
       </c>
       <c r="BC28">
-        <v>0.9889956676941275</v>
+        <v>0.98742179529179352</v>
       </c>
       <c r="BD28">
-        <v>201.74609227432916</v>
+        <v>230.6004196504513</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11442,16 +11442,16 @@
         <v>453</v>
       </c>
       <c r="Y29" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="Z29" t="s">
         <v>593</v>
       </c>
       <c r="AA29">
-        <v>0.99125780375299366</v>
+        <v>0.99600761890991041</v>
       </c>
       <c r="AB29">
-        <v>160.27359786178269</v>
+        <v>73.193653318309615</v>
       </c>
       <c r="AD29" t="s">
         <v>414</v>
@@ -11478,16 +11478,16 @@
         <v>689</v>
       </c>
       <c r="AM29" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AN29" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AO29">
-        <v>0.99631269816920021</v>
+        <v>0.99715437961127318</v>
       </c>
       <c r="AP29">
-        <v>67.600533564663479</v>
+        <v>52.169707126657627</v>
       </c>
       <c r="AR29" t="s">
         <v>414</v>
@@ -11517,13 +11517,13 @@
         <v>996</v>
       </c>
       <c r="BB29" t="s">
-        <v>635</v>
+        <v>911</v>
       </c>
       <c r="BC29">
-        <v>0.99193721244794397</v>
+        <v>0.98389167860462323</v>
       </c>
       <c r="BD29">
-        <v>147.81777178769397</v>
+        <v>295.31922558190735</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11588,16 +11588,16 @@
         <v>455</v>
       </c>
       <c r="Y30" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Z30" t="s">
         <v>594</v>
       </c>
       <c r="AA30">
-        <v>0.99619006668481902</v>
+        <v>0.99700029739711071</v>
       </c>
       <c r="AB30">
-        <v>69.848777444984194</v>
+        <v>54.994547719637801</v>
       </c>
       <c r="AD30" t="s">
         <v>414</v>
@@ -11624,16 +11624,16 @@
         <v>691</v>
       </c>
       <c r="AM30" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AN30" t="s">
-        <v>825</v>
+        <v>595</v>
       </c>
       <c r="AO30">
-        <v>0.99772400077475298</v>
+        <v>0.9950502580620818</v>
       </c>
       <c r="AP30">
-        <v>41.726652462862774</v>
+        <v>90.745268861833736</v>
       </c>
       <c r="AR30" t="s">
         <v>414</v>
@@ -11666,10 +11666,10 @@
         <v>998</v>
       </c>
       <c r="BC30">
-        <v>0.98158890816872557</v>
+        <v>0.99526782804010661</v>
       </c>
       <c r="BD30">
-        <v>337.53668357336363</v>
+        <v>86.756485931379871</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11734,16 +11734,16 @@
         <v>457</v>
       </c>
       <c r="Y31" t="s">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="Z31" t="s">
         <v>595</v>
       </c>
       <c r="AA31">
-        <v>0.99021813732178554</v>
+        <v>0.99408511741207395</v>
       </c>
       <c r="AB31">
-        <v>179.3341491005981</v>
+        <v>108.43951411197776</v>
       </c>
       <c r="AD31" t="s">
         <v>414</v>
@@ -11776,10 +11776,10 @@
         <v>827</v>
       </c>
       <c r="AO31">
-        <v>0.99604673274056554</v>
+        <v>0.99618121233373258</v>
       </c>
       <c r="AP31">
-        <v>72.476566422965192</v>
+        <v>70.011107214903078</v>
       </c>
       <c r="AR31" t="s">
         <v>414</v>
@@ -11809,13 +11809,13 @@
         <v>999</v>
       </c>
       <c r="BB31" t="s">
-        <v>643</v>
+        <v>1000</v>
       </c>
       <c r="BC31">
-        <v>0.98402494782096717</v>
+        <v>0.98605138538291048</v>
       </c>
       <c r="BD31">
-        <v>292.87595661560192</v>
+        <v>255.7246013133088</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11880,16 +11880,16 @@
         <v>459</v>
       </c>
       <c r="Y32" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="Z32" t="s">
         <v>596</v>
       </c>
       <c r="AA32">
-        <v>0.99686736582623381</v>
+        <v>0.99529948277209723</v>
       </c>
       <c r="AB32">
-        <v>57.431626519047455</v>
+        <v>86.176149178218239</v>
       </c>
       <c r="AD32" t="s">
         <v>414</v>
@@ -11922,10 +11922,10 @@
         <v>829</v>
       </c>
       <c r="AO32">
-        <v>0.99533901157332205</v>
+        <v>0.99592364356186902</v>
       </c>
       <c r="AP32">
-        <v>85.451454489096079</v>
+        <v>74.733201365734146</v>
       </c>
       <c r="AR32" t="s">
         <v>414</v>
@@ -11952,16 +11952,16 @@
         <v>962</v>
       </c>
       <c r="BA32" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="BB32" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="BC32">
-        <v>0.99223982078870177</v>
+        <v>0.98158890816872557</v>
       </c>
       <c r="BD32">
-        <v>142.26995220713331</v>
+        <v>337.53668357336363</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -12026,16 +12026,16 @@
         <v>461</v>
       </c>
       <c r="Y33" t="s">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="Z33" t="s">
         <v>597</v>
       </c>
       <c r="AA33">
-        <v>0.99725672762159434</v>
+        <v>0.99462937148232844</v>
       </c>
       <c r="AB33">
-        <v>50.29332693743671</v>
+        <v>98.461522823979266</v>
       </c>
       <c r="AD33" t="s">
         <v>414</v>
@@ -12068,10 +12068,10 @@
         <v>831</v>
       </c>
       <c r="AO33">
-        <v>0.99754339130519476</v>
+        <v>0.99641167752379312</v>
       </c>
       <c r="AP33">
-        <v>45.037826071429087</v>
+        <v>65.785912063792665</v>
       </c>
       <c r="AR33" t="s">
         <v>414</v>
@@ -12098,16 +12098,16 @@
         <v>964</v>
       </c>
       <c r="BA33" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="BB33" t="s">
-        <v>1003</v>
+        <v>606</v>
       </c>
       <c r="BC33">
-        <v>0.98734896749216872</v>
+        <v>0.98402494782096717</v>
       </c>
       <c r="BD33">
-        <v>231.9355959769062</v>
+        <v>292.87595661560192</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -12172,16 +12172,16 @@
         <v>463</v>
       </c>
       <c r="Y34" t="s">
-        <v>349</v>
+        <v>405</v>
       </c>
       <c r="Z34" t="s">
         <v>598</v>
       </c>
       <c r="AA34">
-        <v>0.99569491323214321</v>
+        <v>0.99462643269733408</v>
       </c>
       <c r="AB34">
-        <v>78.926590744041093</v>
+        <v>98.51540054887441</v>
       </c>
       <c r="AD34" t="s">
         <v>414</v>
@@ -12214,10 +12214,10 @@
         <v>833</v>
       </c>
       <c r="AO34">
-        <v>0.99542398891280204</v>
+        <v>0.99584476105827657</v>
       </c>
       <c r="AP34">
-        <v>83.893536598629126</v>
+        <v>76.179380598263194</v>
       </c>
       <c r="AR34" t="s">
         <v>414</v>
@@ -12250,10 +12250,10 @@
         <v>1005</v>
       </c>
       <c r="BC34">
-        <v>0.99308209783432144</v>
+        <v>0.99223982078870177</v>
       </c>
       <c r="BD34">
-        <v>126.82820637077275</v>
+        <v>142.26995220713331</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -12318,16 +12318,16 @@
         <v>465</v>
       </c>
       <c r="Y35" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="Z35" t="s">
         <v>599</v>
       </c>
       <c r="AA35">
-        <v>0.99484118006716937</v>
+        <v>0.99755789282691543</v>
       </c>
       <c r="AB35">
-        <v>94.578365435227795</v>
+        <v>44.77196483988353</v>
       </c>
       <c r="AD35" t="s">
         <v>414</v>
@@ -12360,10 +12360,10 @@
         <v>835</v>
       </c>
       <c r="AO35">
-        <v>0.99617615910816915</v>
+        <v>0.9961146125371938</v>
       </c>
       <c r="AP35">
-        <v>70.103749683564772</v>
+        <v>71.232103484781334</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -12428,16 +12428,16 @@
         <v>467</v>
       </c>
       <c r="Y36" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="Z36" t="s">
         <v>600</v>
       </c>
       <c r="AA36">
-        <v>0.99539558382203508</v>
+        <v>0.99246356041150996</v>
       </c>
       <c r="AB36">
-        <v>84.414296596023817</v>
+        <v>138.16805912231732</v>
       </c>
       <c r="AD36" t="s">
         <v>414</v>
@@ -12470,10 +12470,10 @@
         <v>837</v>
       </c>
       <c r="AO36">
-        <v>0.99660391553167893</v>
+        <v>0.99607298561021362</v>
       </c>
       <c r="AP36">
-        <v>62.261548585886977</v>
+        <v>71.995263812749926</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -12538,16 +12538,16 @@
         <v>469</v>
       </c>
       <c r="Y37" t="s">
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="Z37" t="s">
         <v>601</v>
       </c>
       <c r="AA37">
-        <v>0.99557960200072415</v>
+        <v>0.99125780375299366</v>
       </c>
       <c r="AB37">
-        <v>81.040629986723459</v>
+        <v>160.27359786178269</v>
       </c>
       <c r="AD37" t="s">
         <v>414</v>
@@ -12580,10 +12580,10 @@
         <v>839</v>
       </c>
       <c r="AO37">
-        <v>0.9959136876641268</v>
+        <v>0.9929182563937401</v>
       </c>
       <c r="AP37">
-        <v>74.915726157675209</v>
+        <v>129.83196611476453</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12648,16 +12648,16 @@
         <v>471</v>
       </c>
       <c r="Y38" t="s">
-        <v>398</v>
+        <v>348</v>
       </c>
       <c r="Z38" t="s">
         <v>602</v>
       </c>
       <c r="AA38">
-        <v>0.99295357769237991</v>
+        <v>0.99619006668481902</v>
       </c>
       <c r="AB38">
-        <v>129.18440897303603</v>
+        <v>69.848777444984194</v>
       </c>
       <c r="AD38" t="s">
         <v>414</v>
@@ -12690,10 +12690,10 @@
         <v>841</v>
       </c>
       <c r="AO38">
-        <v>0.9935275292913992</v>
+        <v>0.99628542339510884</v>
       </c>
       <c r="AP38">
-        <v>118.66196299101547</v>
+        <v>68.100571089671959</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12758,16 +12758,16 @@
         <v>473</v>
       </c>
       <c r="Y39" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="Z39" t="s">
         <v>603</v>
       </c>
       <c r="AA39">
-        <v>0.99696751363483405</v>
+        <v>0.99021813732178554</v>
       </c>
       <c r="AB39">
-        <v>55.595583361375894</v>
+        <v>179.3341491005981</v>
       </c>
       <c r="AD39" t="s">
         <v>414</v>
@@ -12800,10 +12800,10 @@
         <v>843</v>
       </c>
       <c r="AO39">
-        <v>0.99687120387267125</v>
+        <v>0.99368259233234391</v>
       </c>
       <c r="AP39">
-        <v>57.361262334360205</v>
+        <v>115.81914057369519</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12868,16 +12868,16 @@
         <v>475</v>
       </c>
       <c r="Y40" t="s">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="Z40" t="s">
         <v>604</v>
       </c>
       <c r="AA40">
-        <v>0.98964014500078279</v>
+        <v>0.99686736582623381</v>
       </c>
       <c r="AB40">
-        <v>189.93067498564957</v>
+        <v>57.431626519047455</v>
       </c>
       <c r="AD40" t="s">
         <v>414</v>
@@ -12910,10 +12910,10 @@
         <v>845</v>
       </c>
       <c r="AO40">
-        <v>0.99568571110966864</v>
+        <v>0.9954443722844073</v>
       </c>
       <c r="AP40">
-        <v>79.095296322741547</v>
+        <v>83.519841452532361</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12978,16 +12978,16 @@
         <v>477</v>
       </c>
       <c r="Y41" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="Z41" t="s">
         <v>605</v>
       </c>
       <c r="AA41">
-        <v>0.9966137462997855</v>
+        <v>0.99725672762159434</v>
       </c>
       <c r="AB41">
-        <v>62.081317837266766</v>
+        <v>50.29332693743671</v>
       </c>
       <c r="AD41" t="s">
         <v>414</v>
@@ -13020,10 +13020,10 @@
         <v>847</v>
       </c>
       <c r="AO41">
-        <v>0.99609062270337045</v>
+        <v>0.99363040616365128</v>
       </c>
       <c r="AP41">
-        <v>71.671917104874566</v>
+        <v>116.77588699972566</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -13088,16 +13088,16 @@
         <v>479</v>
       </c>
       <c r="Y42" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="Z42" t="s">
         <v>606</v>
       </c>
       <c r="AA42">
-        <v>0.99011796851295664</v>
+        <v>0.99282834435956602</v>
       </c>
       <c r="AB42">
-        <v>181.17057726246117</v>
+        <v>131.48035340795542</v>
       </c>
       <c r="AD42" t="s">
         <v>414</v>
@@ -13130,10 +13130,10 @@
         <v>849</v>
       </c>
       <c r="AO42">
-        <v>0.99598588086244633</v>
+        <v>0.99782402570187057</v>
       </c>
       <c r="AP42">
-        <v>73.592184188484865</v>
+        <v>39.892862132373601</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -13198,16 +13198,16 @@
         <v>481</v>
       </c>
       <c r="Y43" t="s">
-        <v>391</v>
+        <v>344</v>
       </c>
       <c r="Z43" t="s">
         <v>607</v>
       </c>
       <c r="AA43">
-        <v>0.99635118654529808</v>
+        <v>0.99569310304523451</v>
       </c>
       <c r="AB43">
-        <v>66.894913336202478</v>
+        <v>78.959777504033639</v>
       </c>
       <c r="AD43" t="s">
         <v>414</v>
@@ -13240,10 +13240,10 @@
         <v>851</v>
       </c>
       <c r="AO43">
-        <v>0.99074948308423383</v>
+        <v>0.99756462867082185</v>
       </c>
       <c r="AP43">
-        <v>169.59281012238051</v>
+        <v>44.648474368267038</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -13308,16 +13308,16 @@
         <v>483</v>
       </c>
       <c r="Y44" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="Z44" t="s">
         <v>608</v>
       </c>
       <c r="AA44">
-        <v>0.99440507690252466</v>
+        <v>0.99502431999137919</v>
       </c>
       <c r="AB44">
-        <v>102.57359012038077</v>
+        <v>91.220800158047325</v>
       </c>
       <c r="AD44" t="s">
         <v>414</v>
@@ -13350,10 +13350,10 @@
         <v>853</v>
       </c>
       <c r="AO44">
-        <v>0.99270401267208797</v>
+        <v>0.99439150850611324</v>
       </c>
       <c r="AP44">
-        <v>133.75976767838793</v>
+        <v>102.82234405458999</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -13418,16 +13418,16 @@
         <v>485</v>
       </c>
       <c r="Y45" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="Z45" t="s">
         <v>609</v>
       </c>
       <c r="AA45">
-        <v>0.99675394464629852</v>
+        <v>0.99584577617815018</v>
       </c>
       <c r="AB45">
-        <v>59.511014817860868</v>
+        <v>76.16077006724673</v>
       </c>
       <c r="AD45" t="s">
         <v>414</v>
@@ -13460,10 +13460,10 @@
         <v>855</v>
       </c>
       <c r="AO45">
-        <v>0.99764772442226368</v>
+        <v>0.99595416313893737</v>
       </c>
       <c r="AP45">
-        <v>43.125052258499352</v>
+        <v>74.173675786148877</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13528,16 +13528,16 @@
         <v>487</v>
       </c>
       <c r="Y46" t="s">
-        <v>369</v>
+        <v>338</v>
       </c>
       <c r="Z46" t="s">
         <v>610</v>
       </c>
       <c r="AA46">
-        <v>0.9962437778559039</v>
+        <v>0.99080344458411729</v>
       </c>
       <c r="AB46">
-        <v>68.86407264176249</v>
+        <v>168.60351595784994</v>
       </c>
       <c r="AD46" t="s">
         <v>414</v>
@@ -13570,10 +13570,10 @@
         <v>857</v>
       </c>
       <c r="AO46">
-        <v>0.99703044337128366</v>
+        <v>0.99687821505939955</v>
       </c>
       <c r="AP46">
-        <v>54.441871526466279</v>
+        <v>57.232723911007447</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13638,16 +13638,16 @@
         <v>489</v>
       </c>
       <c r="Y47" t="s">
-        <v>371</v>
+        <v>410</v>
       </c>
       <c r="Z47" t="s">
         <v>611</v>
       </c>
       <c r="AA47">
-        <v>0.99617006411660358</v>
+        <v>0.98636012609964985</v>
       </c>
       <c r="AB47">
-        <v>70.215491195600634</v>
+        <v>250.06435483975247</v>
       </c>
       <c r="AD47" t="s">
         <v>414</v>
@@ -13680,10 +13680,10 @@
         <v>859</v>
       </c>
       <c r="AO47">
-        <v>0.99618121233373258</v>
+        <v>0.99568571110966864</v>
       </c>
       <c r="AP47">
-        <v>70.011107214903078</v>
+        <v>79.095296322741547</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13748,16 +13748,16 @@
         <v>491</v>
       </c>
       <c r="Y48" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="Z48" t="s">
         <v>612</v>
       </c>
       <c r="AA48">
-        <v>0.99462937148232844</v>
+        <v>0.99598850450039844</v>
       </c>
       <c r="AB48">
-        <v>98.461522823979266</v>
+        <v>73.544084159361034</v>
       </c>
       <c r="AD48" t="s">
         <v>414</v>
@@ -13790,10 +13790,10 @@
         <v>861</v>
       </c>
       <c r="AO48">
-        <v>0.99592364356186902</v>
+        <v>0.99609062270337045</v>
       </c>
       <c r="AP48">
-        <v>74.733201365734146</v>
+        <v>71.671917104874566</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -13858,16 +13858,16 @@
         <v>493</v>
       </c>
       <c r="Y49" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="Z49" t="s">
         <v>613</v>
       </c>
       <c r="AA49">
-        <v>0.99462643269733408</v>
+        <v>0.99310312827752323</v>
       </c>
       <c r="AB49">
-        <v>98.51540054887441</v>
+        <v>126.44264824540761</v>
       </c>
       <c r="AD49" t="s">
         <v>414</v>
@@ -13900,10 +13900,10 @@
         <v>863</v>
       </c>
       <c r="AO49">
-        <v>0.99641167752379312</v>
+        <v>0.99598588086244633</v>
       </c>
       <c r="AP49">
-        <v>65.785912063792665</v>
+        <v>73.592184188484865</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -13968,16 +13968,16 @@
         <v>495</v>
       </c>
       <c r="Y50" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="Z50" t="s">
         <v>614</v>
       </c>
       <c r="AA50">
-        <v>0.99755789282691543</v>
+        <v>0.99478609753984348</v>
       </c>
       <c r="AB50">
-        <v>44.77196483988353</v>
+        <v>95.588211769535249</v>
       </c>
       <c r="AD50" t="s">
         <v>414</v>
@@ -14010,10 +14010,10 @@
         <v>865</v>
       </c>
       <c r="AO50">
-        <v>0.99611612132862803</v>
+        <v>0.99540934349034305</v>
       </c>
       <c r="AP50">
-        <v>71.204442308486065</v>
+        <v>84.162036010377406</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -14078,16 +14078,16 @@
         <v>497</v>
       </c>
       <c r="Y51" t="s">
-        <v>377</v>
+        <v>345</v>
       </c>
       <c r="Z51" t="s">
         <v>615</v>
       </c>
       <c r="AA51">
-        <v>0.99246356041150996</v>
+        <v>0.99568525132868968</v>
       </c>
       <c r="AB51">
-        <v>138.16805912231732</v>
+        <v>79.10372564068922</v>
       </c>
       <c r="AD51" t="s">
         <v>414</v>
@@ -14120,10 +14120,10 @@
         <v>867</v>
       </c>
       <c r="AO51">
-        <v>0.99761105057437038</v>
+        <v>0.99657664224037934</v>
       </c>
       <c r="AP51">
-        <v>43.797406136543607</v>
+        <v>62.761558926379031</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -14188,16 +14188,16 @@
         <v>499</v>
       </c>
       <c r="Y52" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z52" t="s">
         <v>616</v>
       </c>
       <c r="AA52">
-        <v>0.99571525957109708</v>
+        <v>0.99590266392783655</v>
       </c>
       <c r="AB52">
-        <v>78.553574529886689</v>
+        <v>75.117827989662302</v>
       </c>
       <c r="AD52" t="s">
         <v>414</v>
@@ -14230,10 +14230,10 @@
         <v>869</v>
       </c>
       <c r="AO52">
-        <v>0.99615289372526561</v>
+        <v>0.99091245964276031</v>
       </c>
       <c r="AP52">
-        <v>70.530281703464368</v>
+        <v>166.60490654939525</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -14298,16 +14298,16 @@
         <v>501</v>
       </c>
       <c r="Y53" t="s">
-        <v>394</v>
+        <v>357</v>
       </c>
       <c r="Z53" t="s">
         <v>617</v>
       </c>
       <c r="AA53">
-        <v>0.99553579843385909</v>
+        <v>0.99449671322390631</v>
       </c>
       <c r="AB53">
-        <v>81.84369537924907</v>
+        <v>100.89359089505045</v>
       </c>
       <c r="AD53" t="s">
         <v>414</v>
@@ -14340,10 +14340,10 @@
         <v>871</v>
       </c>
       <c r="AO53">
-        <v>0.99720397512579328</v>
+        <v>0.99846230399777702</v>
       </c>
       <c r="AP53">
-        <v>51.260456027123361</v>
+        <v>28.191093374087806</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -14408,16 +14408,16 @@
         <v>503</v>
       </c>
       <c r="Y54" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="Z54" t="s">
         <v>618</v>
       </c>
       <c r="AA54">
-        <v>0.99734372305564056</v>
+        <v>0.99701127670202949</v>
       </c>
       <c r="AB54">
-        <v>48.698410646589842</v>
+        <v>54.793260462791778</v>
       </c>
       <c r="AD54" t="s">
         <v>414</v>
@@ -14450,10 +14450,10 @@
         <v>873</v>
       </c>
       <c r="AO54">
-        <v>0.99565348329230585</v>
+        <v>0.99720397512579328</v>
       </c>
       <c r="AP54">
-        <v>79.686139641060379</v>
+        <v>51.260456027123361</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -14518,16 +14518,16 @@
         <v>505</v>
       </c>
       <c r="Y55" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="Z55" t="s">
         <v>619</v>
       </c>
       <c r="AA55">
-        <v>0.99662670467221526</v>
+        <v>0.99540885392130762</v>
       </c>
       <c r="AB55">
-        <v>61.843747676054292</v>
+        <v>84.171011442693441</v>
       </c>
       <c r="AD55" t="s">
         <v>414</v>
@@ -14560,10 +14560,10 @@
         <v>875</v>
       </c>
       <c r="AO55">
-        <v>0.99368259233234391</v>
+        <v>0.99565348329230585</v>
       </c>
       <c r="AP55">
-        <v>115.81914057369519</v>
+        <v>79.686139641060379</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -14628,16 +14628,16 @@
         <v>507</v>
       </c>
       <c r="Y56" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="Z56" t="s">
         <v>620</v>
       </c>
       <c r="AA56">
-        <v>0.99740761205901929</v>
+        <v>0.99360802526828129</v>
       </c>
       <c r="AB56">
-        <v>47.527112251312907</v>
+        <v>117.18620341484296</v>
       </c>
       <c r="AD56" t="s">
         <v>414</v>
@@ -14670,10 +14670,10 @@
         <v>877</v>
       </c>
       <c r="AO56">
-        <v>0.9954443722844073</v>
+        <v>0.99784941409648109</v>
       </c>
       <c r="AP56">
-        <v>83.519841452532361</v>
+        <v>39.427408231180806</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -14738,16 +14738,16 @@
         <v>509</v>
       </c>
       <c r="Y57" t="s">
-        <v>368</v>
+        <v>400</v>
       </c>
       <c r="Z57" t="s">
         <v>621</v>
       </c>
       <c r="AA57">
-        <v>0.99730769203227776</v>
+        <v>0.99515679011930902</v>
       </c>
       <c r="AB57">
-        <v>49.358979408241737</v>
+        <v>88.792181146001369</v>
       </c>
       <c r="AD57" t="s">
         <v>414</v>
@@ -14780,10 +14780,10 @@
         <v>879</v>
       </c>
       <c r="AO57">
-        <v>0.99363040616365128</v>
+        <v>0.99831921281104818</v>
       </c>
       <c r="AP57">
-        <v>116.77588699972566</v>
+        <v>30.814431797450247</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -14848,16 +14848,16 @@
         <v>511</v>
       </c>
       <c r="Y58" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="Z58" t="s">
         <v>622</v>
       </c>
       <c r="AA58">
-        <v>0.998073964784436</v>
+        <v>0.99409145347725225</v>
       </c>
       <c r="AB58">
-        <v>35.310645618673441</v>
+        <v>108.32335291704148</v>
       </c>
       <c r="AD58" t="s">
         <v>414</v>
@@ -14890,10 +14890,10 @@
         <v>881</v>
       </c>
       <c r="AO58">
-        <v>0.99782402570187057</v>
+        <v>0.99845356202909108</v>
       </c>
       <c r="AP58">
-        <v>39.892862132373601</v>
+        <v>28.351362799997673</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -14958,16 +14958,16 @@
         <v>513</v>
       </c>
       <c r="Y59" t="s">
-        <v>403</v>
+        <v>381</v>
       </c>
       <c r="Z59" t="s">
         <v>623</v>
       </c>
       <c r="AA59">
-        <v>0.99670408962762203</v>
+        <v>0.99464051280908794</v>
       </c>
       <c r="AB59">
-        <v>60.425023493595695</v>
+        <v>98.257265166721183</v>
       </c>
       <c r="AD59" t="s">
         <v>414</v>
@@ -15000,10 +15000,10 @@
         <v>883</v>
       </c>
       <c r="AO59">
-        <v>0.99756462867082185</v>
+        <v>0.99418244113372889</v>
       </c>
       <c r="AP59">
-        <v>44.648474368267038</v>
+        <v>106.6552458816375</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -15068,16 +15068,16 @@
         <v>515</v>
       </c>
       <c r="Y60" t="s">
-        <v>358</v>
+        <v>403</v>
       </c>
       <c r="Z60" t="s">
         <v>624</v>
       </c>
       <c r="AA60">
-        <v>0.9960389195261472</v>
+        <v>0.99670408962762203</v>
       </c>
       <c r="AB60">
-        <v>72.619808687301173</v>
+        <v>60.425023493595695</v>
       </c>
       <c r="AD60" t="s">
         <v>414</v>
@@ -15110,10 +15110,10 @@
         <v>885</v>
       </c>
       <c r="AO60">
-        <v>0.99540934349034305</v>
+        <v>0.99206751173516827</v>
       </c>
       <c r="AP60">
-        <v>84.162036010377406</v>
+        <v>145.42895152191466</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -15178,16 +15178,16 @@
         <v>517</v>
       </c>
       <c r="Y61" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="Z61" t="s">
         <v>625</v>
       </c>
       <c r="AA61">
-        <v>0.99707957985864093</v>
+        <v>0.9960389195261472</v>
       </c>
       <c r="AB61">
-        <v>53.541035924916123</v>
+        <v>72.619808687301173</v>
       </c>
       <c r="AD61" t="s">
         <v>414</v>
@@ -15220,10 +15220,10 @@
         <v>887</v>
       </c>
       <c r="AO61">
-        <v>0.99657664224037934</v>
+        <v>0.99566554346996428</v>
       </c>
       <c r="AP61">
-        <v>62.761558926379031</v>
+        <v>79.46503638398778</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -15288,16 +15288,16 @@
         <v>519</v>
       </c>
       <c r="Y62" t="s">
-        <v>337</v>
+        <v>372</v>
       </c>
       <c r="Z62" t="s">
         <v>626</v>
       </c>
       <c r="AA62">
-        <v>0.99551989204648861</v>
+        <v>0.99707957985864093</v>
       </c>
       <c r="AB62">
-        <v>82.135312481041623</v>
+        <v>53.541035924916123</v>
       </c>
       <c r="AD62" t="s">
         <v>414</v>
@@ -15330,10 +15330,10 @@
         <v>889</v>
       </c>
       <c r="AO62">
-        <v>0.99091245964276031</v>
+        <v>0.99667664296701652</v>
       </c>
       <c r="AP62">
-        <v>166.60490654939525</v>
+        <v>60.928212271363194</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -15398,16 +15398,16 @@
         <v>521</v>
       </c>
       <c r="Y63" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="Z63" t="s">
         <v>627</v>
       </c>
       <c r="AA63">
-        <v>0.9979392050107273</v>
+        <v>0.99578350963230966</v>
       </c>
       <c r="AB63">
-        <v>37.781241469999252</v>
+        <v>77.302323407656075</v>
       </c>
       <c r="AD63" t="s">
         <v>414</v>
@@ -15440,10 +15440,10 @@
         <v>891</v>
       </c>
       <c r="AO63">
-        <v>0.99846230399777702</v>
+        <v>0.99608442334318104</v>
       </c>
       <c r="AP63">
-        <v>28.191093374087806</v>
+        <v>71.785572041680055</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -15508,16 +15508,16 @@
         <v>523</v>
       </c>
       <c r="Y64" t="s">
-        <v>354</v>
+        <v>407</v>
       </c>
       <c r="Z64" t="s">
         <v>628</v>
       </c>
       <c r="AA64">
-        <v>0.9982033297630386</v>
+        <v>0.99720191150310689</v>
       </c>
       <c r="AB64">
-        <v>32.938954344292306</v>
+        <v>51.298289109706943</v>
       </c>
       <c r="AD64" t="s">
         <v>414</v>
@@ -15550,10 +15550,10 @@
         <v>893</v>
       </c>
       <c r="AO64">
-        <v>0.99584476105827657</v>
+        <v>0.9967907157363165</v>
       </c>
       <c r="AP64">
-        <v>76.179380598263194</v>
+        <v>58.836878167530941</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -15618,16 +15618,16 @@
         <v>525</v>
       </c>
       <c r="Y65" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="Z65" t="s">
         <v>629</v>
       </c>
       <c r="AA65">
-        <v>0.99769372286934066</v>
+        <v>0.9954551465796494</v>
       </c>
       <c r="AB65">
-        <v>42.281747395421668</v>
+        <v>83.32231270642734</v>
       </c>
       <c r="AD65" t="s">
         <v>414</v>
@@ -15660,10 +15660,10 @@
         <v>895</v>
       </c>
       <c r="AO65">
-        <v>0.9961146125371938</v>
+        <v>0.99443964677468366</v>
       </c>
       <c r="AP65">
-        <v>71.232103484781334</v>
+        <v>101.93980913079895</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -15728,16 +15728,16 @@
         <v>527</v>
       </c>
       <c r="Y66" t="s">
-        <v>338</v>
+        <v>399</v>
       </c>
       <c r="Z66" t="s">
         <v>630</v>
       </c>
       <c r="AA66">
-        <v>0.99080344458411729</v>
+        <v>0.99552053983611355</v>
       </c>
       <c r="AB66">
-        <v>168.60351595784994</v>
+        <v>82.123436337918946</v>
       </c>
       <c r="AD66" t="s">
         <v>414</v>
@@ -15770,10 +15770,10 @@
         <v>897</v>
       </c>
       <c r="AO66">
-        <v>0.99607298561021362</v>
+        <v>0.99761003390352465</v>
       </c>
       <c r="AP66">
-        <v>71.995263812749926</v>
+        <v>43.816045102048356</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -15838,16 +15838,16 @@
         <v>529</v>
       </c>
       <c r="Y67" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="Z67" t="s">
         <v>631</v>
       </c>
       <c r="AA67">
-        <v>0.98636012609964985</v>
+        <v>0.98935435476104872</v>
       </c>
       <c r="AB67">
-        <v>250.06435483975247</v>
+        <v>195.1701627141077</v>
       </c>
       <c r="AD67" t="s">
         <v>414</v>
@@ -15880,10 +15880,10 @@
         <v>899</v>
       </c>
       <c r="AO67">
-        <v>0.9929182563937401</v>
+        <v>0.99777413567568085</v>
       </c>
       <c r="AP67">
-        <v>129.83196611476453</v>
+        <v>40.807512612516987</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -15948,16 +15948,16 @@
         <v>531</v>
       </c>
       <c r="Y68" t="s">
-        <v>343</v>
+        <v>392</v>
       </c>
       <c r="Z68" t="s">
         <v>632</v>
       </c>
       <c r="AA68">
-        <v>0.99598850450039844</v>
+        <v>0.99775872574768198</v>
       </c>
       <c r="AB68">
-        <v>73.544084159361034</v>
+        <v>41.090027959164246</v>
       </c>
       <c r="AD68" t="s">
         <v>414</v>
@@ -15990,10 +15990,10 @@
         <v>901</v>
       </c>
       <c r="AO68">
-        <v>0.99628542339510884</v>
+        <v>0.99425851119451991</v>
       </c>
       <c r="AP68">
-        <v>68.100571089671959</v>
+        <v>105.26062810046888</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -16058,16 +16058,16 @@
         <v>533</v>
       </c>
       <c r="Y69" t="s">
-        <v>409</v>
+        <v>336</v>
       </c>
       <c r="Z69" t="s">
         <v>633</v>
       </c>
       <c r="AA69">
-        <v>0.99310312827752323</v>
+        <v>0.99359748433922845</v>
       </c>
       <c r="AB69">
-        <v>126.44264824540761</v>
+        <v>117.37945378081078</v>
       </c>
       <c r="AD69" t="s">
         <v>414</v>
@@ -16100,10 +16100,10 @@
         <v>903</v>
       </c>
       <c r="AO69">
-        <v>0.99474825047892679</v>
+        <v>0.99712282780353001</v>
       </c>
       <c r="AP69">
-        <v>96.282074553009053</v>
+        <v>52.74815693528295</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -16168,16 +16168,16 @@
         <v>535</v>
       </c>
       <c r="Y70" t="s">
-        <v>336</v>
+        <v>406</v>
       </c>
       <c r="Z70" t="s">
         <v>634</v>
       </c>
       <c r="AA70">
-        <v>0.99359748433922845</v>
+        <v>0.99592552983543692</v>
       </c>
       <c r="AB70">
-        <v>117.37945378081078</v>
+        <v>74.698619683656872</v>
       </c>
       <c r="AD70" t="s">
         <v>414</v>
@@ -16210,10 +16210,10 @@
         <v>905</v>
       </c>
       <c r="AO70">
-        <v>0.99684527597966854</v>
+        <v>0.99005506097810436</v>
       </c>
       <c r="AP70">
-        <v>57.836607039410005</v>
+        <v>182.32388206808599</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -16278,16 +16278,16 @@
         <v>537</v>
       </c>
       <c r="Y71" t="s">
-        <v>406</v>
+        <v>366</v>
       </c>
       <c r="Z71" t="s">
         <v>635</v>
       </c>
       <c r="AA71">
-        <v>0.99592552983543692</v>
+        <v>0.99463677905825021</v>
       </c>
       <c r="AB71">
-        <v>74.698619683656872</v>
+        <v>98.325717265413417</v>
       </c>
       <c r="AD71" t="s">
         <v>414</v>
@@ -16320,10 +16320,10 @@
         <v>907</v>
       </c>
       <c r="AO71">
-        <v>0.9943927545810437</v>
+        <v>0.99631269816920021</v>
       </c>
       <c r="AP71">
-        <v>102.79949934753229</v>
+        <v>67.600533564663479</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -16388,16 +16388,16 @@
         <v>539</v>
       </c>
       <c r="Y72" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z72" t="s">
         <v>636</v>
       </c>
       <c r="AA72">
-        <v>0.99463677905825021</v>
+        <v>0.99667564038633161</v>
       </c>
       <c r="AB72">
-        <v>98.325717265413417</v>
+        <v>60.946592917253042</v>
       </c>
       <c r="AD72" t="s">
         <v>414</v>
@@ -16430,10 +16430,10 @@
         <v>909</v>
       </c>
       <c r="AO72">
-        <v>0.99784941409648109</v>
+        <v>0.99772400077475298</v>
       </c>
       <c r="AP72">
-        <v>39.427408231180806</v>
+        <v>41.726652462862774</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -16498,16 +16498,16 @@
         <v>541</v>
       </c>
       <c r="Y73" t="s">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="Z73" t="s">
         <v>637</v>
       </c>
       <c r="AA73">
-        <v>0.99667564038633161</v>
+        <v>0.99571525957109708</v>
       </c>
       <c r="AB73">
-        <v>60.946592917253042</v>
+        <v>78.553574529886689</v>
       </c>
       <c r="AD73" t="s">
         <v>414</v>
@@ -16540,10 +16540,10 @@
         <v>911</v>
       </c>
       <c r="AO73">
-        <v>0.99831921281104818</v>
+        <v>0.99604673274056554</v>
       </c>
       <c r="AP73">
-        <v>30.814431797450247</v>
+        <v>72.476566422965192</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -16608,16 +16608,16 @@
         <v>543</v>
       </c>
       <c r="Y74" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Z74" t="s">
         <v>638</v>
       </c>
       <c r="AA74">
-        <v>0.99540885392130762</v>
+        <v>0.99553579843385909</v>
       </c>
       <c r="AB74">
-        <v>84.171011442693441</v>
+        <v>81.84369537924907</v>
       </c>
       <c r="AD74" t="s">
         <v>414</v>
@@ -16650,10 +16650,10 @@
         <v>913</v>
       </c>
       <c r="AO74">
-        <v>0.99845356202909108</v>
+        <v>0.99533901157332205</v>
       </c>
       <c r="AP74">
-        <v>28.351362799997673</v>
+        <v>85.451454489096079</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -16718,16 +16718,16 @@
         <v>545</v>
       </c>
       <c r="Y75" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Z75" t="s">
         <v>639</v>
       </c>
       <c r="AA75">
-        <v>0.99360802526828129</v>
+        <v>0.99734372305564056</v>
       </c>
       <c r="AB75">
-        <v>117.18620341484296</v>
+        <v>48.698410646589842</v>
       </c>
       <c r="AD75" t="s">
         <v>414</v>
@@ -16760,10 +16760,10 @@
         <v>915</v>
       </c>
       <c r="AO75">
-        <v>0.99439150850611324</v>
+        <v>0.99754339130519476</v>
       </c>
       <c r="AP75">
-        <v>102.82234405458999</v>
+        <v>45.037826071429087</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -16828,16 +16828,16 @@
         <v>547</v>
       </c>
       <c r="Y76" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="Z76" t="s">
         <v>640</v>
       </c>
       <c r="AA76">
-        <v>0.99515679011930902</v>
+        <v>0.99662670467221526</v>
       </c>
       <c r="AB76">
-        <v>88.792181146001369</v>
+        <v>61.843747676054292</v>
       </c>
       <c r="AD76" t="s">
         <v>414</v>
@@ -16870,10 +16870,10 @@
         <v>917</v>
       </c>
       <c r="AO76">
-        <v>0.99595416313893737</v>
+        <v>0.99542398891280204</v>
       </c>
       <c r="AP76">
-        <v>74.173675786148877</v>
+        <v>83.893536598629126</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -16938,16 +16938,16 @@
         <v>549</v>
       </c>
       <c r="Y77" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="Z77" t="s">
         <v>641</v>
       </c>
       <c r="AA77">
-        <v>0.99409145347725225</v>
+        <v>0.99740761205901929</v>
       </c>
       <c r="AB77">
-        <v>108.32335291704148</v>
+        <v>47.527112251312907</v>
       </c>
       <c r="AD77" t="s">
         <v>414</v>
@@ -16980,10 +16980,10 @@
         <v>919</v>
       </c>
       <c r="AO77">
-        <v>0.99687821505939955</v>
+        <v>0.99617615910816915</v>
       </c>
       <c r="AP77">
-        <v>57.232723911007447</v>
+        <v>70.103749683564772</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -17048,16 +17048,16 @@
         <v>551</v>
       </c>
       <c r="Y78" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="Z78" t="s">
         <v>642</v>
       </c>
       <c r="AA78">
-        <v>0.99464051280908794</v>
+        <v>0.99730769203227776</v>
       </c>
       <c r="AB78">
-        <v>98.257265166721183</v>
+        <v>49.358979408241737</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -17122,16 +17122,16 @@
         <v>553</v>
       </c>
       <c r="Y79" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="Z79" t="s">
         <v>643</v>
       </c>
       <c r="AA79">
-        <v>0.99282834435956602</v>
+        <v>0.998073964784436</v>
       </c>
       <c r="AB79">
-        <v>131.48035340795542</v>
+        <v>35.310645618673441</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -17196,16 +17196,16 @@
         <v>555</v>
       </c>
       <c r="Y80" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="Z80" t="s">
         <v>644</v>
       </c>
       <c r="AA80">
-        <v>0.99569310304523451</v>
+        <v>0.99569491323214321</v>
       </c>
       <c r="AB80">
-        <v>78.959777504033639</v>
+        <v>78.926590744041093</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -17270,16 +17270,16 @@
         <v>557</v>
       </c>
       <c r="Y81" t="s">
-        <v>411</v>
+        <v>382</v>
       </c>
       <c r="Z81" t="s">
         <v>645</v>
       </c>
       <c r="AA81">
-        <v>0.99502431999137919</v>
+        <v>0.99484118006716937</v>
       </c>
       <c r="AB81">
-        <v>91.220800158047325</v>
+        <v>94.578365435227795</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -17344,16 +17344,16 @@
         <v>559</v>
       </c>
       <c r="Y82" t="s">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="Z82" t="s">
         <v>646</v>
       </c>
       <c r="AA82">
-        <v>0.99584577617815018</v>
+        <v>0.99539558382203508</v>
       </c>
       <c r="AB82">
-        <v>76.16077006724673</v>
+        <v>84.414296596023817</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -17418,16 +17418,16 @@
         <v>561</v>
       </c>
       <c r="Y83" t="s">
-        <v>335</v>
+        <v>404</v>
       </c>
       <c r="Z83" t="s">
         <v>647</v>
       </c>
       <c r="AA83">
-        <v>0.99578350963230966</v>
+        <v>0.99675394464629852</v>
       </c>
       <c r="AB83">
-        <v>77.302323407656075</v>
+        <v>59.511014817860868</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -17492,16 +17492,16 @@
         <v>563</v>
       </c>
       <c r="Y84" t="s">
-        <v>407</v>
+        <v>369</v>
       </c>
       <c r="Z84" t="s">
         <v>648</v>
       </c>
       <c r="AA84">
-        <v>0.99720191150310689</v>
+        <v>0.9962437778559039</v>
       </c>
       <c r="AB84">
-        <v>51.298289109706943</v>
+        <v>68.86407264176249</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -17566,16 +17566,16 @@
         <v>565</v>
       </c>
       <c r="Y85" t="s">
-        <v>401</v>
+        <v>371</v>
       </c>
       <c r="Z85" t="s">
         <v>649</v>
       </c>
       <c r="AA85">
-        <v>0.9954551465796494</v>
+        <v>0.99617006411660358</v>
       </c>
       <c r="AB85">
-        <v>83.32231270642734</v>
+        <v>70.215491195600634</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -17640,16 +17640,16 @@
         <v>567</v>
       </c>
       <c r="Y86" t="s">
-        <v>399</v>
+        <v>359</v>
       </c>
       <c r="Z86" t="s">
         <v>650</v>
       </c>
       <c r="AA86">
-        <v>0.99552053983611355</v>
+        <v>0.99699505644961572</v>
       </c>
       <c r="AB86">
-        <v>82.123436337918946</v>
+        <v>55.090631757044932</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -17714,16 +17714,16 @@
         <v>569</v>
       </c>
       <c r="Y87" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="Z87" t="s">
         <v>651</v>
       </c>
       <c r="AA87">
-        <v>0.98935435476104872</v>
+        <v>0.99170691261633115</v>
       </c>
       <c r="AB87">
-        <v>195.1701627141077</v>
+        <v>152.03993536726261</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -17788,16 +17788,16 @@
         <v>571</v>
       </c>
       <c r="Y88" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="Z88" t="s">
         <v>652</v>
       </c>
       <c r="AA88">
-        <v>0.99775872574768198</v>
+        <v>0.9904035062850528</v>
       </c>
       <c r="AB88">
-        <v>41.090027959164246</v>
+        <v>175.93571810736526</v>
       </c>
     </row>
   </sheetData>
@@ -17806,7 +17806,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC7E37C-B954-44A0-A03C-328FC0A82B0A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA55AE6B-2828-4A51-AA49-E610E69602A6}">
   <dimension ref="B9:Z77"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17918,7 +17918,7 @@
         <v>1006</v>
       </c>
       <c r="K11" t="s">
-        <v>896</v>
+        <v>836</v>
       </c>
       <c r="L11">
         <v>29.7146465744454</v>
@@ -17951,7 +17951,7 @@
         <v>1140</v>
       </c>
       <c r="X11" t="s">
-        <v>981</v>
+        <v>993</v>
       </c>
       <c r="Y11">
         <v>0.33825</v>
@@ -17986,7 +17986,7 @@
         <v>1008</v>
       </c>
       <c r="K12" t="s">
-        <v>797</v>
+        <v>825</v>
       </c>
       <c r="L12">
         <v>13.367096811591049</v>
@@ -18019,7 +18019,7 @@
         <v>1142</v>
       </c>
       <c r="X12" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="Y12">
         <v>10.88325</v>
@@ -18054,7 +18054,7 @@
         <v>1010</v>
       </c>
       <c r="K13" t="s">
-        <v>834</v>
+        <v>918</v>
       </c>
       <c r="L13">
         <v>24.156328337033791</v>
@@ -18087,7 +18087,7 @@
         <v>1144</v>
       </c>
       <c r="X13" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="Y13">
         <v>26.983499999999999</v>
@@ -18122,7 +18122,7 @@
         <v>1012</v>
       </c>
       <c r="K14" t="s">
-        <v>830</v>
+        <v>914</v>
       </c>
       <c r="L14">
         <v>16.006796560234815</v>
@@ -18155,7 +18155,7 @@
         <v>1146</v>
       </c>
       <c r="X14" t="s">
-        <v>1002</v>
+        <v>988</v>
       </c>
       <c r="Y14">
         <v>42.507750000000001</v>
@@ -18190,7 +18190,7 @@
         <v>1014</v>
       </c>
       <c r="K15" t="s">
-        <v>793</v>
+        <v>821</v>
       </c>
       <c r="L15">
         <v>17.682358378036344</v>
@@ -18223,7 +18223,7 @@
         <v>1148</v>
       </c>
       <c r="X15" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="Y15">
         <v>24.900749999999999</v>
@@ -18258,7 +18258,7 @@
         <v>1016</v>
       </c>
       <c r="K16" t="s">
-        <v>912</v>
+        <v>880</v>
       </c>
       <c r="L16">
         <v>29.492382648463739</v>
@@ -18291,7 +18291,7 @@
         <v>1150</v>
       </c>
       <c r="X16" t="s">
-        <v>986</v>
+        <v>979</v>
       </c>
       <c r="Y16">
         <v>18.545249999999999</v>
@@ -18326,7 +18326,7 @@
         <v>1018</v>
       </c>
       <c r="K17" t="s">
-        <v>910</v>
+        <v>878</v>
       </c>
       <c r="L17">
         <v>8.6778699255653748</v>
@@ -18359,7 +18359,7 @@
         <v>1152</v>
       </c>
       <c r="X17" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="Y17">
         <v>29.838000000000001</v>
@@ -18394,7 +18394,7 @@
         <v>1020</v>
       </c>
       <c r="K18" t="s">
-        <v>908</v>
+        <v>876</v>
       </c>
       <c r="L18">
         <v>12.772248157772113</v>
@@ -18427,7 +18427,7 @@
         <v>1154</v>
       </c>
       <c r="X18" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="Y18">
         <v>58.689</v>
@@ -18462,7 +18462,7 @@
         <v>1022</v>
       </c>
       <c r="K19" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="L19">
         <v>15.217638427037592</v>
@@ -18495,7 +18495,7 @@
         <v>1156</v>
       </c>
       <c r="X19" t="s">
-        <v>993</v>
+        <v>968</v>
       </c>
       <c r="Y19">
         <v>48.432000000000002</v>
@@ -18530,7 +18530,7 @@
         <v>1024</v>
       </c>
       <c r="K20" t="s">
-        <v>810</v>
+        <v>894</v>
       </c>
       <c r="L20">
         <v>3.1385663053565613</v>
@@ -18563,7 +18563,7 @@
         <v>1158</v>
       </c>
       <c r="X20" t="s">
-        <v>968</v>
+        <v>990</v>
       </c>
       <c r="Y20">
         <v>47.794499999999999</v>
@@ -18598,7 +18598,7 @@
         <v>1026</v>
       </c>
       <c r="K21" t="s">
-        <v>854</v>
+        <v>811</v>
       </c>
       <c r="L21">
         <v>4.0628682283884237</v>
@@ -18631,7 +18631,7 @@
         <v>1160</v>
       </c>
       <c r="X21" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="Y21">
         <v>7.1767500000000002</v>
@@ -18666,7 +18666,7 @@
         <v>1028</v>
       </c>
       <c r="K22" t="s">
-        <v>918</v>
+        <v>856</v>
       </c>
       <c r="L22">
         <v>19.408837136062758</v>
@@ -18699,7 +18699,7 @@
         <v>1162</v>
       </c>
       <c r="X22" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
       <c r="Y22">
         <v>8.1052499999999998</v>
@@ -18734,7 +18734,7 @@
         <v>1030</v>
       </c>
       <c r="K23" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="L23">
         <v>15.054857587707319</v>
@@ -18767,7 +18767,7 @@
         <v>1164</v>
       </c>
       <c r="X23" t="s">
-        <v>969</v>
+        <v>997</v>
       </c>
       <c r="Y23">
         <v>9.3810000000000002</v>
@@ -18802,7 +18802,7 @@
         <v>1032</v>
       </c>
       <c r="K24" t="s">
-        <v>906</v>
+        <v>791</v>
       </c>
       <c r="L24">
         <v>13.019602602156084</v>
@@ -18835,7 +18835,7 @@
         <v>1166</v>
       </c>
       <c r="X24" t="s">
-        <v>996</v>
+        <v>972</v>
       </c>
       <c r="Y24">
         <v>11.47575</v>
@@ -18870,7 +18870,7 @@
         <v>1034</v>
       </c>
       <c r="K25" t="s">
-        <v>820</v>
+        <v>904</v>
       </c>
       <c r="L25">
         <v>25.094411791551167</v>
@@ -18903,7 +18903,7 @@
         <v>1168</v>
       </c>
       <c r="X25" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="Y25">
         <v>6.1372499999999999</v>
@@ -18938,7 +18938,7 @@
         <v>1036</v>
       </c>
       <c r="K26" t="s">
-        <v>866</v>
+        <v>803</v>
       </c>
       <c r="L26">
         <v>18.31221960055294</v>
@@ -18971,7 +18971,7 @@
         <v>1170</v>
       </c>
       <c r="X26" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="Y26">
         <v>14.57325</v>
@@ -19006,7 +19006,7 @@
         <v>1038</v>
       </c>
       <c r="K27" t="s">
-        <v>814</v>
+        <v>898</v>
       </c>
       <c r="L27">
         <v>27.91719839668141</v>
@@ -19039,7 +19039,7 @@
         <v>1172</v>
       </c>
       <c r="X27" t="s">
-        <v>995</v>
+        <v>970</v>
       </c>
       <c r="Y27">
         <v>10.491</v>
@@ -19074,7 +19074,7 @@
         <v>1040</v>
       </c>
       <c r="K28" t="s">
-        <v>890</v>
+        <v>870</v>
       </c>
       <c r="L28">
         <v>8.5144758814389814</v>
@@ -19107,7 +19107,7 @@
         <v>1174</v>
       </c>
       <c r="X28" t="s">
-        <v>983</v>
+        <v>995</v>
       </c>
       <c r="Y28">
         <v>17.414249999999999</v>
@@ -19142,7 +19142,7 @@
         <v>1042</v>
       </c>
       <c r="K29" t="s">
-        <v>812</v>
+        <v>896</v>
       </c>
       <c r="L29">
         <v>12.144708893333986</v>
@@ -19175,7 +19175,7 @@
         <v>1176</v>
       </c>
       <c r="X29" t="s">
-        <v>989</v>
+        <v>973</v>
       </c>
       <c r="Y29">
         <v>10.968</v>
@@ -19210,7 +19210,7 @@
         <v>1044</v>
       </c>
       <c r="K30" t="s">
-        <v>822</v>
+        <v>906</v>
       </c>
       <c r="L30">
         <v>1.6724491767694549</v>
@@ -19243,7 +19243,7 @@
         <v>1178</v>
       </c>
       <c r="X30" t="s">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="Y30">
         <v>10.79175</v>
@@ -19278,7 +19278,7 @@
         <v>1046</v>
       </c>
       <c r="K31" t="s">
-        <v>824</v>
+        <v>908</v>
       </c>
       <c r="L31">
         <v>13.894741632015101</v>
@@ -19311,7 +19311,7 @@
         <v>1180</v>
       </c>
       <c r="X31" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="Y31">
         <v>20.114249999999998</v>
@@ -19346,7 +19346,7 @@
         <v>1048</v>
       </c>
       <c r="K32" t="s">
-        <v>842</v>
+        <v>799</v>
       </c>
       <c r="L32">
         <v>11.876635800692616</v>
@@ -19379,7 +19379,7 @@
         <v>1182</v>
       </c>
       <c r="X32" t="s">
-        <v>985</v>
+        <v>996</v>
       </c>
       <c r="Y32">
         <v>44.373750000000001</v>
@@ -19414,7 +19414,7 @@
         <v>1050</v>
       </c>
       <c r="K33" t="s">
-        <v>826</v>
+        <v>910</v>
       </c>
       <c r="L33">
         <v>27.15579263061009</v>
@@ -19447,7 +19447,7 @@
         <v>1184</v>
       </c>
       <c r="X33" t="s">
-        <v>971</v>
+        <v>999</v>
       </c>
       <c r="Y33">
         <v>18.57525</v>
@@ -19482,7 +19482,7 @@
         <v>1052</v>
       </c>
       <c r="K34" t="s">
-        <v>898</v>
+        <v>838</v>
       </c>
       <c r="L34">
         <v>27.043339674957092</v>
@@ -19515,7 +19515,7 @@
         <v>1186</v>
       </c>
       <c r="X34" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="Y34">
         <v>18.241499999999998</v>
@@ -19550,7 +19550,7 @@
         <v>1054</v>
       </c>
       <c r="K35" t="s">
-        <v>856</v>
+        <v>813</v>
       </c>
       <c r="L35">
         <v>12.170927347824723</v>
@@ -19585,7 +19585,7 @@
         <v>1056</v>
       </c>
       <c r="K36" t="s">
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="L36">
         <v>26.999240466622091</v>
@@ -19620,7 +19620,7 @@
         <v>1058</v>
       </c>
       <c r="K37" t="s">
-        <v>882</v>
+        <v>850</v>
       </c>
       <c r="L37">
         <v>23.305350986470582</v>
@@ -19655,7 +19655,7 @@
         <v>1060</v>
       </c>
       <c r="K38" t="s">
-        <v>868</v>
+        <v>805</v>
       </c>
       <c r="L38">
         <v>19.293897715957783</v>
@@ -19690,7 +19690,7 @@
         <v>1062</v>
       </c>
       <c r="K39" t="s">
-        <v>832</v>
+        <v>916</v>
       </c>
       <c r="L39">
         <v>34.8352470366899</v>
@@ -19725,7 +19725,7 @@
         <v>1064</v>
       </c>
       <c r="K40" t="s">
-        <v>848</v>
+        <v>862</v>
       </c>
       <c r="L40">
         <v>22.439012549480047</v>
@@ -19760,7 +19760,7 @@
         <v>1066</v>
       </c>
       <c r="K41" t="s">
-        <v>878</v>
+        <v>846</v>
       </c>
       <c r="L41">
         <v>19.571302094407635</v>
@@ -19795,7 +19795,7 @@
         <v>1068</v>
       </c>
       <c r="K42" t="s">
-        <v>888</v>
+        <v>868</v>
       </c>
       <c r="L42">
         <v>16.258507759053195</v>
@@ -19830,7 +19830,7 @@
         <v>1070</v>
       </c>
       <c r="K43" t="s">
-        <v>806</v>
+        <v>890</v>
       </c>
       <c r="L43">
         <v>48.074816212675138</v>
@@ -19865,7 +19865,7 @@
         <v>1072</v>
       </c>
       <c r="K44" t="s">
-        <v>838</v>
+        <v>795</v>
       </c>
       <c r="L44">
         <v>65.59399718970684</v>
@@ -19900,7 +19900,7 @@
         <v>1074</v>
       </c>
       <c r="K45" t="s">
-        <v>802</v>
+        <v>886</v>
       </c>
       <c r="L45">
         <v>65.706815294563484</v>
@@ -19935,7 +19935,7 @@
         <v>1076</v>
       </c>
       <c r="K46" t="s">
-        <v>916</v>
+        <v>854</v>
       </c>
       <c r="L46">
         <v>13.859521883612567</v>
@@ -19970,7 +19970,7 @@
         <v>1078</v>
       </c>
       <c r="K47" t="s">
-        <v>886</v>
+        <v>866</v>
       </c>
       <c r="L47">
         <v>32.682899602232801</v>
@@ -20005,7 +20005,7 @@
         <v>1080</v>
       </c>
       <c r="K48" t="s">
-        <v>862</v>
+        <v>830</v>
       </c>
       <c r="L48">
         <v>39.028686646898073</v>
@@ -20040,7 +20040,7 @@
         <v>1082</v>
       </c>
       <c r="K49" t="s">
-        <v>795</v>
+        <v>823</v>
       </c>
       <c r="L49">
         <v>25.808486809088087</v>
@@ -20075,7 +20075,7 @@
         <v>1084</v>
       </c>
       <c r="K50" t="s">
-        <v>860</v>
+        <v>828</v>
       </c>
       <c r="L50">
         <v>64.703394190718342</v>
@@ -20110,7 +20110,7 @@
         <v>1086</v>
       </c>
       <c r="K51" t="s">
-        <v>846</v>
+        <v>860</v>
       </c>
       <c r="L51">
         <v>46.777110562179843</v>
@@ -20145,7 +20145,7 @@
         <v>1088</v>
       </c>
       <c r="K52" t="s">
-        <v>791</v>
+        <v>819</v>
       </c>
       <c r="L52">
         <v>83.307298494129057</v>
@@ -20180,7 +20180,7 @@
         <v>1090</v>
       </c>
       <c r="K53" t="s">
-        <v>874</v>
+        <v>842</v>
       </c>
       <c r="L53">
         <v>8.0718642408500934</v>
@@ -20215,7 +20215,7 @@
         <v>1092</v>
       </c>
       <c r="K54" t="s">
-        <v>789</v>
+        <v>817</v>
       </c>
       <c r="L54">
         <v>25.555956589747868</v>
@@ -20250,7 +20250,7 @@
         <v>1094</v>
       </c>
       <c r="K55" t="s">
-        <v>876</v>
+        <v>844</v>
       </c>
       <c r="L55">
         <v>26.74310381624198</v>
@@ -20285,7 +20285,7 @@
         <v>1096</v>
       </c>
       <c r="K56" t="s">
-        <v>840</v>
+        <v>797</v>
       </c>
       <c r="L56">
         <v>47.811917655816522</v>
@@ -20320,7 +20320,7 @@
         <v>1098</v>
       </c>
       <c r="K57" t="s">
-        <v>800</v>
+        <v>884</v>
       </c>
       <c r="L57">
         <v>65.898010391046881</v>
@@ -20355,7 +20355,7 @@
         <v>1100</v>
       </c>
       <c r="K58" t="s">
-        <v>836</v>
+        <v>793</v>
       </c>
       <c r="L58">
         <v>49.914822287456737</v>
@@ -20390,7 +20390,7 @@
         <v>1102</v>
       </c>
       <c r="K59" t="s">
-        <v>798</v>
+        <v>882</v>
       </c>
       <c r="L59">
         <v>19.963633091222835</v>
@@ -20425,7 +20425,7 @@
         <v>1104</v>
       </c>
       <c r="K60" t="s">
-        <v>850</v>
+        <v>807</v>
       </c>
       <c r="L60">
         <v>71.04376789192942</v>
@@ -20460,7 +20460,7 @@
         <v>1106</v>
       </c>
       <c r="K61" t="s">
-        <v>828</v>
+        <v>912</v>
       </c>
       <c r="L61">
         <v>43.07229279461999</v>
@@ -20495,7 +20495,7 @@
         <v>1108</v>
       </c>
       <c r="K62" t="s">
-        <v>884</v>
+        <v>864</v>
       </c>
       <c r="L62">
         <v>38.769945374969119</v>
@@ -20530,7 +20530,7 @@
         <v>1110</v>
       </c>
       <c r="K63" t="s">
-        <v>914</v>
+        <v>852</v>
       </c>
       <c r="L63">
         <v>59.009737840109466</v>
@@ -20565,7 +20565,7 @@
         <v>1112</v>
       </c>
       <c r="K64" t="s">
-        <v>904</v>
+        <v>789</v>
       </c>
       <c r="L64">
         <v>28.865927665826828</v>
@@ -20600,7 +20600,7 @@
         <v>1114</v>
       </c>
       <c r="K65" t="s">
-        <v>864</v>
+        <v>801</v>
       </c>
       <c r="L65">
         <v>37.976260419426943</v>
@@ -20635,7 +20635,7 @@
         <v>1116</v>
       </c>
       <c r="K66" t="s">
-        <v>902</v>
+        <v>787</v>
       </c>
       <c r="L66">
         <v>44.88386263672971</v>
@@ -20670,7 +20670,7 @@
         <v>1118</v>
       </c>
       <c r="K67" t="s">
-        <v>844</v>
+        <v>858</v>
       </c>
       <c r="L67">
         <v>23.350121881103082</v>
@@ -20705,7 +20705,7 @@
         <v>1120</v>
       </c>
       <c r="K68" t="s">
-        <v>818</v>
+        <v>902</v>
       </c>
       <c r="L68">
         <v>15.289477961960474</v>
@@ -20740,7 +20740,7 @@
         <v>1122</v>
       </c>
       <c r="K69" t="s">
-        <v>880</v>
+        <v>848</v>
       </c>
       <c r="L69">
         <v>10.395885695189069</v>
@@ -20775,7 +20775,7 @@
         <v>1124</v>
       </c>
       <c r="K70" t="s">
-        <v>808</v>
+        <v>892</v>
       </c>
       <c r="L70">
         <v>23.89105636564183</v>
@@ -20810,7 +20810,7 @@
         <v>1126</v>
       </c>
       <c r="K71" t="s">
-        <v>816</v>
+        <v>900</v>
       </c>
       <c r="L71">
         <v>18.959710131684457</v>
@@ -20845,7 +20845,7 @@
         <v>1128</v>
       </c>
       <c r="K72" t="s">
-        <v>804</v>
+        <v>888</v>
       </c>
       <c r="L72">
         <v>6.6550975614073966</v>
@@ -20880,7 +20880,7 @@
         <v>1130</v>
       </c>
       <c r="K73" t="s">
-        <v>894</v>
+        <v>834</v>
       </c>
       <c r="L73">
         <v>13.961943802326671</v>
@@ -20915,7 +20915,7 @@
         <v>1132</v>
       </c>
       <c r="K74" t="s">
-        <v>852</v>
+        <v>809</v>
       </c>
       <c r="L74">
         <v>51.937776653453852</v>
@@ -20950,7 +20950,7 @@
         <v>1134</v>
       </c>
       <c r="K75" t="s">
-        <v>787</v>
+        <v>815</v>
       </c>
       <c r="L75">
         <v>21.246092446368579</v>
@@ -20985,7 +20985,7 @@
         <v>1136</v>
       </c>
       <c r="K76" t="s">
-        <v>858</v>
+        <v>826</v>
       </c>
       <c r="L76">
         <v>19.42059121972445</v>
@@ -21020,7 +21020,7 @@
         <v>1138</v>
       </c>
       <c r="K77" t="s">
-        <v>892</v>
+        <v>832</v>
       </c>
       <c r="L77">
         <v>30.063621105864488</v>
@@ -21035,7 +21035,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36EED67B-AEF5-4BFD-82A0-17AB65921C61}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE888B3-8665-4012-ACB9-54CAE8E445FF}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22852,7 +22852,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACBE7FF5-C7AF-41F8-9328-726EB9DD8AC5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{767F1B33-AA3C-4DC3-93FD-B5AFA33D82C3}">
   <dimension ref="B2:M11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
